--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="965">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -70,7 +70,13 @@
     <t xml:space="preserve">     Proposta 40436 de 11/08/2026, valida ate 20/08/2026. CNPJ 47.864.839/0001-31. Unica com garantias declaradas.</t>
   </si>
   <si>
-    <t xml:space="preserve">G) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
+    <t xml:space="preserve">G) SunWash (Yuri) - 10 modulos de 650 W = 6,50 kWp + 4 MICROINVERSORES de 2,25 kW  -&gt;  R$ 16.780,54 INSTALADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Unica com 18x SEM JUROS pelo mesmo valor a vista (R$ 932,25/mes). Unica com 1 MPPT por modulo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
   </si>
   <si>
     <t xml:space="preserve">2. AS TRES DESCOBERTAS MAIS IMPORTANTES</t>
@@ -1393,7 +1399,12 @@
 AUXSOL 3 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">G) Bruno G4
+    <t xml:space="preserve">G) SunWash
+MICRO 10x650W
+4x 2,25 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H) Bruno G4
 (a receber)</t>
   </si>
   <si>
@@ -1454,6 +1465,9 @@
     <t xml:space="preserve">Proposta 40436 de 11/08/2026 (val. 20/08)</t>
   </si>
   <si>
+    <t xml:space="preserve">WhatsApp 10/08/2026 17:45</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nada recebido</t>
   </si>
   <si>
@@ -1505,6 +1519,9 @@
     <t xml:space="preserve">RONMA SOLAR bifacial N-type 144 cel</t>
   </si>
   <si>
+    <t xml:space="preserve">Nao informado (650 W)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA sao marcas com pouquissima rede de assistencia de modulo no Brasil - exigir INMETRO e quem honra a garantia aqui.</t>
   </si>
   <si>
@@ -1532,6 +1549,9 @@
     <t xml:space="preserve">AUXSOL 3 kW mono 220V 1 MPPT</t>
   </si>
   <si>
+    <t xml:space="preserve">4x MICROINVERSOR 2,25 kW = 9,0 kW AC</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: AUXSOL tem baixa penetracao no Brasil. Huawei e Solis tem assistencia estabelecida.</t>
   </si>
   <si>
@@ -1553,13 +1573,16 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: a Sun Coast usa inversor de 1 MPPT UNICO. Todos os 8 modulos ficam numa unica string: exige mesma orientacao e inclinacao, e sombra em um modulo derruba a string inteira.</t>
+    <t xml:space="preserve">1 por modulo (10 MPPTs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALERTA: Sun Coast usa 1 MPPT UNICO - os 8 modulos numa string so, exigindo mesma agua e mesma inclinacao, e sombra em 1 modulo derruba tudo. NO OUTRO EXTREMO, a opcao G com microinversor da 1 MPPT POR MODULO: sombra em um modulo nao afeta os outros e da liberdade de usar mais de uma agua do telhado.</t>
   </si>
   <si>
     <t xml:space="preserve">RELACAO DC/AC</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: faixa saudavel de 1,10 a 1,35. Sun Coast fica em 1,56 - acima do limite, com corte de potencia (clipping) nas melhores horas e risco de perder a garantia do inversor. William em 1,34, no limite.</t>
+    <t xml:space="preserve">ALERTA: faixa saudavel de 1,10 a 1,35. Sun Coast em 1,56 = acima do limite, com clipping e risco de perder a garantia. William em 1,34, no limite. Opcao G em 0,72 = o oposto: 4 microinversores de 2,25 kW dao 9 kW AC para so 6,5 kWp. PERGUNTAR ao Yuri quantos modulos cada micro aceita - se sao 4, existem 6 canais livres para expansao futura; se nao, voce esta pagando por um micro a mais.</t>
   </si>
   <si>
     <t xml:space="preserve">Tensao de operacao</t>
@@ -1634,6 +1657,27 @@
     <t xml:space="preserve">ALERTA: a Sun Coast exclui EXPLICITAMENTE a adequacao do padrao de entrada, obras no telhado, eletrodutos e o ART estrutural. E honesto ao declarar, mas o custo e seu. Os outros nao declararam exclusoes - o que nao significa que estejam inclusas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Condicao de pagamento declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIX (cotacao de material)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a vista ou 21x COM juros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIX no kit; restante nao informado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a vista, cartao 12x/21x COM juros ou financiamento 36x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18x de R$ 932,25 SEM JUROS (= preco a vista)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATENCAO: 18x SEM JUROS pelo mesmo valor a vista e uma vantagem financeira REAL - equivale a um desconto, porque o dinheiro fica rendendo na sua mao. Todas as outras oferecem parcelamento COM juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRECOS</t>
   </si>
   <si>
@@ -1817,7 +1861,7 @@
     <t xml:space="preserve">Modulos que ainda cabem no inversor</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: Solis 4 kW e AUXSOL 5 kW e 3 kW nao aceitam nenhum modulo a mais. So as opcoes A e B tem folga - e minima.</t>
+    <t xml:space="preserve">ALERTA: Solis 4 kW e os AUXSOL de 5 e 3 kW nao aceitam nenhum modulo a mais. A e B tem folga minima (1 modulo). A opcao G com microinversores e a unica com folga real - mas o limite verdadeiro e o numero de CANAIS livres nos micros, nao a potencia. CONFIRMAR com o Yuri.</t>
   </si>
   <si>
     <t xml:space="preserve">Geracao extra possivel sem trocar inversor (kWh/ano)</t>
@@ -1826,7 +1870,7 @@
     <t xml:space="preserve">Situacao do inversor</t>
   </si>
   <si>
-    <t xml:space="preserve">'JA SOBRECARREGADO' significa que o inversor esta pequeno para os modulos desde o primeiro dia.</t>
+    <t xml:space="preserve">'JA SOBRECARREGADO' = inversor pequeno para os modulos desde o dia 1 (perde geracao e garantia). 'SUBAPROVEITADO' = voce pagou por potencia de inversor que nao vai usar - aceitavel se for folga proposital para expansao, ruim se for so venda a mais.</t>
   </si>
   <si>
     <t xml:space="preserve">DECISAO ESPECIFICA: AUXSOL x HUAWEI NA PROPOSTA DA SUNWASH</t>
@@ -2186,7 +2230,10 @@
     <t xml:space="preserve">F) Sun Coast RONMA 585W AUXSOL 3 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">G) Bruno G4 (a receber)</t>
+    <t xml:space="preserve">G) SunWash MICRO 10x650W 4x 2,25 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H) Bruno G4 (a receber)</t>
   </si>
   <si>
     <t xml:space="preserve">EXPLICACAO</t>
@@ -2459,6 +2506,18 @@
 Fluxo</t>
   </si>
   <si>
+    <t xml:space="preserve">G) SunWash
+Economia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G) SunWash
+Acumulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G) SunWash
+Fluxo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anos 5, 10 e 20 destacados. As colunas 'Fluxo' viram positivas no ano do payback ja corrigido por inflacao e degradacao.</t>
   </si>
   <si>
@@ -2583,6 +2642,30 @@
   </si>
   <si>
     <t xml:space="preserve">'INVERSOR HIBRIDO' NAO COMPROVADO. A peca publicitaria da TecSolarSP anuncia inversor HIBRIDO 6 kW, mas a cotacao traz 'INVHW-MO-220V-6KW'. Exigir o codigo completo do modelo e a confirmacao por escrito de que aceita bateria - hibrido e nao hibrido tem preco e funcao diferentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-bis) PERGUNTAS ESPECIFICAS DA PROPOSTA COM MICROINVERSORES (opcao G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUAL A MARCA E O MODELO DOS 4 MICROINVERSORES? Deye, Hoymiles, APsystems e Sungrow tem rede no Brasil. Marca desconhecida em microinversor e pior que em inversor string, porque sao 4 equipamentos DEBAIXO dos modulos: trocar um exige desmontar placa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUAL A MARCA DO MODULO DE 650 W? O orcamento nao informa. 650 W e formato grande (cerca de 2,6 m2 por placa): confirmar que cabe na agua Sudeste e que o peso por m2 e compativel com o telhado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANTOS MODULOS CADA MICROINVERSOR ACEITA? 4 micros de 2,25 kW dao 9 kW AC para 6,5 kWp de modulos (relacao 0,72). Se cada micro aceita 4 modulos, sao 16 canais para 10 modulos = 6 canais livres, o que e uma excelente folga de expansao. Se aceita menos, voce esta pagando por um micro desnecessario. Essa unica resposta muda a avaliacao da proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRMAR QUE O PARCELAMENTO EM 18x E REALMENTE SEM JUROS pelo valor a vista (18 x 932,25 = 16.780,54 confere). Pedir por escrito, e confirmar se o preco a vista nao teria desconto adicional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICROINVERSOR EXIGE MANUTENCAO NO TELHADO. Perguntar como e feito o acesso, o prazo de troca em garantia e se o monitoramento e por modulo (deveria ser).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vantagens tecnicas reais do microinversor no SEU caso: sombreamento nunca foi avaliado e o micro isola o problema por modulo; permite dividir os modulos em mais de uma agua do telhado (poderia recuperar parte dos 11% perdidos pela orientacao Sudeste); nao ha tensao alta de corrente continua no telhado; falha de um equipamento nao para o sistema todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-ter) DEMAIS BLOQUEADORES</t>
   </si>
   <si>
     <t xml:space="preserve">SUN COAST: INVERSOR DE 3 kW PARA 4,68 kWp = RELACAO DC/AC DE 1,56. A faixa saudavel e 1,10 a 1,35. Nessa configuracao o inversor corta potencia (clipping) nas melhores horas do dia e a maioria dos fabricantes considera fora da garantia. Exigir do Alexandre o limite de sobrecarga do modelo AUXSOL cotado, por escrito, e a versao com inversor de 4 ou 5 kW.</t>
@@ -3795,7 +3878,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3868,25 +3951,25 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>13</v>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3901,7 +3984,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3911,7 +3994,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3921,7 +4004,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3931,7 +4014,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3946,20 +4029,20 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
-        <v>28</v>
+      <c r="B32" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3974,20 +4057,20 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>33</v>
+      <c r="B38" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="B39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3997,48 +4080,48 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="3" t="s">
-        <v>37</v>
+      <c r="B43" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>38</v>
-      </c>
+      <c r="B44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4"/>
+      <c r="B46" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="3" t="s">
-        <v>40</v>
+      <c r="B47" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="B48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4053,20 +4136,20 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="4"/>
+      <c r="B54" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="3" t="s">
-        <v>47</v>
+      <c r="B55" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4121,20 +4204,20 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="4"/>
+      <c r="B68" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="3" t="s">
-        <v>60</v>
+      <c r="B69" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="B70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4146,6 +4229,16 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4164,85 +4257,94 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>795</v>
+        <v>810</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>811</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="X4" s="17" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4325,6 +4427,18 @@
         <f aca="false">T6-COMPARATIVO!H$31</f>
         <v>-10183.1218586894</v>
       </c>
+      <c r="V6" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="W6" s="105" t="n">
+        <f aca="false">V6</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="X6" s="105" t="n">
+        <f aca="false">W6-COMPARATIVO!I$31</f>
+        <v>-14958.6214780249</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="104" t="n">
@@ -4406,6 +4520,18 @@
         <f aca="false">T7-COMPARATIVO!H$31</f>
         <v>-5171.93970233743</v>
       </c>
+      <c r="V7" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
+        <v>6520.97578083002</v>
+      </c>
+      <c r="W7" s="105" t="n">
+        <f aca="false">W6+V7</f>
+        <v>12642.8943028051</v>
+      </c>
+      <c r="X7" s="105" t="n">
+        <f aca="false">W7-COMPARATIVO!I$31</f>
+        <v>-8437.64569719492</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="104" t="n">
@@ -4487,6 +4613,18 @@
         <f aca="false">T8-COMPARATIVO!H$31</f>
         <v>165.89636287633</v>
       </c>
+      <c r="V8" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
+        <v>6946.04558710342</v>
+      </c>
+      <c r="W8" s="105" t="n">
+        <f aca="false">W7+V8</f>
+        <v>19588.9398899085</v>
+      </c>
+      <c r="X8" s="105" t="n">
+        <f aca="false">W8-COMPARATIVO!I$31</f>
+        <v>-1491.60011009149</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="104" t="n">
@@ -4568,6 +4706,18 @@
         <f aca="false">T9-COMPARATIVO!H$31</f>
         <v>5851.67927200105</v>
       </c>
+      <c r="V9" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
+        <v>7398.82356869876</v>
+      </c>
+      <c r="W9" s="105" t="n">
+        <f aca="false">W8+V9</f>
+        <v>26987.7634586073</v>
+      </c>
+      <c r="X9" s="105" t="n">
+        <f aca="false">W9-COMPARATIVO!I$31</f>
+        <v>5907.22345860726</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="106" t="n">
@@ -4649,6 +4799,18 @@
         <f aca="false">T10-COMPARATIVO!H$31</f>
         <v>11908.0899400571</v>
       </c>
+      <c r="V10" s="108" t="n">
+        <f aca="false">ECONOMIA!I$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
+        <v>7881.11588302439</v>
+      </c>
+      <c r="W10" s="108" t="n">
+        <f aca="false">W9+V10</f>
+        <v>34868.8793416317</v>
+      </c>
+      <c r="X10" s="108" t="n">
+        <f aca="false">W10-COMPARATIVO!I$31</f>
+        <v>13788.3393416317</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="104" t="n">
@@ -4730,6 +4892,18 @@
         <f aca="false">T11-COMPARATIVO!H$31</f>
         <v>18359.2877375103</v>
       </c>
+      <c r="V11" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
+        <v>8394.84642185933</v>
+      </c>
+      <c r="W11" s="105" t="n">
+        <f aca="false">W10+V11</f>
+        <v>43263.725763491</v>
+      </c>
+      <c r="X11" s="105" t="n">
+        <f aca="false">W11-COMPARATIVO!I$31</f>
+        <v>22183.185763491</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="104" t="n">
@@ -4811,6 +4985,18 @@
         <f aca="false">T12-COMPARATIVO!H$31</f>
         <v>25231.0068633905</v>
       </c>
+      <c r="V12" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
+        <v>8942.06448586824</v>
+      </c>
+      <c r="W12" s="105" t="n">
+        <f aca="false">W11+V12</f>
+        <v>52205.7902493592</v>
+      </c>
+      <c r="X12" s="105" t="n">
+        <f aca="false">W12-COMPARATIVO!I$31</f>
+        <v>31125.2502493592</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="104" t="n">
@@ -4892,6 +5078,18 @@
         <f aca="false">T13-COMPARATIVO!H$31</f>
         <v>32550.6590004913</v>
       </c>
+      <c r="V13" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
+        <v>9524.95295937956</v>
+      </c>
+      <c r="W13" s="105" t="n">
+        <f aca="false">W12+V13</f>
+        <v>61730.7432087388</v>
+      </c>
+      <c r="X13" s="105" t="n">
+        <f aca="false">W13-COMPARATIVO!I$31</f>
+        <v>40650.2032087388</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="104" t="n">
@@ -4973,6 +5171,18 @@
         <f aca="false">T14-COMPARATIVO!H$31</f>
         <v>40347.4426621489</v>
       </c>
+      <c r="V14" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
+        <v>10145.8370180367</v>
+      </c>
+      <c r="W14" s="105" t="n">
+        <f aca="false">W13+V14</f>
+        <v>71876.5802267755</v>
+      </c>
+      <c r="X14" s="105" t="n">
+        <f aca="false">W14-COMPARATIVO!I$31</f>
+        <v>50796.0402267755</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="106" t="n">
@@ -5054,6 +5264,18 @@
         <f aca="false">T15-COMPARATIVO!H$31</f>
         <v>48652.4596667917</v>
       </c>
+      <c r="V15" s="108" t="n">
+        <f aca="false">ECONOMIA!I$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
+        <v>10807.1934040574</v>
+      </c>
+      <c r="W15" s="108" t="n">
+        <f aca="false">W14+V15</f>
+        <v>82683.773630833</v>
+      </c>
+      <c r="X15" s="108" t="n">
+        <f aca="false">W15-COMPARATIVO!I$31</f>
+        <v>61603.233630833</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="104" t="n">
@@ -5135,6 +5357,18 @@
         <f aca="false">T16-COMPARATIVO!H$31</f>
         <v>57498.8392048822</v>
       </c>
+      <c r="V16" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
+        <v>11511.6603061009</v>
+      </c>
+      <c r="W16" s="105" t="n">
+        <f aca="false">W15+V16</f>
+        <v>94195.4339369339</v>
+      </c>
+      <c r="X16" s="105" t="n">
+        <f aca="false">W16-COMPARATIVO!I$31</f>
+        <v>73114.8939369339</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="104" t="n">
@@ -5216,6 +5450,18 @@
         <f aca="false">T17-COMPARATIVO!H$31</f>
         <v>66921.869993163</v>
       </c>
+      <c r="V17" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
+        <v>12262.0478831541</v>
+      </c>
+      <c r="W17" s="105" t="n">
+        <f aca="false">W16+V17</f>
+        <v>106457.481820088</v>
+      </c>
+      <c r="X17" s="105" t="n">
+        <f aca="false">W17-COMPARATIVO!I$31</f>
+        <v>85376.941820088</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="104" t="n">
@@ -5297,6 +5543,18 @@
         <f aca="false">T18-COMPARATIVO!H$31</f>
         <v>76959.141043378</v>
       </c>
+      <c r="V18" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
+        <v>13061.3494744175</v>
+      </c>
+      <c r="W18" s="105" t="n">
+        <f aca="false">W17+V18</f>
+        <v>119518.831294506</v>
+      </c>
+      <c r="X18" s="105" t="n">
+        <f aca="false">W18-COMPARATIVO!I$31</f>
+        <v>98438.2912945055</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="104" t="n">
@@ -5378,6 +5636,18 @@
         <f aca="false">T19-COMPARATIVO!H$31</f>
         <v>87650.6916070012</v>
       </c>
+      <c r="V19" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
+        <v>13912.7535399074</v>
+      </c>
+      <c r="W19" s="105" t="n">
+        <f aca="false">W18+V19</f>
+        <v>133431.584834413</v>
+      </c>
+      <c r="X19" s="105" t="n">
+        <f aca="false">W19-COMPARATIVO!I$31</f>
+        <v>112351.044834413</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="104" t="n">
@@ -5459,6 +5729,18 @@
         <f aca="false">T20-COMPARATIVO!H$31</f>
         <v>99039.1708941142</v>
       </c>
+      <c r="V20" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
+        <v>14819.6563794063</v>
+      </c>
+      <c r="W20" s="105" t="n">
+        <f aca="false">W19+V20</f>
+        <v>148251.241213819</v>
+      </c>
+      <c r="X20" s="105" t="n">
+        <f aca="false">W20-COMPARATIVO!I$31</f>
+        <v>127170.701213819</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="104" t="n">
@@ -5540,6 +5822,18 @@
         <f aca="false">T21-COMPARATIVO!H$31</f>
         <v>111170.008203558</v>
       </c>
+      <c r="V21" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
+        <v>15785.6756804979</v>
+      </c>
+      <c r="W21" s="105" t="n">
+        <f aca="false">W20+V21</f>
+        <v>164036.916894317</v>
+      </c>
+      <c r="X21" s="105" t="n">
+        <f aca="false">W21-COMPARATIVO!I$31</f>
+        <v>142956.376894317</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="104" t="n">
@@ -5621,6 +5915,18 @@
         <f aca="false">T22-COMPARATIVO!H$31</f>
         <v>124091.594143017</v>
       </c>
+      <c r="V22" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
+        <v>16814.6649497312</v>
+      </c>
+      <c r="W22" s="105" t="n">
+        <f aca="false">W21+V22</f>
+        <v>180851.581844048</v>
+      </c>
+      <c r="X22" s="105" t="n">
+        <f aca="false">W22-COMPARATIVO!I$31</f>
+        <v>159771.041844048</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="104" t="n">
@@ -5702,6 +6008,18 @@
         <f aca="false">T23-COMPARATIVO!H$31</f>
         <v>137855.47366194</v>
       </c>
+      <c r="V23" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
+        <v>17910.7288844794</v>
+      </c>
+      <c r="W23" s="105" t="n">
+        <f aca="false">W22+V23</f>
+        <v>198762.310728528</v>
+      </c>
+      <c r="X23" s="105" t="n">
+        <f aca="false">W23-COMPARATIVO!I$31</f>
+        <v>177681.770728528</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="104" t="n">
@@ -5783,6 +6101,18 @@
         <f aca="false">T24-COMPARATIVO!H$31</f>
         <v>152516.551667305</v>
       </c>
+      <c r="V24" s="105" t="n">
+        <f aca="false">ECONOMIA!I$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
+        <v>19078.2397468142</v>
+      </c>
+      <c r="W24" s="105" t="n">
+        <f aca="false">W23+V24</f>
+        <v>217840.550475342</v>
+      </c>
+      <c r="X24" s="105" t="n">
+        <f aca="false">W24-COMPARATIVO!I$31</f>
+        <v>196760.010475342</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="106" t="n">
@@ -5864,25 +6194,37 @@
         <f aca="false">T25-COMPARATIVO!H$31</f>
         <v>168133.312042449</v>
       </c>
+      <c r="V25" s="108" t="n">
+        <f aca="false">ECONOMIA!I$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
+        <v>20321.8548047103</v>
+      </c>
+      <c r="W25" s="108" t="n">
+        <f aca="false">W24+V25</f>
+        <v>238162.405280052</v>
+      </c>
+      <c r="X25" s="108" t="n">
+        <f aca="false">W25-COMPARATIVO!I$31</f>
+        <v>217081.865280052</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>796</v>
+        <v>814</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>797</v>
+        <v>815</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>798</v>
+        <v>816</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>799</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -5916,54 +6258,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>800</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>801</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>804</v>
+        <v>822</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>806</v>
+        <v>824</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>808</v>
+        <v>826</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>809</v>
+        <v>827</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>810</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C7" s="32" t="n">
         <f aca="false">CONTA!C38</f>
@@ -5996,7 +6338,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">CONTA!C39</f>
@@ -6029,7 +6371,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">CONTA!C40</f>
@@ -6062,7 +6404,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">CONTA!C41</f>
@@ -6095,7 +6437,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">CONTA!C42</f>
@@ -6128,7 +6470,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">CONTA!C43</f>
@@ -6161,7 +6503,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">CONTA!C44</f>
@@ -6194,7 +6536,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">CONTA!C45</f>
@@ -6227,7 +6569,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">CONTA!C46</f>
@@ -6260,7 +6602,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">CONTA!C47</f>
@@ -6293,7 +6635,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C17" s="32" t="n">
         <f aca="false">CONTA!C48</f>
@@ -6326,7 +6668,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">CONTA!C49</f>
@@ -6359,7 +6701,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C19" s="34" t="n">
         <f aca="false">SUM(C7:C18)</f>
@@ -6384,32 +6726,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>811</v>
+        <v>829</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>812</v>
+        <v>830</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>813</v>
+        <v>831</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>814</v>
+        <v>832</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>815</v>
+        <v>833</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>816</v>
+        <v>834</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6417,12 +6759,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>817</v>
+        <v>835</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>818</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -6441,7 +6783,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -6453,32 +6795,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>824</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>825</v>
+        <v>843</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -6488,10 +6830,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>826</v>
+        <v>844</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E6" s="110"/>
     </row>
@@ -6500,10 +6842,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>828</v>
+        <v>846</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E7" s="110"/>
     </row>
@@ -6512,10 +6854,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>829</v>
+        <v>847</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E8" s="110"/>
     </row>
@@ -6524,10 +6866,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>830</v>
+        <v>848</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E9" s="110"/>
     </row>
@@ -6536,10 +6878,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>831</v>
+        <v>849</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E10" s="110"/>
     </row>
@@ -6548,10 +6890,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="109" t="s">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E11" s="110"/>
     </row>
@@ -6560,10 +6902,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>833</v>
+        <v>851</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E12" s="110"/>
     </row>
@@ -6572,10 +6914,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>834</v>
+        <v>852</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E13" s="110"/>
     </row>
@@ -6584,10 +6926,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>835</v>
+        <v>853</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E14" s="110"/>
     </row>
@@ -6596,10 +6938,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>836</v>
+        <v>854</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E15" s="110"/>
     </row>
@@ -6608,444 +6950,532 @@
         <v>11</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E16" s="110"/>
     </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" s="109" t="s">
-        <v>838</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E17" s="110"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E18" s="110"/>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>858</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E19" s="110"/>
+    </row>
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="109" t="s">
-        <v>840</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E19" s="110"/>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="n">
+      <c r="C20" s="109" t="s">
+        <v>859</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E20" s="110"/>
+    </row>
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C20" s="109" t="s">
-        <v>841</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E20" s="110"/>
-    </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="n">
+      <c r="C21" s="109" t="s">
+        <v>860</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E21" s="110"/>
+    </row>
+    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>842</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E21" s="110"/>
-    </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
+      <c r="C22" s="109" t="s">
+        <v>861</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E22" s="110"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C22" s="109" t="s">
-        <v>843</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E22" s="110"/>
-    </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="n">
+      <c r="C23" s="111" t="s">
+        <v>862</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E23" s="110"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8"/>
+      <c r="C25" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C23" s="109" t="s">
-        <v>844</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E23" s="110"/>
-    </row>
-    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" s="109" t="s">
+      <c r="C26" s="109" t="s">
+        <v>864</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>845</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E24" s="110"/>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C25" s="109" t="s">
-        <v>846</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E25" s="110"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="C26" s="109" t="s">
-        <v>847</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>827</v>
       </c>
       <c r="E26" s="110"/>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E27" s="110"/>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" s="109" t="s">
+        <v>866</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E28" s="110"/>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" s="109" t="s">
+        <v>867</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E29" s="110"/>
+    </row>
+    <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" s="109" t="s">
+        <v>868</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E30" s="110"/>
+    </row>
+    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C28" s="109" t="s">
-        <v>849</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E28" s="110"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="n">
+      <c r="C31" s="109" t="s">
+        <v>869</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E31" s="110"/>
+    </row>
+    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C29" s="109" t="s">
-        <v>850</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E29" s="110"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8"/>
-      <c r="C31" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="n">
+      <c r="C32" s="109" t="s">
+        <v>870</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E32" s="110"/>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="111" t="s">
-        <v>852</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E32" s="110"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="n">
+      <c r="C33" s="109" t="s">
+        <v>871</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E33" s="110"/>
+    </row>
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C33" s="111" t="s">
-        <v>853</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E33" s="110"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="n">
+      <c r="C34" s="109" t="s">
+        <v>872</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E34" s="110"/>
+    </row>
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C34" s="111" t="s">
-        <v>854</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E34" s="110"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="n">
+      <c r="C35" s="109" t="s">
+        <v>873</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E35" s="110"/>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C35" s="111" t="s">
-        <v>855</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E35" s="110"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="n">
+      <c r="C36" s="109" t="s">
+        <v>874</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E36" s="110"/>
+    </row>
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="111" t="s">
-        <v>856</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E36" s="110"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="111" t="s">
-        <v>857</v>
+      <c r="C37" s="109" t="s">
+        <v>875</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E37" s="110"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" s="109" t="s">
+        <v>876</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E38" s="110"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="C38" s="111" t="s">
-        <v>858</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E38" s="110"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="n">
+      <c r="C41" s="111" t="s">
+        <v>878</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E41" s="110"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="C39" s="111" t="s">
-        <v>859</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E39" s="110"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="111" t="s">
-        <v>860</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E40" s="110"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8"/>
-      <c r="C42" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="C42" s="111" t="s">
+        <v>879</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E42" s="110"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="111" t="s">
-        <v>862</v>
+        <v>880</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E43" s="110"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C44" s="111" t="s">
-        <v>863</v>
+        <v>881</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E44" s="110"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45" s="111" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E45" s="110"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C46" s="111" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E46" s="110"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C47" s="111" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E47" s="110"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="111" t="s">
-        <v>867</v>
+        <v>885</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E48" s="110"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" s="111" t="s">
-        <v>868</v>
+        <v>886</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E49" s="110"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="8"/>
       <c r="C51" s="7" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C52" s="111" t="s">
+        <v>888</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E52" s="110"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="C52" s="111" t="s">
-        <v>870</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E52" s="110"/>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="4" t="n">
-        <v>42</v>
-      </c>
       <c r="C53" s="111" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E53" s="110"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" s="111" t="s">
-        <v>872</v>
+        <v>890</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E54" s="110"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C55" s="111" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
       <c r="E55" s="110"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C56" s="111" t="s">
+        <v>892</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E56" s="110"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C56" s="111" t="s">
-        <v>874</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="E56" s="110"/>
+      <c r="C57" s="111" t="s">
+        <v>893</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E57" s="110"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C58" s="111" t="s">
+        <v>894</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E58" s="110"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8"/>
+      <c r="C60" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C61" s="111" t="s">
+        <v>896</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E61" s="110"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C62" s="111" t="s">
+        <v>897</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E62" s="110"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C63" s="111" t="s">
+        <v>898</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E63" s="110"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C64" s="111" t="s">
+        <v>899</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E64" s="110"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C65" s="111" t="s">
+        <v>900</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E65" s="110"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7075,370 +7505,370 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>875</v>
+        <v>901</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>876</v>
+        <v>902</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>877</v>
+        <v>903</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>878</v>
+        <v>904</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>879</v>
+        <v>905</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>880</v>
+        <v>906</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>881</v>
+        <v>907</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="66" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>884</v>
+        <v>910</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="66" t="s">
-        <v>885</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>886</v>
+        <v>912</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="66" t="s">
-        <v>887</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="48" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="66" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="66" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="66" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="66" t="s">
-        <v>893</v>
+        <v>919</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>894</v>
+        <v>920</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="66" t="s">
-        <v>895</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>896</v>
+        <v>922</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="66" t="s">
-        <v>897</v>
+        <v>923</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="66" t="s">
-        <v>898</v>
+        <v>924</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>899</v>
+        <v>925</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="66" t="s">
-        <v>900</v>
+        <v>926</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>901</v>
+        <v>927</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="66" t="s">
-        <v>902</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="66" t="s">
-        <v>903</v>
+        <v>929</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>904</v>
+        <v>930</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="66" t="s">
-        <v>905</v>
+        <v>931</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="66" t="s">
-        <v>907</v>
+        <v>933</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>908</v>
+        <v>934</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="66" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>910</v>
+        <v>936</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="66" t="s">
-        <v>911</v>
+        <v>937</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>912</v>
+        <v>938</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="66" t="s">
-        <v>913</v>
+        <v>939</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>914</v>
+        <v>940</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="66" t="s">
-        <v>915</v>
+        <v>941</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>916</v>
+        <v>942</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="66" t="s">
-        <v>917</v>
+        <v>943</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>918</v>
+        <v>944</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="66" t="s">
-        <v>919</v>
+        <v>945</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>920</v>
+        <v>946</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="66" t="s">
-        <v>921</v>
+        <v>947</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>922</v>
+        <v>948</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="66" t="s">
-        <v>923</v>
+        <v>949</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="48" t="s">
-        <v>924</v>
+        <v>950</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="66" t="s">
-        <v>925</v>
+        <v>951</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>926</v>
+        <v>952</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="66" t="s">
-        <v>927</v>
+        <v>953</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>928</v>
+        <v>954</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="66" t="s">
-        <v>929</v>
+        <v>955</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>930</v>
+        <v>956</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="66" t="s">
-        <v>931</v>
+        <v>957</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>932</v>
+        <v>958</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="66" t="s">
-        <v>933</v>
+        <v>959</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="66" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>936</v>
+        <v>962</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="66" t="s">
-        <v>937</v>
+        <v>963</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="66" t="s">
-        <v>938</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -7469,17 +7899,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7487,93 +7917,93 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -7581,214 +8011,214 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(C16=1,30,IF(C16=2,50,100))</f>
         <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1.02147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0.59643</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.40085</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.02419</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C23" s="15" t="n">
         <f aca="false">C19*C22</f>
         <v>0.357858</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C25" s="15" t="n">
         <f aca="false">C23*C24</f>
         <v>0.2147148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -7796,97 +8226,97 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>0.79</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0.72</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>0.0045</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>300</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>150</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -7894,120 +8324,120 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C42" s="16" t="n">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C43" s="11" t="n">
         <v>40</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C44" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>0.86</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C46" s="16" t="n">
         <v>3.3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C48" s="14" t="n">
         <v>0.15</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8042,53 +8472,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>322.07</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>389</v>
@@ -8101,18 +8531,18 @@
         <v>12.15625</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>216.46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>364</v>
@@ -8125,18 +8555,18 @@
         <v>11.741935483871</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>13.06</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>290</v>
@@ -8149,18 +8579,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>551.59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>375</v>
@@ -8173,18 +8603,18 @@
         <v>11.71875</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>337</v>
@@ -8197,18 +8627,18 @@
         <v>11.2333333333333</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>572.7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>323</v>
@@ -8221,19 +8651,19 @@
         <v>11.1379310344828</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H11" s="23" t="n">
         <f aca="false">IFERROR(H8/540,0)</f>
         <v>1.02146296296296</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>372</v>
@@ -8248,7 +8678,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>348</v>
@@ -8261,12 +8691,12 @@
         <v>11.6</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>354</v>
@@ -8279,18 +8709,18 @@
         <v>12.2068965517241</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>4.14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>394</v>
@@ -8303,18 +8733,18 @@
         <v>12.3125</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>19.12</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>457</v>
@@ -8327,18 +8757,18 @@
         <v>15.2333333333333</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>99.28</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>422</v>
@@ -8351,18 +8781,18 @@
         <v>14.551724137931</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>122.54</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>540</v>
@@ -8377,145 +8807,145 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="G21" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="26" t="n">
         <f aca="false">SUM(C7:C18)</f>
         <v>4576</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C22/12</f>
         <v>381.333333333333</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">SUM(D7:D18)</f>
         <v>366</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C22/C24,0)</f>
         <v>12.5027322404372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">MAX(C7:C18)</f>
         <v>540</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">MIN(C7:C18)</f>
         <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">IFERROR(C26/C27-1,0)</f>
@@ -8523,33 +8953,33 @@
       </c>
       <c r="D28" s="2"/>
       <c r="G28" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">IFERROR(C29/C23-1,0)</f>
@@ -8557,81 +8987,81 @@
       </c>
       <c r="D30" s="2"/>
       <c r="G30" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">AVERAGE(C7:C12)</f>
         <v>343.5</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C32" s="29" t="n">
         <f aca="false">AVERAGE(C13:C18)</f>
         <v>419.166666666667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IFERROR(C32/C31-1,0)</f>
         <v>0.220281416787967</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IFERROR(C18/C6-1,0)</f>
         <v>0.388174807197943</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -8639,162 +9069,162 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C38" s="32" t="n">
         <f aca="false">C12</f>
         <v>372</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C39" s="32" t="n">
         <f aca="false">C13</f>
         <v>348</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="18" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C40" s="32" t="n">
         <f aca="false">C14</f>
         <v>354</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C41" s="32" t="n">
         <f aca="false">C15</f>
         <v>394</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C42" s="32" t="n">
         <f aca="false">C16</f>
         <v>457</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C43" s="32" t="n">
         <f aca="false">C17</f>
         <v>422</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C44" s="32" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C45" s="32" t="n">
         <f aca="false">C7</f>
         <v>364</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C46" s="32" t="n">
         <f aca="false">C8</f>
         <v>290</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C47" s="32" t="n">
         <f aca="false">C9</f>
         <v>375</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C48" s="32" t="n">
         <f aca="false">C10</f>
         <v>337</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C49" s="32" t="n">
         <f aca="false">C11</f>
         <v>323</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">SUM(C38:C49)</f>
@@ -8803,7 +9233,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -8811,7 +9241,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C53" s="35" t="n">
         <f aca="false">C22*H11+H9*12</f>
@@ -8820,7 +9250,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C54" s="35" t="n">
         <f aca="false">C53/12</f>
@@ -8829,7 +9259,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C55" s="35" t="n">
         <f aca="false">H10</f>
@@ -8838,82 +9268,82 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -8948,49 +9378,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>31</v>
@@ -9027,7 +9457,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>28</v>
@@ -9064,7 +9494,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>31</v>
@@ -9101,7 +9531,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>30</v>
@@ -9138,7 +9568,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>31</v>
@@ -9175,7 +9605,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>30</v>
@@ -9212,7 +9642,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>31</v>
@@ -9249,7 +9679,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>31</v>
@@ -9286,7 +9716,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>30</v>
@@ -9323,7 +9753,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>31</v>
@@ -9360,7 +9790,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>30</v>
@@ -9397,7 +9827,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>31</v>
@@ -9434,7 +9864,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="38" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">SUM(C5:C16)</f>
@@ -9469,7 +9899,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I18" s="26" t="n">
         <f aca="false">I17/12</f>
@@ -9482,12 +9912,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9495,37 +9925,37 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9533,12 +9963,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9546,12 +9976,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -9584,17 +10014,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -9605,82 +10035,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">ENTRADAS!C43</f>
         <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="44" t="n">
         <f aca="false">ENTRADAS!C42</f>
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C7" s="29" t="n">
         <f aca="false">C5*C6/100</f>
         <v>6.8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C8" s="43" t="n">
         <f aca="false">ENTRADAS!C44</f>
         <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C9" s="45" t="n">
         <f aca="false">C7*C8</f>
         <v>176.8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -9691,7 +10121,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" s="46" t="n">
         <f aca="false">ENTRADAS!C45</f>
@@ -9699,143 +10129,143 @@
       </c>
       <c r="D12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C13" s="45" t="n">
         <f aca="false">C9/C12</f>
         <v>205.581395348837</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">C13-C9</f>
         <v>28.7813953488372</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C15" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C18</f>
         <v>209.995227906977</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">C15*12</f>
         <v>2519.94273488372</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C25</f>
         <v>44.1413681860465</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15-C17</f>
         <v>165.85385972093</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C18*12</f>
         <v>1990.24631665116</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">IFERROR(C15/(C5*C8),0)</f>
         <v>0.201918488372093</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C21" s="15" t="n">
         <f aca="false">IFERROR(C17/(C5*C8),0)</f>
         <v>0.042443623255814</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -9846,97 +10276,97 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C24" s="44" t="n">
         <f aca="false">ENTRADAS!C46</f>
         <v>3.3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C13/C8/C24,0)</f>
         <v>2.39605355884426</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">IFERROR(ENTRADAS!C41/ENTRADAS!C45/C24,0)</f>
         <v>6.44820295983087</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C27" s="29" t="n">
         <f aca="false">IFERROR(C24*1000/220,0)</f>
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C28" s="29" t="n">
         <f aca="false">IFERROR(C27*1.25,0)</f>
         <v>18.75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">C24*1</f>
         <v>3.3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -9947,27 +10377,27 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -9992,7 +10422,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C34" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -10017,7 +10447,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="48" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C35" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -10054,7 +10484,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -10065,30 +10495,30 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="50" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D42" s="52" t="n">
         <f aca="false">0</f>
@@ -10099,18 +10529,18 @@
         <v>0</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="50" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D43" s="52" t="n">
         <f aca="false">ENTRADAS!C25</f>
@@ -10121,18 +10551,18 @@
         <v>44.1413681860465</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="50" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D44" s="52" t="n">
         <f aca="false">ENTRADAS!C18</f>
@@ -10143,15 +10573,15 @@
         <v>209.995227906977</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10160,17 +10590,17 @@
         <v>529.696418232558</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -10200,17 +10630,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -10219,31 +10649,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">GERACAO!I17</f>
         <v>1264.268995</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C6" s="29" t="n">
         <f aca="false">C5/12</f>
         <v>105.355749583333</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="4" t="str">
         <f aca="false">"kWp necessario = consumo anual / "&amp;TEXT(C5,"0")&amp;" kWh por kWp"</f>
@@ -10253,7 +10683,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -10262,24 +10692,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">BYD!F33</f>
@@ -10300,7 +10730,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">BYD!F34</f>
@@ -10321,7 +10751,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="48" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">BYD!F35</f>
@@ -10342,7 +10772,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -10352,18 +10782,18 @@
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C17" s="56" t="str">
         <f aca="false">"100% do Cenario 2"</f>
@@ -10380,7 +10810,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C18" s="57" t="n">
         <f aca="false">E12</f>
@@ -10397,7 +10827,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C19" s="58" t="n">
         <f aca="false">ROUNDUP(C18*1000/615,0)</f>
@@ -10414,7 +10844,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C20" s="59" t="n">
         <f aca="false">C19*615/1000</f>
@@ -10431,7 +10861,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C21" s="57" t="n">
         <f aca="false">5</f>
@@ -10448,7 +10878,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C22" s="60" t="n">
         <f aca="false">IFERROR(C20/C21,0)</f>
@@ -10465,7 +10895,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C23" s="58" t="n">
         <f aca="false">C20*$C$5</f>
@@ -10482,7 +10912,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C24" s="58" t="n">
         <f aca="false">C23/12</f>
@@ -10499,7 +10929,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IFERROR(C23/$D$12,0)</f>
@@ -10516,7 +10946,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C26" s="62" t="n">
         <f aca="false">IFERROR(C23/$D$13,0)</f>
@@ -10533,7 +10963,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C27" s="58" t="n">
         <f aca="false">MAX(0,C23-$D$13)</f>
@@ -10550,52 +10980,52 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10603,12 +11033,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -10627,171 +11057,186 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>450</v>
+        <v>452</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="64" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="H5" s="65" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I5" s="65" t="s">
         <v>456</v>
       </c>
-      <c r="J5" s="66" t="s">
-        <v>457</v>
+      <c r="J5" s="65" t="s">
+        <v>459</v>
+      </c>
+      <c r="K5" s="66" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="64" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>461</v>
-      </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="68" t="s">
-        <v>462</v>
+        <v>464</v>
+      </c>
+      <c r="I6" s="67" t="s">
+        <v>463</v>
+      </c>
+      <c r="J6" s="65"/>
+      <c r="K6" s="68" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="64" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G7" s="65" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I7" s="65" t="s">
-        <v>469</v>
-      </c>
-      <c r="J7" s="68" t="s">
-        <v>470</v>
+        <v>472</v>
+      </c>
+      <c r="J7" s="65" t="s">
+        <v>473</v>
+      </c>
+      <c r="K7" s="68" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="69" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D8" s="70" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G8" s="70" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>474</v>
-      </c>
-      <c r="J8" s="68" t="s">
-        <v>475</v>
+        <v>477</v>
+      </c>
+      <c r="J8" s="70" t="s">
+        <v>478</v>
+      </c>
+      <c r="K8" s="68" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="64" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C9" s="71" t="n">
         <v>12</v>
@@ -10811,14 +11256,17 @@
       <c r="H9" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="72"/>
-      <c r="J9" s="66" t="s">
-        <v>477</v>
+      <c r="I9" s="71" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="72"/>
+      <c r="K9" s="66" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="64" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C10" s="71" t="n">
         <v>615</v>
@@ -10838,41 +11286,47 @@
       <c r="H10" s="71" t="n">
         <v>585</v>
       </c>
-      <c r="I10" s="72"/>
-      <c r="J10" s="66" t="s">
-        <v>479</v>
+      <c r="I10" s="71" t="n">
+        <v>650</v>
+      </c>
+      <c r="J10" s="72"/>
+      <c r="K10" s="66" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="64" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F11" s="65" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G11" s="65" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H11" s="65" t="s">
-        <v>485</v>
-      </c>
-      <c r="I11" s="65"/>
-      <c r="J11" s="68" t="s">
-        <v>486</v>
+        <v>489</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>490</v>
+      </c>
+      <c r="J11" s="65"/>
+      <c r="K11" s="68" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="69" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C12" s="73" t="n">
         <f aca="false">C9*C10/1000</f>
@@ -10898,41 +11352,48 @@
         <f aca="false">H9*H10/1000</f>
         <v>4.68</v>
       </c>
-      <c r="I12" s="73"/>
-      <c r="J12" s="66" t="s">
-        <v>488</v>
+      <c r="I12" s="73" t="n">
+        <f aca="false">I9*I10/1000</f>
+        <v>6.5</v>
+      </c>
+      <c r="J12" s="73"/>
+      <c r="K12" s="66" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="64" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D13" s="65" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F13" s="65" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G13" s="65" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H13" s="65" t="s">
-        <v>494</v>
-      </c>
-      <c r="I13" s="65"/>
-      <c r="J13" s="68" t="s">
-        <v>495</v>
+        <v>499</v>
+      </c>
+      <c r="I13" s="65" t="s">
+        <v>500</v>
+      </c>
+      <c r="J13" s="65"/>
+      <c r="K13" s="68" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="64" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C14" s="74" t="n">
         <v>6</v>
@@ -10952,41 +11413,47 @@
       <c r="H14" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="66" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="74" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="75"/>
+      <c r="K14" s="66" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="64" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F15" s="65" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="G15" s="65" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>501</v>
-      </c>
-      <c r="I15" s="65"/>
-      <c r="J15" s="68" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>507</v>
+      </c>
+      <c r="I15" s="65" t="s">
+        <v>508</v>
+      </c>
+      <c r="J15" s="65"/>
+      <c r="K15" s="68" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="69" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C16" s="76" t="n">
         <f aca="false">IFERROR(C12/C14,0)</f>
@@ -11012,68 +11479,78 @@
         <f aca="false">IFERROR(H12/H14,0)</f>
         <v>1.56</v>
       </c>
-      <c r="I16" s="76"/>
-      <c r="J16" s="68" t="s">
-        <v>504</v>
+      <c r="I16" s="76" t="n">
+        <f aca="false">IFERROR(I12/I14,0)</f>
+        <v>0.722222222222222</v>
+      </c>
+      <c r="J16" s="76"/>
+      <c r="K16" s="68" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="64" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="G17" s="77" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="H17" s="77" t="s">
-        <v>506</v>
-      </c>
-      <c r="I17" s="77"/>
-      <c r="J17" s="68" t="s">
-        <v>508</v>
+        <v>513</v>
+      </c>
+      <c r="I17" s="77" t="s">
+        <v>514</v>
+      </c>
+      <c r="J17" s="77"/>
+      <c r="K17" s="68" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="64" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E18" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G18" s="65" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>512</v>
-      </c>
-      <c r="I18" s="65"/>
-      <c r="J18" s="68" t="s">
-        <v>513</v>
+        <v>519</v>
+      </c>
+      <c r="I18" s="65" t="s">
+        <v>518</v>
+      </c>
+      <c r="J18" s="65"/>
+      <c r="K18" s="68" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="64" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="C19" s="75" t="n">
         <f aca="false">C9*2.64</f>
@@ -11099,122 +11576,168 @@
         <f aca="false">H9*2.64</f>
         <v>21.12</v>
       </c>
-      <c r="I19" s="75"/>
-      <c r="J19" s="66" t="s">
-        <v>515</v>
+      <c r="I19" s="75" t="n">
+        <f aca="false">I9*2.64</f>
+        <v>26.4</v>
+      </c>
+      <c r="J19" s="75"/>
+      <c r="K19" s="66" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="64" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E20" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F20" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G20" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>517</v>
-      </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="66" t="s">
+        <v>524</v>
+      </c>
+      <c r="I20" s="65" t="s">
         <v>518</v>
+      </c>
+      <c r="J20" s="65"/>
+      <c r="K20" s="66" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="64" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F21" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G21" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>520</v>
-      </c>
-      <c r="I21" s="65"/>
-      <c r="J21" s="66" t="s">
-        <v>521</v>
+        <v>527</v>
+      </c>
+      <c r="I21" s="65" t="s">
+        <v>518</v>
+      </c>
+      <c r="J21" s="65"/>
+      <c r="K21" s="66" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="64" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E22" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F22" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G22" s="65" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>523</v>
-      </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="66" t="s">
-        <v>524</v>
+        <v>530</v>
+      </c>
+      <c r="I22" s="65" t="s">
+        <v>518</v>
+      </c>
+      <c r="J22" s="65"/>
+      <c r="K22" s="66" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="64" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="E23" s="65" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F23" s="65" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="G23" s="65" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="H23" s="67" t="s">
-        <v>527</v>
-      </c>
-      <c r="I23" s="65"/>
-      <c r="J23" s="68" t="s">
-        <v>528</v>
+        <v>534</v>
+      </c>
+      <c r="I23" s="65" t="s">
+        <v>533</v>
+      </c>
+      <c r="J23" s="65"/>
+      <c r="K23" s="68" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="64" t="s">
+        <v>536</v>
+      </c>
+      <c r="C24" s="65" t="s">
+        <v>537</v>
+      </c>
+      <c r="D24" s="65" t="s">
+        <v>537</v>
+      </c>
+      <c r="E24" s="65" t="s">
+        <v>538</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>538</v>
+      </c>
+      <c r="G24" s="65" t="s">
+        <v>539</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>540</v>
+      </c>
+      <c r="I24" s="65" t="s">
+        <v>541</v>
+      </c>
+      <c r="J24" s="65"/>
+      <c r="K24" s="66" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -11224,10 +11747,11 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="64" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="C26" s="78" t="n">
         <v>18228.7</v>
@@ -11247,14 +11771,17 @@
       <c r="H26" s="78" t="n">
         <v>12387.64</v>
       </c>
-      <c r="I26" s="79"/>
-      <c r="J26" s="66" t="s">
-        <v>531</v>
+      <c r="I26" s="78" t="n">
+        <v>16780.54</v>
+      </c>
+      <c r="J26" s="79"/>
+      <c r="K26" s="66" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="64" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="C27" s="78" t="n">
         <v>0</v>
@@ -11274,14 +11801,17 @@
       <c r="H27" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="79"/>
-      <c r="J27" s="68" t="s">
-        <v>533</v>
+      <c r="I27" s="78" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J27" s="79"/>
+      <c r="K27" s="68" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="64" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="C28" s="78" t="n">
         <v>790</v>
@@ -11301,14 +11831,17 @@
       <c r="H28" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="79"/>
-      <c r="J28" s="66" t="s">
-        <v>535</v>
+      <c r="I28" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="79"/>
+      <c r="K28" s="66" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="64" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="C29" s="79" t="n">
         <f aca="false">6900/10*C9</f>
@@ -11330,14 +11863,17 @@
       <c r="H29" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="79"/>
-      <c r="J29" s="68" t="s">
-        <v>537</v>
+      <c r="I29" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="79"/>
+      <c r="K29" s="68" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="64" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -11363,14 +11899,18 @@
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="I30" s="79"/>
-      <c r="J30" s="68" t="s">
-        <v>539</v>
+      <c r="I30" s="79" t="n">
+        <f aca="false">ENTRADAS!$C$28</f>
+        <v>2500</v>
+      </c>
+      <c r="J30" s="79"/>
+      <c r="K30" s="68" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="69" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="C31" s="80" t="n">
         <f aca="false">SUM(C26:C30)</f>
@@ -11396,14 +11936,18 @@
         <f aca="false">SUM(H26:H30)</f>
         <v>14887.64</v>
       </c>
-      <c r="I31" s="80"/>
-      <c r="J31" s="66" t="s">
-        <v>541</v>
+      <c r="I31" s="80" t="n">
+        <f aca="false">SUM(I26:I30)</f>
+        <v>21080.54</v>
+      </c>
+      <c r="J31" s="80"/>
+      <c r="K31" s="66" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="69" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="C32" s="81" t="n">
         <f aca="false">IFERROR(C31/(C12*1000),0)</f>
@@ -11429,14 +11973,18 @@
         <f aca="false">IFERROR(H31/(H12*1000),0)</f>
         <v>3.18111965811966</v>
       </c>
-      <c r="I32" s="81"/>
-      <c r="J32" s="66" t="s">
-        <v>543</v>
+      <c r="I32" s="81" t="n">
+        <f aca="false">IFERROR(I31/(I12*1000),0)</f>
+        <v>3.24316</v>
+      </c>
+      <c r="J32" s="81"/>
+      <c r="K32" s="66" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="64" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="C33" s="82" t="n">
         <f aca="false">IFERROR(C26/(C12*1000),0)</f>
@@ -11447,26 +11995,29 @@
         <v>2.38400826446281</v>
       </c>
       <c r="E33" s="82" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="F33" s="82" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="G33" s="82" t="n">
         <f aca="false">IFERROR(G26/(G12*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
       <c r="H33" s="82" t="s">
-        <v>545</v>
-      </c>
-      <c r="I33" s="82"/>
-      <c r="J33" s="66" t="s">
-        <v>546</v>
+        <v>559</v>
+      </c>
+      <c r="I33" s="82" t="s">
+        <v>559</v>
+      </c>
+      <c r="J33" s="82"/>
+      <c r="K33" s="66" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -11476,10 +12027,11 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="64" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">C12*GERACAO!$I$17</f>
@@ -11505,14 +12057,18 @@
         <f aca="false">H12*GERACAO!$I$17</f>
         <v>5916.7788966</v>
       </c>
-      <c r="I36" s="72"/>
-      <c r="J36" s="66" t="s">
-        <v>549</v>
+      <c r="I36" s="72" t="n">
+        <f aca="false">I12*GERACAO!$I$17</f>
+        <v>8217.7484675</v>
+      </c>
+      <c r="J36" s="72"/>
+      <c r="K36" s="66" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="64" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="C37" s="72" t="n">
         <f aca="false">C36/12</f>
@@ -11538,12 +12094,16 @@
         <f aca="false">H36/12</f>
         <v>493.06490805</v>
       </c>
-      <c r="I37" s="72"/>
-      <c r="J37" s="66"/>
+      <c r="I37" s="72" t="n">
+        <f aca="false">I36/12</f>
+        <v>684.812372291667</v>
+      </c>
+      <c r="J37" s="72"/>
+      <c r="K37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="64" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="C38" s="72" t="n">
         <f aca="false">C36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -11569,14 +12129,18 @@
         <f aca="false">H36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
         <v>5392.5073488</v>
       </c>
-      <c r="I38" s="72"/>
-      <c r="J38" s="66" t="s">
-        <v>552</v>
+      <c r="I38" s="72" t="n">
+        <f aca="false">I36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7489.59354</v>
+      </c>
+      <c r="J38" s="72"/>
+      <c r="K38" s="66" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="64" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="C39" s="71" t="n">
         <v>10554</v>
@@ -11596,14 +12160,17 @@
       <c r="H39" s="71" t="n">
         <v>6367.5</v>
       </c>
-      <c r="I39" s="72"/>
-      <c r="J39" s="66" t="s">
-        <v>554</v>
+      <c r="I39" s="71" t="n">
+        <v>8400</v>
+      </c>
+      <c r="J39" s="72"/>
+      <c r="K39" s="66" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="69" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="C40" s="83" t="n">
         <f aca="false">IFERROR(C36/C39-1,0)</f>
@@ -11629,14 +12196,18 @@
         <f aca="false">IFERROR(H36/H39-1,0)</f>
         <v>-0.0707846255830389</v>
       </c>
-      <c r="I40" s="83"/>
-      <c r="J40" s="68" t="s">
-        <v>556</v>
+      <c r="I40" s="83" t="n">
+        <f aca="false">IFERROR(I36/I39-1,0)</f>
+        <v>-0.0216966110119046</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="68" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="64" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C41" s="72" t="n">
         <f aca="false">C12*GERACAO!$J$17</f>
@@ -11662,14 +12233,18 @@
         <f aca="false">H12*GERACAO!$J$17</f>
         <v>6651.3774132</v>
       </c>
-      <c r="I41" s="72"/>
-      <c r="J41" s="66" t="s">
-        <v>558</v>
+      <c r="I41" s="72" t="n">
+        <f aca="false">I12*GERACAO!$J$17</f>
+        <v>9238.024185</v>
+      </c>
+      <c r="J41" s="72"/>
+      <c r="K41" s="66" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -11679,10 +12254,11 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="64" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="C44" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$33*12),0)</f>
@@ -11708,14 +12284,18 @@
         <f aca="false">IFERROR(H36/(BYD!$F$33*12),0)</f>
         <v>1.29300238125</v>
       </c>
-      <c r="I44" s="84"/>
-      <c r="J44" s="66" t="s">
-        <v>561</v>
+      <c r="I44" s="84" t="n">
+        <f aca="false">IFERROR(I36/(BYD!$F$33*12),0)</f>
+        <v>1.795836640625</v>
+      </c>
+      <c r="J44" s="84"/>
+      <c r="K44" s="66" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="64" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="C45" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$34*12),0)</f>
@@ -11741,12 +12321,16 @@
         <f aca="false">IFERROR(H36/(BYD!$F$34*12),0)</f>
         <v>0.840096327378091</v>
       </c>
-      <c r="I45" s="84"/>
-      <c r="J45" s="66"/>
+      <c r="I45" s="84" t="n">
+        <f aca="false">IFERROR(I36/(BYD!$F$34*12),0)</f>
+        <v>1.16680045469179</v>
+      </c>
+      <c r="J45" s="84"/>
+      <c r="K45" s="66"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="69" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="C46" s="85" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$35*12),0)</f>
@@ -11772,14 +12356,18 @@
         <f aca="false">IFERROR(H36/(BYD!$F$35*12),0)</f>
         <v>0.730518545546166</v>
       </c>
-      <c r="I46" s="85"/>
-      <c r="J46" s="66" t="s">
-        <v>564</v>
+      <c r="I46" s="85" t="n">
+        <f aca="false">IFERROR(I36/(BYD!$F$35*12),0)</f>
+        <v>1.01460909103634</v>
+      </c>
+      <c r="J46" s="85"/>
+      <c r="K46" s="66" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="64" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="C47" s="72" t="n">
         <f aca="false">C36-BYD!$G$35</f>
@@ -11805,14 +12393,18 @@
         <f aca="false">H36-BYD!$G$35</f>
         <v>-2182.64435921395</v>
       </c>
-      <c r="I47" s="72"/>
-      <c r="J47" s="66" t="s">
-        <v>566</v>
+      <c r="I47" s="72" t="n">
+        <f aca="false">I36-BYD!$G$35</f>
+        <v>118.325211686048</v>
+      </c>
+      <c r="J47" s="72"/>
+      <c r="K47" s="66" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="69" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="C48" s="86" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C36)/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -11838,12 +12430,16 @@
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-H36)/GERACAO!$I$17*1000/H10,0),0)</f>
         <v>3</v>
       </c>
-      <c r="I48" s="86"/>
-      <c r="J48" s="66"/>
+      <c r="I48" s="86" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-I36)/GERACAO!$I$17*1000/I10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="86"/>
+      <c r="K48" s="66"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="69" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="C49" s="87" t="n">
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -11869,14 +12465,18 @@
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/H10,0),0)</f>
         <v>4</v>
       </c>
-      <c r="I49" s="87"/>
-      <c r="J49" s="66" t="s">
-        <v>569</v>
+      <c r="I49" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/I10,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="J49" s="87"/>
+      <c r="K49" s="66" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -11886,10 +12486,11 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="64" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="C52" s="79" t="n">
         <f aca="false">CONTA!$C$54</f>
@@ -11915,14 +12516,18 @@
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="I52" s="79"/>
-      <c r="J52" s="66" t="s">
-        <v>572</v>
+      <c r="I52" s="79" t="n">
+        <f aca="false">CONTA!$C$54</f>
+        <v>410.62787654321</v>
+      </c>
+      <c r="J52" s="79"/>
+      <c r="K52" s="66" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="64" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="C53" s="79" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
@@ -11948,14 +12553,18 @@
         <f aca="false">ECONOMIA!H8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="I53" s="79"/>
-      <c r="J53" s="66" t="s">
-        <v>574</v>
+      <c r="I53" s="79" t="n">
+        <f aca="false">ECONOMIA!I8/12</f>
+        <v>710.553156093023</v>
+      </c>
+      <c r="J53" s="79"/>
+      <c r="K53" s="66" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="69" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C54" s="88" t="n">
         <f aca="false">ECONOMIA!C19</f>
@@ -11981,14 +12590,18 @@
         <f aca="false">ECONOMIA!H19</f>
         <v>281.009977650472</v>
       </c>
-      <c r="I54" s="88"/>
-      <c r="J54" s="68" t="s">
-        <v>576</v>
+      <c r="I54" s="88" t="n">
+        <f aca="false">ECONOMIA!I19</f>
+        <v>162.893279261767</v>
+      </c>
+      <c r="J54" s="88"/>
+      <c r="K54" s="68" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="64" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="C55" s="79" t="n">
         <f aca="false">ECONOMIA!C26</f>
@@ -12014,12 +12627,16 @@
         <f aca="false">ECONOMIA!H26</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="I55" s="79"/>
-      <c r="J55" s="66"/>
+      <c r="I55" s="79" t="n">
+        <f aca="false">ECONOMIA!I26</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="J55" s="79"/>
+      <c r="K55" s="66"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="69" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="C56" s="88" t="n">
         <f aca="false">C55/12</f>
@@ -12045,12 +12662,16 @@
         <f aca="false">H55/12</f>
         <v>392.043178442552</v>
       </c>
-      <c r="I56" s="88"/>
-      <c r="J56" s="66"/>
+      <c r="I56" s="88" t="n">
+        <f aca="false">I55/12</f>
+        <v>510.159876831256</v>
+      </c>
+      <c r="J56" s="88"/>
+      <c r="K56" s="66"/>
     </row>
     <row r="57" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="69" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C57" s="89" t="n">
         <f aca="false">IFERROR(C31/C55,0)</f>
@@ -12076,14 +12697,18 @@
         <f aca="false">IFERROR(H31/H55,0)</f>
         <v>3.1645408844895</v>
       </c>
-      <c r="I57" s="89"/>
-      <c r="J57" s="66" t="s">
-        <v>580</v>
+      <c r="I57" s="89" t="n">
+        <f aca="false">IFERROR(I31/I55,0)</f>
+        <v>3.44345321231079</v>
+      </c>
+      <c r="J57" s="89"/>
+      <c r="K57" s="66" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="64" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="C58" s="90" t="n">
         <f aca="false">PROJECAO!E10</f>
@@ -12109,12 +12734,16 @@
         <f aca="false">PROJECAO!T10</f>
         <v>26795.7299400571</v>
       </c>
-      <c r="I58" s="90"/>
-      <c r="J58" s="66"/>
+      <c r="I58" s="90" t="n">
+        <f aca="false">PROJECAO!W10</f>
+        <v>34868.8793416317</v>
+      </c>
+      <c r="J58" s="90"/>
+      <c r="K58" s="66"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="64" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="C59" s="90" t="n">
         <f aca="false">PROJECAO!E15</f>
@@ -12140,12 +12769,16 @@
         <f aca="false">PROJECAO!T15</f>
         <v>63540.0996667917</v>
       </c>
-      <c r="I59" s="90"/>
-      <c r="J59" s="66"/>
+      <c r="I59" s="90" t="n">
+        <f aca="false">PROJECAO!W15</f>
+        <v>82683.773630833</v>
+      </c>
+      <c r="J59" s="90"/>
+      <c r="K59" s="66"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="64" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="C60" s="90" t="n">
         <f aca="false">PROJECAO!E25</f>
@@ -12171,12 +12804,16 @@
         <f aca="false">PROJECAO!T25</f>
         <v>183020.952042449</v>
       </c>
-      <c r="I60" s="90"/>
-      <c r="J60" s="66"/>
+      <c r="I60" s="90" t="n">
+        <f aca="false">PROJECAO!W25</f>
+        <v>238162.405280052</v>
+      </c>
+      <c r="J60" s="90"/>
+      <c r="K60" s="66"/>
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="69" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="C61" s="91" t="n">
         <f aca="false">C60-C31</f>
@@ -12202,14 +12839,18 @@
         <f aca="false">H60-H31</f>
         <v>168133.312042449</v>
       </c>
-      <c r="I61" s="91"/>
-      <c r="J61" s="66" t="s">
-        <v>585</v>
+      <c r="I61" s="91" t="n">
+        <f aca="false">I60-I31</f>
+        <v>217081.865280052</v>
+      </c>
+      <c r="J61" s="91"/>
+      <c r="K61" s="66" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="64" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="C62" s="84" t="n">
         <f aca="false">IFERROR(C61/C31,0)</f>
@@ -12235,12 +12876,16 @@
         <f aca="false">IFERROR(H61/H31,0)</f>
         <v>11.2934831875602</v>
       </c>
-      <c r="I62" s="84"/>
-      <c r="J62" s="66"/>
+      <c r="I62" s="84" t="n">
+        <f aca="false">IFERROR(I61/I31,0)</f>
+        <v>10.2977374052113</v>
+      </c>
+      <c r="J62" s="84"/>
+      <c r="K62" s="66"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="7" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -12250,10 +12895,11 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="64" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="C65" s="75" t="n">
         <f aca="false">C14*1.35</f>
@@ -12279,12 +12925,16 @@
         <f aca="false">H14*1.35</f>
         <v>4.05</v>
       </c>
-      <c r="I65" s="75"/>
-      <c r="J65" s="66"/>
-    </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="75" t="n">
+        <f aca="false">I14*1.35</f>
+        <v>12.15</v>
+      </c>
+      <c r="J65" s="75"/>
+      <c r="K65" s="66"/>
+    </row>
+    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="69" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="C66" s="86" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((C65-C12)*1000/C10,0))</f>
@@ -12310,14 +12960,18 @@
         <f aca="false">MAX(0,ROUNDDOWN((H65-H12)*1000/H10,0))</f>
         <v>0</v>
       </c>
-      <c r="I66" s="86"/>
-      <c r="J66" s="68" t="s">
-        <v>590</v>
+      <c r="I66" s="86" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((I65-I12)*1000/I10,0))</f>
+        <v>8</v>
+      </c>
+      <c r="J66" s="86"/>
+      <c r="K66" s="68" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="64" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="C67" s="72" t="n">
         <f aca="false">C66*C10/1000*GERACAO!$I$17</f>
@@ -12343,12 +12997,16 @@
         <f aca="false">H66*H10/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="I67" s="72"/>
-      <c r="J67" s="66"/>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="72" t="n">
+        <f aca="false">I66*I10/1000*GERACAO!$I$17</f>
+        <v>6574.198774</v>
+      </c>
+      <c r="J67" s="72"/>
+      <c r="K67" s="66"/>
+    </row>
+    <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="69" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="C68" s="92" t="str">
         <f aca="false">IF(C16&gt;1.35,"JA SOBRECARREGADO",IF(C16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
@@ -12374,14 +13032,18 @@
         <f aca="false">IF(H16&gt;1.35,"JA SOBRECARREGADO",IF(H16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>JA SOBRECARREGADO</v>
       </c>
-      <c r="I68" s="92"/>
-      <c r="J68" s="66" t="s">
-        <v>593</v>
+      <c r="I68" s="92" t="str">
+        <f aca="false">IF(I16&gt;1.35,"JA SOBRECARREGADO",IF(I16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+        <v>SUBAPROVEITADO</v>
+      </c>
+      <c r="J68" s="92"/>
+      <c r="K68" s="66" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="7" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -12391,10 +13053,11 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="21" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="C71" s="35" t="n">
         <f aca="false">F26-E26</f>
@@ -12403,7 +13066,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C72" s="29" t="n">
         <f aca="false">IFERROR(F57-E57,0)</f>
@@ -12412,7 +13075,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="C73" s="93" t="n">
         <f aca="false">F61-E61</f>
@@ -12421,22 +13084,22 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="5" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12444,17 +13107,17 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="5" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -12484,325 +13147,325 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="F5" s="94" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="F8" s="94" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="F10" s="94" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="F13" s="95" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="F14" s="94" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
+        <v>676</v>
+      </c>
+      <c r="C17" s="96" t="s">
         <v>662</v>
       </c>
-      <c r="C17" s="96" t="s">
-        <v>648</v>
-      </c>
       <c r="D17" s="96" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="F20" s="94" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -12816,7 +13479,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -12830,7 +13493,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -12844,7 +13507,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -12858,7 +13521,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="C28" s="47" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -12875,7 +13538,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="C30" s="44" t="str">
         <f aca="false">COMPARATIVO!C11</f>
@@ -12892,7 +13555,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="C31" s="97" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
@@ -12909,44 +13572,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>691</v>
+        <v>705</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="C34" s="98" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -12955,7 +13618,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">COMPARATIVO!C28-COMPARATIVO!D28</f>
@@ -12964,7 +13627,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
@@ -12973,14 +13636,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="C41" s="99" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -12999,57 +13662,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>712</v>
+        <v>726</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -13075,14 +13741,18 @@
         <f aca="false">BYD!$G$35</f>
         <v>8099.42325581395</v>
       </c>
-      <c r="I5" s="100"/>
-      <c r="J5" s="66" t="s">
-        <v>714</v>
+      <c r="I5" s="36" t="n">
+        <f aca="false">BYD!$G$35</f>
+        <v>8099.42325581395</v>
+      </c>
+      <c r="J5" s="100"/>
+      <c r="K5" s="66" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COMPARATIVO!C36</f>
@@ -13108,14 +13778,18 @@
         <f aca="false">COMPARATIVO!H36</f>
         <v>5916.7788966</v>
       </c>
-      <c r="I6" s="100"/>
-      <c r="J6" s="66" t="s">
-        <v>716</v>
+      <c r="I6" s="36" t="n">
+        <f aca="false">COMPARATIVO!I36</f>
+        <v>8217.7484675</v>
+      </c>
+      <c r="J6" s="100"/>
+      <c r="K6" s="66" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="C7" s="101" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -13141,14 +13815,18 @@
         <f aca="false">ENTRADAS!$C$18</f>
         <v>1.02147</v>
       </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="66" t="s">
-        <v>718</v>
+      <c r="I7" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$18</f>
+        <v>1.02147</v>
+      </c>
+      <c r="J7" s="100"/>
+      <c r="K7" s="66" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="C8" s="102" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -13174,14 +13852,18 @@
         <f aca="false">H5*H7+ENTRADAS!$C$26*12</f>
         <v>8526.63787311628</v>
       </c>
-      <c r="I8" s="100"/>
-      <c r="J8" s="66" t="s">
-        <v>720</v>
+      <c r="I8" s="102" t="n">
+        <f aca="false">I5*I7+ENTRADAS!$C$26*12</f>
+        <v>8526.63787311628</v>
+      </c>
+      <c r="J8" s="100"/>
+      <c r="K8" s="66" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -13207,14 +13889,18 @@
         <f aca="false">MIN(H5,H6)*ENTRADAS!$C$37</f>
         <v>1775.03366898</v>
       </c>
-      <c r="I9" s="100"/>
-      <c r="J9" s="66" t="s">
-        <v>722</v>
+      <c r="I9" s="36" t="n">
+        <f aca="false">MIN(I5,I6)*ENTRADAS!$C$37</f>
+        <v>2429.82697674419</v>
+      </c>
+      <c r="J9" s="100"/>
+      <c r="K9" s="66" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">C6-C9</f>
@@ -13240,14 +13926,18 @@
         <f aca="false">H6-H9</f>
         <v>4141.74522762</v>
       </c>
-      <c r="I10" s="100"/>
-      <c r="J10" s="66" t="s">
-        <v>724</v>
+      <c r="I10" s="36" t="n">
+        <f aca="false">I6-I9</f>
+        <v>5787.92149075582</v>
+      </c>
+      <c r="J10" s="100"/>
+      <c r="K10" s="66" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -13273,14 +13963,18 @@
         <f aca="false">ENTRADAS!$C$17*12</f>
         <v>600</v>
       </c>
-      <c r="I11" s="100"/>
-      <c r="J11" s="66" t="s">
-        <v>726</v>
+      <c r="I11" s="36" t="n">
+        <f aca="false">ENTRADAS!$C$17*12</f>
+        <v>600</v>
+      </c>
+      <c r="J11" s="100"/>
+      <c r="K11" s="66" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -13306,14 +14000,18 @@
         <f aca="false">MAX(0,MIN(H10,H5-H9-H11))</f>
         <v>4141.74522762</v>
       </c>
-      <c r="I12" s="100"/>
-      <c r="J12" s="66" t="s">
-        <v>728</v>
+      <c r="I12" s="36" t="n">
+        <f aca="false">MAX(0,MIN(I10,I5-I9-I11))</f>
+        <v>5069.59627906977</v>
+      </c>
+      <c r="J12" s="100"/>
+      <c r="K12" s="66" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">C10-C12</f>
@@ -13339,14 +14037,18 @@
         <f aca="false">H10-H12</f>
         <v>0</v>
       </c>
-      <c r="I13" s="100"/>
-      <c r="J13" s="66" t="s">
-        <v>730</v>
+      <c r="I13" s="36" t="n">
+        <f aca="false">I10-I12</f>
+        <v>718.325211686048</v>
+      </c>
+      <c r="J13" s="100"/>
+      <c r="K13" s="66" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -13372,14 +14074,18 @@
         <f aca="false">MAX(H11,H5-H9-H12)</f>
         <v>2182.64435921395</v>
       </c>
-      <c r="I14" s="100"/>
-      <c r="J14" s="66" t="s">
-        <v>732</v>
+      <c r="I14" s="36" t="n">
+        <f aca="false">MAX(I11,I5-I9-I12)</f>
+        <v>600</v>
+      </c>
+      <c r="J14" s="100"/>
+      <c r="K14" s="66" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="C15" s="101" t="n">
         <f aca="false">C14*C7</f>
@@ -13405,12 +14111,16 @@
         <f aca="false">H14*H7</f>
         <v>2229.50573360628</v>
       </c>
-      <c r="I15" s="100"/>
-      <c r="J15" s="66"/>
+      <c r="I15" s="101" t="n">
+        <f aca="false">I14*I7</f>
+        <v>612.882</v>
+      </c>
+      <c r="J15" s="100"/>
+      <c r="K15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="C16" s="101" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -13436,14 +14146,18 @@
         <f aca="false">H12*ENTRADAS!$C$25</f>
         <v>889.293998199383</v>
       </c>
-      <c r="I16" s="100"/>
-      <c r="J16" s="66" t="s">
-        <v>735</v>
+      <c r="I16" s="101" t="n">
+        <f aca="false">I12*ENTRADAS!$C$25</f>
+        <v>1088.51735114121</v>
+      </c>
+      <c r="J16" s="100"/>
+      <c r="K16" s="66" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="C17" s="101" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -13469,14 +14183,18 @@
         <f aca="false">ENTRADAS!$C$26*12</f>
         <v>253.32</v>
       </c>
-      <c r="I17" s="100"/>
-      <c r="J17" s="66" t="s">
-        <v>737</v>
+      <c r="I17" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$26*12</f>
+        <v>253.32</v>
+      </c>
+      <c r="J17" s="100"/>
+      <c r="K17" s="66" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -13502,14 +14220,18 @@
         <f aca="false">H15+H16+H17</f>
         <v>3372.11973180566</v>
       </c>
-      <c r="I18" s="100"/>
-      <c r="J18" s="66" t="s">
-        <v>739</v>
+      <c r="I18" s="47" t="n">
+        <f aca="false">I15+I16+I17</f>
+        <v>1954.71935114121</v>
+      </c>
+      <c r="J18" s="100"/>
+      <c r="K18" s="66" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">C18/12</f>
@@ -13535,14 +14257,18 @@
         <f aca="false">H18/12</f>
         <v>281.009977650472</v>
       </c>
-      <c r="I19" s="100"/>
-      <c r="J19" s="66" t="s">
-        <v>741</v>
+      <c r="I19" s="47" t="n">
+        <f aca="false">I18/12</f>
+        <v>162.893279261767</v>
+      </c>
+      <c r="J19" s="100"/>
+      <c r="K19" s="66" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="C20" s="37" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -13568,12 +14294,16 @@
         <f aca="false">IFERROR(1-H18/H8,0)</f>
         <v>0.604519415274143</v>
       </c>
-      <c r="I20" s="100"/>
-      <c r="J20" s="66"/>
+      <c r="I20" s="37" t="n">
+        <f aca="false">IFERROR(1-I18/I8,0)</f>
+        <v>0.770751452069489</v>
+      </c>
+      <c r="J20" s="100"/>
+      <c r="K20" s="66"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="C21" s="101" t="n">
         <f aca="false">C8-C18</f>
@@ -13599,12 +14329,16 @@
         <f aca="false">H8-H18</f>
         <v>5154.51814131062</v>
       </c>
-      <c r="I21" s="100"/>
-      <c r="J21" s="66"/>
+      <c r="I21" s="101" t="n">
+        <f aca="false">I8-I18</f>
+        <v>6571.91852197507</v>
+      </c>
+      <c r="J21" s="100"/>
+      <c r="K21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="C22" s="101" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -13630,14 +14364,18 @@
         <f aca="false">ENTRADAS!$C$35</f>
         <v>300</v>
       </c>
-      <c r="I22" s="100"/>
-      <c r="J22" s="66" t="s">
-        <v>745</v>
+      <c r="I22" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$35</f>
+        <v>300</v>
+      </c>
+      <c r="J22" s="100"/>
+      <c r="K22" s="66" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="C23" s="101" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -13663,14 +14401,18 @@
         <f aca="false">ENTRADAS!$C$36</f>
         <v>150</v>
       </c>
-      <c r="I23" s="100"/>
-      <c r="J23" s="66" t="s">
-        <v>747</v>
+      <c r="I23" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$36</f>
+        <v>150</v>
+      </c>
+      <c r="J23" s="100"/>
+      <c r="K23" s="66" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="C24" s="101" t="n">
         <f aca="false">0</f>
@@ -13696,14 +14438,18 @@
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I24" s="100"/>
-      <c r="J24" s="66" t="s">
-        <v>749</v>
+      <c r="I24" s="101" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="100"/>
+      <c r="K24" s="66" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="C25" s="101" t="n">
         <f aca="false">C22+C23</f>
@@ -13729,12 +14475,16 @@
         <f aca="false">H22+H23</f>
         <v>450</v>
       </c>
-      <c r="I25" s="100"/>
-      <c r="J25" s="66"/>
+      <c r="I25" s="101" t="n">
+        <f aca="false">I22+I23</f>
+        <v>450</v>
+      </c>
+      <c r="J25" s="100"/>
+      <c r="K25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="C26" s="103" t="n">
         <f aca="false">C21-C25</f>
@@ -13760,14 +14510,18 @@
         <f aca="false">H21-H25</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="I26" s="100"/>
-      <c r="J26" s="66" t="s">
-        <v>752</v>
+      <c r="I26" s="103" t="n">
+        <f aca="false">I21-I25</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="J26" s="100"/>
+      <c r="K26" s="66" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -13777,125 +14531,126 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4576</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>755</v>
+      <c r="K29" s="2" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>7042.97674418605</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>757</v>
+      <c r="K30" s="2" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
         <v>2466.97674418605</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>759</v>
+      <c r="K31" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.539112050739958</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>761</v>
+      <c r="K32" s="2" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4927.56672</v>
       </c>
-      <c r="J33" s="2" t="s">
-        <v>763</v>
+      <c r="K33" s="2" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7447.50945488372</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>765</v>
+      <c r="K34" s="2" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2519.94273488372</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>767</v>
+      <c r="K35" s="2" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>529.696418232558</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>769</v>
+      <c r="K36" s="2" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>1990.24631665116</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>771</v>
+      <c r="K37" s="2" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>773</v>
+      <c r="K38" s="2" t="s">
+        <v>788</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="1007">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -76,7 +76,19 @@
     <t xml:space="preserve">     Unica com 18x SEM JUROS pelo mesmo valor a vista (R$ 932,25/mes). Unica com 1 MPPT por modulo.</t>
   </si>
   <si>
-    <t xml:space="preserve">H) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
+    <t xml:space="preserve">H) Sfero (indicacao do Renato) - 10 modulos Longi/DAH 590 W = 5,90 kWp + 2 microinversores Solis/Growatt de 2,5 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     -&gt; R$ 18.733,00 INSTALADO. A UNICA com marcas Tier 1 nos DOIS equipamentos, seguro All Risk e garantia de performance em contrato.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2 (Alexandre) - 11 modulos TCL 620 W = 6,82 kWp + AUXSOL 7,5 kW 2 MPPT  -&gt;  R$ 16.890,00 INSTALADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Substitui a proposta F: corrigiu a relacao DC/AC de 1,56 para 0,91 e passou de 1 para 2 MPPTs. Melhor R$/Wp de todos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
   </si>
   <si>
     <t xml:space="preserve">2. AS TRES DESCOBERTAS MAIS IMPORTANTES</t>
@@ -1394,9 +1406,10 @@
 Solis 4 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">F) Sun Coast
+    <t xml:space="preserve">F) Sun Coast v1
 RONMA 585W
-AUXSOL 3 kW</t>
+AUXSOL 3 kW
+(SUPERADA)</t>
   </si>
   <si>
     <t xml:space="preserve">G) SunWash
@@ -1404,7 +1417,17 @@
 4x 2,25 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">H) Bruno G4
+    <t xml:space="preserve">H) Sfero (Renato)
+Longi/DAH 590W
+2x micro 2,5 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2
+TCL 620W x11
+AUXSOL 7,5 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J) Bruno G4
 (a receber)</t>
   </si>
   <si>
@@ -1426,6 +1449,9 @@
     <t xml:space="preserve">Sun Coast - Alexandre (11) 91544-8947</t>
   </si>
   <si>
+    <t xml:space="preserve">Sfero - indic. Renato (11) 99705-1311</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bruno G4 (11) 96861-7830</t>
   </si>
   <si>
@@ -1444,6 +1470,9 @@
     <t xml:space="preserve">47.864.839/0001-31</t>
   </si>
   <si>
+    <t xml:space="preserve">NAO INFORMADO na proposta</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: SunWash e William nao informaram CNPJ. Sem CNPJ nao existe garantia exigivel. Sun Coast e a unica que trouxe CNPJ na propria proposta.</t>
   </si>
   <si>
@@ -1468,6 +1497,12 @@
     <t xml:space="preserve">WhatsApp 10/08/2026 17:45</t>
   </si>
   <si>
+    <t xml:space="preserve">Proposta 0664/2026 de 11/08/2026 (val. 10 dias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposta 40438 de 11/08/2026 (val. 20/08)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nada recebido</t>
   </si>
   <si>
@@ -1522,6 +1557,12 @@
     <t xml:space="preserve">Nao informado (650 W)</t>
   </si>
   <si>
+    <t xml:space="preserve">Longi ou DAH Solar (Tier 1 de verdade)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCL Solar bifacial N-type 132 cel</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA sao marcas com pouquissima rede de assistencia de modulo no Brasil - exigir INMETRO e quem honra a garantia aqui.</t>
   </si>
   <si>
@@ -1552,6 +1593,12 @@
     <t xml:space="preserve">4x MICROINVERSOR 2,25 kW = 9,0 kW AC</t>
   </si>
   <si>
+    <t xml:space="preserve">2x microinversor 2,5 kW = 5,0 kW AC - Solis ou Growatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUXSOL 7,5 kW mono 220V 2 MPPT (100% over)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: AUXSOL tem baixa penetracao no Brasil. Huawei e Solis tem assistencia estabelecida.</t>
   </si>
   <si>
@@ -1609,13 +1656,16 @@
     <t xml:space="preserve">Colonial</t>
   </si>
   <si>
+    <t xml:space="preserve">Ceramico / colonial</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: William e Sun Coast dizem COLONIAL, TecSolarSP diz FIBROCIMENTO. Dois contra um: provavelmente a TecSolarSP errou a estrutura inteira. RESOLVER isso antes de qualquer compra.</t>
   </si>
   <si>
-    <t xml:space="preserve">Area de telhado estimada (m2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base: a Sun Coast declara 21,12 m2 para 8 modulos, ou 2,64 m2 por modulo. Sem fotos do telhado NAO foi possivel verificar se essa area existe na agua Sudeste.</t>
+    <t xml:space="preserve">Area de telhado necessaria (m2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores em azul foram DECLARADOS pelo fornecedor; os demais sao estimados a 0,00452 m2 por watt (calibrado pelas areas declaradas). Sem fotos do telhado NAO foi verificado se essa area existe na agua Sudeste.</t>
   </si>
   <si>
     <t xml:space="preserve">Garantia declarada do modulo</t>
@@ -1624,6 +1674,9 @@
     <t xml:space="preserve">25 anos eficiencia / 15 anos defeito</t>
   </si>
   <si>
+    <t xml:space="preserve">12 anos produto / 25 anos eficiencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">So a Sun Coast declarou garantias na proposta. Dos outros, exigir por escrito.</t>
   </si>
   <si>
@@ -1633,6 +1686,9 @@
     <t xml:space="preserve">10 a 25 anos</t>
   </si>
   <si>
+    <t xml:space="preserve">7 a 10 anos</t>
+  </si>
+  <si>
     <t xml:space="preserve">'10 a 25 anos' da Sun Coast e vago: exigir o numero exato para o modelo cotado.</t>
   </si>
   <si>
@@ -1642,6 +1698,9 @@
     <t xml:space="preserve">12 meses</t>
   </si>
   <si>
+    <t xml:space="preserve">1 ano instalacao + SEGURO ALL RISK 1 ano + GARANTIA DE PERFORMANCE EM CONTRATO</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 meses de servico e o minimo de mercado.</t>
   </si>
   <si>
@@ -1654,6 +1713,9 @@
     <t xml:space="preserve">padrao de entrada, obras civis, telhado, eletrodutos, ART estrutural</t>
   </si>
   <si>
+    <t xml:space="preserve">obras civis, reformas no telhado/laje e no PADRAO DE ENTRADA</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: a Sun Coast exclui EXPLICITAMENTE a adequacao do padrao de entrada, obras no telhado, eletrodutos e o ART estrutural. E honesto ao declarar, mas o custo e seu. Os outros nao declararam exclusoes - o que nao significa que estejam inclusas.</t>
   </si>
   <si>
@@ -1675,6 +1737,12 @@
     <t xml:space="preserve">18x de R$ 932,25 SEM JUROS (= preco a vista)</t>
   </si>
   <si>
+    <t xml:space="preserve">3x: 60% entrada / 20% montado / 20% ligado; ou Santander 60x R$ 553 ou 72x R$ 507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a vista, cartao 12x/21x COM juros ou financiamento 36x ate 120x</t>
+  </si>
+  <si>
     <t xml:space="preserve">ATENCAO: 18x SEM JUROS pelo mesmo valor a vista e uma vantagem financeira REAL - equivale a um desconto, porque o dinheiro fica rendendo na sua mao. Todas as outras oferecem parcelamento COM juros.</t>
   </si>
   <si>
@@ -1799,6 +1867,12 @@
   </si>
   <si>
     <t xml:space="preserve">Placas que existem no projeto apenas para compensar o carregamento do carro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potencia AC a declarar na homologacao (kW) e corrente em 220 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALERTA POUCO OBVIO: a potencia declarada a Enel e a do INVERSOR (AC), nao a dos modulos. Quanto maior, maior o disjuntor e o padrao exigidos - e mais caro fica o item da linha 30. Sfero com 5 kW e a menos exigente; a opcao G com 9 kW AC e a mais exigente.</t>
   </si>
   <si>
     <t xml:space="preserve">RESULTADO FINANCEIRO</t>
@@ -2227,13 +2301,19 @@
     <t xml:space="preserve">E) William Maxeon 535W Solis 4 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">F) Sun Coast RONMA 585W AUXSOL 3 kW</t>
+    <t xml:space="preserve">F) Sun Coast v1 RONMA 585W AUXSOL 3 kW (SUPERADA)</t>
   </si>
   <si>
     <t xml:space="preserve">G) SunWash MICRO 10x650W 4x 2,25 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">H) Bruno G4 (a receber)</t>
+    <t xml:space="preserve">H) Sfero (Renato) Longi/DAH 590W 2x micro 2,5 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2 TCL 620W x11 AUXSOL 7,5 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J) Bruno G4 (a receber)</t>
   </si>
   <si>
     <t xml:space="preserve">EXPLICACAO</t>
@@ -2494,15 +2574,15 @@
 Fluxo</t>
   </si>
   <si>
-    <t xml:space="preserve">F) Sun Coast
+    <t xml:space="preserve">F) Sun Coast v1
 Economia</t>
   </si>
   <si>
-    <t xml:space="preserve">F) Sun Coast
+    <t xml:space="preserve">F) Sun Coast v1
 Acumulado</t>
   </si>
   <si>
-    <t xml:space="preserve">F) Sun Coast
+    <t xml:space="preserve">F) Sun Coast v1
 Fluxo</t>
   </si>
   <si>
@@ -2518,6 +2598,30 @@
 Fluxo</t>
   </si>
   <si>
+    <t xml:space="preserve">H) Sfero (Renato)
+Economia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H) Sfero (Renato)
+Acumulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H) Sfero (Renato)
+Fluxo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2
+Economia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2
+Acumulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I) Sun Coast v2
+Fluxo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anos 5, 10 e 20 destacados. As colunas 'Fluxo' viram positivas no ano do payback ja corrigido por inflacao e degradacao.</t>
   </si>
   <si>
@@ -2663,6 +2767,39 @@
   </si>
   <si>
     <t xml:space="preserve">Vantagens tecnicas reais do microinversor no SEU caso: sombreamento nunca foi avaliado e o micro isola o problema por modulo; permite dividir os modulos em mais de uma agua do telhado (poderia recuperar parte dos 11% perdidos pela orientacao Sudeste); nao ha tensao alta de corrente continua no telhado; falha de um equipamento nao para o sistema todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-quater) PERGUNTAS DA PROPOSTA SFERO (opcao H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCA COM BARRA NAO E MARCA. A proposta diz 'Longi/ DAH Solar' e 'Solis/ Growatt', ou seja, um OU outro. Exigir por escrito qual modelo exato sera entregue ANTES de assinar - a diferenca entre Longi e DAH, e entre Solis e Growatt, e real em preco e em suporte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,90 kWp COBRE SO 92% DO CENARIO 3. Pedir a versao com 12 modulos e 3 microinversores (7,08 kWp, DC/AC 0,94), que levaria a cobertura para ~110%, e comparar o preco. Com 2 micros de 2,5 kW nao da para so acrescentar modulos: 12 x 590 W daria DC/AC de 1,42, acima do limite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60% DE ENTRADA E RISCO ALTO. Sao R$ 11.240 pagos antes de qualquer equipamento chegar ao telhado. Negociar para 30-40% de entrada, ou exigir garantia contratual e nota fiscal do material no ato do pagamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A SFERO DIMENSIONOU COM 600 kWh/mes, e nao com os 381 kWh/mes reais da sua conta. Coincidentemente 600 e proximo do consumo COM o BYD (587). VOCE INFORMOU O CARRO PARA ELES? Se sim, e a unica empresa que considerou. Se nao, foi sorte - e vale confirmar de onde saiu esse numero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTOS FORTES REAIS DA SFERO, que nenhuma outra tem: modulo Longi ou DAH (Tier 1 com rede no Brasil) E microinversor Solis ou Growatt (marcas estabelecidas); seguro All Risk de 1 ano cobrindo danos, furto e responsabilidade civil; garantia de performance e resultado em contrato desde o 1o ano; string box com protecoes e monitoramento WiFi ja no escopo; relacao DC/AC de 1,18, a melhor de todas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-quinquies) SOBRE A SUN COAST v2 (opcao I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sun Coast CORRIGIU os dois defeitos apontados: a relacao DC/AC saiu de 1,56 para 0,91 e o inversor passou de 1 para 2 MPPTs, com 11 modulos em vez de 8. O preco marginal do acrescimo foi de R$ 2,10 por Wp, abaixo do preco medio dela - ou seja, foi um upgrade barato. Hoje tem o melhor R$/Wp de todos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAS AS MARCAS CONTINUAM SENDO TCL (modulo) E AUXSOL (inversor), ambas com pouquissima rede de assistencia no Brasil. Garantia de '10 a 25 anos' no inversor so vale se existir empresa para honrar em 2040. Exigir INMETRO, o representante no Brasil com CNPJ e o prazo de atendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS NUMEROS DE MARKETING SEGUEM INFLADOS: 'Retorno do investimento R$ 368.037,69' e 'Rendimento 40,69% ao ano' sobre um investimento de R$ 16.890. Meu calculo da cerca de R$ 219 mil de lucro em 20 anos, que ja e otimo. Ignore esses numeros e use a aba COMPARATIVO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUXSOL DE 7,5 kW SIGNIFICA 7,5 kW DECLARADOS NA HOMOLOGACAO = 34 A em 220 V. Isso pode exigir padrao de entrada maior (e mais caro) do que 6,82 kWp precisaria. Perguntar se um inversor de 6 kW nao serviria, com preco menor.</t>
   </si>
   <si>
     <t xml:space="preserve">1-ter) DEMAIS BLOQUEADORES</t>
@@ -3878,7 +4015,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3961,40 +4098,40 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>15</v>
+      <c r="B18" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>16</v>
+      <c r="B19" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4034,77 +4171,79 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
-        <v>30</v>
+      <c r="B34" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="B37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="3" t="s">
-        <v>35</v>
+      <c r="B40" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="B43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4"/>
+      <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="3" t="s">
-        <v>39</v>
+      <c r="B45" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="s">
-        <v>40</v>
+      <c r="B46" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4112,64 +4251,62 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="4" t="s">
-        <v>43</v>
+      <c r="B50" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="B52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="4"/>
+      <c r="B56" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="3" t="s">
-        <v>49</v>
+      <c r="B57" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="4" t="s">
-        <v>50</v>
+      <c r="B58" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="4" t="s">
-        <v>51</v>
+      <c r="B59" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4214,31 +4351,51 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="3" t="s">
-        <v>62</v>
+      <c r="B71" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="B74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4257,94 +4414,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>789</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>792</v>
+        <v>817</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>794</v>
+        <v>819</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>801</v>
+        <v>826</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>807</v>
+        <v>832</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>813</v>
+        <v>838</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>839</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="AC4" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4439,6 +4614,30 @@
         <f aca="false">W6-COMPARATIVO!I$31</f>
         <v>-14958.6214780249</v>
       </c>
+      <c r="Y6" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
+        <v>6048.21731490014</v>
+      </c>
+      <c r="Z6" s="105" t="n">
+        <f aca="false">Y6</f>
+        <v>6048.21731490014</v>
+      </c>
+      <c r="AA6" s="105" t="n">
+        <f aca="false">Z6-COMPARATIVO!J$31</f>
+        <v>-15184.7826850999</v>
+      </c>
+      <c r="AB6" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="AC6" s="105" t="n">
+        <f aca="false">AB6</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="AD6" s="105" t="n">
+        <f aca="false">AC6-COMPARATIVO!K$31</f>
+        <v>-13268.0814780249</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="104" t="n">
@@ -4532,6 +4731,30 @@
         <f aca="false">W7-COMPARATIVO!I$31</f>
         <v>-8437.64569719492</v>
       </c>
+      <c r="Y7" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
+        <v>6442.47036057191</v>
+      </c>
+      <c r="Z7" s="105" t="n">
+        <f aca="false">Z6+Y7</f>
+        <v>12490.687675472</v>
+      </c>
+      <c r="AA7" s="105" t="n">
+        <f aca="false">Z7-COMPARATIVO!J$31</f>
+        <v>-8742.31232452795</v>
+      </c>
+      <c r="AB7" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
+        <v>6520.97578083002</v>
+      </c>
+      <c r="AC7" s="105" t="n">
+        <f aca="false">AC6+AB7</f>
+        <v>12642.8943028051</v>
+      </c>
+      <c r="AD7" s="105" t="n">
+        <f aca="false">AC7-COMPARATIVO!K$31</f>
+        <v>-6747.10569719492</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="104" t="n">
@@ -4625,6 +4848,30 @@
         <f aca="false">W8-COMPARATIVO!I$31</f>
         <v>-1491.60011009149</v>
       </c>
+      <c r="Y8" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
+        <v>6862.42279102579</v>
+      </c>
+      <c r="Z8" s="105" t="n">
+        <f aca="false">Z7+Y8</f>
+        <v>19353.1104664978</v>
+      </c>
+      <c r="AA8" s="105" t="n">
+        <f aca="false">Z8-COMPARATIVO!J$31</f>
+        <v>-1879.88953350216</v>
+      </c>
+      <c r="AB8" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
+        <v>6946.04558710342</v>
+      </c>
+      <c r="AC8" s="105" t="n">
+        <f aca="false">AC7+AB8</f>
+        <v>19588.9398899085</v>
+      </c>
+      <c r="AD8" s="105" t="n">
+        <f aca="false">AC8-COMPARATIVO!K$31</f>
+        <v>198.939889908506</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="104" t="n">
@@ -4718,6 +4965,30 @@
         <f aca="false">W9-COMPARATIVO!I$31</f>
         <v>5907.22345860726</v>
       </c>
+      <c r="Y9" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
+        <v>7309.7498206588</v>
+      </c>
+      <c r="Z9" s="105" t="n">
+        <f aca="false">Z8+Y9</f>
+        <v>26662.8602871566</v>
+      </c>
+      <c r="AA9" s="105" t="n">
+        <f aca="false">Z9-COMPARATIVO!J$31</f>
+        <v>5429.86028715664</v>
+      </c>
+      <c r="AB9" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
+        <v>7398.82356869876</v>
+      </c>
+      <c r="AC9" s="105" t="n">
+        <f aca="false">AC8+AB9</f>
+        <v>26987.7634586073</v>
+      </c>
+      <c r="AD9" s="105" t="n">
+        <f aca="false">AC9-COMPARATIVO!K$31</f>
+        <v>7597.76345860726</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="106" t="n">
@@ -4811,6 +5082,30 @@
         <f aca="false">W10-COMPARATIVO!I$31</f>
         <v>13788.3393416317</v>
       </c>
+      <c r="Y10" s="108" t="n">
+        <f aca="false">ECONOMIA!J$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
+        <v>7786.23586271845</v>
+      </c>
+      <c r="Z10" s="108" t="n">
+        <f aca="false">Z9+Y10</f>
+        <v>34449.0961498751</v>
+      </c>
+      <c r="AA10" s="108" t="n">
+        <f aca="false">Z10-COMPARATIVO!J$31</f>
+        <v>13216.0961498751</v>
+      </c>
+      <c r="AB10" s="108" t="n">
+        <f aca="false">ECONOMIA!K$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
+        <v>7881.11588302439</v>
+      </c>
+      <c r="AC10" s="108" t="n">
+        <f aca="false">AC9+AB10</f>
+        <v>34868.8793416317</v>
+      </c>
+      <c r="AD10" s="108" t="n">
+        <f aca="false">AC10-COMPARATIVO!K$31</f>
+        <v>15478.8793416317</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="104" t="n">
@@ -4904,6 +5199,30 @@
         <f aca="false">W11-COMPARATIVO!I$31</f>
         <v>22183.185763491</v>
       </c>
+      <c r="Y11" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
+        <v>8293.78164742975</v>
+      </c>
+      <c r="Z11" s="105" t="n">
+        <f aca="false">Z10+Y11</f>
+        <v>42742.8777973048</v>
+      </c>
+      <c r="AA11" s="105" t="n">
+        <f aca="false">Z11-COMPARATIVO!J$31</f>
+        <v>21509.8777973048</v>
+      </c>
+      <c r="AB11" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
+        <v>8394.84642185933</v>
+      </c>
+      <c r="AC11" s="105" t="n">
+        <f aca="false">AC10+AB11</f>
+        <v>43263.725763491</v>
+      </c>
+      <c r="AD11" s="105" t="n">
+        <f aca="false">AC11-COMPARATIVO!K$31</f>
+        <v>23873.725763491</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="104" t="n">
@@ -4997,6 +5316,30 @@
         <f aca="false">W12-COMPARATIVO!I$31</f>
         <v>31125.2502493592</v>
       </c>
+      <c r="Y12" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
+        <v>8834.41180411746</v>
+      </c>
+      <c r="Z12" s="105" t="n">
+        <f aca="false">Z11+Y12</f>
+        <v>51577.2896014223</v>
+      </c>
+      <c r="AA12" s="105" t="n">
+        <f aca="false">Z12-COMPARATIVO!J$31</f>
+        <v>30344.2896014223</v>
+      </c>
+      <c r="AB12" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
+        <v>8942.06448586824</v>
+      </c>
+      <c r="AC12" s="105" t="n">
+        <f aca="false">AC11+AB12</f>
+        <v>52205.7902493592</v>
+      </c>
+      <c r="AD12" s="105" t="n">
+        <f aca="false">AC12-COMPARATIVO!K$31</f>
+        <v>32815.7902493592</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="104" t="n">
@@ -5090,6 +5433,30 @@
         <f aca="false">W13-COMPARATIVO!I$31</f>
         <v>40650.2032087388</v>
       </c>
+      <c r="Y13" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
+        <v>9410.28293756886</v>
+      </c>
+      <c r="Z13" s="105" t="n">
+        <f aca="false">Z12+Y13</f>
+        <v>60987.5725389912</v>
+      </c>
+      <c r="AA13" s="105" t="n">
+        <f aca="false">Z13-COMPARATIVO!J$31</f>
+        <v>39754.5725389912</v>
+      </c>
+      <c r="AB13" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
+        <v>9524.95295937956</v>
+      </c>
+      <c r="AC13" s="105" t="n">
+        <f aca="false">AC12+AB13</f>
+        <v>61730.7432087388</v>
+      </c>
+      <c r="AD13" s="105" t="n">
+        <f aca="false">AC13-COMPARATIVO!K$31</f>
+        <v>42340.7432087388</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="104" t="n">
@@ -5183,6 +5550,30 @@
         <f aca="false">W14-COMPARATIVO!I$31</f>
         <v>50796.0402267755</v>
       </c>
+      <c r="Y14" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
+        <v>10023.6922308543</v>
+      </c>
+      <c r="Z14" s="105" t="n">
+        <f aca="false">Z13+Y14</f>
+        <v>71011.2647698455</v>
+      </c>
+      <c r="AA14" s="105" t="n">
+        <f aca="false">Z14-COMPARATIVO!J$31</f>
+        <v>49778.2647698455</v>
+      </c>
+      <c r="AB14" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
+        <v>10145.8370180367</v>
+      </c>
+      <c r="AC14" s="105" t="n">
+        <f aca="false">AC13+AB14</f>
+        <v>71876.5802267755</v>
+      </c>
+      <c r="AD14" s="105" t="n">
+        <f aca="false">AC14-COMPARATIVO!K$31</f>
+        <v>52486.5802267755</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="106" t="n">
@@ -5276,6 +5667,30 @@
         <f aca="false">W15-COMPARATIVO!I$31</f>
         <v>61603.233630833</v>
       </c>
+      <c r="Y15" s="108" t="n">
+        <f aca="false">ECONOMIA!J$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
+        <v>10677.0866089225</v>
+      </c>
+      <c r="Z15" s="108" t="n">
+        <f aca="false">Z14+Y15</f>
+        <v>81688.351378768</v>
+      </c>
+      <c r="AA15" s="108" t="n">
+        <f aca="false">Z15-COMPARATIVO!J$31</f>
+        <v>60455.351378768</v>
+      </c>
+      <c r="AB15" s="108" t="n">
+        <f aca="false">ECONOMIA!K$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
+        <v>10807.1934040574</v>
+      </c>
+      <c r="AC15" s="108" t="n">
+        <f aca="false">AC14+AB15</f>
+        <v>82683.773630833</v>
+      </c>
+      <c r="AD15" s="108" t="n">
+        <f aca="false">AC15-COMPARATIVO!K$31</f>
+        <v>63293.773630833</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="104" t="n">
@@ -5369,6 +5784,30 @@
         <f aca="false">W16-COMPARATIVO!I$31</f>
         <v>73114.8939369339</v>
       </c>
+      <c r="Y16" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
+        <v>11373.0724995251</v>
+      </c>
+      <c r="Z16" s="105" t="n">
+        <f aca="false">Z15+Y16</f>
+        <v>93061.4238782931</v>
+      </c>
+      <c r="AA16" s="105" t="n">
+        <f aca="false">Z16-COMPARATIVO!J$31</f>
+        <v>71828.4238782931</v>
+      </c>
+      <c r="AB16" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
+        <v>11511.6603061009</v>
+      </c>
+      <c r="AC16" s="105" t="n">
+        <f aca="false">AC15+AB16</f>
+        <v>94195.4339369339</v>
+      </c>
+      <c r="AD16" s="105" t="n">
+        <f aca="false">AC16-COMPARATIVO!K$31</f>
+        <v>74805.4339369339</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="104" t="n">
@@ -5462,6 +5901,30 @@
         <f aca="false">W17-COMPARATIVO!I$31</f>
         <v>85376.941820088</v>
       </c>
+      <c r="Y17" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
+        <v>12114.4262304067</v>
+      </c>
+      <c r="Z17" s="105" t="n">
+        <f aca="false">Z16+Y17</f>
+        <v>105175.8501087</v>
+      </c>
+      <c r="AA17" s="105" t="n">
+        <f aca="false">Z17-COMPARATIVO!J$31</f>
+        <v>83942.8501086998</v>
+      </c>
+      <c r="AB17" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
+        <v>12262.0478831541</v>
+      </c>
+      <c r="AC17" s="105" t="n">
+        <f aca="false">AC16+AB17</f>
+        <v>106457.481820088</v>
+      </c>
+      <c r="AD17" s="105" t="n">
+        <f aca="false">AC17-COMPARATIVO!K$31</f>
+        <v>87067.481820088</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="104" t="n">
@@ -5555,6 +6018,30 @@
         <f aca="false">W18-COMPARATIVO!I$31</f>
         <v>98438.2912945055</v>
       </c>
+      <c r="Y18" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
+        <v>12904.1051042357</v>
+      </c>
+      <c r="Z18" s="105" t="n">
+        <f aca="false">Z17+Y18</f>
+        <v>118079.955212936</v>
+      </c>
+      <c r="AA18" s="105" t="n">
+        <f aca="false">Z18-COMPARATIVO!J$31</f>
+        <v>96846.9552129356</v>
+      </c>
+      <c r="AB18" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
+        <v>13061.3494744175</v>
+      </c>
+      <c r="AC18" s="105" t="n">
+        <f aca="false">AC17+AB18</f>
+        <v>119518.831294506</v>
+      </c>
+      <c r="AD18" s="105" t="n">
+        <f aca="false">AC18-COMPARATIVO!K$31</f>
+        <v>100128.831294506</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="104" t="n">
@@ -5648,6 +6135,30 @@
         <f aca="false">W19-COMPARATIVO!I$31</f>
         <v>112351.044834413</v>
       </c>
+      <c r="Y19" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
+        <v>13745.2591954554</v>
+      </c>
+      <c r="Z19" s="105" t="n">
+        <f aca="false">Z18+Y19</f>
+        <v>131825.214408391</v>
+      </c>
+      <c r="AA19" s="105" t="n">
+        <f aca="false">Z19-COMPARATIVO!J$31</f>
+        <v>110592.214408391</v>
+      </c>
+      <c r="AB19" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
+        <v>13912.7535399074</v>
+      </c>
+      <c r="AC19" s="105" t="n">
+        <f aca="false">AC18+AB19</f>
+        <v>133431.584834413</v>
+      </c>
+      <c r="AD19" s="105" t="n">
+        <f aca="false">AC19-COMPARATIVO!K$31</f>
+        <v>114041.584834413</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="104" t="n">
@@ -5741,6 +6252,30 @@
         <f aca="false">W20-COMPARATIVO!I$31</f>
         <v>127170.701213819</v>
       </c>
+      <c r="Y20" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
+        <v>14641.2439161111</v>
+      </c>
+      <c r="Z20" s="105" t="n">
+        <f aca="false">Z19+Y20</f>
+        <v>146466.458324502</v>
+      </c>
+      <c r="AA20" s="105" t="n">
+        <f aca="false">Z20-COMPARATIVO!J$31</f>
+        <v>125233.458324502</v>
+      </c>
+      <c r="AB20" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
+        <v>14819.6563794063</v>
+      </c>
+      <c r="AC20" s="105" t="n">
+        <f aca="false">AC19+AB20</f>
+        <v>148251.241213819</v>
+      </c>
+      <c r="AD20" s="105" t="n">
+        <f aca="false">AC20-COMPARATIVO!K$31</f>
+        <v>128861.241213819</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="104" t="n">
@@ -5834,6 +6369,30 @@
         <f aca="false">W21-COMPARATIVO!I$31</f>
         <v>142956.376894317</v>
       </c>
+      <c r="Y21" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
+        <v>15595.6334007828</v>
+      </c>
+      <c r="Z21" s="105" t="n">
+        <f aca="false">Z20+Y21</f>
+        <v>162062.091725285</v>
+      </c>
+      <c r="AA21" s="105" t="n">
+        <f aca="false">Z21-COMPARATIVO!J$31</f>
+        <v>140829.091725285</v>
+      </c>
+      <c r="AB21" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
+        <v>15785.6756804979</v>
+      </c>
+      <c r="AC21" s="105" t="n">
+        <f aca="false">AC20+AB21</f>
+        <v>164036.916894317</v>
+      </c>
+      <c r="AD21" s="105" t="n">
+        <f aca="false">AC21-COMPARATIVO!K$31</f>
+        <v>144646.916894317</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="104" t="n">
@@ -5927,6 +6486,30 @@
         <f aca="false">W22-COMPARATIVO!I$31</f>
         <v>159771.041844048</v>
       </c>
+      <c r="Y22" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
+        <v>16612.2347640129</v>
+      </c>
+      <c r="Z22" s="105" t="n">
+        <f aca="false">Z21+Y22</f>
+        <v>178674.326489298</v>
+      </c>
+      <c r="AA22" s="105" t="n">
+        <f aca="false">Z22-COMPARATIVO!J$31</f>
+        <v>157441.326489298</v>
+      </c>
+      <c r="AB22" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
+        <v>16814.6649497312</v>
+      </c>
+      <c r="AC22" s="105" t="n">
+        <f aca="false">AC21+AB22</f>
+        <v>180851.581844048</v>
+      </c>
+      <c r="AD22" s="105" t="n">
+        <f aca="false">AC22-COMPARATIVO!K$31</f>
+        <v>161461.581844048</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="104" t="n">
@@ -6020,6 +6603,30 @@
         <f aca="false">W23-COMPARATIVO!I$31</f>
         <v>177681.770728528</v>
       </c>
+      <c r="Y23" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
+        <v>17695.103287105</v>
+      </c>
+      <c r="Z23" s="105" t="n">
+        <f aca="false">Z22+Y23</f>
+        <v>196369.429776403</v>
+      </c>
+      <c r="AA23" s="105" t="n">
+        <f aca="false">Z23-COMPARATIVO!J$31</f>
+        <v>175136.429776403</v>
+      </c>
+      <c r="AB23" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
+        <v>17910.7288844794</v>
+      </c>
+      <c r="AC23" s="105" t="n">
+        <f aca="false">AC22+AB23</f>
+        <v>198762.310728528</v>
+      </c>
+      <c r="AD23" s="105" t="n">
+        <f aca="false">AC23-COMPARATIVO!K$31</f>
+        <v>179372.310728528</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="104" t="n">
@@ -6113,6 +6720,30 @@
         <f aca="false">W24-COMPARATIVO!I$31</f>
         <v>196760.010475342</v>
       </c>
+      <c r="Y24" s="105" t="n">
+        <f aca="false">ECONOMIA!J$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
+        <v>18848.558594875</v>
+      </c>
+      <c r="Z24" s="105" t="n">
+        <f aca="false">Z23+Y24</f>
+        <v>215217.988371278</v>
+      </c>
+      <c r="AA24" s="105" t="n">
+        <f aca="false">Z24-COMPARATIVO!J$31</f>
+        <v>193984.988371278</v>
+      </c>
+      <c r="AB24" s="105" t="n">
+        <f aca="false">ECONOMIA!K$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
+        <v>19078.2397468142</v>
+      </c>
+      <c r="AC24" s="105" t="n">
+        <f aca="false">AC23+AB24</f>
+        <v>217840.550475342</v>
+      </c>
+      <c r="AD24" s="105" t="n">
+        <f aca="false">AC24-COMPARATIVO!K$31</f>
+        <v>198450.550475342</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="106" t="n">
@@ -6206,25 +6837,49 @@
         <f aca="false">W25-COMPARATIVO!I$31</f>
         <v>217081.865280052</v>
       </c>
+      <c r="Y25" s="108" t="n">
+        <f aca="false">ECONOMIA!J$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
+        <v>20077.2018868819</v>
+      </c>
+      <c r="Z25" s="108" t="n">
+        <f aca="false">Z24+Y25</f>
+        <v>235295.19025816</v>
+      </c>
+      <c r="AA25" s="108" t="n">
+        <f aca="false">Z25-COMPARATIVO!J$31</f>
+        <v>214062.19025816</v>
+      </c>
+      <c r="AB25" s="108" t="n">
+        <f aca="false">ECONOMIA!K$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
+        <v>20321.8548047103</v>
+      </c>
+      <c r="AC25" s="108" t="n">
+        <f aca="false">AC24+AB25</f>
+        <v>238162.405280052</v>
+      </c>
+      <c r="AD25" s="108" t="n">
+        <f aca="false">AC25-COMPARATIVO!K$31</f>
+        <v>218772.405280052</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>814</v>
+        <v>845</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>815</v>
+        <v>846</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -6258,54 +6913,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>818</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>819</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>822</v>
+        <v>853</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>823</v>
+        <v>854</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>826</v>
+        <v>857</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>828</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C7" s="32" t="n">
         <f aca="false">CONTA!C38</f>
@@ -6338,7 +6993,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">CONTA!C39</f>
@@ -6371,7 +7026,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">CONTA!C40</f>
@@ -6404,7 +7059,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">CONTA!C41</f>
@@ -6437,7 +7092,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">CONTA!C42</f>
@@ -6470,7 +7125,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">CONTA!C43</f>
@@ -6503,7 +7158,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">CONTA!C44</f>
@@ -6536,7 +7191,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">CONTA!C45</f>
@@ -6569,7 +7224,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">CONTA!C46</f>
@@ -6602,7 +7257,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">CONTA!C47</f>
@@ -6635,7 +7290,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C17" s="32" t="n">
         <f aca="false">CONTA!C48</f>
@@ -6668,7 +7323,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">CONTA!C49</f>
@@ -6701,7 +7356,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C19" s="34" t="n">
         <f aca="false">SUM(C7:C18)</f>
@@ -6726,32 +7381,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>830</v>
+        <v>861</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>832</v>
+        <v>863</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>833</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>834</v>
+        <v>865</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6759,12 +7414,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>835</v>
+        <v>866</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>836</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -6783,7 +7438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -6795,32 +7450,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>837</v>
+        <v>868</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>838</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>840</v>
+        <v>871</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>841</v>
+        <v>872</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>842</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>843</v>
+        <v>874</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -6830,10 +7485,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>844</v>
+        <v>875</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E6" s="110"/>
     </row>
@@ -6842,10 +7497,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E7" s="110"/>
     </row>
@@ -6854,10 +7509,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>847</v>
+        <v>878</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E8" s="110"/>
     </row>
@@ -6866,10 +7521,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>848</v>
+        <v>879</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E9" s="110"/>
     </row>
@@ -6878,10 +7533,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>849</v>
+        <v>880</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E10" s="110"/>
     </row>
@@ -6890,10 +7545,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="109" t="s">
-        <v>850</v>
+        <v>881</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E11" s="110"/>
     </row>
@@ -6902,10 +7557,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>851</v>
+        <v>882</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E12" s="110"/>
     </row>
@@ -6914,10 +7569,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E13" s="110"/>
     </row>
@@ -6926,10 +7581,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>853</v>
+        <v>884</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E14" s="110"/>
     </row>
@@ -6938,10 +7593,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>854</v>
+        <v>885</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E15" s="110"/>
     </row>
@@ -6950,17 +7605,17 @@
         <v>11</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>855</v>
+        <v>886</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E16" s="110"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="8"/>
       <c r="C17" s="7" t="s">
-        <v>856</v>
+        <v>887</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -6970,10 +7625,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>857</v>
+        <v>888</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E18" s="110"/>
     </row>
@@ -6982,10 +7637,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>858</v>
+        <v>889</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E19" s="110"/>
     </row>
@@ -6994,10 +7649,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>859</v>
+        <v>890</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E20" s="110"/>
     </row>
@@ -7006,10 +7661,10 @@
         <v>15</v>
       </c>
       <c r="C21" s="109" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E21" s="110"/>
     </row>
@@ -7018,10 +7673,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E22" s="110"/>
     </row>
@@ -7030,30 +7685,30 @@
         <v>17</v>
       </c>
       <c r="C23" s="111" t="s">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E23" s="110"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="8"/>
       <c r="C25" s="7" t="s">
-        <v>863</v>
+        <v>894</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E26" s="110"/>
     </row>
@@ -7062,10 +7717,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>865</v>
+        <v>896</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E27" s="110"/>
     </row>
@@ -7074,10 +7729,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>866</v>
+        <v>897</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E28" s="110"/>
     </row>
@@ -7086,396 +7741,520 @@
         <v>21</v>
       </c>
       <c r="C29" s="109" t="s">
-        <v>867</v>
+        <v>898</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E29" s="110"/>
     </row>
-    <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="109" t="s">
-        <v>868</v>
+      <c r="C30" s="111" t="s">
+        <v>899</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E30" s="110"/>
     </row>
-    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="8"/>
+      <c r="C32" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C31" s="109" t="s">
-        <v>869</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E31" s="110"/>
-    </row>
-    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C32" s="109" t="s">
-        <v>870</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E32" s="110"/>
-    </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C33" s="109" t="s">
-        <v>871</v>
+      <c r="C33" s="111" t="s">
+        <v>901</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E33" s="110"/>
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34" s="109" t="s">
-        <v>872</v>
+        <v>902</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E34" s="110"/>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C35" s="109" t="s">
-        <v>873</v>
+        <v>903</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E35" s="110"/>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C36" s="109" t="s">
+        <v>904</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E36" s="110"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="8"/>
+      <c r="C38" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C39" s="109" t="s">
+        <v>906</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E39" s="110"/>
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C36" s="109" t="s">
-        <v>874</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E36" s="110"/>
-    </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="n">
+      <c r="C40" s="109" t="s">
+        <v>907</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E40" s="110"/>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C37" s="109" t="s">
-        <v>875</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E37" s="110"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="n">
+      <c r="C41" s="109" t="s">
+        <v>908</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E41" s="110"/>
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C38" s="109" t="s">
+      <c r="C42" s="109" t="s">
+        <v>909</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>876</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E38" s="110"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8"/>
-      <c r="C40" s="7" t="s">
-        <v>877</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="n">
+      <c r="E42" s="110"/>
+    </row>
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="C41" s="111" t="s">
-        <v>878</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E41" s="110"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="n">
+      <c r="C43" s="109" t="s">
+        <v>910</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E43" s="110"/>
+    </row>
+    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="C42" s="111" t="s">
-        <v>879</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E42" s="110"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="n">
+      <c r="C44" s="109" t="s">
+        <v>911</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E44" s="110"/>
+    </row>
+    <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="C43" s="111" t="s">
-        <v>880</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E43" s="110"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="n">
+      <c r="C45" s="109" t="s">
+        <v>912</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E45" s="110"/>
+    </row>
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="C44" s="111" t="s">
-        <v>881</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E44" s="110"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="4" t="n">
+      <c r="C46" s="109" t="s">
+        <v>913</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E46" s="110"/>
+    </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="C45" s="111" t="s">
-        <v>882</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E45" s="110"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="n">
+      <c r="C47" s="109" t="s">
+        <v>914</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E47" s="110"/>
+    </row>
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="C46" s="111" t="s">
-        <v>883</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E46" s="110"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="n">
+      <c r="C48" s="109" t="s">
+        <v>915</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E48" s="110"/>
+    </row>
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="C47" s="111" t="s">
-        <v>884</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E47" s="110"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="n">
+      <c r="C49" s="109" t="s">
+        <v>916</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E49" s="110"/>
+    </row>
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="C48" s="111" t="s">
-        <v>885</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E48" s="110"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="n">
+      <c r="C50" s="109" t="s">
+        <v>917</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E50" s="110"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="C49" s="111" t="s">
-        <v>886</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E49" s="110"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="8"/>
-      <c r="C51" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C52" s="111" t="s">
-        <v>888</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E52" s="110"/>
+      <c r="C51" s="109" t="s">
+        <v>918</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E51" s="110"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="C53" s="111" t="s">
-        <v>889</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E53" s="110"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C54" s="111" t="s">
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E54" s="110"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C55" s="111" t="s">
-        <v>891</v>
+        <v>921</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E55" s="110"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C56" s="111" t="s">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E56" s="110"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C57" s="111" t="s">
-        <v>893</v>
+        <v>923</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E57" s="110"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C58" s="111" t="s">
+        <v>924</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E58" s="110"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="C59" s="111" t="s">
+        <v>925</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E59" s="110"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="C58" s="111" t="s">
-        <v>894</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E58" s="110"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8"/>
-      <c r="C60" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="C60" s="111" t="s">
+        <v>926</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E60" s="110"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="n">
         <v>47</v>
       </c>
       <c r="C61" s="111" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E61" s="110"/>
     </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="n">
         <v>48</v>
       </c>
       <c r="C62" s="111" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="E62" s="110"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C63" s="111" t="s">
-        <v>898</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E63" s="110"/>
-    </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C64" s="111" t="s">
-        <v>899</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E64" s="110"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="7" t="s">
+        <v>929</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C65" s="111" t="s">
+        <v>930</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E65" s="110"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C66" s="111" t="s">
+        <v>931</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E66" s="110"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="C65" s="111" t="s">
-        <v>900</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="E65" s="110"/>
+      <c r="C67" s="111" t="s">
+        <v>932</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E67" s="110"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="C68" s="111" t="s">
+        <v>933</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E68" s="110"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C69" s="111" t="s">
+        <v>934</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E69" s="110"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="C70" s="111" t="s">
+        <v>935</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E70" s="110"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C71" s="111" t="s">
+        <v>936</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E71" s="110"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="8"/>
+      <c r="C73" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C74" s="111" t="s">
+        <v>938</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E74" s="110"/>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="C75" s="111" t="s">
+        <v>939</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E75" s="110"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C76" s="111" t="s">
+        <v>940</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E76" s="110"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="C77" s="111" t="s">
+        <v>941</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E77" s="110"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C78" s="111" t="s">
+        <v>942</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="E78" s="110"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7505,370 +8284,370 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>901</v>
+        <v>943</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>902</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>903</v>
+        <v>945</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>904</v>
+        <v>946</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>905</v>
+        <v>947</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>906</v>
+        <v>948</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>907</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>908</v>
+        <v>950</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="66" t="s">
-        <v>909</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>910</v>
+        <v>952</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="66" t="s">
-        <v>911</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>912</v>
+        <v>954</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="66" t="s">
-        <v>913</v>
+        <v>955</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="48" t="s">
-        <v>914</v>
+        <v>956</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="66" t="s">
-        <v>915</v>
+        <v>957</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="66" t="s">
-        <v>916</v>
+        <v>958</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="66" t="s">
-        <v>917</v>
+        <v>959</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>918</v>
+        <v>960</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="66" t="s">
-        <v>919</v>
+        <v>961</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>920</v>
+        <v>962</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="66" t="s">
-        <v>921</v>
+        <v>963</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>922</v>
+        <v>964</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="66" t="s">
-        <v>923</v>
+        <v>965</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="66" t="s">
-        <v>924</v>
+        <v>966</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>925</v>
+        <v>967</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="66" t="s">
-        <v>926</v>
+        <v>968</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>927</v>
+        <v>969</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="66" t="s">
-        <v>928</v>
+        <v>970</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="66" t="s">
-        <v>929</v>
+        <v>971</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>930</v>
+        <v>972</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="66" t="s">
-        <v>931</v>
+        <v>973</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>932</v>
+        <v>974</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="66" t="s">
-        <v>933</v>
+        <v>975</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>934</v>
+        <v>976</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="66" t="s">
-        <v>935</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>936</v>
+        <v>978</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="66" t="s">
-        <v>937</v>
+        <v>979</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>938</v>
+        <v>980</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="66" t="s">
-        <v>939</v>
+        <v>981</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>940</v>
+        <v>982</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="66" t="s">
-        <v>941</v>
+        <v>983</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>942</v>
+        <v>984</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="66" t="s">
-        <v>943</v>
+        <v>985</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>944</v>
+        <v>986</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="66" t="s">
-        <v>945</v>
+        <v>987</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>946</v>
+        <v>988</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="66" t="s">
-        <v>947</v>
+        <v>989</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>948</v>
+        <v>990</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="66" t="s">
-        <v>949</v>
+        <v>991</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="48" t="s">
-        <v>950</v>
+        <v>992</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="66" t="s">
-        <v>951</v>
+        <v>993</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="66" t="s">
-        <v>953</v>
+        <v>995</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>954</v>
+        <v>996</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="66" t="s">
-        <v>955</v>
+        <v>997</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>956</v>
+        <v>998</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="66" t="s">
-        <v>957</v>
+        <v>999</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="66" t="s">
-        <v>959</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>960</v>
+        <v>1002</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="66" t="s">
-        <v>961</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>962</v>
+        <v>1004</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="66" t="s">
-        <v>963</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="66" t="s">
-        <v>964</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -7899,17 +8678,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7917,93 +8696,93 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -8011,214 +8790,214 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(C16=1,30,IF(C16=2,50,100))</f>
         <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1.02147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0.59643</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.40085</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.02419</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C23" s="15" t="n">
         <f aca="false">C19*C22</f>
         <v>0.357858</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C25" s="15" t="n">
         <f aca="false">C23*C24</f>
         <v>0.2147148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -8226,97 +9005,97 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>0.79</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0.72</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>0.0045</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>300</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>150</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -8324,120 +9103,120 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C41" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C42" s="16" t="n">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C43" s="11" t="n">
         <v>40</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C44" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>0.86</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C46" s="16" t="n">
         <v>3.3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C48" s="14" t="n">
         <v>0.15</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -8472,53 +9251,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="17" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>322.07</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>389</v>
@@ -8531,18 +9310,18 @@
         <v>12.15625</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>216.46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>364</v>
@@ -8555,18 +9334,18 @@
         <v>11.741935483871</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>13.06</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>290</v>
@@ -8579,18 +9358,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>551.59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>375</v>
@@ -8603,18 +9382,18 @@
         <v>11.71875</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>337</v>
@@ -8627,18 +9406,18 @@
         <v>11.2333333333333</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>572.7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>323</v>
@@ -8651,19 +9430,19 @@
         <v>11.1379310344828</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H11" s="23" t="n">
         <f aca="false">IFERROR(H8/540,0)</f>
         <v>1.02146296296296</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>372</v>
@@ -8678,7 +9457,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>348</v>
@@ -8691,12 +9470,12 @@
         <v>11.6</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>354</v>
@@ -8709,18 +9488,18 @@
         <v>12.2068965517241</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>4.14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>394</v>
@@ -8733,18 +9512,18 @@
         <v>12.3125</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>19.12</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>457</v>
@@ -8757,18 +9536,18 @@
         <v>15.2333333333333</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>99.28</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>422</v>
@@ -8781,18 +9560,18 @@
         <v>14.551724137931</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>122.54</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>540</v>
@@ -8807,145 +9586,145 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="G21" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C22" s="26" t="n">
         <f aca="false">SUM(C7:C18)</f>
         <v>4576</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C22/12</f>
         <v>381.333333333333</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">SUM(D7:D18)</f>
         <v>366</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C22/C24,0)</f>
         <v>12.5027322404372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">MAX(C7:C18)</f>
         <v>540</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">MIN(C7:C18)</f>
         <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">IFERROR(C26/C27-1,0)</f>
@@ -8953,33 +9732,33 @@
       </c>
       <c r="D28" s="2"/>
       <c r="G28" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">IFERROR(C29/C23-1,0)</f>
@@ -8987,81 +9766,81 @@
       </c>
       <c r="D30" s="2"/>
       <c r="G30" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">AVERAGE(C7:C12)</f>
         <v>343.5</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C32" s="29" t="n">
         <f aca="false">AVERAGE(C13:C18)</f>
         <v>419.166666666667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IFERROR(C32/C31-1,0)</f>
         <v>0.220281416787967</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IFERROR(C18/C6-1,0)</f>
         <v>0.388174807197943</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -9069,162 +9848,162 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C38" s="32" t="n">
         <f aca="false">C12</f>
         <v>372</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="18" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C39" s="32" t="n">
         <f aca="false">C13</f>
         <v>348</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="18" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C40" s="32" t="n">
         <f aca="false">C14</f>
         <v>354</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C41" s="32" t="n">
         <f aca="false">C15</f>
         <v>394</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C42" s="32" t="n">
         <f aca="false">C16</f>
         <v>457</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C43" s="32" t="n">
         <f aca="false">C17</f>
         <v>422</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C44" s="32" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C45" s="32" t="n">
         <f aca="false">C7</f>
         <v>364</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C46" s="32" t="n">
         <f aca="false">C8</f>
         <v>290</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C47" s="32" t="n">
         <f aca="false">C9</f>
         <v>375</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C48" s="32" t="n">
         <f aca="false">C10</f>
         <v>337</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C49" s="32" t="n">
         <f aca="false">C11</f>
         <v>323</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">SUM(C38:C49)</f>
@@ -9233,7 +10012,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -9241,7 +10020,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C53" s="35" t="n">
         <f aca="false">C22*H11+H9*12</f>
@@ -9250,7 +10029,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="21" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C54" s="35" t="n">
         <f aca="false">C53/12</f>
@@ -9259,7 +10038,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="21" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C55" s="35" t="n">
         <f aca="false">H10</f>
@@ -9268,82 +10047,82 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -9378,49 +10157,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>31</v>
@@ -9457,7 +10236,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>28</v>
@@ -9494,7 +10273,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>31</v>
@@ -9531,7 +10310,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>30</v>
@@ -9568,7 +10347,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>31</v>
@@ -9605,7 +10384,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>30</v>
@@ -9642,7 +10421,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>31</v>
@@ -9679,7 +10458,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>31</v>
@@ -9716,7 +10495,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>30</v>
@@ -9753,7 +10532,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>31</v>
@@ -9790,7 +10569,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>30</v>
@@ -9827,7 +10606,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>31</v>
@@ -9864,7 +10643,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="38" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">SUM(C5:C16)</f>
@@ -9899,7 +10678,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I18" s="26" t="n">
         <f aca="false">I17/12</f>
@@ -9912,12 +10691,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9925,37 +10704,37 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9963,12 +10742,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9976,12 +10755,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -10014,17 +10793,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -10035,82 +10814,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">ENTRADAS!C43</f>
         <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C6" s="44" t="n">
         <f aca="false">ENTRADAS!C42</f>
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C7" s="29" t="n">
         <f aca="false">C5*C6/100</f>
         <v>6.8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C8" s="43" t="n">
         <f aca="false">ENTRADAS!C44</f>
         <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C9" s="45" t="n">
         <f aca="false">C7*C8</f>
         <v>176.8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -10121,7 +10900,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C12" s="46" t="n">
         <f aca="false">ENTRADAS!C45</f>
@@ -10129,143 +10908,143 @@
       </c>
       <c r="D12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C13" s="45" t="n">
         <f aca="false">C9/C12</f>
         <v>205.581395348837</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">C13-C9</f>
         <v>28.7813953488372</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C15" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C18</f>
         <v>209.995227906977</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">C15*12</f>
         <v>2519.94273488372</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C25</f>
         <v>44.1413681860465</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15-C17</f>
         <v>165.85385972093</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C18*12</f>
         <v>1990.24631665116</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">IFERROR(C15/(C5*C8),0)</f>
         <v>0.201918488372093</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C21" s="15" t="n">
         <f aca="false">IFERROR(C17/(C5*C8),0)</f>
         <v>0.042443623255814</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -10276,97 +11055,97 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C24" s="44" t="n">
         <f aca="false">ENTRADAS!C46</f>
         <v>3.3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C13/C8/C24,0)</f>
         <v>2.39605355884426</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">IFERROR(ENTRADAS!C41/ENTRADAS!C45/C24,0)</f>
         <v>6.44820295983087</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C27" s="29" t="n">
         <f aca="false">IFERROR(C24*1000/220,0)</f>
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C28" s="29" t="n">
         <f aca="false">IFERROR(C27*1.25,0)</f>
         <v>18.75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">C24*1</f>
         <v>3.3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -10377,27 +11156,27 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -10422,7 +11201,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C34" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -10447,7 +11226,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="48" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C35" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -10484,7 +11263,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -10495,30 +11274,30 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="50" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D42" s="52" t="n">
         <f aca="false">0</f>
@@ -10529,18 +11308,18 @@
         <v>0</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="50" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D43" s="52" t="n">
         <f aca="false">ENTRADAS!C25</f>
@@ -10551,18 +11330,18 @@
         <v>44.1413681860465</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="50" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D44" s="52" t="n">
         <f aca="false">ENTRADAS!C18</f>
@@ -10573,15 +11352,15 @@
         <v>209.995227906977</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10590,17 +11369,17 @@
         <v>529.696418232558</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -10630,17 +11409,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -10649,31 +11428,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">GERACAO!I17</f>
         <v>1264.268995</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C6" s="29" t="n">
         <f aca="false">C5/12</f>
         <v>105.355749583333</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C7" s="4" t="str">
         <f aca="false">"kWp necessario = consumo anual / "&amp;TEXT(C5,"0")&amp;" kWh por kWp"</f>
@@ -10683,7 +11462,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -10692,24 +11471,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">BYD!F33</f>
@@ -10730,7 +11509,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">BYD!F34</f>
@@ -10751,7 +11530,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="48" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">BYD!F35</f>
@@ -10772,7 +11551,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -10782,18 +11561,18 @@
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C17" s="56" t="str">
         <f aca="false">"100% do Cenario 2"</f>
@@ -10810,7 +11589,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C18" s="57" t="n">
         <f aca="false">E12</f>
@@ -10827,7 +11606,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C19" s="58" t="n">
         <f aca="false">ROUNDUP(C18*1000/615,0)</f>
@@ -10844,7 +11623,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C20" s="59" t="n">
         <f aca="false">C19*615/1000</f>
@@ -10861,7 +11640,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C21" s="57" t="n">
         <f aca="false">5</f>
@@ -10878,7 +11657,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C22" s="60" t="n">
         <f aca="false">IFERROR(C20/C21,0)</f>
@@ -10895,7 +11674,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C23" s="58" t="n">
         <f aca="false">C20*$C$5</f>
@@ -10912,7 +11691,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C24" s="58" t="n">
         <f aca="false">C23/12</f>
@@ -10929,7 +11708,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IFERROR(C23/$D$12,0)</f>
@@ -10946,7 +11725,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C26" s="62" t="n">
         <f aca="false">IFERROR(C23/$D$13,0)</f>
@@ -10963,7 +11742,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C27" s="58" t="n">
         <f aca="false">MAX(0,C23-$D$13)</f>
@@ -10980,52 +11759,52 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11033,12 +11812,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -11057,186 +11836,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>453</v>
+        <v>457</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="64" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H5" s="65" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="I5" s="65" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="J5" s="65" t="s">
-        <v>459</v>
-      </c>
-      <c r="K5" s="66" t="s">
-        <v>460</v>
+        <v>465</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>464</v>
+      </c>
+      <c r="L5" s="65" t="s">
+        <v>466</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="64" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>463</v>
-      </c>
-      <c r="J6" s="65"/>
-      <c r="K6" s="68" t="s">
-        <v>465</v>
+        <v>470</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>472</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>471</v>
+      </c>
+      <c r="L6" s="65"/>
+      <c r="M6" s="68" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="64" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="G7" s="65" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="I7" s="65" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="J7" s="65" t="s">
-        <v>473</v>
-      </c>
-      <c r="K7" s="68" t="s">
-        <v>474</v>
+        <v>481</v>
+      </c>
+      <c r="K7" s="65" t="s">
+        <v>482</v>
+      </c>
+      <c r="L7" s="65" t="s">
+        <v>483</v>
+      </c>
+      <c r="M7" s="68" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="69" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="D8" s="70" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G8" s="70" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>478</v>
-      </c>
-      <c r="K8" s="68" t="s">
-        <v>479</v>
+        <v>487</v>
+      </c>
+      <c r="K8" s="70" t="s">
+        <v>487</v>
+      </c>
+      <c r="L8" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="M8" s="68" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="64" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C9" s="71" t="n">
         <v>12</v>
@@ -11259,14 +12068,20 @@
       <c r="I9" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="72"/>
-      <c r="K9" s="66" t="s">
-        <v>481</v>
+      <c r="J9" s="71" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="71" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" s="72"/>
+      <c r="M9" s="66" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="64" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="C10" s="71" t="n">
         <v>615</v>
@@ -11289,44 +12104,56 @@
       <c r="I10" s="71" t="n">
         <v>650</v>
       </c>
-      <c r="J10" s="72"/>
-      <c r="K10" s="66" t="s">
-        <v>483</v>
+      <c r="J10" s="71" t="n">
+        <v>590</v>
+      </c>
+      <c r="K10" s="71" t="n">
+        <v>620</v>
+      </c>
+      <c r="L10" s="72"/>
+      <c r="M10" s="66" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="64" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F11" s="65" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="G11" s="65" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="H11" s="65" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="I11" s="65" t="s">
-        <v>490</v>
-      </c>
-      <c r="J11" s="65"/>
-      <c r="K11" s="68" t="s">
-        <v>491</v>
+        <v>500</v>
+      </c>
+      <c r="J11" s="65" t="s">
+        <v>501</v>
+      </c>
+      <c r="K11" s="65" t="s">
+        <v>502</v>
+      </c>
+      <c r="L11" s="65"/>
+      <c r="M11" s="68" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="69" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C12" s="73" t="n">
         <f aca="false">C9*C10/1000</f>
@@ -11356,44 +12183,58 @@
         <f aca="false">I9*I10/1000</f>
         <v>6.5</v>
       </c>
-      <c r="J12" s="73"/>
-      <c r="K12" s="66" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="73" t="n">
+        <f aca="false">J9*J10/1000</f>
+        <v>5.9</v>
+      </c>
+      <c r="K12" s="73" t="n">
+        <f aca="false">K9*K10/1000</f>
+        <v>6.82</v>
+      </c>
+      <c r="L12" s="73"/>
+      <c r="M12" s="66" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="64" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D13" s="65" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="F13" s="65" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="G13" s="65" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H13" s="65" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="I13" s="65" t="s">
-        <v>500</v>
-      </c>
-      <c r="J13" s="65"/>
-      <c r="K13" s="68" t="s">
-        <v>501</v>
+        <v>512</v>
+      </c>
+      <c r="J13" s="65" t="s">
+        <v>513</v>
+      </c>
+      <c r="K13" s="65" t="s">
+        <v>514</v>
+      </c>
+      <c r="L13" s="65"/>
+      <c r="M13" s="68" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="64" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="C14" s="74" t="n">
         <v>6</v>
@@ -11416,44 +12257,56 @@
       <c r="I14" s="74" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="75"/>
-      <c r="K14" s="66" t="s">
-        <v>503</v>
+      <c r="J14" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="74" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L14" s="75"/>
+      <c r="M14" s="66" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="64" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="F15" s="65" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="G15" s="65" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="I15" s="65" t="s">
-        <v>508</v>
-      </c>
-      <c r="J15" s="65"/>
-      <c r="K15" s="68" t="s">
-        <v>509</v>
+        <v>522</v>
+      </c>
+      <c r="J15" s="65" t="s">
+        <v>522</v>
+      </c>
+      <c r="K15" s="65" t="s">
+        <v>519</v>
+      </c>
+      <c r="L15" s="65"/>
+      <c r="M15" s="68" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="69" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="C16" s="76" t="n">
         <f aca="false">IFERROR(C12/C14,0)</f>
@@ -11483,261 +12336,316 @@
         <f aca="false">IFERROR(I12/I14,0)</f>
         <v>0.722222222222222</v>
       </c>
-      <c r="J16" s="76"/>
-      <c r="K16" s="68" t="s">
-        <v>511</v>
+      <c r="J16" s="76" t="n">
+        <f aca="false">IFERROR(J12/J14,0)</f>
+        <v>1.18</v>
+      </c>
+      <c r="K16" s="76" t="n">
+        <f aca="false">IFERROR(K12/K14,0)</f>
+        <v>0.909333333333333</v>
+      </c>
+      <c r="L16" s="76"/>
+      <c r="M16" s="68" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="64" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="G17" s="77" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="H17" s="77" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="I17" s="77" t="s">
-        <v>514</v>
-      </c>
-      <c r="J17" s="77"/>
-      <c r="K17" s="68" t="s">
-        <v>515</v>
+        <v>528</v>
+      </c>
+      <c r="J17" s="77" t="s">
+        <v>528</v>
+      </c>
+      <c r="K17" s="77" t="s">
+        <v>527</v>
+      </c>
+      <c r="L17" s="77"/>
+      <c r="M17" s="68" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="64" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E18" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G18" s="65" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="I18" s="65" t="s">
-        <v>518</v>
-      </c>
-      <c r="J18" s="65"/>
-      <c r="K18" s="68" t="s">
-        <v>520</v>
+        <v>532</v>
+      </c>
+      <c r="J18" s="65" t="s">
+        <v>534</v>
+      </c>
+      <c r="K18" s="65" t="s">
+        <v>533</v>
+      </c>
+      <c r="L18" s="65"/>
+      <c r="M18" s="68" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="64" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="C19" s="75" t="n">
-        <f aca="false">C9*2.64</f>
-        <v>31.68</v>
+        <f aca="false">C9*C10*0.00452</f>
+        <v>33.3576</v>
       </c>
       <c r="D19" s="75" t="n">
-        <f aca="false">D9*2.64</f>
-        <v>31.68</v>
+        <f aca="false">D9*D10*0.00452</f>
+        <v>32.8152</v>
       </c>
       <c r="E19" s="75" t="n">
-        <f aca="false">E9*2.64</f>
-        <v>26.4</v>
+        <f aca="false">E9*E10*0.00452</f>
+        <v>28.024</v>
       </c>
       <c r="F19" s="75" t="n">
-        <f aca="false">F9*2.64</f>
-        <v>26.4</v>
+        <f aca="false">F9*F10*0.00452</f>
+        <v>28.024</v>
       </c>
       <c r="G19" s="75" t="n">
-        <f aca="false">G9*2.64</f>
-        <v>26.4</v>
+        <f aca="false">G9*G10*0.00452</f>
+        <v>24.182</v>
       </c>
       <c r="H19" s="75" t="n">
-        <f aca="false">H9*2.64</f>
         <v>21.12</v>
       </c>
       <c r="I19" s="75" t="n">
-        <f aca="false">I9*2.64</f>
-        <v>26.4</v>
-      </c>
-      <c r="J19" s="75"/>
-      <c r="K19" s="66" t="s">
-        <v>522</v>
+        <f aca="false">I9*I10*0.00452</f>
+        <v>29.38</v>
+      </c>
+      <c r="J19" s="75" t="n">
+        <v>28</v>
+      </c>
+      <c r="K19" s="75" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="L19" s="75"/>
+      <c r="M19" s="66" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="64" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="E20" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F20" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G20" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="I20" s="65" t="s">
-        <v>518</v>
-      </c>
-      <c r="J20" s="65"/>
-      <c r="K20" s="66" t="s">
-        <v>525</v>
+        <v>532</v>
+      </c>
+      <c r="J20" s="65" t="s">
+        <v>540</v>
+      </c>
+      <c r="K20" s="65" t="s">
+        <v>539</v>
+      </c>
+      <c r="L20" s="65"/>
+      <c r="M20" s="66" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="64" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F21" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G21" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="I21" s="65" t="s">
-        <v>518</v>
-      </c>
-      <c r="J21" s="65"/>
-      <c r="K21" s="66" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>532</v>
+      </c>
+      <c r="J21" s="65" t="s">
+        <v>544</v>
+      </c>
+      <c r="K21" s="65" t="s">
+        <v>543</v>
+      </c>
+      <c r="L21" s="65"/>
+      <c r="M21" s="66" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="64" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="E22" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F22" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G22" s="65" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="I22" s="65" t="s">
-        <v>518</v>
-      </c>
-      <c r="J22" s="65"/>
-      <c r="K22" s="66" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>532</v>
+      </c>
+      <c r="J22" s="65" t="s">
+        <v>548</v>
+      </c>
+      <c r="K22" s="65" t="s">
+        <v>547</v>
+      </c>
+      <c r="L22" s="65"/>
+      <c r="M22" s="66" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="64" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="E23" s="65" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="F23" s="65" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="G23" s="65" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="H23" s="67" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="I23" s="65" t="s">
-        <v>533</v>
-      </c>
-      <c r="J23" s="65"/>
-      <c r="K23" s="68" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>551</v>
+      </c>
+      <c r="J23" s="65" t="s">
+        <v>553</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>552</v>
+      </c>
+      <c r="L23" s="65"/>
+      <c r="M23" s="68" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="64" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="D24" s="65" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="E24" s="65" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="F24" s="65" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="G24" s="65" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="H24" s="65" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="I24" s="65" t="s">
-        <v>541</v>
-      </c>
-      <c r="J24" s="65"/>
-      <c r="K24" s="66" t="s">
-        <v>542</v>
+        <v>560</v>
+      </c>
+      <c r="J24" s="65" t="s">
+        <v>561</v>
+      </c>
+      <c r="K24" s="65" t="s">
+        <v>562</v>
+      </c>
+      <c r="L24" s="65"/>
+      <c r="M24" s="66" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -11748,10 +12656,12 @@
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="64" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="C26" s="78" t="n">
         <v>18228.7</v>
@@ -11774,14 +12684,20 @@
       <c r="I26" s="78" t="n">
         <v>16780.54</v>
       </c>
-      <c r="J26" s="79"/>
-      <c r="K26" s="66" t="s">
-        <v>545</v>
+      <c r="J26" s="78" t="n">
+        <v>18733</v>
+      </c>
+      <c r="K26" s="78" t="n">
+        <v>16890</v>
+      </c>
+      <c r="L26" s="79"/>
+      <c r="M26" s="66" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="64" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="C27" s="78" t="n">
         <v>0</v>
@@ -11804,14 +12720,20 @@
       <c r="I27" s="78" t="n">
         <v>1800</v>
       </c>
-      <c r="J27" s="79"/>
-      <c r="K27" s="68" t="s">
-        <v>547</v>
+      <c r="J27" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="79"/>
+      <c r="M27" s="68" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="64" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="C28" s="78" t="n">
         <v>790</v>
@@ -11834,14 +12756,20 @@
       <c r="I28" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="79"/>
-      <c r="K28" s="66" t="s">
-        <v>549</v>
+      <c r="J28" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="79"/>
+      <c r="M28" s="66" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="64" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="C29" s="79" t="n">
         <f aca="false">6900/10*C9</f>
@@ -11866,14 +12794,20 @@
       <c r="I29" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="79"/>
-      <c r="K29" s="68" t="s">
-        <v>551</v>
+      <c r="J29" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="79"/>
+      <c r="M29" s="68" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="64" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -11903,14 +12837,22 @@
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="J30" s="79"/>
-      <c r="K30" s="68" t="s">
-        <v>553</v>
+      <c r="J30" s="79" t="n">
+        <f aca="false">ENTRADAS!$C$28</f>
+        <v>2500</v>
+      </c>
+      <c r="K30" s="79" t="n">
+        <f aca="false">ENTRADAS!$C$28</f>
+        <v>2500</v>
+      </c>
+      <c r="L30" s="79"/>
+      <c r="M30" s="68" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="69" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="C31" s="80" t="n">
         <f aca="false">SUM(C26:C30)</f>
@@ -11940,14 +12882,22 @@
         <f aca="false">SUM(I26:I30)</f>
         <v>21080.54</v>
       </c>
-      <c r="J31" s="80"/>
-      <c r="K31" s="66" t="s">
-        <v>555</v>
+      <c r="J31" s="80" t="n">
+        <f aca="false">SUM(J26:J30)</f>
+        <v>21233</v>
+      </c>
+      <c r="K31" s="80" t="n">
+        <f aca="false">SUM(K26:K30)</f>
+        <v>19390</v>
+      </c>
+      <c r="L31" s="80"/>
+      <c r="M31" s="66" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="69" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C32" s="81" t="n">
         <f aca="false">IFERROR(C31/(C12*1000),0)</f>
@@ -11977,14 +12927,22 @@
         <f aca="false">IFERROR(I31/(I12*1000),0)</f>
         <v>3.24316</v>
       </c>
-      <c r="J32" s="81"/>
-      <c r="K32" s="66" t="s">
-        <v>557</v>
+      <c r="J32" s="81" t="n">
+        <f aca="false">IFERROR(J31/(J12*1000),0)</f>
+        <v>3.59881355932203</v>
+      </c>
+      <c r="K32" s="81" t="n">
+        <f aca="false">IFERROR(K31/(K12*1000),0)</f>
+        <v>2.84310850439883</v>
+      </c>
+      <c r="L32" s="81"/>
+      <c r="M32" s="66" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="64" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C33" s="82" t="n">
         <f aca="false">IFERROR(C26/(C12*1000),0)</f>
@@ -11995,29 +12953,35 @@
         <v>2.38400826446281</v>
       </c>
       <c r="E33" s="82" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="F33" s="82" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="G33" s="82" t="n">
         <f aca="false">IFERROR(G26/(G12*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
       <c r="H33" s="82" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="I33" s="82" t="s">
-        <v>559</v>
-      </c>
-      <c r="J33" s="82"/>
-      <c r="K33" s="66" t="s">
-        <v>560</v>
+        <v>580</v>
+      </c>
+      <c r="J33" s="82" t="s">
+        <v>580</v>
+      </c>
+      <c r="K33" s="82" t="s">
+        <v>580</v>
+      </c>
+      <c r="L33" s="82"/>
+      <c r="M33" s="66" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -12028,10 +12992,12 @@
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="64" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">C12*GERACAO!$I$17</f>
@@ -12061,14 +13027,22 @@
         <f aca="false">I12*GERACAO!$I$17</f>
         <v>8217.7484675</v>
       </c>
-      <c r="J36" s="72"/>
-      <c r="K36" s="66" t="s">
-        <v>563</v>
+      <c r="J36" s="72" t="n">
+        <f aca="false">J12*GERACAO!$I$17</f>
+        <v>7459.1870705</v>
+      </c>
+      <c r="K36" s="72" t="n">
+        <f aca="false">K12*GERACAO!$I$17</f>
+        <v>8622.3145459</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="66" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="64" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="C37" s="72" t="n">
         <f aca="false">C36/12</f>
@@ -12098,12 +13072,20 @@
         <f aca="false">I36/12</f>
         <v>684.812372291667</v>
       </c>
-      <c r="J37" s="72"/>
-      <c r="K37" s="66"/>
+      <c r="J37" s="72" t="n">
+        <f aca="false">J36/12</f>
+        <v>621.598922541667</v>
+      </c>
+      <c r="K37" s="72" t="n">
+        <f aca="false">K36/12</f>
+        <v>718.526212158333</v>
+      </c>
+      <c r="L37" s="72"/>
+      <c r="M37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="64" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="C38" s="72" t="n">
         <f aca="false">C36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -12133,14 +13115,22 @@
         <f aca="false">I36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
         <v>7489.59354</v>
       </c>
-      <c r="J38" s="72"/>
-      <c r="K38" s="66" t="s">
-        <v>566</v>
+      <c r="J38" s="72" t="n">
+        <f aca="false">J36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>6798.246444</v>
+      </c>
+      <c r="K38" s="72" t="n">
+        <f aca="false">K36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7858.3119912</v>
+      </c>
+      <c r="L38" s="72"/>
+      <c r="M38" s="66" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="64" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C39" s="71" t="n">
         <v>10554</v>
@@ -12163,14 +13153,20 @@
       <c r="I39" s="71" t="n">
         <v>8400</v>
       </c>
-      <c r="J39" s="72"/>
-      <c r="K39" s="66" t="s">
-        <v>568</v>
+      <c r="J39" s="71" t="n">
+        <v>7329.96</v>
+      </c>
+      <c r="K39" s="71" t="n">
+        <v>9279.13</v>
+      </c>
+      <c r="L39" s="72"/>
+      <c r="M39" s="66" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="69" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C40" s="83" t="n">
         <f aca="false">IFERROR(C36/C39-1,0)</f>
@@ -12200,14 +13196,22 @@
         <f aca="false">IFERROR(I36/I39-1,0)</f>
         <v>-0.0216966110119046</v>
       </c>
-      <c r="J40" s="83"/>
-      <c r="K40" s="68" t="s">
-        <v>570</v>
+      <c r="J40" s="83" t="n">
+        <f aca="false">IFERROR(J36/J39-1,0)</f>
+        <v>0.0176299830421995</v>
+      </c>
+      <c r="K40" s="83" t="n">
+        <f aca="false">IFERROR(K36/K39-1,0)</f>
+        <v>-0.0707841633967838</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="68" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="64" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="C41" s="72" t="n">
         <f aca="false">C12*GERACAO!$J$17</f>
@@ -12237,14 +13241,22 @@
         <f aca="false">I12*GERACAO!$J$17</f>
         <v>9238.024185</v>
       </c>
-      <c r="J41" s="72"/>
-      <c r="K41" s="66" t="s">
-        <v>572</v>
+      <c r="J41" s="72" t="n">
+        <f aca="false">J12*GERACAO!$J$17</f>
+        <v>8385.283491</v>
+      </c>
+      <c r="K41" s="72" t="n">
+        <f aca="false">K12*GERACAO!$J$17</f>
+        <v>9692.8192218</v>
+      </c>
+      <c r="L41" s="72"/>
+      <c r="M41" s="66" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -12255,10 +13267,12 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="64" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C44" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$33*12),0)</f>
@@ -12288,14 +13302,22 @@
         <f aca="false">IFERROR(I36/(BYD!$F$33*12),0)</f>
         <v>1.795836640625</v>
       </c>
-      <c r="J44" s="84"/>
-      <c r="K44" s="66" t="s">
-        <v>575</v>
+      <c r="J44" s="84" t="n">
+        <f aca="false">IFERROR(J36/(BYD!$F$33*12),0)</f>
+        <v>1.63006710456731</v>
+      </c>
+      <c r="K44" s="84" t="n">
+        <f aca="false">IFERROR(K36/(BYD!$F$33*12),0)</f>
+        <v>1.88424705985577</v>
+      </c>
+      <c r="L44" s="84"/>
+      <c r="M44" s="66" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="64" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="C45" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$34*12),0)</f>
@@ -12325,12 +13347,20 @@
         <f aca="false">IFERROR(I36/(BYD!$F$34*12),0)</f>
         <v>1.16680045469179</v>
       </c>
-      <c r="J45" s="84"/>
-      <c r="K45" s="66"/>
+      <c r="J45" s="84" t="n">
+        <f aca="false">IFERROR(J36/(BYD!$F$34*12),0)</f>
+        <v>1.05909579733563</v>
+      </c>
+      <c r="K45" s="84" t="n">
+        <f aca="false">IFERROR(K36/(BYD!$F$34*12),0)</f>
+        <v>1.22424293861508</v>
+      </c>
+      <c r="L45" s="84"/>
+      <c r="M45" s="66"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="69" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="C46" s="85" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$35*12),0)</f>
@@ -12360,14 +13390,22 @@
         <f aca="false">IFERROR(I36/(BYD!$F$35*12),0)</f>
         <v>1.01460909103634</v>
       </c>
-      <c r="J46" s="85"/>
-      <c r="K46" s="66" t="s">
-        <v>578</v>
+      <c r="J46" s="85" t="n">
+        <f aca="false">IFERROR(J36/(BYD!$F$35*12),0)</f>
+        <v>0.920952867248371</v>
+      </c>
+      <c r="K46" s="85" t="n">
+        <f aca="false">IFERROR(K36/(BYD!$F$35*12),0)</f>
+        <v>1.06455907705659</v>
+      </c>
+      <c r="L46" s="85"/>
+      <c r="M46" s="66" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="64" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="C47" s="72" t="n">
         <f aca="false">C36-BYD!$G$35</f>
@@ -12397,14 +13435,22 @@
         <f aca="false">I36-BYD!$G$35</f>
         <v>118.325211686048</v>
       </c>
-      <c r="J47" s="72"/>
-      <c r="K47" s="66" t="s">
-        <v>580</v>
+      <c r="J47" s="72" t="n">
+        <f aca="false">J36-BYD!$G$35</f>
+        <v>-640.236185313953</v>
+      </c>
+      <c r="K47" s="72" t="n">
+        <f aca="false">K36-BYD!$G$35</f>
+        <v>522.891290086047</v>
+      </c>
+      <c r="L47" s="72"/>
+      <c r="M47" s="66" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="69" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C48" s="86" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C36)/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -12434,12 +13480,20 @@
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-I36)/GERACAO!$I$17*1000/I10,0),0)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="86"/>
-      <c r="K48" s="66"/>
+      <c r="J48" s="86" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-J36)/GERACAO!$I$17*1000/J10,0),0)</f>
+        <v>1</v>
+      </c>
+      <c r="K48" s="86" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-K36)/GERACAO!$I$17*1000/K10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="86"/>
+      <c r="M48" s="66"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="69" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="C49" s="87" t="n">
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -12469,14 +13523,67 @@
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/I10,0),0)</f>
         <v>4</v>
       </c>
-      <c r="J49" s="87"/>
-      <c r="K49" s="66" t="s">
-        <v>583</v>
+      <c r="J49" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/J10,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K49" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/K10,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="L49" s="87"/>
+      <c r="M49" s="66" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="64" t="s">
+        <v>605</v>
+      </c>
+      <c r="C50" s="65" t="str">
+        <f aca="false">C14&amp;" kW = "&amp;TEXT(C14*1000/220,"0")&amp;" A"</f>
+        <v>6 kW = 27 A</v>
+      </c>
+      <c r="D50" s="65" t="str">
+        <f aca="false">D14&amp;" kW = "&amp;TEXT(D14*1000/220,"0")&amp;" A"</f>
+        <v>6 kW = 27 A</v>
+      </c>
+      <c r="E50" s="65" t="str">
+        <f aca="false">E14&amp;" kW = "&amp;TEXT(E14*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="F50" s="65" t="str">
+        <f aca="false">F14&amp;" kW = "&amp;TEXT(F14*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="G50" s="65" t="str">
+        <f aca="false">G14&amp;" kW = "&amp;TEXT(G14*1000/220,"0")&amp;" A"</f>
+        <v>4 kW = 18 A</v>
+      </c>
+      <c r="H50" s="65" t="str">
+        <f aca="false">H14&amp;" kW = "&amp;TEXT(H14*1000/220,"0")&amp;" A"</f>
+        <v>3 kW = 14 A</v>
+      </c>
+      <c r="I50" s="65" t="str">
+        <f aca="false">I14&amp;" kW = "&amp;TEXT(I14*1000/220,"0")&amp;" A"</f>
+        <v>9 kW = 41 A</v>
+      </c>
+      <c r="J50" s="65" t="str">
+        <f aca="false">J14&amp;" kW = "&amp;TEXT(J14*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="K50" s="65" t="str">
+        <f aca="false">K14&amp;" kW = "&amp;TEXT(K14*1000/220,"0")&amp;" A"</f>
+        <v>7.5 kW = 34 A</v>
+      </c>
+      <c r="L50" s="65"/>
+      <c r="M50" s="68" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -12487,10 +13594,12 @@
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="64" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="C52" s="79" t="n">
         <f aca="false">CONTA!$C$54</f>
@@ -12520,14 +13629,22 @@
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="J52" s="79"/>
-      <c r="K52" s="66" t="s">
-        <v>586</v>
+      <c r="J52" s="79" t="n">
+        <f aca="false">CONTA!$C$54</f>
+        <v>410.62787654321</v>
+      </c>
+      <c r="K52" s="79" t="n">
+        <f aca="false">CONTA!$C$54</f>
+        <v>410.62787654321</v>
+      </c>
+      <c r="L52" s="79"/>
+      <c r="M52" s="66" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="64" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="C53" s="79" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
@@ -12557,14 +13674,22 @@
         <f aca="false">ECONOMIA!I8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="J53" s="79"/>
-      <c r="K53" s="66" t="s">
-        <v>588</v>
+      <c r="J53" s="79" t="n">
+        <f aca="false">ECONOMIA!J8/12</f>
+        <v>710.553156093023</v>
+      </c>
+      <c r="K53" s="79" t="n">
+        <f aca="false">ECONOMIA!K8/12</f>
+        <v>710.553156093023</v>
+      </c>
+      <c r="L53" s="79"/>
+      <c r="M53" s="66" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="69" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="C54" s="88" t="n">
         <f aca="false">ECONOMIA!C19</f>
@@ -12594,14 +13719,22 @@
         <f aca="false">ECONOMIA!I19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="J54" s="88"/>
-      <c r="K54" s="68" t="s">
-        <v>590</v>
+      <c r="J54" s="88" t="n">
+        <f aca="false">ECONOMIA!J19</f>
+        <v>169.035046518012</v>
+      </c>
+      <c r="K54" s="88" t="n">
+        <f aca="false">ECONOMIA!K19</f>
+        <v>162.893279261767</v>
+      </c>
+      <c r="L54" s="88"/>
+      <c r="M54" s="68" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="64" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="C55" s="79" t="n">
         <f aca="false">ECONOMIA!C26</f>
@@ -12631,12 +13764,20 @@
         <f aca="false">ECONOMIA!I26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="J55" s="79"/>
-      <c r="K55" s="66"/>
+      <c r="J55" s="79" t="n">
+        <f aca="false">ECONOMIA!J26</f>
+        <v>6048.21731490014</v>
+      </c>
+      <c r="K55" s="79" t="n">
+        <f aca="false">ECONOMIA!K26</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="L55" s="79"/>
+      <c r="M55" s="66"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="69" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="C56" s="88" t="n">
         <f aca="false">C55/12</f>
@@ -12666,12 +13807,20 @@
         <f aca="false">I55/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="J56" s="88"/>
-      <c r="K56" s="66"/>
+      <c r="J56" s="88" t="n">
+        <f aca="false">J55/12</f>
+        <v>504.018109575012</v>
+      </c>
+      <c r="K56" s="88" t="n">
+        <f aca="false">K55/12</f>
+        <v>510.159876831256</v>
+      </c>
+      <c r="L56" s="88"/>
+      <c r="M56" s="66"/>
     </row>
     <row r="57" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="69" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="C57" s="89" t="n">
         <f aca="false">IFERROR(C31/C55,0)</f>
@@ -12701,14 +13850,22 @@
         <f aca="false">IFERROR(I31/I55,0)</f>
         <v>3.44345321231079</v>
       </c>
-      <c r="J57" s="89"/>
-      <c r="K57" s="66" t="s">
-        <v>594</v>
+      <c r="J57" s="89" t="n">
+        <f aca="false">IFERROR(J31/J55,0)</f>
+        <v>3.51062121192161</v>
+      </c>
+      <c r="K57" s="89" t="n">
+        <f aca="false">IFERROR(K31/K55,0)</f>
+        <v>3.16730775334533</v>
+      </c>
+      <c r="L57" s="89"/>
+      <c r="M57" s="66" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="64" t="s">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="C58" s="90" t="n">
         <f aca="false">PROJECAO!E10</f>
@@ -12738,12 +13895,20 @@
         <f aca="false">PROJECAO!W10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="J58" s="90"/>
-      <c r="K58" s="66"/>
+      <c r="J58" s="90" t="n">
+        <f aca="false">PROJECAO!Z10</f>
+        <v>34449.0961498751</v>
+      </c>
+      <c r="K58" s="90" t="n">
+        <f aca="false">PROJECAO!AC10</f>
+        <v>34868.8793416317</v>
+      </c>
+      <c r="L58" s="90"/>
+      <c r="M58" s="66"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="64" t="s">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="C59" s="90" t="n">
         <f aca="false">PROJECAO!E15</f>
@@ -12773,12 +13938,20 @@
         <f aca="false">PROJECAO!W15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="J59" s="90"/>
-      <c r="K59" s="66"/>
+      <c r="J59" s="90" t="n">
+        <f aca="false">PROJECAO!Z15</f>
+        <v>81688.351378768</v>
+      </c>
+      <c r="K59" s="90" t="n">
+        <f aca="false">PROJECAO!AC15</f>
+        <v>82683.773630833</v>
+      </c>
+      <c r="L59" s="90"/>
+      <c r="M59" s="66"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="64" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="C60" s="90" t="n">
         <f aca="false">PROJECAO!E25</f>
@@ -12808,12 +13981,20 @@
         <f aca="false">PROJECAO!W25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="J60" s="90"/>
-      <c r="K60" s="66"/>
+      <c r="J60" s="90" t="n">
+        <f aca="false">PROJECAO!Z25</f>
+        <v>235295.19025816</v>
+      </c>
+      <c r="K60" s="90" t="n">
+        <f aca="false">PROJECAO!AC25</f>
+        <v>238162.405280052</v>
+      </c>
+      <c r="L60" s="90"/>
+      <c r="M60" s="66"/>
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="69" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="C61" s="91" t="n">
         <f aca="false">C60-C31</f>
@@ -12843,14 +14024,22 @@
         <f aca="false">I60-I31</f>
         <v>217081.865280052</v>
       </c>
-      <c r="J61" s="91"/>
-      <c r="K61" s="66" t="s">
-        <v>599</v>
+      <c r="J61" s="91" t="n">
+        <f aca="false">J60-J31</f>
+        <v>214062.19025816</v>
+      </c>
+      <c r="K61" s="91" t="n">
+        <f aca="false">K60-K31</f>
+        <v>218772.405280052</v>
+      </c>
+      <c r="L61" s="91"/>
+      <c r="M61" s="66" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="64" t="s">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="C62" s="84" t="n">
         <f aca="false">IFERROR(C61/C31,0)</f>
@@ -12880,12 +14069,20 @@
         <f aca="false">IFERROR(I61/I31,0)</f>
         <v>10.2977374052113</v>
       </c>
-      <c r="J62" s="84"/>
-      <c r="K62" s="66"/>
+      <c r="J62" s="84" t="n">
+        <f aca="false">IFERROR(J61/J31,0)</f>
+        <v>10.0815800997579</v>
+      </c>
+      <c r="K62" s="84" t="n">
+        <f aca="false">IFERROR(K61/K31,0)</f>
+        <v>11.2827439546185</v>
+      </c>
+      <c r="L62" s="84"/>
+      <c r="M62" s="66"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="7" t="s">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -12896,10 +14093,12 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="64" t="s">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="C65" s="75" t="n">
         <f aca="false">C14*1.35</f>
@@ -12929,12 +14128,20 @@
         <f aca="false">I14*1.35</f>
         <v>12.15</v>
       </c>
-      <c r="J65" s="75"/>
-      <c r="K65" s="66"/>
+      <c r="J65" s="75" t="n">
+        <f aca="false">J14*1.35</f>
+        <v>6.75</v>
+      </c>
+      <c r="K65" s="75" t="n">
+        <f aca="false">K14*1.35</f>
+        <v>10.125</v>
+      </c>
+      <c r="L65" s="75"/>
+      <c r="M65" s="66"/>
     </row>
     <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="69" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="C66" s="86" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((C65-C12)*1000/C10,0))</f>
@@ -12964,14 +14171,22 @@
         <f aca="false">MAX(0,ROUNDDOWN((I65-I12)*1000/I10,0))</f>
         <v>8</v>
       </c>
-      <c r="J66" s="86"/>
-      <c r="K66" s="68" t="s">
-        <v>604</v>
+      <c r="J66" s="86" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((J65-J12)*1000/J10,0))</f>
+        <v>1</v>
+      </c>
+      <c r="K66" s="86" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((K65-K12)*1000/K10,0))</f>
+        <v>5</v>
+      </c>
+      <c r="L66" s="86"/>
+      <c r="M66" s="68" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="64" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="C67" s="72" t="n">
         <f aca="false">C66*C10/1000*GERACAO!$I$17</f>
@@ -13001,12 +14216,20 @@
         <f aca="false">I66*I10/1000*GERACAO!$I$17</f>
         <v>6574.198774</v>
       </c>
-      <c r="J67" s="72"/>
-      <c r="K67" s="66"/>
+      <c r="J67" s="72" t="n">
+        <f aca="false">J66*J10/1000*GERACAO!$I$17</f>
+        <v>745.91870705</v>
+      </c>
+      <c r="K67" s="72" t="n">
+        <f aca="false">K66*K10/1000*GERACAO!$I$17</f>
+        <v>3919.2338845</v>
+      </c>
+      <c r="L67" s="72"/>
+      <c r="M67" s="66"/>
     </row>
     <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="69" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="C68" s="92" t="str">
         <f aca="false">IF(C16&gt;1.35,"JA SOBRECARREGADO",IF(C16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
@@ -13036,14 +14259,22 @@
         <f aca="false">IF(I16&gt;1.35,"JA SOBRECARREGADO",IF(I16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="J68" s="92"/>
-      <c r="K68" s="66" t="s">
-        <v>607</v>
+      <c r="J68" s="92" t="str">
+        <f aca="false">IF(J16&gt;1.35,"JA SOBRECARREGADO",IF(J16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="K68" s="92" t="str">
+        <f aca="false">IF(K16&gt;1.35,"JA SOBRECARREGADO",IF(K16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+        <v>SUBAPROVEITADO</v>
+      </c>
+      <c r="L68" s="92"/>
+      <c r="M68" s="66" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="7" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -13054,10 +14285,12 @@
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="21" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="C71" s="35" t="n">
         <f aca="false">F26-E26</f>
@@ -13066,7 +14299,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="C72" s="29" t="n">
         <f aca="false">IFERROR(F57-E57,0)</f>
@@ -13075,7 +14308,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="C73" s="93" t="n">
         <f aca="false">F61-E61</f>
@@ -13084,22 +14317,22 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="5" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13107,17 +14340,17 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="5" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>617</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -13147,325 +14380,325 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>619</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
       <c r="F5" s="94" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>639</v>
+        <v>662</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="F8" s="94" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>642</v>
+        <v>665</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>645</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>647</v>
+        <v>670</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>647</v>
+        <v>670</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>648</v>
+        <v>671</v>
       </c>
       <c r="F10" s="94" t="s">
-        <v>649</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>652</v>
+        <v>675</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>653</v>
+        <v>676</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>654</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>656</v>
+        <v>679</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>657</v>
+        <v>680</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>659</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>660</v>
+        <v>683</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>661</v>
+        <v>684</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="F13" s="95" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="F14" s="94" t="s">
-        <v>668</v>
+        <v>691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>669</v>
+        <v>692</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>670</v>
+        <v>693</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>671</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>672</v>
+        <v>695</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>674</v>
+        <v>697</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>675</v>
+        <v>698</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="D17" s="96" t="s">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>677</v>
+        <v>700</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>678</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>679</v>
+        <v>702</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>681</v>
+        <v>704</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>682</v>
+        <v>705</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>683</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>684</v>
+        <v>707</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>687</v>
+        <v>710</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>688</v>
+        <v>711</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="F20" s="94" t="s">
-        <v>691</v>
+        <v>714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>692</v>
+        <v>715</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>693</v>
+        <v>716</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>694</v>
+        <v>717</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>695</v>
+        <v>718</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>696</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>697</v>
+        <v>720</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -13479,7 +14712,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -13493,7 +14726,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -13507,7 +14740,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>700</v>
+        <v>723</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -13521,7 +14754,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="C28" s="47" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -13538,7 +14771,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="C30" s="44" t="str">
         <f aca="false">COMPARATIVO!C11</f>
@@ -13555,7 +14788,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="C31" s="97" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
@@ -13572,44 +14805,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>704</v>
+        <v>727</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>706</v>
+        <v>729</v>
       </c>
       <c r="C34" s="98" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>707</v>
+        <v>730</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>708</v>
+        <v>731</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>709</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>710</v>
+        <v>733</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>711</v>
+        <v>734</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -13618,7 +14851,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">COMPARATIVO!C28-COMPARATIVO!D28</f>
@@ -13627,7 +14860,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
@@ -13636,14 +14869,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="C41" s="99" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>715</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -13662,60 +14895,66 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>716</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>717</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>718</v>
+        <v>741</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>719</v>
+        <v>742</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>722</v>
+        <v>745</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>727</v>
+        <v>750</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -13745,14 +14984,22 @@
         <f aca="false">BYD!$G$35</f>
         <v>8099.42325581395</v>
       </c>
-      <c r="J5" s="100"/>
-      <c r="K5" s="66" t="s">
-        <v>729</v>
+      <c r="J5" s="36" t="n">
+        <f aca="false">BYD!$G$35</f>
+        <v>8099.42325581395</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <f aca="false">BYD!$G$35</f>
+        <v>8099.42325581395</v>
+      </c>
+      <c r="L5" s="100"/>
+      <c r="M5" s="66" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COMPARATIVO!C36</f>
@@ -13782,14 +15029,22 @@
         <f aca="false">COMPARATIVO!I36</f>
         <v>8217.7484675</v>
       </c>
-      <c r="J6" s="100"/>
-      <c r="K6" s="66" t="s">
-        <v>731</v>
+      <c r="J6" s="36" t="n">
+        <f aca="false">COMPARATIVO!J36</f>
+        <v>7459.1870705</v>
+      </c>
+      <c r="K6" s="36" t="n">
+        <f aca="false">COMPARATIVO!K36</f>
+        <v>8622.3145459</v>
+      </c>
+      <c r="L6" s="100"/>
+      <c r="M6" s="66" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="C7" s="101" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -13819,14 +15074,22 @@
         <f aca="false">ENTRADAS!$C$18</f>
         <v>1.02147</v>
       </c>
-      <c r="J7" s="100"/>
-      <c r="K7" s="66" t="s">
-        <v>733</v>
+      <c r="J7" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$18</f>
+        <v>1.02147</v>
+      </c>
+      <c r="K7" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$18</f>
+        <v>1.02147</v>
+      </c>
+      <c r="L7" s="100"/>
+      <c r="M7" s="66" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="C8" s="102" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -13856,14 +15119,22 @@
         <f aca="false">I5*I7+ENTRADAS!$C$26*12</f>
         <v>8526.63787311628</v>
       </c>
-      <c r="J8" s="100"/>
-      <c r="K8" s="66" t="s">
-        <v>735</v>
+      <c r="J8" s="102" t="n">
+        <f aca="false">J5*J7+ENTRADAS!$C$26*12</f>
+        <v>8526.63787311628</v>
+      </c>
+      <c r="K8" s="102" t="n">
+        <f aca="false">K5*K7+ENTRADAS!$C$26*12</f>
+        <v>8526.63787311628</v>
+      </c>
+      <c r="L8" s="100"/>
+      <c r="M8" s="66" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -13893,14 +15164,22 @@
         <f aca="false">MIN(I5,I6)*ENTRADAS!$C$37</f>
         <v>2429.82697674419</v>
       </c>
-      <c r="J9" s="100"/>
-      <c r="K9" s="66" t="s">
-        <v>737</v>
+      <c r="J9" s="36" t="n">
+        <f aca="false">MIN(J5,J6)*ENTRADAS!$C$37</f>
+        <v>2237.75612115</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <f aca="false">MIN(K5,K6)*ENTRADAS!$C$37</f>
+        <v>2429.82697674419</v>
+      </c>
+      <c r="L9" s="100"/>
+      <c r="M9" s="66" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">C6-C9</f>
@@ -13930,14 +15209,22 @@
         <f aca="false">I6-I9</f>
         <v>5787.92149075582</v>
       </c>
-      <c r="J10" s="100"/>
-      <c r="K10" s="66" t="s">
-        <v>739</v>
+      <c r="J10" s="36" t="n">
+        <f aca="false">J6-J9</f>
+        <v>5221.43094935</v>
+      </c>
+      <c r="K10" s="36" t="n">
+        <f aca="false">K6-K9</f>
+        <v>6192.48756915581</v>
+      </c>
+      <c r="L10" s="100"/>
+      <c r="M10" s="66" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -13967,14 +15254,22 @@
         <f aca="false">ENTRADAS!$C$17*12</f>
         <v>600</v>
       </c>
-      <c r="J11" s="100"/>
-      <c r="K11" s="66" t="s">
-        <v>741</v>
+      <c r="J11" s="36" t="n">
+        <f aca="false">ENTRADAS!$C$17*12</f>
+        <v>600</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <f aca="false">ENTRADAS!$C$17*12</f>
+        <v>600</v>
+      </c>
+      <c r="L11" s="100"/>
+      <c r="M11" s="66" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -14004,14 +15299,22 @@
         <f aca="false">MAX(0,MIN(I10,I5-I9-I11))</f>
         <v>5069.59627906977</v>
       </c>
-      <c r="J12" s="100"/>
-      <c r="K12" s="66" t="s">
-        <v>743</v>
+      <c r="J12" s="36" t="n">
+        <f aca="false">MAX(0,MIN(J10,J5-J9-J11))</f>
+        <v>5221.43094935</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <f aca="false">MAX(0,MIN(K10,K5-K9-K11))</f>
+        <v>5069.59627906977</v>
+      </c>
+      <c r="L12" s="100"/>
+      <c r="M12" s="66" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">C10-C12</f>
@@ -14041,14 +15344,22 @@
         <f aca="false">I10-I12</f>
         <v>718.325211686048</v>
       </c>
-      <c r="J13" s="100"/>
-      <c r="K13" s="66" t="s">
-        <v>745</v>
+      <c r="J13" s="36" t="n">
+        <f aca="false">J10-J12</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <f aca="false">K10-K12</f>
+        <v>1122.89129008605</v>
+      </c>
+      <c r="L13" s="100"/>
+      <c r="M13" s="66" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -14078,14 +15389,22 @@
         <f aca="false">MAX(I11,I5-I9-I12)</f>
         <v>600</v>
       </c>
-      <c r="J14" s="100"/>
-      <c r="K14" s="66" t="s">
-        <v>747</v>
+      <c r="J14" s="36" t="n">
+        <f aca="false">MAX(J11,J5-J9-J12)</f>
+        <v>640.236185313954</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <f aca="false">MAX(K11,K5-K9-K12)</f>
+        <v>600</v>
+      </c>
+      <c r="L14" s="100"/>
+      <c r="M14" s="66" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="C15" s="101" t="n">
         <f aca="false">C14*C7</f>
@@ -14115,12 +15434,20 @@
         <f aca="false">I14*I7</f>
         <v>612.882</v>
       </c>
-      <c r="J15" s="100"/>
-      <c r="K15" s="66"/>
+      <c r="J15" s="101" t="n">
+        <f aca="false">J14*J7</f>
+        <v>653.982056212644</v>
+      </c>
+      <c r="K15" s="101" t="n">
+        <f aca="false">K14*K7</f>
+        <v>612.882</v>
+      </c>
+      <c r="L15" s="100"/>
+      <c r="M15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="C16" s="101" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -14150,14 +15477,22 @@
         <f aca="false">I12*ENTRADAS!$C$25</f>
         <v>1088.51735114121</v>
       </c>
-      <c r="J16" s="100"/>
-      <c r="K16" s="66" t="s">
-        <v>750</v>
+      <c r="J16" s="101" t="n">
+        <f aca="false">J12*ENTRADAS!$C$25</f>
+        <v>1121.1185020035</v>
+      </c>
+      <c r="K16" s="101" t="n">
+        <f aca="false">K12*ENTRADAS!$C$25</f>
+        <v>1088.51735114121</v>
+      </c>
+      <c r="L16" s="100"/>
+      <c r="M16" s="66" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="C17" s="101" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -14187,14 +15522,22 @@
         <f aca="false">ENTRADAS!$C$26*12</f>
         <v>253.32</v>
       </c>
-      <c r="J17" s="100"/>
-      <c r="K17" s="66" t="s">
-        <v>752</v>
+      <c r="J17" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$26*12</f>
+        <v>253.32</v>
+      </c>
+      <c r="K17" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$26*12</f>
+        <v>253.32</v>
+      </c>
+      <c r="L17" s="100"/>
+      <c r="M17" s="66" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -14224,14 +15567,22 @@
         <f aca="false">I15+I16+I17</f>
         <v>1954.71935114121</v>
       </c>
-      <c r="J18" s="100"/>
-      <c r="K18" s="66" t="s">
-        <v>754</v>
+      <c r="J18" s="47" t="n">
+        <f aca="false">J15+J16+J17</f>
+        <v>2028.42055821614</v>
+      </c>
+      <c r="K18" s="47" t="n">
+        <f aca="false">K15+K16+K17</f>
+        <v>1954.71935114121</v>
+      </c>
+      <c r="L18" s="100"/>
+      <c r="M18" s="66" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">C18/12</f>
@@ -14261,14 +15612,22 @@
         <f aca="false">I18/12</f>
         <v>162.893279261767</v>
       </c>
-      <c r="J19" s="100"/>
-      <c r="K19" s="66" t="s">
-        <v>756</v>
+      <c r="J19" s="47" t="n">
+        <f aca="false">J18/12</f>
+        <v>169.035046518012</v>
+      </c>
+      <c r="K19" s="47" t="n">
+        <f aca="false">K18/12</f>
+        <v>162.893279261767</v>
+      </c>
+      <c r="L19" s="100"/>
+      <c r="M19" s="66" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>757</v>
+        <v>782</v>
       </c>
       <c r="C20" s="37" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -14298,12 +15657,20 @@
         <f aca="false">IFERROR(1-I18/I8,0)</f>
         <v>0.770751452069489</v>
       </c>
-      <c r="J20" s="100"/>
-      <c r="K20" s="66"/>
+      <c r="J20" s="37" t="n">
+        <f aca="false">IFERROR(1-J18/J8,0)</f>
+        <v>0.762107809854155</v>
+      </c>
+      <c r="K20" s="37" t="n">
+        <f aca="false">IFERROR(1-K18/K8,0)</f>
+        <v>0.770751452069489</v>
+      </c>
+      <c r="L20" s="100"/>
+      <c r="M20" s="66"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="C21" s="101" t="n">
         <f aca="false">C8-C18</f>
@@ -14333,12 +15700,20 @@
         <f aca="false">I8-I18</f>
         <v>6571.91852197507</v>
       </c>
-      <c r="J21" s="100"/>
-      <c r="K21" s="66"/>
+      <c r="J21" s="101" t="n">
+        <f aca="false">J8-J18</f>
+        <v>6498.21731490014</v>
+      </c>
+      <c r="K21" s="101" t="n">
+        <f aca="false">K8-K18</f>
+        <v>6571.91852197507</v>
+      </c>
+      <c r="L21" s="100"/>
+      <c r="M21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="C22" s="101" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -14368,14 +15743,22 @@
         <f aca="false">ENTRADAS!$C$35</f>
         <v>300</v>
       </c>
-      <c r="J22" s="100"/>
-      <c r="K22" s="66" t="s">
-        <v>760</v>
+      <c r="J22" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$35</f>
+        <v>300</v>
+      </c>
+      <c r="K22" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$35</f>
+        <v>300</v>
+      </c>
+      <c r="L22" s="100"/>
+      <c r="M22" s="66" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="C23" s="101" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -14405,14 +15788,22 @@
         <f aca="false">ENTRADAS!$C$36</f>
         <v>150</v>
       </c>
-      <c r="J23" s="100"/>
-      <c r="K23" s="66" t="s">
-        <v>762</v>
+      <c r="J23" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$36</f>
+        <v>150</v>
+      </c>
+      <c r="K23" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$36</f>
+        <v>150</v>
+      </c>
+      <c r="L23" s="100"/>
+      <c r="M23" s="66" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>763</v>
+        <v>788</v>
       </c>
       <c r="C24" s="101" t="n">
         <f aca="false">0</f>
@@ -14442,14 +15833,22 @@
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="J24" s="100"/>
-      <c r="K24" s="66" t="s">
-        <v>764</v>
+      <c r="J24" s="101" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="101" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="100"/>
+      <c r="M24" s="66" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="C25" s="101" t="n">
         <f aca="false">C22+C23</f>
@@ -14479,12 +15878,20 @@
         <f aca="false">I22+I23</f>
         <v>450</v>
       </c>
-      <c r="J25" s="100"/>
-      <c r="K25" s="66"/>
+      <c r="J25" s="101" t="n">
+        <f aca="false">J22+J23</f>
+        <v>450</v>
+      </c>
+      <c r="K25" s="101" t="n">
+        <f aca="false">K22+K23</f>
+        <v>450</v>
+      </c>
+      <c r="L25" s="100"/>
+      <c r="M25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="C26" s="103" t="n">
         <f aca="false">C21-C25</f>
@@ -14514,14 +15921,22 @@
         <f aca="false">I21-I25</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="J26" s="100"/>
-      <c r="K26" s="66" t="s">
-        <v>767</v>
+      <c r="J26" s="103" t="n">
+        <f aca="false">J21-J25</f>
+        <v>6048.21731490014</v>
+      </c>
+      <c r="K26" s="103" t="n">
+        <f aca="false">K21-K25</f>
+        <v>6121.91852197507</v>
+      </c>
+      <c r="L26" s="100"/>
+      <c r="M26" s="66" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -14532,125 +15947,127 @@
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4576</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>770</v>
+      <c r="M29" s="2" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>7042.97674418605</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>772</v>
+      <c r="M30" s="2" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
         <v>2466.97674418605</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>774</v>
+      <c r="M31" s="2" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.539112050739958</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>776</v>
+      <c r="M32" s="2" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4927.56672</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>778</v>
+      <c r="M33" s="2" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7447.50945488372</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>780</v>
+      <c r="M34" s="2" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2519.94273488372</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>782</v>
+      <c r="M35" s="2" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>783</v>
+        <v>808</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>529.696418232558</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>784</v>
+      <c r="M36" s="2" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>1990.24631665116</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>786</v>
+      <c r="M37" s="2" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>788</v>
+      <c r="M38" s="2" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1034">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -88,7 +88,16 @@
     <t xml:space="preserve">     Substitui a proposta F: corrigiu a relacao DC/AC de 1,56 para 0,91 e passou de 1 para 2 MPPTs. Melhor R$/Wp de todos.</t>
   </si>
   <si>
-    <t xml:space="preserve">J) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
+    <t xml:space="preserve">J) AD BioSolar (Adriano Melo) - 8 modulos JA Solar 615 W = 4,92 kWp + HUAWEI SUN2000-5KTL-L1  -&gt;  R$ 17.442,00 INSTALADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     A UNICA que informou o MODELO EXATO do inversor, e a de melhores garantias: 30 anos de eficiencia no modulo e 10 anos no inversor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Em contrapartida e a mais cara por Wp entre as turnkey e cobre so 77% do consumo com o carro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K) Bruno G4 (11) 96861-7830 - nada recebido ainda. Coluna reservada na aba COMPARATIVO.</t>
   </si>
   <si>
     <t xml:space="preserve">2. AS TRES DESCOBERTAS MAIS IMPORTANTES</t>
@@ -1427,7 +1436,12 @@
 AUXSOL 7,5 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">J) Bruno G4
+    <t xml:space="preserve">J) AD BioSolar
+JA Solar 615W x8
+Huawei SUN2000-5KTL-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K) Bruno G4
 (a receber)</t>
   </si>
   <si>
@@ -1452,6 +1466,9 @@
     <t xml:space="preserve">Sfero - indic. Renato (11) 99705-1311</t>
   </si>
   <si>
+    <t xml:space="preserve">AD BioSolar - Adriano Melo (11) 97350-3103 / (11) 91408-8892</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bruno G4 (11) 96861-7830</t>
   </si>
   <si>
@@ -1473,6 +1490,9 @@
     <t xml:space="preserve">NAO INFORMADO na proposta</t>
   </si>
   <si>
+    <t xml:space="preserve">64.313.573/0001-58</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: SunWash e William nao informaram CNPJ. Sem CNPJ nao existe garantia exigivel. Sun Coast e a unica que trouxe CNPJ na propria proposta.</t>
   </si>
   <si>
@@ -1503,6 +1523,9 @@
     <t xml:space="preserve">Proposta 40438 de 11/08/2026 (val. 20/08)</t>
   </si>
   <si>
+    <t xml:space="preserve">Proposta #01225 de 11/08/2026 (val. 26/08)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nada recebido</t>
   </si>
   <si>
@@ -1563,6 +1586,9 @@
     <t xml:space="preserve">TCL Solar bifacial N-type 132 cel</t>
   </si>
   <si>
+    <t xml:space="preserve">JA Solar bifacial N-type 132 cel - TIER 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA sao marcas com pouquissima rede de assistencia de modulo no Brasil - exigir INMETRO e quem honra a garantia aqui.</t>
   </si>
   <si>
@@ -1599,6 +1625,9 @@
     <t xml:space="preserve">AUXSOL 7,5 kW mono 220V 2 MPPT (100% over)</t>
   </si>
   <si>
+    <t xml:space="preserve">HUAWEI SUN2000-5KTL-L1 5.000 W (modelo EXATO informado)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: AUXSOL tem baixa penetracao no Brasil. Huawei e Solis tem assistencia estabelecida.</t>
   </si>
   <si>
@@ -1623,6 +1652,9 @@
     <t xml:space="preserve">1 por modulo (10 MPPTs)</t>
   </si>
   <si>
+    <t xml:space="preserve">2 (a confirmar)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: Sun Coast usa 1 MPPT UNICO - os 8 modulos numa string so, exigindo mesma agua e mesma inclinacao, e sombra em 1 modulo derruba tudo. NO OUTRO EXTREMO, a opcao G com microinversor da 1 MPPT POR MODULO: sombra em um modulo nao afeta os outros e da liberdade de usar mais de uma agua do telhado.</t>
   </si>
   <si>
@@ -1677,6 +1709,9 @@
     <t xml:space="preserve">12 anos produto / 25 anos eficiencia</t>
   </si>
   <si>
+    <t xml:space="preserve">15 anos defeito / 30 anos eficiencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">So a Sun Coast declarou garantias na proposta. Dos outros, exigir por escrito.</t>
   </si>
   <si>
@@ -1689,6 +1724,9 @@
     <t xml:space="preserve">7 a 10 anos</t>
   </si>
   <si>
+    <t xml:space="preserve">10 anos</t>
+  </si>
+  <si>
     <t xml:space="preserve">'10 a 25 anos' da Sun Coast e vago: exigir o numero exato para o modelo cotado.</t>
   </si>
   <si>
@@ -1701,6 +1739,9 @@
     <t xml:space="preserve">1 ano instalacao + SEGURO ALL RISK 1 ano + GARANTIA DE PERFORMANCE EM CONTRATO</t>
   </si>
   <si>
+    <t xml:space="preserve">vistoria tecnica, ART, licencas, gestao de obra e frete inclusos</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 meses de servico e o minimo de mercado.</t>
   </si>
   <si>
@@ -1716,6 +1757,9 @@
     <t xml:space="preserve">obras civis, reformas no telhado/laje e no PADRAO DE ENTRADA</t>
   </si>
   <si>
+    <t xml:space="preserve">alvenaria, reforco estrutural e alteracoes na rede pedidas pela concessionaria</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALERTA: a Sun Coast exclui EXPLICITAMENTE a adequacao do padrao de entrada, obras no telhado, eletrodutos e o ART estrutural. E honesto ao declarar, mas o custo e seu. Os outros nao declararam exclusoes - o que nao significa que estejam inclusas.</t>
   </si>
   <si>
@@ -1741,6 +1785,9 @@
   </si>
   <si>
     <t xml:space="preserve">a vista, cartao 12x/21x COM juros ou financiamento 36x ate 120x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a vista ou financiamento em ate 60x</t>
   </si>
   <si>
     <t xml:space="preserve">ATENCAO: 18x SEM JUROS pelo mesmo valor a vista e uma vantagem financeira REAL - equivale a um desconto, porque o dinheiro fica rendendo na sua mao. Todas as outras oferecem parcelamento COM juros.</t>
@@ -2313,7 +2360,10 @@
     <t xml:space="preserve">I) Sun Coast v2 TCL 620W x11 AUXSOL 7,5 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">J) Bruno G4 (a receber)</t>
+    <t xml:space="preserve">J) AD BioSolar JA Solar 615W x8 Huawei SUN2000-5KTL-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K) Bruno G4 (a receber)</t>
   </si>
   <si>
     <t xml:space="preserve">EXPLICACAO</t>
@@ -2622,6 +2672,18 @@
 Fluxo</t>
   </si>
   <si>
+    <t xml:space="preserve">J) AD BioSolar
+Economia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J) AD BioSolar
+Acumulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J) AD BioSolar
+Fluxo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anos 5, 10 e 20 destacados. As colunas 'Fluxo' viram positivas no ano do payback ja corrigido por inflacao e degradacao.</t>
   </si>
   <si>
@@ -2725,6 +2787,30 @@
   </si>
   <si>
     <t xml:space="preserve">NENHUM ORCAMENTO CONSIDEROU O BYD. Informar a todos que havera carregamento diario do veiculo e pedir redimensionamento. A proposta do William (5,35 kWp) fica subdimensionada e o inversor Solis de 4 kW nao permite ampliar depois.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-sexies) SOBRE A AD BIOSOLAR (opcao J) - E A VERIFICACAO MAIS IMPORTANTE DE TODAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTOS FORTES: unica que informou o MODELO EXATO do inversor (Huawei SUN2000-5KTL-L1); modulo JA Solar Tier 1 com 30 anos de garantia de eficiencia e 15 de defeito; inversor com 10 anos de garantia; CNPJ na proposta; vistoria tecnica, ART, licencas, gestao de obra e frete no escopo; unica a informar o peso por m2 (8,33 kg/m2), dado que importa em telhado ceramico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGORA DA PARA FECHAR A CONTA QUE ESTAVA ABERTA: baixe a ficha tecnica do Huawei SUN2000-5KTL-L1 e a do modulo JA Solar de 615 W e compare a CORRENTE MAXIMA DE ENTRADA POR MPPT do inversor com a CORRENTE DE OPERACAO (Impp) do modulo. Modulos de 615 W nesse formato tem Impp na faixa de 16 A. Varias versoes da linha SUN2000-L1 aceitam de 12,5 a 13,5 A por MPPT. Se a corrente do modulo for maior que a do MPPT, o inversor NAO consegue extrair toda a potencia nas melhores horas do dia - perda permanente que nenhuma simulacao mostra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESSA MESMA VERIFICACAO VALE PARA AS OPCOES A, B, C, D e I, que usam modulos de 605 a 620 W. Exigir de cada fornecedor o PROJETO DE STRING por escrito: quantos modulos em serie por MPPT, tensao minima e maxima nas temperaturas extremas, e a corrente por MPPT comparada ao limite do inversor. Fornecedor que nao souber responder isso nao fez projeto - fez lista de compras.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD BIOSOLAR: 4,92 kWp COBRE SO 77% DO CENARIO 3, porque dimensionaram com 460 kWh/mes. Pedir a versao com 11 ou 12 modulos. O SUN2000-5KTL-L1 aceita ate cerca de 6,75 kWp (DC/AC 1,35), ou seja, cabem mais 2 a 3 modulos sem trocar inversor - e o preco marginal do modulo e baixo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD BIOSOLAR E A MAIS CARA POR Wp entre todas as turnkey (R$ 4,05/Wp com o padrao). Equipamento e otimo, mas o sistema e pequeno. Pedir preco para 11 modulos antes de comparar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUMEROS DE MARKETING DA AD BIOSOLAR: 'Economia total em 25 anos R$ 419.713,53', 'ROI 24,06 vezes' e 'TIR 35,81%' usam reajuste de energia de 10% ao ano composto por 25 anos. Ignore. Alem disso a 'conta COM sistema de R$ 75,31/mes' vale para 460 kWh/mes SEM o carro - com o BYD o meu modelo da cerca de R$ 259/mes nessa potencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRES VENDEDORES USARAM TRES CONSUMOS DIFERENTES: William usou 381 kWh/mes (a media real da conta), AD BioSolar usou 460 e Sfero usou 600. Nenhum deles explicou de onde veio o numero. Padronize: mande para TODOS o mesmo dado - 381 kWh/mes de historico MAIS 206 kWh/mes do BYD - e peca que refacam. So assim os orcamentos ficam comparaveis.</t>
   </si>
   <si>
     <t xml:space="preserve">CORRENTE DO MODULO x CORRENTE MAXIMA DO MPPT. Modulos de 605 a 615 W tem corrente de operacao na faixa de 14 a 17 A. Inversores residenciais da linha Huawei SUN2000-L1 costumam aceitar de 12,5 a 13,5 A por MPPT. Se a corrente do modulo ultrapassar a do inversor, perde-se geracao nas melhores horas. Exigir as duas fichas tecnicas e o calculo da string.</t>
@@ -4015,7 +4101,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4118,30 +4204,30 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>19</v>
+      <c r="B22" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>20</v>
+      <c r="B23" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4151,7 +4237,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4166,12 +4252,12 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4186,7 +4272,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4196,25 +4282,25 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>34</v>
+      <c r="B38" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="B40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4224,76 +4310,76 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="3" t="s">
-        <v>39</v>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="3" t="s">
-        <v>43</v>
+      <c r="B49" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="6" t="s">
-        <v>44</v>
+      <c r="B50" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="B51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="4"/>
+      <c r="B52" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="3" t="s">
-        <v>46</v>
+      <c r="B53" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4303,25 +4389,25 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="4"/>
+      <c r="B60" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="3" t="s">
-        <v>53</v>
+      <c r="B61" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4" t="s">
-        <v>54</v>
+      <c r="B62" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="B63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4371,31 +4457,46 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="4"/>
+      <c r="B74" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="3" t="s">
-        <v>66</v>
+      <c r="B75" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="B77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4414,112 +4515,121 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AG30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>814</v>
+        <v>830</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>825</v>
+        <v>841</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>836</v>
+        <v>852</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>837</v>
+        <v>853</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="AA4" s="17" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="AC4" s="17" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>844</v>
+        <v>860</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>861</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="AG4" s="17" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4638,6 +4748,18 @@
         <f aca="false">AC6-COMPARATIVO!K$31</f>
         <v>-13268.0814780249</v>
       </c>
+      <c r="AE6" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
+        <v>4968.85240496757</v>
+      </c>
+      <c r="AF6" s="105" t="n">
+        <f aca="false">AE6</f>
+        <v>4968.85240496757</v>
+      </c>
+      <c r="AG6" s="105" t="n">
+        <f aca="false">AF6-COMPARATIVO!L$31</f>
+        <v>-14973.1475950324</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="104" t="n">
@@ -4755,6 +4877,18 @@
         <f aca="false">AC7-COMPARATIVO!K$31</f>
         <v>-6747.10569719492</v>
       </c>
+      <c r="AE7" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
+        <v>5292.74704898539</v>
+      </c>
+      <c r="AF7" s="105" t="n">
+        <f aca="false">AF6+AE7</f>
+        <v>10261.599453953</v>
+      </c>
+      <c r="AG7" s="105" t="n">
+        <f aca="false">AF7-COMPARATIVO!L$31</f>
+        <v>-9680.40054604704</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="104" t="n">
@@ -4872,6 +5006,18 @@
         <f aca="false">AC8-COMPARATIVO!K$31</f>
         <v>198.939889908506</v>
       </c>
+      <c r="AE8" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
+        <v>5637.7547653735</v>
+      </c>
+      <c r="AF8" s="105" t="n">
+        <f aca="false">AF7+AE8</f>
+        <v>15899.3542193265</v>
+      </c>
+      <c r="AG8" s="105" t="n">
+        <f aca="false">AF8-COMPARATIVO!L$31</f>
+        <v>-4042.64578067354</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="104" t="n">
@@ -4989,6 +5135,18 @@
         <f aca="false">AC9-COMPARATIVO!K$31</f>
         <v>7597.76345860726</v>
       </c>
+      <c r="AE9" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
+        <v>6005.25180975437</v>
+      </c>
+      <c r="AF9" s="105" t="n">
+        <f aca="false">AF8+AE9</f>
+        <v>21904.6060290808</v>
+      </c>
+      <c r="AG9" s="105" t="n">
+        <f aca="false">AF9-COMPARATIVO!L$31</f>
+        <v>1962.60602908083</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="106" t="n">
@@ -5106,6 +5264,18 @@
         <f aca="false">AC10-COMPARATIVO!K$31</f>
         <v>15478.8793416317</v>
       </c>
+      <c r="AE10" s="108" t="n">
+        <f aca="false">ECONOMIA!L$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
+        <v>6396.70414897321</v>
+      </c>
+      <c r="AF10" s="108" t="n">
+        <f aca="false">AF9+AE10</f>
+        <v>28301.310178054</v>
+      </c>
+      <c r="AG10" s="108" t="n">
+        <f aca="false">AF10-COMPARATIVO!L$31</f>
+        <v>8359.31017805404</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="104" t="n">
@@ -5223,6 +5393,18 @@
         <f aca="false">AC11-COMPARATIVO!K$31</f>
         <v>23873.725763491</v>
       </c>
+      <c r="AE11" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
+        <v>6813.67330892403</v>
+      </c>
+      <c r="AF11" s="105" t="n">
+        <f aca="false">AF10+AE11</f>
+        <v>35114.9834869781</v>
+      </c>
+      <c r="AG11" s="105" t="n">
+        <f aca="false">AF11-COMPARATIVO!L$31</f>
+        <v>15172.9834869781</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="104" t="n">
@@ -5340,6 +5522,18 @@
         <f aca="false">AC12-COMPARATIVO!K$31</f>
         <v>32815.7902493592</v>
       </c>
+      <c r="AE12" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
+        <v>7257.82260356625</v>
+      </c>
+      <c r="AF12" s="105" t="n">
+        <f aca="false">AF11+AE12</f>
+        <v>42372.8060905443</v>
+      </c>
+      <c r="AG12" s="105" t="n">
+        <f aca="false">AF12-COMPARATIVO!L$31</f>
+        <v>22430.8060905443</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="104" t="n">
@@ -5457,6 +5651,18 @@
         <f aca="false">AC13-COMPARATIVO!K$31</f>
         <v>42340.7432087388</v>
       </c>
+      <c r="AE13" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
+        <v>7730.92376997971</v>
+      </c>
+      <c r="AF13" s="105" t="n">
+        <f aca="false">AF12+AE13</f>
+        <v>50103.729860524</v>
+      </c>
+      <c r="AG13" s="105" t="n">
+        <f aca="false">AF13-COMPARATIVO!L$31</f>
+        <v>30161.729860524</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="104" t="n">
@@ -5574,6 +5780,18 @@
         <f aca="false">AC14-COMPARATIVO!K$31</f>
         <v>52486.5802267755</v>
       </c>
+      <c r="AE14" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
+        <v>8234.86403592584</v>
+      </c>
+      <c r="AF14" s="105" t="n">
+        <f aca="false">AF13+AE14</f>
+        <v>58338.5938964499</v>
+      </c>
+      <c r="AG14" s="105" t="n">
+        <f aca="false">AF14-COMPARATIVO!L$31</f>
+        <v>38396.5938964499</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="106" t="n">
@@ -5691,6 +5909,18 @@
         <f aca="false">AC15-COMPARATIVO!K$31</f>
         <v>63293.773630833</v>
       </c>
+      <c r="AE15" s="108" t="n">
+        <f aca="false">ECONOMIA!L$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
+        <v>8771.65364810767</v>
+      </c>
+      <c r="AF15" s="108" t="n">
+        <f aca="false">AF14+AE15</f>
+        <v>67110.2475445575</v>
+      </c>
+      <c r="AG15" s="108" t="n">
+        <f aca="false">AF15-COMPARATIVO!L$31</f>
+        <v>47168.2475445575</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="104" t="n">
@@ -5808,6 +6038,18 @@
         <f aca="false">AC16-COMPARATIVO!K$31</f>
         <v>74805.4339369339</v>
       </c>
+      <c r="AE16" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
+        <v>9343.43389115956</v>
+      </c>
+      <c r="AF16" s="105" t="n">
+        <f aca="false">AF15+AE16</f>
+        <v>76453.6814357171</v>
+      </c>
+      <c r="AG16" s="105" t="n">
+        <f aca="false">AF16-COMPARATIVO!L$31</f>
+        <v>56511.6814357171</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="104" t="n">
@@ -5925,6 +6167,18 @@
         <f aca="false">AC17-COMPARATIVO!K$31</f>
         <v>87067.481820088</v>
       </c>
+      <c r="AE17" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
+        <v>9952.4856293548</v>
+      </c>
+      <c r="AF17" s="105" t="n">
+        <f aca="false">AF16+AE17</f>
+        <v>86406.1670650719</v>
+      </c>
+      <c r="AG17" s="105" t="n">
+        <f aca="false">AF17-COMPARATIVO!L$31</f>
+        <v>66464.1670650719</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="104" t="n">
@@ -6042,6 +6296,18 @@
         <f aca="false">AC18-COMPARATIVO!K$31</f>
         <v>100128.831294506</v>
       </c>
+      <c r="AE18" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
+        <v>10601.2384051043</v>
+      </c>
+      <c r="AF18" s="105" t="n">
+        <f aca="false">AF17+AE18</f>
+        <v>97007.4054701762</v>
+      </c>
+      <c r="AG18" s="105" t="n">
+        <f aca="false">AF18-COMPARATIVO!L$31</f>
+        <v>77065.4054701762</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="104" t="n">
@@ -6159,6 +6425,18 @@
         <f aca="false">AC19-COMPARATIVO!K$31</f>
         <v>114041.584834413</v>
       </c>
+      <c r="AE19" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
+        <v>11292.280130541</v>
+      </c>
+      <c r="AF19" s="105" t="n">
+        <f aca="false">AF18+AE19</f>
+        <v>108299.685600717</v>
+      </c>
+      <c r="AG19" s="105" t="n">
+        <f aca="false">AF19-COMPARATIVO!L$31</f>
+        <v>88357.6856007172</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="104" t="n">
@@ -6276,6 +6554,18 @@
         <f aca="false">AC20-COMPARATIVO!K$31</f>
         <v>128861.241213819</v>
       </c>
+      <c r="AE20" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
+        <v>12028.3674108503</v>
+      </c>
+      <c r="AF20" s="105" t="n">
+        <f aca="false">AF19+AE20</f>
+        <v>120328.053011568</v>
+      </c>
+      <c r="AG20" s="105" t="n">
+        <f aca="false">AF20-COMPARATIVO!L$31</f>
+        <v>100386.053011568</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="104" t="n">
@@ -6393,6 +6683,18 @@
         <f aca="false">AC21-COMPARATIVO!K$31</f>
         <v>144646.916894317</v>
       </c>
+      <c r="AE21" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
+        <v>12812.4365405266</v>
+      </c>
+      <c r="AF21" s="105" t="n">
+        <f aca="false">AF20+AE21</f>
+        <v>133140.489552094</v>
+      </c>
+      <c r="AG21" s="105" t="n">
+        <f aca="false">AF21-COMPARATIVO!L$31</f>
+        <v>113198.489552094</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="104" t="n">
@@ -6510,6 +6812,18 @@
         <f aca="false">AC22-COMPARATIVO!K$31</f>
         <v>161461.581844048</v>
       </c>
+      <c r="AE22" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
+        <v>13647.6152164209</v>
+      </c>
+      <c r="AF22" s="105" t="n">
+        <f aca="false">AF21+AE22</f>
+        <v>146788.104768515</v>
+      </c>
+      <c r="AG22" s="105" t="n">
+        <f aca="false">AF22-COMPARATIVO!L$31</f>
+        <v>126846.104768515</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="104" t="n">
@@ -6627,6 +6941,18 @@
         <f aca="false">AC23-COMPARATIVO!K$31</f>
         <v>179372.310728528</v>
       </c>
+      <c r="AE23" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
+        <v>14537.2350143032</v>
+      </c>
+      <c r="AF23" s="105" t="n">
+        <f aca="false">AF22+AE23</f>
+        <v>161325.339782818</v>
+      </c>
+      <c r="AG23" s="105" t="n">
+        <f aca="false">AF23-COMPARATIVO!L$31</f>
+        <v>141383.339782818</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="104" t="n">
@@ -6744,6 +7070,18 @@
         <f aca="false">AC24-COMPARATIVO!K$31</f>
         <v>198450.550475342</v>
       </c>
+      <c r="AE24" s="105" t="n">
+        <f aca="false">ECONOMIA!L$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
+        <v>15484.8446787106</v>
+      </c>
+      <c r="AF24" s="105" t="n">
+        <f aca="false">AF23+AE24</f>
+        <v>176810.184461529</v>
+      </c>
+      <c r="AG24" s="105" t="n">
+        <f aca="false">AF24-COMPARATIVO!L$31</f>
+        <v>156868.184461529</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="106" t="n">
@@ -6861,25 +7199,37 @@
         <f aca="false">AC25-COMPARATIVO!K$31</f>
         <v>218772.405280052</v>
       </c>
+      <c r="AE25" s="108" t="n">
+        <f aca="false">ECONOMIA!L$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
+        <v>16494.2242790924</v>
+      </c>
+      <c r="AF25" s="108" t="n">
+        <f aca="false">AF24+AE25</f>
+        <v>193304.408740621</v>
+      </c>
+      <c r="AG25" s="108" t="n">
+        <f aca="false">AF25-COMPARATIVO!L$31</f>
+        <v>173362.408740621</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>848</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -6913,54 +7263,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>850</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>852</v>
+        <v>871</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>855</v>
+        <v>874</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>856</v>
+        <v>875</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C7" s="32" t="n">
         <f aca="false">CONTA!C38</f>
@@ -6993,7 +7343,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">CONTA!C39</f>
@@ -7026,7 +7376,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">CONTA!C40</f>
@@ -7059,7 +7409,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">CONTA!C41</f>
@@ -7092,7 +7442,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">CONTA!C42</f>
@@ -7125,7 +7475,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">CONTA!C43</f>
@@ -7158,7 +7508,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">CONTA!C44</f>
@@ -7191,7 +7541,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">CONTA!C45</f>
@@ -7224,7 +7574,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">CONTA!C46</f>
@@ -7257,7 +7607,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">CONTA!C47</f>
@@ -7290,7 +7640,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C17" s="32" t="n">
         <f aca="false">CONTA!C48</f>
@@ -7323,7 +7673,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">CONTA!C49</f>
@@ -7356,7 +7706,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C19" s="34" t="n">
         <f aca="false">SUM(C7:C18)</f>
@@ -7381,32 +7731,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>860</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>861</v>
+        <v>880</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>862</v>
+        <v>881</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>864</v>
+        <v>883</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>865</v>
+        <v>884</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7414,12 +7764,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>866</v>
+        <v>885</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>867</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -7438,7 +7788,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -7450,32 +7800,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -7485,10 +7835,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>875</v>
+        <v>894</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E6" s="110"/>
     </row>
@@ -7497,10 +7847,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E7" s="110"/>
     </row>
@@ -7509,10 +7859,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E8" s="110"/>
     </row>
@@ -7521,206 +7871,206 @@
         <v>4</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E9" s="110"/>
     </row>
-    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="8"/>
+      <c r="C10" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="109" t="s">
-        <v>880</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E10" s="110"/>
-    </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="n">
+      <c r="C11" s="111" t="s">
+        <v>900</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E11" s="110"/>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="109" t="s">
-        <v>881</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E11" s="110"/>
-    </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="n">
+      <c r="C12" s="109" t="s">
+        <v>901</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E12" s="110"/>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="109" t="s">
-        <v>882</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E12" s="110"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="n">
+      <c r="C13" s="109" t="s">
+        <v>902</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E13" s="110"/>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="109" t="s">
-        <v>883</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E13" s="110"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="C14" s="109" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E14" s="110"/>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>904</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E15" s="110"/>
+    </row>
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="109" t="s">
-        <v>885</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E15" s="110"/>
-    </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="n">
+      <c r="C16" s="109" t="s">
+        <v>905</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E16" s="110"/>
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="109" t="s">
-        <v>886</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E16" s="110"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8"/>
-      <c r="C17" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="n">
+      <c r="C17" s="109" t="s">
+        <v>906</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E17" s="110"/>
+    </row>
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="109" t="s">
-        <v>888</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E18" s="110"/>
-    </row>
-    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="n">
+      <c r="C19" s="109" t="s">
+        <v>907</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E19" s="110"/>
+    </row>
+    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="109" t="s">
-        <v>889</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E19" s="110"/>
-    </row>
-    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="C20" s="109" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E20" s="110"/>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="109" t="s">
+        <v>909</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E21" s="110"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>891</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E21" s="110"/>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
+      <c r="C22" s="109" t="s">
+        <v>910</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E22" s="110"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="109" t="s">
-        <v>892</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E22" s="110"/>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="n">
+      <c r="C23" s="109" t="s">
+        <v>911</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E23" s="110"/>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="111" t="s">
-        <v>893</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E23" s="110"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8"/>
-      <c r="C25" s="7" t="s">
-        <v>894</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="n">
+      <c r="C24" s="109" t="s">
+        <v>912</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E24" s="110"/>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="109" t="s">
+      <c r="C25" s="109" t="s">
+        <v>913</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>895</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E26" s="110"/>
+      <c r="E25" s="110"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="8"/>
+      <c r="C26" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E27" s="110"/>
     </row>
@@ -7729,78 +8079,78 @@
         <v>20</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E28" s="110"/>
     </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="109" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E29" s="110"/>
     </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="111" t="s">
-        <v>899</v>
+      <c r="C30" s="109" t="s">
+        <v>918</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E30" s="110"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8"/>
-      <c r="C32" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="n">
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C33" s="111" t="s">
-        <v>901</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E33" s="110"/>
-    </row>
-    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="n">
+      <c r="C31" s="109" t="s">
+        <v>919</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E31" s="110"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C34" s="109" t="s">
-        <v>902</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E34" s="110"/>
+      <c r="C32" s="111" t="s">
+        <v>920</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E32" s="110"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="8"/>
+      <c r="C34" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C35" s="109" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E35" s="110"/>
     </row>
@@ -7809,254 +8159,254 @@
         <v>26</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E36" s="110"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8"/>
-      <c r="C38" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C37" s="109" t="s">
+        <v>924</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E37" s="110"/>
+    </row>
+    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="109" t="s">
+        <v>925</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E38" s="110"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C39" s="109" t="s">
-        <v>906</v>
+        <v>29</v>
+      </c>
+      <c r="C39" s="111" t="s">
+        <v>926</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E39" s="110"/>
     </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="C40" s="109" t="s">
-        <v>907</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E40" s="110"/>
-    </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="C41" s="109" t="s">
-        <v>908</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E41" s="110"/>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="8"/>
+      <c r="C41" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C42" s="109" t="s">
-        <v>909</v>
+      <c r="C42" s="111" t="s">
+        <v>928</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E42" s="110"/>
     </row>
-    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="n">
         <v>31</v>
       </c>
       <c r="C43" s="109" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E43" s="110"/>
     </row>
-    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="n">
         <v>32</v>
       </c>
       <c r="C44" s="109" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E44" s="110"/>
     </row>
-    <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="n">
         <v>33</v>
       </c>
       <c r="C45" s="109" t="s">
-        <v>912</v>
+        <v>931</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E45" s="110"/>
     </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="8"/>
+      <c r="C47" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="C46" s="109" t="s">
-        <v>913</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E46" s="110"/>
-    </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C47" s="109" t="s">
-        <v>914</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E47" s="110"/>
-    </row>
-    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="n">
-        <v>36</v>
-      </c>
       <c r="C48" s="109" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E48" s="110"/>
     </row>
     <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C49" s="109" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E49" s="110"/>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C50" s="109" t="s">
+        <v>935</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E50" s="110"/>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C51" s="109" t="s">
+        <v>936</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E51" s="110"/>
+    </row>
+    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="C50" s="109" t="s">
-        <v>917</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E50" s="110"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="n">
+      <c r="C52" s="109" t="s">
+        <v>937</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E52" s="110"/>
+    </row>
+    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="C51" s="109" t="s">
-        <v>918</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E51" s="110"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="8"/>
-      <c r="C53" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="109" t="s">
+        <v>938</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E53" s="110"/>
+    </row>
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C54" s="111" t="s">
-        <v>920</v>
+      <c r="C54" s="109" t="s">
+        <v>939</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E54" s="110"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="C55" s="111" t="s">
-        <v>921</v>
+      <c r="C55" s="109" t="s">
+        <v>940</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E55" s="110"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="C56" s="111" t="s">
-        <v>922</v>
+      <c r="C56" s="109" t="s">
+        <v>941</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E56" s="110"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="C57" s="111" t="s">
-        <v>923</v>
+      <c r="C57" s="109" t="s">
+        <v>942</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E57" s="110"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="C58" s="111" t="s">
-        <v>924</v>
+      <c r="C58" s="109" t="s">
+        <v>943</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E58" s="110"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C59" s="111" t="s">
-        <v>925</v>
+      <c r="C59" s="109" t="s">
+        <v>944</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E59" s="110"/>
     </row>
@@ -8064,55 +8414,55 @@
       <c r="B60" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="C60" s="111" t="s">
-        <v>926</v>
+      <c r="C60" s="109" t="s">
+        <v>945</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E60" s="110"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="4" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="8"/>
+      <c r="C62" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="C61" s="111" t="s">
-        <v>927</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E61" s="110"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4" t="n">
+      <c r="C63" s="111" t="s">
+        <v>947</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E63" s="110"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="C62" s="111" t="s">
-        <v>928</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="E62" s="110"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="8"/>
-      <c r="C64" s="7" t="s">
-        <v>929</v>
-      </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="C64" s="111" t="s">
+        <v>948</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E64" s="110"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="n">
         <v>49</v>
       </c>
       <c r="C65" s="111" t="s">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E65" s="110"/>
     </row>
@@ -8121,10 +8471,10 @@
         <v>50</v>
       </c>
       <c r="C66" s="111" t="s">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E66" s="110"/>
     </row>
@@ -8133,10 +8483,10 @@
         <v>51</v>
       </c>
       <c r="C67" s="111" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E67" s="110"/>
     </row>
@@ -8145,10 +8495,10 @@
         <v>52</v>
       </c>
       <c r="C68" s="111" t="s">
-        <v>933</v>
+        <v>952</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E68" s="110"/>
     </row>
@@ -8157,10 +8507,10 @@
         <v>53</v>
       </c>
       <c r="C69" s="111" t="s">
-        <v>934</v>
+        <v>953</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E69" s="110"/>
     </row>
@@ -8169,10 +8519,10 @@
         <v>54</v>
       </c>
       <c r="C70" s="111" t="s">
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E70" s="110"/>
     </row>
@@ -8181,17 +8531,17 @@
         <v>55</v>
       </c>
       <c r="C71" s="111" t="s">
-        <v>936</v>
+        <v>955</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E71" s="110"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="8"/>
       <c r="C73" s="7" t="s">
-        <v>937</v>
+        <v>956</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
@@ -8201,22 +8551,22 @@
         <v>56</v>
       </c>
       <c r="C74" s="111" t="s">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E74" s="110"/>
     </row>
-    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="n">
         <v>57</v>
       </c>
       <c r="C75" s="111" t="s">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E75" s="110"/>
     </row>
@@ -8225,10 +8575,10 @@
         <v>58</v>
       </c>
       <c r="C76" s="111" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E76" s="110"/>
     </row>
@@ -8237,10 +8587,10 @@
         <v>59</v>
       </c>
       <c r="C77" s="111" t="s">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E77" s="110"/>
     </row>
@@ -8249,12 +8599,104 @@
         <v>60</v>
       </c>
       <c r="C78" s="111" t="s">
-        <v>942</v>
+        <v>961</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E78" s="110"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="C79" s="111" t="s">
+        <v>962</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E79" s="110"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="C80" s="111" t="s">
+        <v>963</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E80" s="110"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="8"/>
+      <c r="C82" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="C83" s="111" t="s">
+        <v>965</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E83" s="110"/>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C84" s="111" t="s">
+        <v>966</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E84" s="110"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="C85" s="111" t="s">
+        <v>967</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E85" s="110"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="C86" s="111" t="s">
+        <v>968</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E86" s="110"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C87" s="111" t="s">
+        <v>969</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E87" s="110"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8284,370 +8726,370 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="66" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="66" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="66" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="48" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="66" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="66" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="66" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="66" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="66" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="66" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="66" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="66" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="66" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="66" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="66" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="66" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="66" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="66" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="66" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="66" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="66" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="66" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="66" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="66" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="48" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="66" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="66" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="66" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="66" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="66" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="66" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="66" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="66" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
     </row>
   </sheetData>
@@ -8678,17 +9120,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -8696,93 +9138,93 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -8790,214 +9232,214 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(C16=1,30,IF(C16=2,50,100))</f>
         <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1.02147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0.59643</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.40085</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.02419</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C23" s="15" t="n">
         <f aca="false">C19*C22</f>
         <v>0.357858</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C25" s="15" t="n">
         <f aca="false">C23*C24</f>
         <v>0.2147148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -9005,97 +9447,97 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>0.79</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0.72</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>0.0045</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>300</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>150</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -9103,120 +9545,120 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C41" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C42" s="16" t="n">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C43" s="11" t="n">
         <v>40</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C44" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>0.86</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C46" s="16" t="n">
         <v>3.3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C48" s="14" t="n">
         <v>0.15</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -9251,53 +9693,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>322.07</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>389</v>
@@ -9310,18 +9752,18 @@
         <v>12.15625</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>216.46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>364</v>
@@ -9334,18 +9776,18 @@
         <v>11.741935483871</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>13.06</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>290</v>
@@ -9358,18 +9800,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>551.59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>375</v>
@@ -9382,18 +9824,18 @@
         <v>11.71875</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>21.11</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>337</v>
@@ -9406,18 +9848,18 @@
         <v>11.2333333333333</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>572.7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>323</v>
@@ -9430,19 +9872,19 @@
         <v>11.1379310344828</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H11" s="23" t="n">
         <f aca="false">IFERROR(H8/540,0)</f>
         <v>1.02146296296296</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>372</v>
@@ -9457,7 +9899,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>348</v>
@@ -9470,12 +9912,12 @@
         <v>11.6</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>354</v>
@@ -9488,18 +9930,18 @@
         <v>12.2068965517241</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>4.14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>394</v>
@@ -9512,18 +9954,18 @@
         <v>12.3125</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>19.12</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>457</v>
@@ -9536,18 +9978,18 @@
         <v>15.2333333333333</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>99.28</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>422</v>
@@ -9560,18 +10002,18 @@
         <v>14.551724137931</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>122.54</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>540</v>
@@ -9586,145 +10028,145 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="G21" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C22" s="26" t="n">
         <f aca="false">SUM(C7:C18)</f>
         <v>4576</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C22/12</f>
         <v>381.333333333333</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">SUM(D7:D18)</f>
         <v>366</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C22/C24,0)</f>
         <v>12.5027322404372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">MAX(C7:C18)</f>
         <v>540</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">MIN(C7:C18)</f>
         <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">IFERROR(C26/C27-1,0)</f>
@@ -9732,33 +10174,33 @@
       </c>
       <c r="D28" s="2"/>
       <c r="G28" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">IFERROR(C29/C23-1,0)</f>
@@ -9766,81 +10208,81 @@
       </c>
       <c r="D30" s="2"/>
       <c r="G30" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">AVERAGE(C7:C12)</f>
         <v>343.5</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C32" s="29" t="n">
         <f aca="false">AVERAGE(C13:C18)</f>
         <v>419.166666666667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IFERROR(C32/C31-1,0)</f>
         <v>0.220281416787967</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IFERROR(C18/C6-1,0)</f>
         <v>0.388174807197943</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -9848,162 +10290,162 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="18" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C38" s="32" t="n">
         <f aca="false">C12</f>
         <v>372</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C39" s="32" t="n">
         <f aca="false">C13</f>
         <v>348</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C40" s="32" t="n">
         <f aca="false">C14</f>
         <v>354</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C41" s="32" t="n">
         <f aca="false">C15</f>
         <v>394</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C42" s="32" t="n">
         <f aca="false">C16</f>
         <v>457</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C43" s="32" t="n">
         <f aca="false">C17</f>
         <v>422</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C44" s="32" t="n">
         <f aca="false">C18</f>
         <v>540</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C45" s="32" t="n">
         <f aca="false">C7</f>
         <v>364</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C46" s="32" t="n">
         <f aca="false">C8</f>
         <v>290</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="18" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C47" s="32" t="n">
         <f aca="false">C9</f>
         <v>375</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C48" s="32" t="n">
         <f aca="false">C10</f>
         <v>337</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C49" s="32" t="n">
         <f aca="false">C11</f>
         <v>323</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">SUM(C38:C49)</f>
@@ -10012,7 +10454,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -10020,7 +10462,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C53" s="35" t="n">
         <f aca="false">C22*H11+H9*12</f>
@@ -10029,7 +10471,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C54" s="35" t="n">
         <f aca="false">C53/12</f>
@@ -10038,7 +10480,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C55" s="35" t="n">
         <f aca="false">H10</f>
@@ -10047,82 +10489,82 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -10157,49 +10599,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>31</v>
@@ -10236,7 +10678,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>28</v>
@@ -10273,7 +10715,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>31</v>
@@ -10310,7 +10752,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>30</v>
@@ -10347,7 +10789,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>31</v>
@@ -10384,7 +10826,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>30</v>
@@ -10421,7 +10863,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>31</v>
@@ -10458,7 +10900,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>31</v>
@@ -10495,7 +10937,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>30</v>
@@ -10532,7 +10974,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>31</v>
@@ -10569,7 +11011,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>30</v>
@@ -10606,7 +11048,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>31</v>
@@ -10643,7 +11085,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="38" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">SUM(C5:C16)</f>
@@ -10678,7 +11120,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I18" s="26" t="n">
         <f aca="false">I17/12</f>
@@ -10691,12 +11133,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10704,37 +11146,37 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10742,12 +11184,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10755,12 +11197,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -10793,17 +11235,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -10814,82 +11256,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">ENTRADAS!C43</f>
         <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C6" s="44" t="n">
         <f aca="false">ENTRADAS!C42</f>
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C7" s="29" t="n">
         <f aca="false">C5*C6/100</f>
         <v>6.8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C8" s="43" t="n">
         <f aca="false">ENTRADAS!C44</f>
         <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C9" s="45" t="n">
         <f aca="false">C7*C8</f>
         <v>176.8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -10900,7 +11342,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C12" s="46" t="n">
         <f aca="false">ENTRADAS!C45</f>
@@ -10908,143 +11350,143 @@
       </c>
       <c r="D12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C13" s="45" t="n">
         <f aca="false">C9/C12</f>
         <v>205.581395348837</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">C13-C9</f>
         <v>28.7813953488372</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C15" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C18</f>
         <v>209.995227906977</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">C15*12</f>
         <v>2519.94273488372</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C13*ENTRADAS!C25</f>
         <v>44.1413681860465</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15-C17</f>
         <v>165.85385972093</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C18*12</f>
         <v>1990.24631665116</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">IFERROR(C15/(C5*C8),0)</f>
         <v>0.201918488372093</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C21" s="15" t="n">
         <f aca="false">IFERROR(C17/(C5*C8),0)</f>
         <v>0.042443623255814</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -11055,97 +11497,97 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C24" s="44" t="n">
         <f aca="false">ENTRADAS!C46</f>
         <v>3.3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">IFERROR(C13/C8/C24,0)</f>
         <v>2.39605355884426</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">IFERROR(ENTRADAS!C41/ENTRADAS!C45/C24,0)</f>
         <v>6.44820295983087</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C27" s="29" t="n">
         <f aca="false">IFERROR(C24*1000/220,0)</f>
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C28" s="29" t="n">
         <f aca="false">IFERROR(C27*1.25,0)</f>
         <v>18.75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">C24*1</f>
         <v>3.3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -11156,27 +11598,27 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -11201,7 +11643,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C34" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -11226,7 +11668,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="48" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C35" s="32" t="n">
         <f aca="false">CONTA!C23</f>
@@ -11263,7 +11705,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -11274,30 +11716,30 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="50" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D42" s="52" t="n">
         <f aca="false">0</f>
@@ -11308,18 +11750,18 @@
         <v>0</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="50" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D43" s="52" t="n">
         <f aca="false">ENTRADAS!C25</f>
@@ -11330,18 +11772,18 @@
         <v>44.1413681860465</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="50" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D44" s="52" t="n">
         <f aca="false">ENTRADAS!C18</f>
@@ -11352,15 +11794,15 @@
         <v>209.995227906977</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11369,17 +11811,17 @@
         <v>529.696418232558</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -11409,17 +11851,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11428,31 +11870,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C5" s="43" t="n">
         <f aca="false">GERACAO!I17</f>
         <v>1264.268995</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C6" s="29" t="n">
         <f aca="false">C5/12</f>
         <v>105.355749583333</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C7" s="4" t="str">
         <f aca="false">"kWp necessario = consumo anual / "&amp;TEXT(C5,"0")&amp;" kWh por kWp"</f>
@@ -11462,7 +11904,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -11471,24 +11913,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">BYD!F33</f>
@@ -11509,7 +11951,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C12" s="32" t="n">
         <f aca="false">BYD!F34</f>
@@ -11530,7 +11972,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="48" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">BYD!F35</f>
@@ -11551,7 +11993,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -11561,18 +12003,18 @@
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C17" s="56" t="str">
         <f aca="false">"100% do Cenario 2"</f>
@@ -11589,7 +12031,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C18" s="57" t="n">
         <f aca="false">E12</f>
@@ -11606,7 +12048,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C19" s="58" t="n">
         <f aca="false">ROUNDUP(C18*1000/615,0)</f>
@@ -11623,7 +12065,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C20" s="59" t="n">
         <f aca="false">C19*615/1000</f>
@@ -11640,7 +12082,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C21" s="57" t="n">
         <f aca="false">5</f>
@@ -11657,7 +12099,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C22" s="60" t="n">
         <f aca="false">IFERROR(C20/C21,0)</f>
@@ -11674,7 +12116,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C23" s="58" t="n">
         <f aca="false">C20*$C$5</f>
@@ -11691,7 +12133,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C24" s="58" t="n">
         <f aca="false">C23/12</f>
@@ -11708,7 +12150,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IFERROR(C23/$D$12,0)</f>
@@ -11725,7 +12167,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C26" s="62" t="n">
         <f aca="false">IFERROR(C23/$D$13,0)</f>
@@ -11742,7 +12184,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C27" s="58" t="n">
         <f aca="false">MAX(0,C23-$D$13)</f>
@@ -11759,52 +12201,52 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11812,12 +12254,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -11836,216 +12278,231 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="64" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H5" s="65" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I5" s="65" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="J5" s="65" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="K5" s="65" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L5" s="65" t="s">
-        <v>466</v>
-      </c>
-      <c r="M5" s="66" t="s">
-        <v>467</v>
+        <v>470</v>
+      </c>
+      <c r="M5" s="65" t="s">
+        <v>471</v>
+      </c>
+      <c r="N5" s="66" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="64" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K6" s="65" t="s">
-        <v>471</v>
-      </c>
-      <c r="L6" s="65"/>
-      <c r="M6" s="68" t="s">
-        <v>473</v>
+        <v>476</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>478</v>
+      </c>
+      <c r="M6" s="65"/>
+      <c r="N6" s="68" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="64" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="G7" s="65" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="I7" s="65" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="J7" s="65" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="K7" s="65" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="L7" s="65" t="s">
-        <v>483</v>
-      </c>
-      <c r="M7" s="68" t="s">
-        <v>484</v>
+        <v>489</v>
+      </c>
+      <c r="M7" s="65" t="s">
+        <v>490</v>
+      </c>
+      <c r="N7" s="68" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="69" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D8" s="70" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="G8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="K8" s="70" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="L8" s="70" t="s">
-        <v>488</v>
-      </c>
-      <c r="M8" s="68" t="s">
-        <v>489</v>
+        <v>494</v>
+      </c>
+      <c r="M8" s="70" t="s">
+        <v>495</v>
+      </c>
+      <c r="N8" s="68" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="64" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C9" s="71" t="n">
         <v>12</v>
@@ -12074,14 +12531,17 @@
       <c r="K9" s="71" t="n">
         <v>11</v>
       </c>
-      <c r="L9" s="72"/>
-      <c r="M9" s="66" t="s">
-        <v>491</v>
+      <c r="L9" s="71" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="72"/>
+      <c r="N9" s="66" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="64" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C10" s="71" t="n">
         <v>615</v>
@@ -12110,50 +12570,56 @@
       <c r="K10" s="71" t="n">
         <v>620</v>
       </c>
-      <c r="L10" s="72"/>
-      <c r="M10" s="66" t="s">
-        <v>493</v>
+      <c r="L10" s="71" t="n">
+        <v>615</v>
+      </c>
+      <c r="M10" s="72"/>
+      <c r="N10" s="66" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="64" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F11" s="65" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="G11" s="65" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="H11" s="65" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I11" s="65" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="J11" s="65" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="K11" s="65" t="s">
-        <v>502</v>
-      </c>
-      <c r="L11" s="65"/>
-      <c r="M11" s="68" t="s">
-        <v>503</v>
+        <v>509</v>
+      </c>
+      <c r="L11" s="65" t="s">
+        <v>510</v>
+      </c>
+      <c r="M11" s="65"/>
+      <c r="N11" s="68" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="69" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C12" s="73" t="n">
         <f aca="false">C9*C10/1000</f>
@@ -12191,50 +12657,57 @@
         <f aca="false">K9*K10/1000</f>
         <v>6.82</v>
       </c>
-      <c r="L12" s="73"/>
-      <c r="M12" s="66" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L12" s="73" t="n">
+        <f aca="false">L9*L10/1000</f>
+        <v>4.92</v>
+      </c>
+      <c r="M12" s="73"/>
+      <c r="N12" s="66" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="64" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D13" s="65" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F13" s="65" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="G13" s="65" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="H13" s="65" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="I13" s="65" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="J13" s="65" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="K13" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="L13" s="65"/>
-      <c r="M13" s="68" t="s">
-        <v>515</v>
+        <v>522</v>
+      </c>
+      <c r="L13" s="65" t="s">
+        <v>523</v>
+      </c>
+      <c r="M13" s="65"/>
+      <c r="N13" s="68" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="64" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C14" s="74" t="n">
         <v>6</v>
@@ -12263,50 +12736,56 @@
       <c r="K14" s="74" t="n">
         <v>7.5</v>
       </c>
-      <c r="L14" s="75"/>
-      <c r="M14" s="66" t="s">
-        <v>517</v>
+      <c r="L14" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="75"/>
+      <c r="N14" s="66" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="64" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F15" s="65" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="G15" s="65" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="I15" s="65" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="J15" s="65" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="K15" s="65" t="s">
-        <v>519</v>
-      </c>
-      <c r="L15" s="65"/>
-      <c r="M15" s="68" t="s">
-        <v>523</v>
+        <v>528</v>
+      </c>
+      <c r="L15" s="65" t="s">
+        <v>532</v>
+      </c>
+      <c r="M15" s="65"/>
+      <c r="N15" s="68" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="69" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C16" s="76" t="n">
         <f aca="false">IFERROR(C12/C14,0)</f>
@@ -12344,86 +12823,96 @@
         <f aca="false">IFERROR(K12/K14,0)</f>
         <v>0.909333333333333</v>
       </c>
-      <c r="L16" s="76"/>
-      <c r="M16" s="68" t="s">
-        <v>525</v>
+      <c r="L16" s="76" t="n">
+        <f aca="false">IFERROR(L12/L14,0)</f>
+        <v>0.984</v>
+      </c>
+      <c r="M16" s="76"/>
+      <c r="N16" s="68" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="64" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="G17" s="77" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="H17" s="77" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="I17" s="77" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="J17" s="77" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="K17" s="77" t="s">
-        <v>527</v>
-      </c>
-      <c r="L17" s="77"/>
-      <c r="M17" s="68" t="s">
-        <v>529</v>
+        <v>537</v>
+      </c>
+      <c r="L17" s="77" t="s">
+        <v>537</v>
+      </c>
+      <c r="M17" s="77"/>
+      <c r="N17" s="68" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="64" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="E18" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="G18" s="65" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="I18" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="J18" s="65" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="K18" s="65" t="s">
-        <v>533</v>
-      </c>
-      <c r="L18" s="65"/>
-      <c r="M18" s="68" t="s">
-        <v>535</v>
+        <v>543</v>
+      </c>
+      <c r="L18" s="65" t="s">
+        <v>542</v>
+      </c>
+      <c r="M18" s="65"/>
+      <c r="N18" s="68" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="64" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="C19" s="75" t="n">
         <f aca="false">C9*C10*0.00452</f>
@@ -12458,194 +12947,212 @@
       <c r="K19" s="75" t="n">
         <v>30.58</v>
       </c>
-      <c r="L19" s="75"/>
-      <c r="M19" s="66" t="s">
-        <v>537</v>
+      <c r="L19" s="75" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="M19" s="75"/>
+      <c r="N19" s="66" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="64" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="E20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="G20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="I20" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="J20" s="65" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K20" s="65" t="s">
-        <v>539</v>
-      </c>
-      <c r="L20" s="65"/>
-      <c r="M20" s="66" t="s">
-        <v>541</v>
+        <v>549</v>
+      </c>
+      <c r="L20" s="65" t="s">
+        <v>551</v>
+      </c>
+      <c r="M20" s="65"/>
+      <c r="N20" s="66" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="64" t="s">
+        <v>553</v>
+      </c>
+      <c r="C21" s="65" t="s">
         <v>542</v>
       </c>
-      <c r="C21" s="65" t="s">
-        <v>532</v>
-      </c>
       <c r="D21" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F21" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="G21" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="I21" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="J21" s="65" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="K21" s="65" t="s">
-        <v>543</v>
-      </c>
-      <c r="L21" s="65"/>
-      <c r="M21" s="66" t="s">
-        <v>545</v>
+        <v>554</v>
+      </c>
+      <c r="L21" s="65" t="s">
+        <v>556</v>
+      </c>
+      <c r="M21" s="65"/>
+      <c r="N21" s="66" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="64" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="E22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="G22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="I22" s="65" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="J22" s="65" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="K22" s="65" t="s">
-        <v>547</v>
-      </c>
-      <c r="L22" s="65"/>
-      <c r="M22" s="66" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>559</v>
+      </c>
+      <c r="L22" s="65" t="s">
+        <v>561</v>
+      </c>
+      <c r="M22" s="65"/>
+      <c r="N22" s="66" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="64" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="E23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="F23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="G23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="H23" s="67" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="I23" s="65" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="J23" s="65" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="K23" s="67" t="s">
-        <v>552</v>
-      </c>
-      <c r="L23" s="65"/>
-      <c r="M23" s="68" t="s">
-        <v>554</v>
+        <v>565</v>
+      </c>
+      <c r="L23" s="65" t="s">
+        <v>567</v>
+      </c>
+      <c r="M23" s="65"/>
+      <c r="N23" s="68" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="64" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="D24" s="65" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="E24" s="65" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="F24" s="65" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="G24" s="65" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="H24" s="65" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="I24" s="65" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="J24" s="65" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="K24" s="65" t="s">
-        <v>562</v>
-      </c>
-      <c r="L24" s="65"/>
-      <c r="M24" s="66" t="s">
-        <v>563</v>
+        <v>576</v>
+      </c>
+      <c r="L24" s="65" t="s">
+        <v>577</v>
+      </c>
+      <c r="M24" s="65"/>
+      <c r="N24" s="66" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -12658,10 +13165,11 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="64" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C26" s="78" t="n">
         <v>18228.7</v>
@@ -12690,14 +13198,17 @@
       <c r="K26" s="78" t="n">
         <v>16890</v>
       </c>
-      <c r="L26" s="79"/>
-      <c r="M26" s="66" t="s">
-        <v>566</v>
+      <c r="L26" s="78" t="n">
+        <v>17442</v>
+      </c>
+      <c r="M26" s="79"/>
+      <c r="N26" s="66" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="64" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C27" s="78" t="n">
         <v>0</v>
@@ -12726,14 +13237,17 @@
       <c r="K27" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="79"/>
-      <c r="M27" s="68" t="s">
-        <v>568</v>
+      <c r="L27" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="79"/>
+      <c r="N27" s="68" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="64" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C28" s="78" t="n">
         <v>790</v>
@@ -12762,14 +13276,17 @@
       <c r="K28" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="79"/>
-      <c r="M28" s="66" t="s">
-        <v>570</v>
+      <c r="L28" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="79"/>
+      <c r="N28" s="66" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="64" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="C29" s="79" t="n">
         <f aca="false">6900/10*C9</f>
@@ -12800,14 +13317,17 @@
       <c r="K29" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="79"/>
-      <c r="M29" s="68" t="s">
-        <v>572</v>
+      <c r="L29" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="79"/>
+      <c r="N29" s="68" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="64" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -12845,14 +13365,18 @@
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="L30" s="79"/>
-      <c r="M30" s="68" t="s">
-        <v>574</v>
+      <c r="L30" s="79" t="n">
+        <f aca="false">ENTRADAS!$C$28</f>
+        <v>2500</v>
+      </c>
+      <c r="M30" s="79"/>
+      <c r="N30" s="68" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="69" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="C31" s="80" t="n">
         <f aca="false">SUM(C26:C30)</f>
@@ -12890,14 +13414,18 @@
         <f aca="false">SUM(K26:K30)</f>
         <v>19390</v>
       </c>
-      <c r="L31" s="80"/>
-      <c r="M31" s="66" t="s">
-        <v>576</v>
+      <c r="L31" s="80" t="n">
+        <f aca="false">SUM(L26:L30)</f>
+        <v>19942</v>
+      </c>
+      <c r="M31" s="80"/>
+      <c r="N31" s="66" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="69" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="C32" s="81" t="n">
         <f aca="false">IFERROR(C31/(C12*1000),0)</f>
@@ -12935,14 +13463,18 @@
         <f aca="false">IFERROR(K31/(K12*1000),0)</f>
         <v>2.84310850439883</v>
       </c>
-      <c r="L32" s="81"/>
-      <c r="M32" s="66" t="s">
-        <v>578</v>
+      <c r="L32" s="81" t="n">
+        <f aca="false">IFERROR(L31/(L12*1000),0)</f>
+        <v>4.05325203252033</v>
+      </c>
+      <c r="M32" s="81"/>
+      <c r="N32" s="66" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="64" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="C33" s="82" t="n">
         <f aca="false">IFERROR(C26/(C12*1000),0)</f>
@@ -12953,35 +13485,38 @@
         <v>2.38400826446281</v>
       </c>
       <c r="E33" s="82" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="F33" s="82" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="G33" s="82" t="n">
         <f aca="false">IFERROR(G26/(G12*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
       <c r="H33" s="82" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="I33" s="82" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="J33" s="82" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="K33" s="82" t="s">
-        <v>580</v>
-      </c>
-      <c r="L33" s="82"/>
-      <c r="M33" s="66" t="s">
-        <v>581</v>
+        <v>595</v>
+      </c>
+      <c r="L33" s="82" t="s">
+        <v>595</v>
+      </c>
+      <c r="M33" s="82"/>
+      <c r="N33" s="66" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -12994,10 +13529,11 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="64" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">C12*GERACAO!$I$17</f>
@@ -13035,14 +13571,18 @@
         <f aca="false">K12*GERACAO!$I$17</f>
         <v>8622.3145459</v>
       </c>
-      <c r="L36" s="72"/>
-      <c r="M36" s="66" t="s">
-        <v>584</v>
+      <c r="L36" s="72" t="n">
+        <f aca="false">L12*GERACAO!$I$17</f>
+        <v>6220.2034554</v>
+      </c>
+      <c r="M36" s="72"/>
+      <c r="N36" s="66" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="64" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="C37" s="72" t="n">
         <f aca="false">C36/12</f>
@@ -13080,12 +13620,16 @@
         <f aca="false">K36/12</f>
         <v>718.526212158333</v>
       </c>
-      <c r="L37" s="72"/>
-      <c r="M37" s="66"/>
+      <c r="L37" s="72" t="n">
+        <f aca="false">L36/12</f>
+        <v>518.35028795</v>
+      </c>
+      <c r="M37" s="72"/>
+      <c r="N37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="64" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C38" s="72" t="n">
         <f aca="false">C36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -13123,14 +13667,18 @@
         <f aca="false">K36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
         <v>7858.3119912</v>
       </c>
-      <c r="L38" s="72"/>
-      <c r="M38" s="66" t="s">
-        <v>587</v>
+      <c r="L38" s="72" t="n">
+        <f aca="false">L36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>5669.0461872</v>
+      </c>
+      <c r="M38" s="72"/>
+      <c r="N38" s="66" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="64" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="C39" s="71" t="n">
         <v>10554</v>
@@ -13159,14 +13707,17 @@
       <c r="K39" s="71" t="n">
         <v>9279.13</v>
       </c>
-      <c r="L39" s="72"/>
-      <c r="M39" s="66" t="s">
-        <v>589</v>
+      <c r="L39" s="71" t="n">
+        <v>6385.01</v>
+      </c>
+      <c r="M39" s="72"/>
+      <c r="N39" s="66" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="69" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="C40" s="83" t="n">
         <f aca="false">IFERROR(C36/C39-1,0)</f>
@@ -13204,14 +13755,18 @@
         <f aca="false">IFERROR(K36/K39-1,0)</f>
         <v>-0.0707841633967838</v>
       </c>
-      <c r="L40" s="83"/>
-      <c r="M40" s="68" t="s">
-        <v>591</v>
+      <c r="L40" s="83" t="n">
+        <f aca="false">IFERROR(L36/L39-1,0)</f>
+        <v>-0.0258114779146783</v>
+      </c>
+      <c r="M40" s="83"/>
+      <c r="N40" s="68" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="64" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="C41" s="72" t="n">
         <f aca="false">C12*GERACAO!$J$17</f>
@@ -13249,14 +13804,18 @@
         <f aca="false">K12*GERACAO!$J$17</f>
         <v>9692.8192218</v>
       </c>
-      <c r="L41" s="72"/>
-      <c r="M41" s="66" t="s">
-        <v>593</v>
+      <c r="L41" s="72" t="n">
+        <f aca="false">L12*GERACAO!$J$17</f>
+        <v>6992.4736908</v>
+      </c>
+      <c r="M41" s="72"/>
+      <c r="N41" s="66" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -13269,10 +13828,11 @@
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="64" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="C44" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$33*12),0)</f>
@@ -13310,14 +13870,18 @@
         <f aca="false">IFERROR(K36/(BYD!$F$33*12),0)</f>
         <v>1.88424705985577</v>
       </c>
-      <c r="L44" s="84"/>
-      <c r="M44" s="66" t="s">
-        <v>596</v>
+      <c r="L44" s="84" t="n">
+        <f aca="false">IFERROR(L36/(BYD!$F$33*12),0)</f>
+        <v>1.35931019567308</v>
+      </c>
+      <c r="M44" s="84"/>
+      <c r="N44" s="66" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="64" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="C45" s="84" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$34*12),0)</f>
@@ -13355,12 +13919,16 @@
         <f aca="false">IFERROR(K36/(BYD!$F$34*12),0)</f>
         <v>1.22424293861508</v>
       </c>
-      <c r="L45" s="84"/>
-      <c r="M45" s="66"/>
+      <c r="L45" s="84" t="n">
+        <f aca="false">IFERROR(L36/(BYD!$F$34*12),0)</f>
+        <v>0.883178190320557</v>
+      </c>
+      <c r="M45" s="84"/>
+      <c r="N45" s="66"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="69" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="C46" s="85" t="n">
         <f aca="false">IFERROR(C36/(BYD!$F$35*12),0)</f>
@@ -13398,14 +13966,18 @@
         <f aca="false">IFERROR(K36/(BYD!$F$35*12),0)</f>
         <v>1.06455907705659</v>
       </c>
-      <c r="L46" s="85"/>
-      <c r="M46" s="66" t="s">
-        <v>599</v>
+      <c r="L46" s="85" t="n">
+        <f aca="false">IFERROR(L36/(BYD!$F$35*12),0)</f>
+        <v>0.767981035061354</v>
+      </c>
+      <c r="M46" s="85"/>
+      <c r="N46" s="66" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="64" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="C47" s="72" t="n">
         <f aca="false">C36-BYD!$G$35</f>
@@ -13443,14 +14015,18 @@
         <f aca="false">K36-BYD!$G$35</f>
         <v>522.891290086047</v>
       </c>
-      <c r="L47" s="72"/>
-      <c r="M47" s="66" t="s">
-        <v>601</v>
+      <c r="L47" s="72" t="n">
+        <f aca="false">L36-BYD!$G$35</f>
+        <v>-1879.21980041395</v>
+      </c>
+      <c r="M47" s="72"/>
+      <c r="N47" s="66" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="69" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="C48" s="86" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C36)/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -13488,12 +14064,16 @@
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-K36)/GERACAO!$I$17*1000/K10,0),0)</f>
         <v>0</v>
       </c>
-      <c r="L48" s="86"/>
-      <c r="M48" s="66"/>
+      <c r="L48" s="86" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-L36)/GERACAO!$I$17*1000/L10,0),0)</f>
+        <v>3</v>
+      </c>
+      <c r="M48" s="86"/>
+      <c r="N48" s="66"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="69" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="C49" s="87" t="n">
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C10,0),0)</f>
@@ -13531,14 +14111,18 @@
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/K10,0),0)</f>
         <v>4</v>
       </c>
-      <c r="L49" s="87"/>
-      <c r="M49" s="66" t="s">
-        <v>604</v>
+      <c r="L49" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/L10,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="M49" s="87"/>
+      <c r="N49" s="66" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="64" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="C50" s="65" t="str">
         <f aca="false">C14&amp;" kW = "&amp;TEXT(C14*1000/220,"0")&amp;" A"</f>
@@ -13576,14 +14160,18 @@
         <f aca="false">K14&amp;" kW = "&amp;TEXT(K14*1000/220,"0")&amp;" A"</f>
         <v>7.5 kW = 34 A</v>
       </c>
-      <c r="L50" s="65"/>
-      <c r="M50" s="68" t="s">
-        <v>606</v>
+      <c r="L50" s="65" t="str">
+        <f aca="false">L14&amp;" kW = "&amp;TEXT(L14*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="M50" s="65"/>
+      <c r="N50" s="68" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -13596,10 +14184,11 @@
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="64" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="C52" s="79" t="n">
         <f aca="false">CONTA!$C$54</f>
@@ -13637,14 +14226,18 @@
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="L52" s="79"/>
-      <c r="M52" s="66" t="s">
-        <v>609</v>
+      <c r="L52" s="79" t="n">
+        <f aca="false">CONTA!$C$54</f>
+        <v>410.62787654321</v>
+      </c>
+      <c r="M52" s="79"/>
+      <c r="N52" s="66" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="64" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="C53" s="79" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
@@ -13682,14 +14275,18 @@
         <f aca="false">ECONOMIA!K8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="L53" s="79"/>
-      <c r="M53" s="66" t="s">
-        <v>611</v>
+      <c r="L53" s="79" t="n">
+        <f aca="false">ECONOMIA!L8/12</f>
+        <v>710.553156093023</v>
+      </c>
+      <c r="M53" s="79"/>
+      <c r="N53" s="66" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="69" t="s">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="C54" s="88" t="n">
         <f aca="false">ECONOMIA!C19</f>
@@ -13727,14 +14324,18 @@
         <f aca="false">ECONOMIA!K19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="L54" s="88"/>
-      <c r="M54" s="68" t="s">
-        <v>613</v>
+      <c r="L54" s="88" t="n">
+        <f aca="false">ECONOMIA!L19</f>
+        <v>258.982122345726</v>
+      </c>
+      <c r="M54" s="88"/>
+      <c r="N54" s="68" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="64" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="C55" s="79" t="n">
         <f aca="false">ECONOMIA!C26</f>
@@ -13772,12 +14373,16 @@
         <f aca="false">ECONOMIA!K26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="L55" s="79"/>
-      <c r="M55" s="66"/>
+      <c r="L55" s="79" t="n">
+        <f aca="false">ECONOMIA!L26</f>
+        <v>4968.85240496757</v>
+      </c>
+      <c r="M55" s="79"/>
+      <c r="N55" s="66"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="69" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="C56" s="88" t="n">
         <f aca="false">C55/12</f>
@@ -13815,12 +14420,16 @@
         <f aca="false">K55/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="L56" s="88"/>
-      <c r="M56" s="66"/>
+      <c r="L56" s="88" t="n">
+        <f aca="false">L55/12</f>
+        <v>414.071033747298</v>
+      </c>
+      <c r="M56" s="88"/>
+      <c r="N56" s="66"/>
     </row>
     <row r="57" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="69" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="C57" s="89" t="n">
         <f aca="false">IFERROR(C31/C55,0)</f>
@@ -13858,14 +14467,18 @@
         <f aca="false">IFERROR(K31/K55,0)</f>
         <v>3.16730775334533</v>
       </c>
-      <c r="L57" s="89"/>
-      <c r="M57" s="66" t="s">
-        <v>617</v>
+      <c r="L57" s="89" t="n">
+        <f aca="false">IFERROR(L31/L55,0)</f>
+        <v>4.01340156130682</v>
+      </c>
+      <c r="M57" s="89"/>
+      <c r="N57" s="66" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="64" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="C58" s="90" t="n">
         <f aca="false">PROJECAO!E10</f>
@@ -13903,12 +14516,16 @@
         <f aca="false">PROJECAO!AC10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="L58" s="90"/>
-      <c r="M58" s="66"/>
+      <c r="L58" s="90" t="n">
+        <f aca="false">PROJECAO!AF10</f>
+        <v>28301.310178054</v>
+      </c>
+      <c r="M58" s="90"/>
+      <c r="N58" s="66"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="64" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="C59" s="90" t="n">
         <f aca="false">PROJECAO!E15</f>
@@ -13946,12 +14563,16 @@
         <f aca="false">PROJECAO!AC15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="L59" s="90"/>
-      <c r="M59" s="66"/>
+      <c r="L59" s="90" t="n">
+        <f aca="false">PROJECAO!AF15</f>
+        <v>67110.2475445575</v>
+      </c>
+      <c r="M59" s="90"/>
+      <c r="N59" s="66"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="64" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="C60" s="90" t="n">
         <f aca="false">PROJECAO!E25</f>
@@ -13989,12 +14610,16 @@
         <f aca="false">PROJECAO!AC25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="L60" s="90"/>
-      <c r="M60" s="66"/>
+      <c r="L60" s="90" t="n">
+        <f aca="false">PROJECAO!AF25</f>
+        <v>193304.408740621</v>
+      </c>
+      <c r="M60" s="90"/>
+      <c r="N60" s="66"/>
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="69" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="C61" s="91" t="n">
         <f aca="false">C60-C31</f>
@@ -14032,14 +14657,18 @@
         <f aca="false">K60-K31</f>
         <v>218772.405280052</v>
       </c>
-      <c r="L61" s="91"/>
-      <c r="M61" s="66" t="s">
-        <v>622</v>
+      <c r="L61" s="91" t="n">
+        <f aca="false">L60-L31</f>
+        <v>173362.408740621</v>
+      </c>
+      <c r="M61" s="91"/>
+      <c r="N61" s="66" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="64" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="C62" s="84" t="n">
         <f aca="false">IFERROR(C61/C31,0)</f>
@@ -14077,12 +14706,16 @@
         <f aca="false">IFERROR(K61/K31,0)</f>
         <v>11.2827439546185</v>
       </c>
-      <c r="L62" s="84"/>
-      <c r="M62" s="66"/>
+      <c r="L62" s="84" t="n">
+        <f aca="false">IFERROR(L61/L31,0)</f>
+        <v>8.69333109721298</v>
+      </c>
+      <c r="M62" s="84"/>
+      <c r="N62" s="66"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="7" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -14095,10 +14728,11 @@
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="64" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="C65" s="75" t="n">
         <f aca="false">C14*1.35</f>
@@ -14136,12 +14770,16 @@
         <f aca="false">K14*1.35</f>
         <v>10.125</v>
       </c>
-      <c r="L65" s="75"/>
-      <c r="M65" s="66"/>
+      <c r="L65" s="75" t="n">
+        <f aca="false">L14*1.35</f>
+        <v>6.75</v>
+      </c>
+      <c r="M65" s="75"/>
+      <c r="N65" s="66"/>
     </row>
     <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="69" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="C66" s="86" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((C65-C12)*1000/C10,0))</f>
@@ -14179,14 +14817,18 @@
         <f aca="false">MAX(0,ROUNDDOWN((K65-K12)*1000/K10,0))</f>
         <v>5</v>
       </c>
-      <c r="L66" s="86"/>
-      <c r="M66" s="68" t="s">
-        <v>627</v>
+      <c r="L66" s="86" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((L65-L12)*1000/L10,0))</f>
+        <v>2</v>
+      </c>
+      <c r="M66" s="86"/>
+      <c r="N66" s="68" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="64" t="s">
-        <v>628</v>
+        <v>643</v>
       </c>
       <c r="C67" s="72" t="n">
         <f aca="false">C66*C10/1000*GERACAO!$I$17</f>
@@ -14224,12 +14866,16 @@
         <f aca="false">K66*K10/1000*GERACAO!$I$17</f>
         <v>3919.2338845</v>
       </c>
-      <c r="L67" s="72"/>
-      <c r="M67" s="66"/>
+      <c r="L67" s="72" t="n">
+        <f aca="false">L66*L10/1000*GERACAO!$I$17</f>
+        <v>1555.05086385</v>
+      </c>
+      <c r="M67" s="72"/>
+      <c r="N67" s="66"/>
     </row>
     <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="69" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="C68" s="92" t="str">
         <f aca="false">IF(C16&gt;1.35,"JA SOBRECARREGADO",IF(C16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
@@ -14267,14 +14913,18 @@
         <f aca="false">IF(K16&gt;1.35,"JA SOBRECARREGADO",IF(K16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="L68" s="92"/>
-      <c r="M68" s="66" t="s">
-        <v>630</v>
+      <c r="L68" s="92" t="str">
+        <f aca="false">IF(L16&gt;1.35,"JA SOBRECARREGADO",IF(L16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+        <v>SUBAPROVEITADO</v>
+      </c>
+      <c r="M68" s="92"/>
+      <c r="N68" s="66" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="7" t="s">
-        <v>631</v>
+        <v>646</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -14287,10 +14937,11 @@
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
       <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="21" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="C71" s="35" t="n">
         <f aca="false">F26-E26</f>
@@ -14299,7 +14950,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="C72" s="29" t="n">
         <f aca="false">IFERROR(F57-E57,0)</f>
@@ -14308,7 +14959,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="C73" s="93" t="n">
         <f aca="false">F61-E61</f>
@@ -14317,22 +14968,22 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="5" t="s">
-        <v>635</v>
+        <v>650</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14340,17 +14991,17 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="5" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -14380,325 +15031,325 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="F5" s="94" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="F8" s="94" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="F10" s="94" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>682</v>
+        <v>697</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>683</v>
+        <v>698</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="F13" s="95" t="s">
-        <v>687</v>
+        <v>702</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="F14" s="94" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>694</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D17" s="96" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>701</v>
+        <v>716</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="F20" s="94" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -14712,7 +15363,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -14726,7 +15377,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -14740,7 +15391,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -14754,7 +15405,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="C28" s="47" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -14771,7 +15422,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="C30" s="44" t="str">
         <f aca="false">COMPARATIVO!C11</f>
@@ -14788,7 +15439,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="C31" s="97" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
@@ -14805,44 +15456,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="C34" s="98" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -14851,7 +15502,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">COMPARATIVO!C28-COMPARATIVO!D28</f>
@@ -14860,7 +15511,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
@@ -14869,14 +15520,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="C41" s="99" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -14895,66 +15546,69 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>752</v>
+        <v>767</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -14992,14 +15646,18 @@
         <f aca="false">BYD!$G$35</f>
         <v>8099.42325581395</v>
       </c>
-      <c r="L5" s="100"/>
-      <c r="M5" s="66" t="s">
-        <v>754</v>
+      <c r="L5" s="36" t="n">
+        <f aca="false">BYD!$G$35</f>
+        <v>8099.42325581395</v>
+      </c>
+      <c r="M5" s="100"/>
+      <c r="N5" s="66" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COMPARATIVO!C36</f>
@@ -15037,14 +15695,18 @@
         <f aca="false">COMPARATIVO!K36</f>
         <v>8622.3145459</v>
       </c>
-      <c r="L6" s="100"/>
-      <c r="M6" s="66" t="s">
-        <v>756</v>
+      <c r="L6" s="36" t="n">
+        <f aca="false">COMPARATIVO!L36</f>
+        <v>6220.2034554</v>
+      </c>
+      <c r="M6" s="100"/>
+      <c r="N6" s="66" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="C7" s="101" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -15082,14 +15744,18 @@
         <f aca="false">ENTRADAS!$C$18</f>
         <v>1.02147</v>
       </c>
-      <c r="L7" s="100"/>
-      <c r="M7" s="66" t="s">
-        <v>758</v>
+      <c r="L7" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$18</f>
+        <v>1.02147</v>
+      </c>
+      <c r="M7" s="100"/>
+      <c r="N7" s="66" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="C8" s="102" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -15127,14 +15793,18 @@
         <f aca="false">K5*K7+ENTRADAS!$C$26*12</f>
         <v>8526.63787311628</v>
       </c>
-      <c r="L8" s="100"/>
-      <c r="M8" s="66" t="s">
-        <v>760</v>
+      <c r="L8" s="102" t="n">
+        <f aca="false">L5*L7+ENTRADAS!$C$26*12</f>
+        <v>8526.63787311628</v>
+      </c>
+      <c r="M8" s="100"/>
+      <c r="N8" s="66" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -15172,14 +15842,18 @@
         <f aca="false">MIN(K5,K6)*ENTRADAS!$C$37</f>
         <v>2429.82697674419</v>
       </c>
-      <c r="L9" s="100"/>
-      <c r="M9" s="66" t="s">
-        <v>762</v>
+      <c r="L9" s="36" t="n">
+        <f aca="false">MIN(L5,L6)*ENTRADAS!$C$37</f>
+        <v>1866.06103662</v>
+      </c>
+      <c r="M9" s="100"/>
+      <c r="N9" s="66" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">C6-C9</f>
@@ -15217,14 +15891,18 @@
         <f aca="false">K6-K9</f>
         <v>6192.48756915581</v>
       </c>
-      <c r="L10" s="100"/>
-      <c r="M10" s="66" t="s">
-        <v>764</v>
+      <c r="L10" s="36" t="n">
+        <f aca="false">L6-L9</f>
+        <v>4354.14241878</v>
+      </c>
+      <c r="M10" s="100"/>
+      <c r="N10" s="66" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -15262,14 +15940,18 @@
         <f aca="false">ENTRADAS!$C$17*12</f>
         <v>600</v>
       </c>
-      <c r="L11" s="100"/>
-      <c r="M11" s="66" t="s">
-        <v>766</v>
+      <c r="L11" s="36" t="n">
+        <f aca="false">ENTRADAS!$C$17*12</f>
+        <v>600</v>
+      </c>
+      <c r="M11" s="100"/>
+      <c r="N11" s="66" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -15307,14 +15989,18 @@
         <f aca="false">MAX(0,MIN(K10,K5-K9-K11))</f>
         <v>5069.59627906977</v>
       </c>
-      <c r="L12" s="100"/>
-      <c r="M12" s="66" t="s">
-        <v>768</v>
+      <c r="L12" s="36" t="n">
+        <f aca="false">MAX(0,MIN(L10,L5-L9-L11))</f>
+        <v>4354.14241878</v>
+      </c>
+      <c r="M12" s="100"/>
+      <c r="N12" s="66" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">C10-C12</f>
@@ -15352,14 +16038,18 @@
         <f aca="false">K10-K12</f>
         <v>1122.89129008605</v>
       </c>
-      <c r="L13" s="100"/>
-      <c r="M13" s="66" t="s">
-        <v>770</v>
+      <c r="L13" s="36" t="n">
+        <f aca="false">L10-L12</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="100"/>
+      <c r="N13" s="66" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -15397,14 +16087,18 @@
         <f aca="false">MAX(K11,K5-K9-K12)</f>
         <v>600</v>
       </c>
-      <c r="L14" s="100"/>
-      <c r="M14" s="66" t="s">
-        <v>772</v>
+      <c r="L14" s="36" t="n">
+        <f aca="false">MAX(L11,L5-L9-L12)</f>
+        <v>1879.21980041395</v>
+      </c>
+      <c r="M14" s="100"/>
+      <c r="N14" s="66" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="C15" s="101" t="n">
         <f aca="false">C14*C7</f>
@@ -15442,12 +16136,16 @@
         <f aca="false">K14*K7</f>
         <v>612.882</v>
       </c>
-      <c r="L15" s="100"/>
-      <c r="M15" s="66"/>
+      <c r="L15" s="101" t="n">
+        <f aca="false">L14*L7</f>
+        <v>1919.56664952884</v>
+      </c>
+      <c r="M15" s="100"/>
+      <c r="N15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="C16" s="101" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -15485,14 +16183,18 @@
         <f aca="false">K12*ENTRADAS!$C$25</f>
         <v>1088.51735114121</v>
       </c>
-      <c r="L16" s="100"/>
-      <c r="M16" s="66" t="s">
-        <v>775</v>
+      <c r="L16" s="101" t="n">
+        <f aca="false">L12*ENTRADAS!$C$25</f>
+        <v>934.898818619864</v>
+      </c>
+      <c r="M16" s="100"/>
+      <c r="N16" s="66" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="C17" s="101" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -15530,14 +16232,18 @@
         <f aca="false">ENTRADAS!$C$26*12</f>
         <v>253.32</v>
       </c>
-      <c r="L17" s="100"/>
-      <c r="M17" s="66" t="s">
-        <v>777</v>
+      <c r="L17" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$26*12</f>
+        <v>253.32</v>
+      </c>
+      <c r="M17" s="100"/>
+      <c r="N17" s="66" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -15575,14 +16281,18 @@
         <f aca="false">K15+K16+K17</f>
         <v>1954.71935114121</v>
       </c>
-      <c r="L18" s="100"/>
-      <c r="M18" s="66" t="s">
-        <v>779</v>
+      <c r="L18" s="47" t="n">
+        <f aca="false">L15+L16+L17</f>
+        <v>3107.78546814871</v>
+      </c>
+      <c r="M18" s="100"/>
+      <c r="N18" s="66" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">C18/12</f>
@@ -15620,14 +16330,18 @@
         <f aca="false">K18/12</f>
         <v>162.893279261767</v>
       </c>
-      <c r="L19" s="100"/>
-      <c r="M19" s="66" t="s">
-        <v>781</v>
+      <c r="L19" s="47" t="n">
+        <f aca="false">L18/12</f>
+        <v>258.982122345726</v>
+      </c>
+      <c r="M19" s="100"/>
+      <c r="N19" s="66" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
       <c r="C20" s="37" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -15665,12 +16379,16 @@
         <f aca="false">IFERROR(1-K18/K8,0)</f>
         <v>0.770751452069489</v>
       </c>
-      <c r="L20" s="100"/>
-      <c r="M20" s="66"/>
+      <c r="L20" s="37" t="n">
+        <f aca="false">IFERROR(1-L18/L8,0)</f>
+        <v>0.635520410929228</v>
+      </c>
+      <c r="M20" s="100"/>
+      <c r="N20" s="66"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="C21" s="101" t="n">
         <f aca="false">C8-C18</f>
@@ -15708,12 +16426,16 @@
         <f aca="false">K8-K18</f>
         <v>6571.91852197507</v>
       </c>
-      <c r="L21" s="100"/>
-      <c r="M21" s="66"/>
+      <c r="L21" s="101" t="n">
+        <f aca="false">L8-L18</f>
+        <v>5418.85240496757</v>
+      </c>
+      <c r="M21" s="100"/>
+      <c r="N21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="C22" s="101" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -15751,14 +16473,18 @@
         <f aca="false">ENTRADAS!$C$35</f>
         <v>300</v>
       </c>
-      <c r="L22" s="100"/>
-      <c r="M22" s="66" t="s">
-        <v>785</v>
+      <c r="L22" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$35</f>
+        <v>300</v>
+      </c>
+      <c r="M22" s="100"/>
+      <c r="N22" s="66" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="C23" s="101" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -15796,14 +16522,18 @@
         <f aca="false">ENTRADAS!$C$36</f>
         <v>150</v>
       </c>
-      <c r="L23" s="100"/>
-      <c r="M23" s="66" t="s">
-        <v>787</v>
+      <c r="L23" s="101" t="n">
+        <f aca="false">ENTRADAS!$C$36</f>
+        <v>150</v>
+      </c>
+      <c r="M23" s="100"/>
+      <c r="N23" s="66" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="C24" s="101" t="n">
         <f aca="false">0</f>
@@ -15841,14 +16571,18 @@
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L24" s="100"/>
-      <c r="M24" s="66" t="s">
-        <v>789</v>
+      <c r="L24" s="101" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="100"/>
+      <c r="N24" s="66" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="C25" s="101" t="n">
         <f aca="false">C22+C23</f>
@@ -15886,12 +16620,16 @@
         <f aca="false">K22+K23</f>
         <v>450</v>
       </c>
-      <c r="L25" s="100"/>
-      <c r="M25" s="66"/>
+      <c r="L25" s="101" t="n">
+        <f aca="false">L22+L23</f>
+        <v>450</v>
+      </c>
+      <c r="M25" s="100"/>
+      <c r="N25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="C26" s="103" t="n">
         <f aca="false">C21-C25</f>
@@ -15929,14 +16667,18 @@
         <f aca="false">K21-K25</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="L26" s="100"/>
-      <c r="M26" s="66" t="s">
-        <v>792</v>
+      <c r="L26" s="103" t="n">
+        <f aca="false">L21-L25</f>
+        <v>4968.85240496757</v>
+      </c>
+      <c r="M26" s="100"/>
+      <c r="N26" s="66" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -15949,125 +16691,126 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4576</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>795</v>
+      <c r="N29" s="2" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>7042.97674418605</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>797</v>
+      <c r="N30" s="2" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>798</v>
+        <v>814</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
         <v>2466.97674418605</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>799</v>
+      <c r="N31" s="2" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.539112050739958</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>801</v>
+      <c r="N32" s="2" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4927.56672</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>803</v>
+      <c r="N33" s="2" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7447.50945488372</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>805</v>
+      <c r="N34" s="2" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2519.94273488372</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>807</v>
+      <c r="N35" s="2" t="s">
+        <v>823</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>529.696418232558</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>809</v>
+      <c r="N36" s="2" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>1990.24631665116</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>811</v>
+      <c r="N37" s="2" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>812</v>
+        <v>828</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>813</v>
+      <c r="N38" s="2" t="s">
+        <v>829</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="1051">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -1384,7 +1384,7 @@
     <t xml:space="preserve">COMPARATIVO DOS ORCAMENTOS - QUADRO PRINCIPAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Colunas A e B: TecSolarSP, preco de MATERIAL. Colunas C a F: preco INSTALADO. Coluna G reservada. A linha 31 e a unica comparavel entre todos.</t>
+    <t xml:space="preserve">Contatos nas linhas 5 a 7. Colunas A e B: TecSolarSP, preco de MATERIAL. As demais: preco INSTALADO. A linha do PRECO TOTAL INSTALADO e a unica comparavel entre todos.</t>
   </si>
   <si>
     <t xml:space="preserve">ITEM</t>
@@ -1448,31 +1448,85 @@
     <t xml:space="preserve">OBSERVACOES / ALERTAS</t>
   </si>
   <si>
-    <t xml:space="preserve">Fornecedor / contato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TecSolarSP (11) 97365-9192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SunWash - Yuri (16) 99353-4346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William (11) 99636-5333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun Coast - Alexandre (11) 91544-8947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sfero - indic. Renato (11) 99705-1311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD BioSolar - Adriano Melo (11) 97350-3103 / (11) 91408-8892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruno G4 (11) 96861-7830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seis orcamentos de cinco empresas diferentes. O Bruno G4 ainda nao enviou nada.</t>
+    <t xml:space="preserve">EMPRESA / razao social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TecSolarSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SunWash Energia Solar e Ar-Condicionado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nao informada na proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun Coast Materiais Eletricos e Energia Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sfero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD BioSolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G4 (razao social a confirmar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALERTA: SunWash, William e Sfero nao informaram razao social. Sem empresa identificada nao existe garantia exigivel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME DO RESPONSAVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nao informado (razao social: Edijane Gomes dos Santos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nao informado (indicacao do Renato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriano Melo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem falou com voce. Peca sempre que a proposta saia com nome e CNPJ da empresa, nao apenas o contato pessoal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELEFONE DE CONTATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 97365-9192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16) 99353-4346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 99636-5333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 91544-8947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 99705-1311 (Renato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 97350-3103 / (11) 91408-8892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 96861-7830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sfero chegou por indicacao do Renato - o telefone e dele, nao da empresa. Pedir o contato direto da Sfero.</t>
   </si>
   <si>
     <t xml:space="preserve">CNPJ informado na proposta</t>
@@ -1493,7 +1547,7 @@
     <t xml:space="preserve">64.313.573/0001-58</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: SunWash e William nao informaram CNPJ. Sem CNPJ nao existe garantia exigivel. Sun Coast e a unica que trouxe CNPJ na propria proposta.</t>
+    <t xml:space="preserve">ALERTA: so Sun Coast, AD BioSolar e TecSolarSP (via cotacao do distribuidor) tem CNPJ identificado.</t>
   </si>
   <si>
     <t xml:space="preserve">Documento recebido</t>
@@ -1529,7 +1583,7 @@
     <t xml:space="preserve">Nada recebido</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: orcamento por WhatsApp nao e proposta comercial. So Sun Coast e William entregaram documento formal.</t>
+    <t xml:space="preserve">ALERTA: orcamento por WhatsApp nao e proposta comercial. Sfero, Sun Coast, AD BioSolar e William entregaram documento formal.</t>
   </si>
   <si>
     <t xml:space="preserve">TIPO DE PRECO</t>
@@ -1544,7 +1598,7 @@
     <t xml:space="preserve">?</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: comparar MATERIAL com INSTALADO e o erro mais comum. As linhas 28 a 30 corrigem isso.</t>
+    <t xml:space="preserve">ALERTA: comparar MATERIAL com INSTALADO e o erro mais comum. As linhas de homologacao e instalacao corrigem isso.</t>
   </si>
   <si>
     <t xml:space="preserve">Quantidade de modulos</t>
@@ -1556,7 +1610,7 @@
     <t xml:space="preserve">Potencia por modulo (W)</t>
   </si>
   <si>
-    <t xml:space="preserve">A SunWash escreveu '620kw', erro de digitacao para 620 W.</t>
+    <t xml:space="preserve">A SunWash escreveu '620kw' e '650w' - erro de digitacao para watts.</t>
   </si>
   <si>
     <t xml:space="preserve">Fabricante / tecnologia do modulo</t>
@@ -1589,13 +1643,13 @@
     <t xml:space="preserve">JA Solar bifacial N-type 132 cel - TIER 1</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA sao marcas com pouquissima rede de assistencia de modulo no Brasil - exigir INMETRO e quem honra a garantia aqui.</t>
+    <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA tem pouquissima rede de assistencia no Brasil. JA Solar, Longi e DAH sao Tier 1 com representacao aqui.</t>
   </si>
   <si>
     <t xml:space="preserve">POTENCIA DC (kWp)</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantidade x potencia / 1000.</t>
+    <t xml:space="preserve">Quantidade x potencia do modulo / 1000.</t>
   </si>
   <si>
     <t xml:space="preserve">Inversor</t>
@@ -1628,13 +1682,13 @@
     <t xml:space="preserve">HUAWEI SUN2000-5KTL-L1 5.000 W (modelo EXATO informado)</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: AUXSOL tem baixa penetracao no Brasil. Huawei e Solis tem assistencia estabelecida.</t>
+    <t xml:space="preserve">ALERTA: AUXSOL tem baixa penetracao no Brasil. Huawei, Solis e Growatt tem assistencia estabelecida. So a AD BioSolar informou o MODELO EXATO.</t>
   </si>
   <si>
     <t xml:space="preserve">Potencia AC do inversor (kW)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exigir o codigo exato do modelo e a confirmacao de que e 220 V.</t>
+    <t xml:space="preserve">Exigir o codigo exato do modelo, como fez a AD BioSolar (SUN2000-5KTL-L1).</t>
   </si>
   <si>
     <t xml:space="preserve">Numero de MPPTs</t>
@@ -1655,13 +1709,13 @@
     <t xml:space="preserve">2 (a confirmar)</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: Sun Coast usa 1 MPPT UNICO - os 8 modulos numa string so, exigindo mesma agua e mesma inclinacao, e sombra em 1 modulo derruba tudo. NO OUTRO EXTREMO, a opcao G com microinversor da 1 MPPT POR MODULO: sombra em um modulo nao afeta os outros e da liberdade de usar mais de uma agua do telhado.</t>
+    <t xml:space="preserve">ALERTA: Sun Coast v1 usava 1 MPPT UNICO para 8 modulos. As opcoes com microinversor dao 1 MPPT POR MODULO: sombra em um modulo nao afeta os outros e permite usar mais de uma agua do telhado.</t>
   </si>
   <si>
     <t xml:space="preserve">RELACAO DC/AC</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: faixa saudavel de 1,10 a 1,35. Sun Coast em 1,56 = acima do limite, com clipping e risco de perder a garantia. William em 1,34, no limite. Opcao G em 0,72 = o oposto: 4 microinversores de 2,25 kW dao 9 kW AC para so 6,5 kWp. PERGUNTAR ao Yuri quantos modulos cada micro aceita - se sao 4, existem 6 canais livres para expansao futura; se nao, voce esta pagando por um micro a mais.</t>
+    <t xml:space="preserve">ALERTA: faixa saudavel de 1,10 a 1,35. Sun Coast v1 em 1,56 = clipping e risco de perder garantia. Abaixo de 1,10 voce pagou por inversor que nao vai usar - aceitavel se for folga proposital para expansao.</t>
   </si>
   <si>
     <t xml:space="preserve">Tensao de operacao</t>
@@ -1691,13 +1745,13 @@
     <t xml:space="preserve">Ceramico / colonial</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: William e Sun Coast dizem COLONIAL, TecSolarSP diz FIBROCIMENTO. Dois contra um: provavelmente a TecSolarSP errou a estrutura inteira. RESOLVER isso antes de qualquer compra.</t>
+    <t xml:space="preserve">ALERTA: William, Sun Coast e Sfero dizem CERAMICA/COLONIAL; a TecSolarSP diz FIBROCIMENTO. Tres contra um. Se for ceramica, a estrutura das duas cotacoes da TecSolarSP esta errada. Uma foto resolve.</t>
   </si>
   <si>
     <t xml:space="preserve">Area de telhado necessaria (m2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Valores em azul foram DECLARADOS pelo fornecedor; os demais sao estimados a 0,00452 m2 por watt (calibrado pelas areas declaradas). Sem fotos do telhado NAO foi verificado se essa area existe na agua Sudeste.</t>
+    <t xml:space="preserve">Valores em azul foram DECLARADOS pelo fornecedor; os demais estimados a 0,00452 m2 por watt. Sem fotos do telhado NAO foi verificado se essa area existe na agua Sudeste.</t>
   </si>
   <si>
     <t xml:space="preserve">Garantia declarada do modulo</t>
@@ -1712,7 +1766,7 @@
     <t xml:space="preserve">15 anos defeito / 30 anos eficiencia</t>
   </si>
   <si>
-    <t xml:space="preserve">So a Sun Coast declarou garantias na proposta. Dos outros, exigir por escrito.</t>
+    <t xml:space="preserve">AD BioSolar tem a melhor: 30 anos de eficiencia e 15 de defeito. TecSolarSP, SunWash e William nao declararam nada.</t>
   </si>
   <si>
     <t xml:space="preserve">Garantia declarada do inversor</t>
@@ -1727,10 +1781,10 @@
     <t xml:space="preserve">10 anos</t>
   </si>
   <si>
-    <t xml:space="preserve">'10 a 25 anos' da Sun Coast e vago: exigir o numero exato para o modelo cotado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantia declarada do servico</t>
+    <t xml:space="preserve">AD BioSolar declara 10 anos para um modelo Huawei nomeado - e a unica verificavel. '10 a 25 anos' da Sun Coast e vago.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantia de servico / seguro</t>
   </si>
   <si>
     <t xml:space="preserve">12 meses</t>
@@ -1742,7 +1796,7 @@
     <t xml:space="preserve">vistoria tecnica, ART, licencas, gestao de obra e frete inclusos</t>
   </si>
   <si>
-    <t xml:space="preserve">12 meses de servico e o minimo de mercado.</t>
+    <t xml:space="preserve">So a Sfero oferece seguro All Risk e garantia de performance em contrato. Isso vale dinheiro em risco.</t>
   </si>
   <si>
     <t xml:space="preserve">Exclusoes declaradas na proposta</t>
@@ -1760,7 +1814,7 @@
     <t xml:space="preserve">alvenaria, reforco estrutural e alteracoes na rede pedidas pela concessionaria</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: a Sun Coast exclui EXPLICITAMENTE a adequacao do padrao de entrada, obras no telhado, eletrodutos e o ART estrutural. E honesto ao declarar, mas o custo e seu. Os outros nao declararam exclusoes - o que nao significa que estejam inclusas.</t>
+    <t xml:space="preserve">ALERTA: Sun Coast, Sfero e AD BioSolar excluem por escrito a adequacao do padrao. E honesto declarar, mas o custo e seu. Quem nao declarou exclusao tambem nao incluiu - so nao avisou.</t>
   </si>
   <si>
     <t xml:space="preserve">Condicao de pagamento declarada</t>
@@ -1790,7 +1844,7 @@
     <t xml:space="preserve">a vista ou financiamento em ate 60x</t>
   </si>
   <si>
-    <t xml:space="preserve">ATENCAO: 18x SEM JUROS pelo mesmo valor a vista e uma vantagem financeira REAL - equivale a um desconto, porque o dinheiro fica rendendo na sua mao. Todas as outras oferecem parcelamento COM juros.</t>
+    <t xml:space="preserve">ATENCAO: 18x SEM JUROS pelo valor a vista (SunWash micro) e vantagem real. Ja o financiamento Sfero em 72x custa cerca de R$ 17,8 mil de juros sobre R$ 18,7 mil - quase dobra o preco.</t>
   </si>
   <si>
     <t xml:space="preserve">PRECOS</t>
@@ -1799,19 +1853,19 @@
     <t xml:space="preserve">Preco BASE informado (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">A, B e E: valor do KIT/material (cotacoes Belenergy). C, D e F: projeto completo, ja com instalacao - por isso as linhas 28 e 29 ficam zeradas nelas.</t>
+    <t xml:space="preserve">A, B e E: valor do KIT/material. As demais: projeto completo, ja com instalacao - por isso as linhas de homologacao e instalacao ficam zeradas nelas.</t>
   </si>
   <si>
     <t xml:space="preserve">Acrescimo regional a confirmar (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: a SunWash citou +R$ 1.800 pela sua regiao no kit Intelbras e nao repetiu no orcamento TCL. Mantido por PRUDENCIA. Se nao incidir, zere e o payback melhora.</t>
+    <t xml:space="preserve">ALERTA: a SunWash citou +R$ 1.800 pela sua regiao no kit Intelbras e nao repetiu nos demais. Mantido por PRUDENCIA. Se nao incidir, zere e o payback melhora.</t>
   </si>
   <si>
     <t xml:space="preserve">Homologacao / engenharia / ART (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">E: R$ 790 declarado pelo William. A e B: mesmo valor como ESTIMATIVA - a TecSolarSP nunca informou o preco de venda. C, D e F declaram homologacao inclusa.</t>
+    <t xml:space="preserve">E: R$ 790 declarado pelo William. A e B: mesmo valor como ESTIMATIVA - a TecSolarSP nunca informou o preco de venda.</t>
   </si>
   <si>
     <t xml:space="preserve">Instalacao / mao de obra (R$)</t>
@@ -1823,7 +1877,7 @@
     <t xml:space="preserve">Adequacao do padrao mono -&gt; bifasico (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: NENHUM dos seis incluiu, e a Sun Coast exclui por escrito. Necessario para qualquer inversor de 220 V. Editavel em ENTRADAS!C28.</t>
+    <t xml:space="preserve">ALERTA: NENHUM dos orcamentos incluiu. Necessario para qualquer inversor de 220 V. Editavel em ENTRADAS!C28.</t>
   </si>
   <si>
     <t xml:space="preserve">PRECO TOTAL INSTALADO (R$)</t>
@@ -1868,19 +1922,19 @@
     <t xml:space="preserve">Geracao PROMETIDA pelo vendedor (kWh/ano)</t>
   </si>
   <si>
-    <t xml:space="preserve">A: 10.554 na peca da TecSolarSP. C e D: 700 kWh/mes x 12. E: 6.151. F: 6.367,50 (530,62 x 12). B: nao informada.</t>
+    <t xml:space="preserve">A: 10.554. C, D e G: 700 kWh/mes x 12. E: 6.151. F: 6.367,50. H: 7.329,96. I: 9.279,13. J: 6.385,01. B: nao informada.</t>
   </si>
   <si>
     <t xml:space="preserve">DESVIO DA PROMESSA</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: negativo = o vendedor promete mais do que o telhado entrega. Positivo = foi conservador.</t>
+    <t xml:space="preserve">ALERTA: negativo = o vendedor promete mais do que o telhado entrega. Positivo = foi conservador. Sfero e a unica positiva.</t>
   </si>
   <si>
     <t xml:space="preserve">Geracao se o telhado fosse NORTE (kWh)</t>
   </si>
   <si>
-    <t xml:space="preserve">Compare com a linha 39: e daqui que saem os numeros otimistas.</t>
+    <t xml:space="preserve">Compare com a linha da promessa: e daqui que saem os numeros otimistas.</t>
   </si>
   <si>
     <t xml:space="preserve">ATENDIMENTO DO CONSUMO</t>
@@ -1916,10 +1970,10 @@
     <t xml:space="preserve">Placas que existem no projeto apenas para compensar o carregamento do carro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Potencia AC a declarar na homologacao (kW) e corrente em 220 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALERTA POUCO OBVIO: a potencia declarada a Enel e a do INVERSOR (AC), nao a dos modulos. Quanto maior, maior o disjuntor e o padrao exigidos - e mais caro fica o item da linha 30. Sfero com 5 kW e a menos exigente; a opcao G com 9 kW AC e a mais exigente.</t>
+    <t xml:space="preserve">Potencia AC a declarar na homologacao e corrente em 220 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALERTA POUCO OBVIO: a potencia declarada a Enel e a do INVERSOR (AC), nao a dos modulos. Quanto maior, maior o disjuntor e o padrao exigidos - e mais caro fica o item de adequacao do padrao.</t>
   </si>
   <si>
     <t xml:space="preserve">RESULTADO FINANCEIRO</t>
@@ -1952,7 +2006,7 @@
     <t xml:space="preserve">PAYBACK SIMPLES (anos)</t>
   </si>
   <si>
-    <t xml:space="preserve">Investimento total dividido pela economia do ano 1. CUIDADO: payback bom nao significa melhor negocio - ver linha 61.</t>
+    <t xml:space="preserve">Investimento total dividido pela economia do ano 1. CUIDADO: payback bom nao significa melhor negocio - ver a linha do lucro em 20 anos.</t>
   </si>
   <si>
     <t xml:space="preserve">Economia acumulada em 5 anos (R$)</t>
@@ -1982,7 +2036,7 @@
     <t xml:space="preserve">Modulos que ainda cabem no inversor</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: Solis 4 kW e os AUXSOL de 5 e 3 kW nao aceitam nenhum modulo a mais. A e B tem folga minima (1 modulo). A opcao G com microinversores e a unica com folga real - mas o limite verdadeiro e o numero de CANAIS livres nos micros, nao a potencia. CONFIRMAR com o Yuri.</t>
+    <t xml:space="preserve">ALERTA: os inversores de 5 kW da SunWash (C e D) nao aceitam nenhum modulo a mais. Sun Coast v2 (+5) e a opcao com microinversores tem folga real - mas nos micros o limite verdadeiro e o numero de CANAIS livres, nao a potencia.</t>
   </si>
   <si>
     <t xml:space="preserve">Geracao extra possivel sem trocar inversor (kWh/ano)</t>
@@ -1991,7 +2045,7 @@
     <t xml:space="preserve">Situacao do inversor</t>
   </si>
   <si>
-    <t xml:space="preserve">'JA SOBRECARREGADO' = inversor pequeno para os modulos desde o dia 1 (perde geracao e garantia). 'SUBAPROVEITADO' = voce pagou por potencia de inversor que nao vai usar - aceitavel se for folga proposital para expansao, ruim se for so venda a mais.</t>
+    <t xml:space="preserve">'JA SOBRECARREGADO' = inversor pequeno para os modulos desde o dia 1 (perde geracao e garantia). 'SUBAPROVEITADO' = folga; boa se proposital para expansao, ruim se foi venda a mais.</t>
   </si>
   <si>
     <t xml:space="preserve">DECISAO ESPECIFICA: AUXSOL x HUAWEI NA PROPOSTA DA SUNWASH</t>
@@ -2006,7 +2060,7 @@
     <t xml:space="preserve">Diferenca no lucro de 20 anos</t>
   </si>
   <si>
-    <t xml:space="preserve">RECOMENDACAO: pagar os R$ 1.000 e ficar com o HUAWEI.</t>
+    <t xml:space="preserve">RECOMENDACAO: entre as duas da SunWash com inversor string, pagar os R$ 1.000 e ficar com o HUAWEI.</t>
   </si>
   <si>
     <t xml:space="preserve">O inversor e o unico componente que quase certamente sera trocado dentro da vida do sistema. Huawei tem garantia de fabrica mais longa,</t>
@@ -2018,13 +2072,10 @@
     <t xml:space="preserve">voce fica com o sistema parado esperando peca. O atraso de cerca de 2 meses no payback nao paga esse risco.</t>
   </si>
   <si>
-    <t xml:space="preserve">OBSERVACAO SOBRE PAYBACK x LUCRO: a Sun Coast tem payback parecido com o da SunWash, mas o sistema e 25% menor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payback ignora a energia que voce NAO compensou. Um sistema pequeno se paga rapido e depois te deixa pagando conta para sempre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por isso a linha 61 (lucro em 20 anos) e o criterio correto, e nao a linha 57.</t>
+    <t xml:space="preserve">OBSERVACAO SOBRE PAYBACK x LUCRO: sistema pequeno se paga rapido e depois te deixa pagando conta para sempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payback ignora a energia que voce NAO compensou. Por isso o criterio correto e o LUCRO LIQUIDO EM 20 ANOS.</t>
   </si>
   <si>
     <t xml:space="preserve">LISTA DE MATERIAIS - AS TRES COTACOES BELENERGY LADO A LADO</t>
@@ -3657,16 +3708,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3677,8 +3724,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3766,10 +3821,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4526,110 +4577,110 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>831</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>833</v>
+        <v>850</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>834</v>
+        <v>851</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>835</v>
+        <v>852</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>836</v>
+        <v>853</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>841</v>
+        <v>858</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>842</v>
+        <v>859</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>843</v>
+        <v>860</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>844</v>
+        <v>861</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>850</v>
+        <v>867</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>855</v>
+        <v>872</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>856</v>
+        <v>873</v>
       </c>
       <c r="AA4" s="17" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
       <c r="AC4" s="17" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>861</v>
+        <v>878</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>863</v>
+        <v>880</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,7 +4700,7 @@
         <v>6121.91852197507</v>
       </c>
       <c r="F6" s="105" t="n">
-        <f aca="false">E6-COMPARATIVO!C$31</f>
+        <f aca="false">E6-COMPARATIVO!C$34</f>
         <v>-23676.7814780249</v>
       </c>
       <c r="G6" s="105" t="n">
@@ -4661,7 +4712,7 @@
         <v>6121.91852197507</v>
       </c>
       <c r="I6" s="105" t="n">
-        <f aca="false">H6-COMPARATIVO!D$31</f>
+        <f aca="false">H6-COMPARATIVO!D$34</f>
         <v>-22755.9814780249</v>
       </c>
       <c r="J6" s="105" t="n">
@@ -4673,7 +4724,7 @@
         <v>6105.10922042702</v>
       </c>
       <c r="L6" s="105" t="n">
-        <f aca="false">K6-COMPARATIVO!E$31</f>
+        <f aca="false">K6-COMPARATIVO!E$34</f>
         <v>-12415.230779573</v>
       </c>
       <c r="M6" s="105" t="n">
@@ -4685,7 +4736,7 @@
         <v>6105.10922042702</v>
       </c>
       <c r="O6" s="105" t="n">
-        <f aca="false">N6-COMPARATIVO!F$31</f>
+        <f aca="false">N6-COMPARATIVO!F$34</f>
         <v>-13415.230779573</v>
       </c>
       <c r="P6" s="105" t="n">
@@ -4697,7 +4748,7 @@
         <v>5442.45129401962</v>
       </c>
       <c r="R6" s="105" t="n">
-        <f aca="false">Q6-COMPARATIVO!G$31</f>
+        <f aca="false">Q6-COMPARATIVO!G$34</f>
         <v>-15906.4587059804</v>
       </c>
       <c r="S6" s="105" t="n">
@@ -4709,7 +4760,7 @@
         <v>4704.51814131062</v>
       </c>
       <c r="U6" s="105" t="n">
-        <f aca="false">T6-COMPARATIVO!H$31</f>
+        <f aca="false">T6-COMPARATIVO!H$34</f>
         <v>-10183.1218586894</v>
       </c>
       <c r="V6" s="105" t="n">
@@ -4721,7 +4772,7 @@
         <v>6121.91852197507</v>
       </c>
       <c r="X6" s="105" t="n">
-        <f aca="false">W6-COMPARATIVO!I$31</f>
+        <f aca="false">W6-COMPARATIVO!I$34</f>
         <v>-14958.6214780249</v>
       </c>
       <c r="Y6" s="105" t="n">
@@ -4733,7 +4784,7 @@
         <v>6048.21731490014</v>
       </c>
       <c r="AA6" s="105" t="n">
-        <f aca="false">Z6-COMPARATIVO!J$31</f>
+        <f aca="false">Z6-COMPARATIVO!J$34</f>
         <v>-15184.7826850999</v>
       </c>
       <c r="AB6" s="105" t="n">
@@ -4745,7 +4796,7 @@
         <v>6121.91852197507</v>
       </c>
       <c r="AD6" s="105" t="n">
-        <f aca="false">AC6-COMPARATIVO!K$31</f>
+        <f aca="false">AC6-COMPARATIVO!K$34</f>
         <v>-13268.0814780249</v>
       </c>
       <c r="AE6" s="105" t="n">
@@ -4757,7 +4808,7 @@
         <v>4968.85240496757</v>
       </c>
       <c r="AG6" s="105" t="n">
-        <f aca="false">AF6-COMPARATIVO!L$31</f>
+        <f aca="false">AF6-COMPARATIVO!L$34</f>
         <v>-14973.1475950324</v>
       </c>
     </row>
@@ -4778,7 +4829,7 @@
         <v>12642.8943028051</v>
       </c>
       <c r="F7" s="105" t="n">
-        <f aca="false">E7-COMPARATIVO!C$31</f>
+        <f aca="false">E7-COMPARATIVO!C$34</f>
         <v>-17155.8056971949</v>
       </c>
       <c r="G7" s="105" t="n">
@@ -4790,7 +4841,7 @@
         <v>12642.8943028051</v>
       </c>
       <c r="I7" s="105" t="n">
-        <f aca="false">H7-COMPARATIVO!D$31</f>
+        <f aca="false">H7-COMPARATIVO!D$34</f>
         <v>-16235.0056971949</v>
       </c>
       <c r="J7" s="105" t="n">
@@ -4802,7 +4853,7 @@
         <v>12608.1799853876</v>
       </c>
       <c r="L7" s="105" t="n">
-        <f aca="false">K7-COMPARATIVO!E$31</f>
+        <f aca="false">K7-COMPARATIVO!E$34</f>
         <v>-5912.16001461242</v>
       </c>
       <c r="M7" s="105" t="n">
@@ -4814,7 +4865,7 @@
         <v>12608.1799853876</v>
       </c>
       <c r="O7" s="105" t="n">
-        <f aca="false">N7-COMPARATIVO!F$31</f>
+        <f aca="false">N7-COMPARATIVO!F$34</f>
         <v>-6912.16001461242</v>
       </c>
       <c r="P7" s="105" t="n">
@@ -4826,7 +4877,7 @@
         <v>11239.6687756399</v>
       </c>
       <c r="R7" s="105" t="n">
-        <f aca="false">Q7-COMPARATIVO!G$31</f>
+        <f aca="false">Q7-COMPARATIVO!G$34</f>
         <v>-10109.2412243601</v>
       </c>
       <c r="S7" s="105" t="n">
@@ -4838,7 +4889,7 @@
         <v>9715.70029766257</v>
       </c>
       <c r="U7" s="105" t="n">
-        <f aca="false">T7-COMPARATIVO!H$31</f>
+        <f aca="false">T7-COMPARATIVO!H$34</f>
         <v>-5171.93970233743</v>
       </c>
       <c r="V7" s="105" t="n">
@@ -4850,7 +4901,7 @@
         <v>12642.8943028051</v>
       </c>
       <c r="X7" s="105" t="n">
-        <f aca="false">W7-COMPARATIVO!I$31</f>
+        <f aca="false">W7-COMPARATIVO!I$34</f>
         <v>-8437.64569719492</v>
       </c>
       <c r="Y7" s="105" t="n">
@@ -4862,7 +4913,7 @@
         <v>12490.687675472</v>
       </c>
       <c r="AA7" s="105" t="n">
-        <f aca="false">Z7-COMPARATIVO!J$31</f>
+        <f aca="false">Z7-COMPARATIVO!J$34</f>
         <v>-8742.31232452795</v>
       </c>
       <c r="AB7" s="105" t="n">
@@ -4874,7 +4925,7 @@
         <v>12642.8943028051</v>
       </c>
       <c r="AD7" s="105" t="n">
-        <f aca="false">AC7-COMPARATIVO!K$31</f>
+        <f aca="false">AC7-COMPARATIVO!K$34</f>
         <v>-6747.10569719492</v>
       </c>
       <c r="AE7" s="105" t="n">
@@ -4886,7 +4937,7 @@
         <v>10261.599453953</v>
       </c>
       <c r="AG7" s="105" t="n">
-        <f aca="false">AF7-COMPARATIVO!L$31</f>
+        <f aca="false">AF7-COMPARATIVO!L$34</f>
         <v>-9680.40054604704</v>
       </c>
     </row>
@@ -4907,7 +4958,7 @@
         <v>19588.9398899085</v>
       </c>
       <c r="F8" s="105" t="n">
-        <f aca="false">E8-COMPARATIVO!C$31</f>
+        <f aca="false">E8-COMPARATIVO!C$34</f>
         <v>-10209.7601100915</v>
       </c>
       <c r="G8" s="105" t="n">
@@ -4919,7 +4970,7 @@
         <v>19588.9398899085</v>
       </c>
       <c r="I8" s="105" t="n">
-        <f aca="false">H8-COMPARATIVO!D$31</f>
+        <f aca="false">H8-COMPARATIVO!D$34</f>
         <v>-9288.9601100915</v>
       </c>
       <c r="J8" s="105" t="n">
@@ -4931,7 +4982,7 @@
         <v>19535.1534181621</v>
       </c>
       <c r="L8" s="105" t="n">
-        <f aca="false">K8-COMPARATIVO!E$31</f>
+        <f aca="false">K8-COMPARATIVO!E$34</f>
         <v>1014.8134181621</v>
       </c>
       <c r="M8" s="105" t="n">
@@ -4943,7 +4994,7 @@
         <v>19535.1534181621</v>
       </c>
       <c r="O8" s="105" t="n">
-        <f aca="false">N8-COMPARATIVO!F$31</f>
+        <f aca="false">N8-COMPARATIVO!F$34</f>
         <v>14.8134181620953</v>
       </c>
       <c r="P8" s="105" t="n">
@@ -4955,7 +5006,7 @@
         <v>17414.7778787996</v>
       </c>
       <c r="R8" s="105" t="n">
-        <f aca="false">Q8-COMPARATIVO!G$31</f>
+        <f aca="false">Q8-COMPARATIVO!G$34</f>
         <v>-3934.13212120039</v>
       </c>
       <c r="S8" s="105" t="n">
@@ -4967,7 +5018,7 @@
         <v>15053.5363628763</v>
       </c>
       <c r="U8" s="105" t="n">
-        <f aca="false">T8-COMPARATIVO!H$31</f>
+        <f aca="false">T8-COMPARATIVO!H$34</f>
         <v>165.89636287633</v>
       </c>
       <c r="V8" s="105" t="n">
@@ -4979,7 +5030,7 @@
         <v>19588.9398899085</v>
       </c>
       <c r="X8" s="105" t="n">
-        <f aca="false">W8-COMPARATIVO!I$31</f>
+        <f aca="false">W8-COMPARATIVO!I$34</f>
         <v>-1491.60011009149</v>
       </c>
       <c r="Y8" s="105" t="n">
@@ -4991,7 +5042,7 @@
         <v>19353.1104664978</v>
       </c>
       <c r="AA8" s="105" t="n">
-        <f aca="false">Z8-COMPARATIVO!J$31</f>
+        <f aca="false">Z8-COMPARATIVO!J$34</f>
         <v>-1879.88953350216</v>
       </c>
       <c r="AB8" s="105" t="n">
@@ -5003,7 +5054,7 @@
         <v>19588.9398899085</v>
       </c>
       <c r="AD8" s="105" t="n">
-        <f aca="false">AC8-COMPARATIVO!K$31</f>
+        <f aca="false">AC8-COMPARATIVO!K$34</f>
         <v>198.939889908506</v>
       </c>
       <c r="AE8" s="105" t="n">
@@ -5015,7 +5066,7 @@
         <v>15899.3542193265</v>
       </c>
       <c r="AG8" s="105" t="n">
-        <f aca="false">AF8-COMPARATIVO!L$31</f>
+        <f aca="false">AF8-COMPARATIVO!L$34</f>
         <v>-4042.64578067354</v>
       </c>
     </row>
@@ -5036,7 +5087,7 @@
         <v>26987.7634586073</v>
       </c>
       <c r="F9" s="105" t="n">
-        <f aca="false">E9-COMPARATIVO!C$31</f>
+        <f aca="false">E9-COMPARATIVO!C$34</f>
         <v>-2810.93654139274</v>
       </c>
       <c r="G9" s="105" t="n">
@@ -5048,7 +5099,7 @@
         <v>26987.7634586073</v>
       </c>
       <c r="I9" s="105" t="n">
-        <f aca="false">H9-COMPARATIVO!D$31</f>
+        <f aca="false">H9-COMPARATIVO!D$34</f>
         <v>-1890.13654139274</v>
       </c>
       <c r="J9" s="105" t="n">
@@ -5060,7 +5111,7 @@
         <v>26913.661614152</v>
       </c>
       <c r="L9" s="105" t="n">
-        <f aca="false">K9-COMPARATIVO!E$31</f>
+        <f aca="false">K9-COMPARATIVO!E$34</f>
         <v>8393.32161415201</v>
       </c>
       <c r="M9" s="105" t="n">
@@ -5072,7 +5123,7 @@
         <v>26913.661614152</v>
       </c>
       <c r="O9" s="105" t="n">
-        <f aca="false">N9-COMPARATIVO!F$31</f>
+        <f aca="false">N9-COMPARATIVO!F$34</f>
         <v>7393.32161415201</v>
       </c>
       <c r="P9" s="105" t="n">
@@ -5084,7 +5135,7 @@
         <v>23992.4114688488</v>
       </c>
       <c r="R9" s="105" t="n">
-        <f aca="false">Q9-COMPARATIVO!G$31</f>
+        <f aca="false">Q9-COMPARATIVO!G$34</f>
         <v>2643.50146884879</v>
       </c>
       <c r="S9" s="105" t="n">
@@ -5096,7 +5147,7 @@
         <v>20739.319272001</v>
       </c>
       <c r="U9" s="105" t="n">
-        <f aca="false">T9-COMPARATIVO!H$31</f>
+        <f aca="false">T9-COMPARATIVO!H$34</f>
         <v>5851.67927200105</v>
       </c>
       <c r="V9" s="105" t="n">
@@ -5108,7 +5159,7 @@
         <v>26987.7634586073</v>
       </c>
       <c r="X9" s="105" t="n">
-        <f aca="false">W9-COMPARATIVO!I$31</f>
+        <f aca="false">W9-COMPARATIVO!I$34</f>
         <v>5907.22345860726</v>
       </c>
       <c r="Y9" s="105" t="n">
@@ -5120,7 +5171,7 @@
         <v>26662.8602871566</v>
       </c>
       <c r="AA9" s="105" t="n">
-        <f aca="false">Z9-COMPARATIVO!J$31</f>
+        <f aca="false">Z9-COMPARATIVO!J$34</f>
         <v>5429.86028715664</v>
       </c>
       <c r="AB9" s="105" t="n">
@@ -5132,7 +5183,7 @@
         <v>26987.7634586073</v>
       </c>
       <c r="AD9" s="105" t="n">
-        <f aca="false">AC9-COMPARATIVO!K$31</f>
+        <f aca="false">AC9-COMPARATIVO!K$34</f>
         <v>7597.76345860726</v>
       </c>
       <c r="AE9" s="105" t="n">
@@ -5144,7 +5195,7 @@
         <v>21904.6060290808</v>
       </c>
       <c r="AG9" s="105" t="n">
-        <f aca="false">AF9-COMPARATIVO!L$31</f>
+        <f aca="false">AF9-COMPARATIVO!L$34</f>
         <v>1962.60602908083</v>
       </c>
     </row>
@@ -5165,7 +5216,7 @@
         <v>34868.8793416317</v>
       </c>
       <c r="F10" s="108" t="n">
-        <f aca="false">E10-COMPARATIVO!C$31</f>
+        <f aca="false">E10-COMPARATIVO!C$34</f>
         <v>5070.17934163165</v>
       </c>
       <c r="G10" s="108" t="n">
@@ -5177,7 +5228,7 @@
         <v>34868.8793416317</v>
       </c>
       <c r="I10" s="108" t="n">
-        <f aca="false">H10-COMPARATIVO!D$31</f>
+        <f aca="false">H10-COMPARATIVO!D$34</f>
         <v>5990.97934163165</v>
       </c>
       <c r="J10" s="108" t="n">
@@ -5189,7 +5240,7 @@
         <v>34773.1378668975</v>
       </c>
       <c r="L10" s="108" t="n">
-        <f aca="false">K10-COMPARATIVO!E$31</f>
+        <f aca="false">K10-COMPARATIVO!E$34</f>
         <v>16252.7978668975</v>
       </c>
       <c r="M10" s="108" t="n">
@@ -5201,7 +5252,7 @@
         <v>34773.1378668975</v>
       </c>
       <c r="O10" s="108" t="n">
-        <f aca="false">N10-COMPARATIVO!F$31</f>
+        <f aca="false">N10-COMPARATIVO!F$34</f>
         <v>15252.7978668975</v>
       </c>
       <c r="P10" s="108" t="n">
@@ -5213,7 +5264,7 @@
         <v>30998.8081044653</v>
       </c>
       <c r="R10" s="108" t="n">
-        <f aca="false">Q10-COMPARATIVO!G$31</f>
+        <f aca="false">Q10-COMPARATIVO!G$34</f>
         <v>9649.89810446532</v>
       </c>
       <c r="S10" s="108" t="n">
@@ -5225,7 +5276,7 @@
         <v>26795.7299400571</v>
       </c>
       <c r="U10" s="108" t="n">
-        <f aca="false">T10-COMPARATIVO!H$31</f>
+        <f aca="false">T10-COMPARATIVO!H$34</f>
         <v>11908.0899400571</v>
       </c>
       <c r="V10" s="108" t="n">
@@ -5237,7 +5288,7 @@
         <v>34868.8793416317</v>
       </c>
       <c r="X10" s="108" t="n">
-        <f aca="false">W10-COMPARATIVO!I$31</f>
+        <f aca="false">W10-COMPARATIVO!I$34</f>
         <v>13788.3393416317</v>
       </c>
       <c r="Y10" s="108" t="n">
@@ -5249,7 +5300,7 @@
         <v>34449.0961498751</v>
       </c>
       <c r="AA10" s="108" t="n">
-        <f aca="false">Z10-COMPARATIVO!J$31</f>
+        <f aca="false">Z10-COMPARATIVO!J$34</f>
         <v>13216.0961498751</v>
       </c>
       <c r="AB10" s="108" t="n">
@@ -5261,7 +5312,7 @@
         <v>34868.8793416317</v>
       </c>
       <c r="AD10" s="108" t="n">
-        <f aca="false">AC10-COMPARATIVO!K$31</f>
+        <f aca="false">AC10-COMPARATIVO!K$34</f>
         <v>15478.8793416317</v>
       </c>
       <c r="AE10" s="108" t="n">
@@ -5273,7 +5324,7 @@
         <v>28301.310178054</v>
       </c>
       <c r="AG10" s="108" t="n">
-        <f aca="false">AF10-COMPARATIVO!L$31</f>
+        <f aca="false">AF10-COMPARATIVO!L$34</f>
         <v>8359.31017805404</v>
       </c>
     </row>
@@ -5294,7 +5345,7 @@
         <v>43263.725763491</v>
       </c>
       <c r="F11" s="105" t="n">
-        <f aca="false">E11-COMPARATIVO!C$31</f>
+        <f aca="false">E11-COMPARATIVO!C$34</f>
         <v>13465.025763491</v>
       </c>
       <c r="G11" s="105" t="n">
@@ -5306,7 +5357,7 @@
         <v>43263.725763491</v>
       </c>
       <c r="I11" s="105" t="n">
-        <f aca="false">H11-COMPARATIVO!D$31</f>
+        <f aca="false">H11-COMPARATIVO!D$34</f>
         <v>14385.825763491</v>
       </c>
       <c r="J11" s="105" t="n">
@@ -5318,7 +5369,7 @@
         <v>43144.9340791783</v>
       </c>
       <c r="L11" s="105" t="n">
-        <f aca="false">K11-COMPARATIVO!E$31</f>
+        <f aca="false">K11-COMPARATIVO!E$34</f>
         <v>24624.5940791783</v>
       </c>
       <c r="M11" s="105" t="n">
@@ -5330,7 +5381,7 @@
         <v>43144.9340791783</v>
       </c>
       <c r="O11" s="105" t="n">
-        <f aca="false">N11-COMPARATIVO!F$31</f>
+        <f aca="false">N11-COMPARATIVO!F$34</f>
         <v>23624.5940791783</v>
       </c>
       <c r="P11" s="105" t="n">
@@ -5342,7 +5393,7 @@
         <v>38461.9167047745</v>
       </c>
       <c r="R11" s="105" t="n">
-        <f aca="false">Q11-COMPARATIVO!G$31</f>
+        <f aca="false">Q11-COMPARATIVO!G$34</f>
         <v>17113.0067047745</v>
       </c>
       <c r="S11" s="105" t="n">
@@ -5354,7 +5405,7 @@
         <v>33246.9277375103</v>
       </c>
       <c r="U11" s="105" t="n">
-        <f aca="false">T11-COMPARATIVO!H$31</f>
+        <f aca="false">T11-COMPARATIVO!H$34</f>
         <v>18359.2877375103</v>
       </c>
       <c r="V11" s="105" t="n">
@@ -5366,7 +5417,7 @@
         <v>43263.725763491</v>
       </c>
       <c r="X11" s="105" t="n">
-        <f aca="false">W11-COMPARATIVO!I$31</f>
+        <f aca="false">W11-COMPARATIVO!I$34</f>
         <v>22183.185763491</v>
       </c>
       <c r="Y11" s="105" t="n">
@@ -5378,7 +5429,7 @@
         <v>42742.8777973048</v>
       </c>
       <c r="AA11" s="105" t="n">
-        <f aca="false">Z11-COMPARATIVO!J$31</f>
+        <f aca="false">Z11-COMPARATIVO!J$34</f>
         <v>21509.8777973048</v>
       </c>
       <c r="AB11" s="105" t="n">
@@ -5390,7 +5441,7 @@
         <v>43263.725763491</v>
       </c>
       <c r="AD11" s="105" t="n">
-        <f aca="false">AC11-COMPARATIVO!K$31</f>
+        <f aca="false">AC11-COMPARATIVO!K$34</f>
         <v>23873.725763491</v>
       </c>
       <c r="AE11" s="105" t="n">
@@ -5402,7 +5453,7 @@
         <v>35114.9834869781</v>
       </c>
       <c r="AG11" s="105" t="n">
-        <f aca="false">AF11-COMPARATIVO!L$31</f>
+        <f aca="false">AF11-COMPARATIVO!L$34</f>
         <v>15172.9834869781</v>
       </c>
     </row>
@@ -5423,7 +5474,7 @@
         <v>52205.7902493592</v>
       </c>
       <c r="F12" s="105" t="n">
-        <f aca="false">E12-COMPARATIVO!C$31</f>
+        <f aca="false">E12-COMPARATIVO!C$34</f>
         <v>22407.0902493592</v>
       </c>
       <c r="G12" s="105" t="n">
@@ -5435,7 +5486,7 @@
         <v>52205.7902493592</v>
       </c>
       <c r="I12" s="105" t="n">
-        <f aca="false">H12-COMPARATIVO!D$31</f>
+        <f aca="false">H12-COMPARATIVO!D$34</f>
         <v>23327.8902493592</v>
       </c>
       <c r="J12" s="105" t="n">
@@ -5447,7 +5498,7 @@
         <v>52062.4458275565</v>
       </c>
       <c r="L12" s="105" t="n">
-        <f aca="false">K12-COMPARATIVO!E$31</f>
+        <f aca="false">K12-COMPARATIVO!E$34</f>
         <v>33542.1058275565</v>
       </c>
       <c r="M12" s="105" t="n">
@@ -5459,7 +5510,7 @@
         <v>52062.4458275565</v>
       </c>
       <c r="O12" s="105" t="n">
-        <f aca="false">N12-COMPARATIVO!F$31</f>
+        <f aca="false">N12-COMPARATIVO!F$34</f>
         <v>32542.1058275565</v>
       </c>
       <c r="P12" s="105" t="n">
@@ -5471,7 +5522,7 @@
         <v>46411.5080391949</v>
       </c>
       <c r="R12" s="105" t="n">
-        <f aca="false">Q12-COMPARATIVO!G$31</f>
+        <f aca="false">Q12-COMPARATIVO!G$34</f>
         <v>25062.5980391949</v>
       </c>
       <c r="S12" s="105" t="n">
@@ -5483,7 +5534,7 @@
         <v>40118.6468633905</v>
       </c>
       <c r="U12" s="105" t="n">
-        <f aca="false">T12-COMPARATIVO!H$31</f>
+        <f aca="false">T12-COMPARATIVO!H$34</f>
         <v>25231.0068633905</v>
       </c>
       <c r="V12" s="105" t="n">
@@ -5495,7 +5546,7 @@
         <v>52205.7902493592</v>
       </c>
       <c r="X12" s="105" t="n">
-        <f aca="false">W12-COMPARATIVO!I$31</f>
+        <f aca="false">W12-COMPARATIVO!I$34</f>
         <v>31125.2502493592</v>
       </c>
       <c r="Y12" s="105" t="n">
@@ -5507,7 +5558,7 @@
         <v>51577.2896014223</v>
       </c>
       <c r="AA12" s="105" t="n">
-        <f aca="false">Z12-COMPARATIVO!J$31</f>
+        <f aca="false">Z12-COMPARATIVO!J$34</f>
         <v>30344.2896014223</v>
       </c>
       <c r="AB12" s="105" t="n">
@@ -5519,7 +5570,7 @@
         <v>52205.7902493592</v>
       </c>
       <c r="AD12" s="105" t="n">
-        <f aca="false">AC12-COMPARATIVO!K$31</f>
+        <f aca="false">AC12-COMPARATIVO!K$34</f>
         <v>32815.7902493592</v>
       </c>
       <c r="AE12" s="105" t="n">
@@ -5531,7 +5582,7 @@
         <v>42372.8060905443</v>
       </c>
       <c r="AG12" s="105" t="n">
-        <f aca="false">AF12-COMPARATIVO!L$31</f>
+        <f aca="false">AF12-COMPARATIVO!L$34</f>
         <v>22430.8060905443</v>
       </c>
     </row>
@@ -5552,7 +5603,7 @@
         <v>61730.7432087388</v>
       </c>
       <c r="F13" s="105" t="n">
-        <f aca="false">E13-COMPARATIVO!C$31</f>
+        <f aca="false">E13-COMPARATIVO!C$34</f>
         <v>31932.0432087388</v>
       </c>
       <c r="G13" s="105" t="n">
@@ -5564,7 +5615,7 @@
         <v>61730.7432087388</v>
       </c>
       <c r="I13" s="105" t="n">
-        <f aca="false">H13-COMPARATIVO!D$31</f>
+        <f aca="false">H13-COMPARATIVO!D$34</f>
         <v>32852.8432087388</v>
       </c>
       <c r="J13" s="105" t="n">
@@ -5576,7 +5627,7 @@
         <v>61561.2455792528</v>
       </c>
       <c r="L13" s="105" t="n">
-        <f aca="false">K13-COMPARATIVO!E$31</f>
+        <f aca="false">K13-COMPARATIVO!E$34</f>
         <v>43040.9055792528</v>
       </c>
       <c r="M13" s="105" t="n">
@@ -5588,7 +5639,7 @@
         <v>61561.2455792528</v>
       </c>
       <c r="O13" s="105" t="n">
-        <f aca="false">N13-COMPARATIVO!F$31</f>
+        <f aca="false">N13-COMPARATIVO!F$34</f>
         <v>42040.9055792528</v>
       </c>
       <c r="P13" s="105" t="n">
@@ -5600,7 +5651,7 @@
         <v>54879.2934847494</v>
       </c>
       <c r="R13" s="105" t="n">
-        <f aca="false">Q13-COMPARATIVO!G$31</f>
+        <f aca="false">Q13-COMPARATIVO!G$34</f>
         <v>33530.3834847494</v>
       </c>
       <c r="S13" s="105" t="n">
@@ -5612,7 +5663,7 @@
         <v>47438.2990004913</v>
       </c>
       <c r="U13" s="105" t="n">
-        <f aca="false">T13-COMPARATIVO!H$31</f>
+        <f aca="false">T13-COMPARATIVO!H$34</f>
         <v>32550.6590004913</v>
       </c>
       <c r="V13" s="105" t="n">
@@ -5624,7 +5675,7 @@
         <v>61730.7432087388</v>
       </c>
       <c r="X13" s="105" t="n">
-        <f aca="false">W13-COMPARATIVO!I$31</f>
+        <f aca="false">W13-COMPARATIVO!I$34</f>
         <v>40650.2032087388</v>
       </c>
       <c r="Y13" s="105" t="n">
@@ -5636,7 +5687,7 @@
         <v>60987.5725389912</v>
       </c>
       <c r="AA13" s="105" t="n">
-        <f aca="false">Z13-COMPARATIVO!J$31</f>
+        <f aca="false">Z13-COMPARATIVO!J$34</f>
         <v>39754.5725389912</v>
       </c>
       <c r="AB13" s="105" t="n">
@@ -5648,7 +5699,7 @@
         <v>61730.7432087388</v>
       </c>
       <c r="AD13" s="105" t="n">
-        <f aca="false">AC13-COMPARATIVO!K$31</f>
+        <f aca="false">AC13-COMPARATIVO!K$34</f>
         <v>42340.7432087388</v>
       </c>
       <c r="AE13" s="105" t="n">
@@ -5660,7 +5711,7 @@
         <v>50103.729860524</v>
       </c>
       <c r="AG13" s="105" t="n">
-        <f aca="false">AF13-COMPARATIVO!L$31</f>
+        <f aca="false">AF13-COMPARATIVO!L$34</f>
         <v>30161.729860524</v>
       </c>
     </row>
@@ -5681,7 +5732,7 @@
         <v>71876.5802267755</v>
       </c>
       <c r="F14" s="105" t="n">
-        <f aca="false">E14-COMPARATIVO!C$31</f>
+        <f aca="false">E14-COMPARATIVO!C$34</f>
         <v>42077.8802267755</v>
       </c>
       <c r="G14" s="105" t="n">
@@ -5693,7 +5744,7 @@
         <v>71876.5802267755</v>
       </c>
       <c r="I14" s="105" t="n">
-        <f aca="false">H14-COMPARATIVO!D$31</f>
+        <f aca="false">H14-COMPARATIVO!D$34</f>
         <v>42998.6802267755</v>
       </c>
       <c r="J14" s="105" t="n">
@@ -5705,7 +5756,7 @@
         <v>71679.2245927635</v>
       </c>
       <c r="L14" s="105" t="n">
-        <f aca="false">K14-COMPARATIVO!E$31</f>
+        <f aca="false">K14-COMPARATIVO!E$34</f>
         <v>53158.8845927635</v>
       </c>
       <c r="M14" s="105" t="n">
@@ -5717,7 +5768,7 @@
         <v>71679.2245927635</v>
       </c>
       <c r="O14" s="105" t="n">
-        <f aca="false">N14-COMPARATIVO!F$31</f>
+        <f aca="false">N14-COMPARATIVO!F$34</f>
         <v>52158.8845927635</v>
       </c>
       <c r="P14" s="105" t="n">
@@ -5729,7 +5780,7 @@
         <v>63899.0515245724</v>
       </c>
       <c r="R14" s="105" t="n">
-        <f aca="false">Q14-COMPARATIVO!G$31</f>
+        <f aca="false">Q14-COMPARATIVO!G$34</f>
         <v>42550.1415245724</v>
       </c>
       <c r="S14" s="105" t="n">
@@ -5741,7 +5792,7 @@
         <v>55235.0826621489</v>
       </c>
       <c r="U14" s="105" t="n">
-        <f aca="false">T14-COMPARATIVO!H$31</f>
+        <f aca="false">T14-COMPARATIVO!H$34</f>
         <v>40347.4426621489</v>
       </c>
       <c r="V14" s="105" t="n">
@@ -5753,7 +5804,7 @@
         <v>71876.5802267755</v>
       </c>
       <c r="X14" s="105" t="n">
-        <f aca="false">W14-COMPARATIVO!I$31</f>
+        <f aca="false">W14-COMPARATIVO!I$34</f>
         <v>50796.0402267755</v>
       </c>
       <c r="Y14" s="105" t="n">
@@ -5765,7 +5816,7 @@
         <v>71011.2647698455</v>
       </c>
       <c r="AA14" s="105" t="n">
-        <f aca="false">Z14-COMPARATIVO!J$31</f>
+        <f aca="false">Z14-COMPARATIVO!J$34</f>
         <v>49778.2647698455</v>
       </c>
       <c r="AB14" s="105" t="n">
@@ -5777,7 +5828,7 @@
         <v>71876.5802267755</v>
       </c>
       <c r="AD14" s="105" t="n">
-        <f aca="false">AC14-COMPARATIVO!K$31</f>
+        <f aca="false">AC14-COMPARATIVO!K$34</f>
         <v>52486.5802267755</v>
       </c>
       <c r="AE14" s="105" t="n">
@@ -5789,7 +5840,7 @@
         <v>58338.5938964499</v>
       </c>
       <c r="AG14" s="105" t="n">
-        <f aca="false">AF14-COMPARATIVO!L$31</f>
+        <f aca="false">AF14-COMPARATIVO!L$34</f>
         <v>38396.5938964499</v>
       </c>
     </row>
@@ -5810,7 +5861,7 @@
         <v>82683.773630833</v>
       </c>
       <c r="F15" s="108" t="n">
-        <f aca="false">E15-COMPARATIVO!C$31</f>
+        <f aca="false">E15-COMPARATIVO!C$34</f>
         <v>52885.073630833</v>
       </c>
       <c r="G15" s="108" t="n">
@@ -5822,7 +5873,7 @@
         <v>82683.773630833</v>
       </c>
       <c r="I15" s="108" t="n">
-        <f aca="false">H15-COMPARATIVO!D$31</f>
+        <f aca="false">H15-COMPARATIVO!D$34</f>
         <v>53805.8736308329</v>
       </c>
       <c r="J15" s="108" t="n">
@@ -5834,7 +5885,7 @@
         <v>82456.7440682698</v>
       </c>
       <c r="L15" s="108" t="n">
-        <f aca="false">K15-COMPARATIVO!E$31</f>
+        <f aca="false">K15-COMPARATIVO!E$34</f>
         <v>63936.4040682698</v>
       </c>
       <c r="M15" s="108" t="n">
@@ -5846,7 +5897,7 @@
         <v>82456.7440682698</v>
       </c>
       <c r="O15" s="108" t="n">
-        <f aca="false">N15-COMPARATIVO!F$31</f>
+        <f aca="false">N15-COMPARATIVO!F$34</f>
         <v>62936.4040682698</v>
       </c>
       <c r="P15" s="108" t="n">
@@ -5858,7 +5909,7 @@
         <v>73506.7624922213</v>
       </c>
       <c r="R15" s="108" t="n">
-        <f aca="false">Q15-COMPARATIVO!G$31</f>
+        <f aca="false">Q15-COMPARATIVO!G$34</f>
         <v>52157.8524922213</v>
       </c>
       <c r="S15" s="108" t="n">
@@ -5870,7 +5921,7 @@
         <v>63540.0996667917</v>
       </c>
       <c r="U15" s="108" t="n">
-        <f aca="false">T15-COMPARATIVO!H$31</f>
+        <f aca="false">T15-COMPARATIVO!H$34</f>
         <v>48652.4596667917</v>
       </c>
       <c r="V15" s="108" t="n">
@@ -5882,7 +5933,7 @@
         <v>82683.773630833</v>
       </c>
       <c r="X15" s="108" t="n">
-        <f aca="false">W15-COMPARATIVO!I$31</f>
+        <f aca="false">W15-COMPARATIVO!I$34</f>
         <v>61603.233630833</v>
       </c>
       <c r="Y15" s="108" t="n">
@@ -5894,7 +5945,7 @@
         <v>81688.351378768</v>
       </c>
       <c r="AA15" s="108" t="n">
-        <f aca="false">Z15-COMPARATIVO!J$31</f>
+        <f aca="false">Z15-COMPARATIVO!J$34</f>
         <v>60455.351378768</v>
       </c>
       <c r="AB15" s="108" t="n">
@@ -5906,7 +5957,7 @@
         <v>82683.773630833</v>
       </c>
       <c r="AD15" s="108" t="n">
-        <f aca="false">AC15-COMPARATIVO!K$31</f>
+        <f aca="false">AC15-COMPARATIVO!K$34</f>
         <v>63293.773630833</v>
       </c>
       <c r="AE15" s="108" t="n">
@@ -5918,7 +5969,7 @@
         <v>67110.2475445575</v>
       </c>
       <c r="AG15" s="108" t="n">
-        <f aca="false">AF15-COMPARATIVO!L$31</f>
+        <f aca="false">AF15-COMPARATIVO!L$34</f>
         <v>47168.2475445575</v>
       </c>
     </row>
@@ -5939,7 +5990,7 @@
         <v>94195.4339369339</v>
       </c>
       <c r="F16" s="105" t="n">
-        <f aca="false">E16-COMPARATIVO!C$31</f>
+        <f aca="false">E16-COMPARATIVO!C$34</f>
         <v>64396.7339369339</v>
       </c>
       <c r="G16" s="105" t="n">
@@ -5951,7 +6002,7 @@
         <v>94195.4339369339</v>
       </c>
       <c r="I16" s="105" t="n">
-        <f aca="false">H16-COMPARATIVO!D$31</f>
+        <f aca="false">H16-COMPARATIVO!D$34</f>
         <v>65317.5339369339</v>
       </c>
       <c r="J16" s="105" t="n">
@@ -5963,7 +6014,7 @@
         <v>93936.796150787</v>
       </c>
       <c r="L16" s="105" t="n">
-        <f aca="false">K16-COMPARATIVO!E$31</f>
+        <f aca="false">K16-COMPARATIVO!E$34</f>
         <v>75416.456150787</v>
       </c>
       <c r="M16" s="105" t="n">
@@ -5975,7 +6026,7 @@
         <v>93936.796150787</v>
       </c>
       <c r="O16" s="105" t="n">
-        <f aca="false">N16-COMPARATIVO!F$31</f>
+        <f aca="false">N16-COMPARATIVO!F$34</f>
         <v>74416.456150787</v>
       </c>
       <c r="P16" s="105" t="n">
@@ -5987,7 +6038,7 @@
         <v>83740.7520992964</v>
       </c>
       <c r="R16" s="105" t="n">
-        <f aca="false">Q16-COMPARATIVO!G$31</f>
+        <f aca="false">Q16-COMPARATIVO!G$34</f>
         <v>62391.8420992964</v>
       </c>
       <c r="S16" s="105" t="n">
@@ -5999,7 +6050,7 @@
         <v>72386.4792048822</v>
       </c>
       <c r="U16" s="105" t="n">
-        <f aca="false">T16-COMPARATIVO!H$31</f>
+        <f aca="false">T16-COMPARATIVO!H$34</f>
         <v>57498.8392048822</v>
       </c>
       <c r="V16" s="105" t="n">
@@ -6011,7 +6062,7 @@
         <v>94195.4339369339</v>
       </c>
       <c r="X16" s="105" t="n">
-        <f aca="false">W16-COMPARATIVO!I$31</f>
+        <f aca="false">W16-COMPARATIVO!I$34</f>
         <v>73114.8939369339</v>
       </c>
       <c r="Y16" s="105" t="n">
@@ -6023,7 +6074,7 @@
         <v>93061.4238782931</v>
       </c>
       <c r="AA16" s="105" t="n">
-        <f aca="false">Z16-COMPARATIVO!J$31</f>
+        <f aca="false">Z16-COMPARATIVO!J$34</f>
         <v>71828.4238782931</v>
       </c>
       <c r="AB16" s="105" t="n">
@@ -6035,7 +6086,7 @@
         <v>94195.4339369339</v>
       </c>
       <c r="AD16" s="105" t="n">
-        <f aca="false">AC16-COMPARATIVO!K$31</f>
+        <f aca="false">AC16-COMPARATIVO!K$34</f>
         <v>74805.4339369339</v>
       </c>
       <c r="AE16" s="105" t="n">
@@ -6047,7 +6098,7 @@
         <v>76453.6814357171</v>
       </c>
       <c r="AG16" s="105" t="n">
-        <f aca="false">AF16-COMPARATIVO!L$31</f>
+        <f aca="false">AF16-COMPARATIVO!L$34</f>
         <v>56511.6814357171</v>
       </c>
     </row>
@@ -6068,7 +6119,7 @@
         <v>106457.481820088</v>
       </c>
       <c r="F17" s="105" t="n">
-        <f aca="false">E17-COMPARATIVO!C$31</f>
+        <f aca="false">E17-COMPARATIVO!C$34</f>
         <v>76658.781820088</v>
       </c>
       <c r="G17" s="105" t="n">
@@ -6080,7 +6131,7 @@
         <v>106457.481820088</v>
       </c>
       <c r="I17" s="105" t="n">
-        <f aca="false">H17-COMPARATIVO!D$31</f>
+        <f aca="false">H17-COMPARATIVO!D$34</f>
         <v>77579.581820088</v>
       </c>
       <c r="J17" s="105" t="n">
@@ -6092,7 +6143,7 @@
         <v>106165.175428303</v>
       </c>
       <c r="L17" s="105" t="n">
-        <f aca="false">K17-COMPARATIVO!E$31</f>
+        <f aca="false">K17-COMPARATIVO!E$34</f>
         <v>87644.8354283031</v>
       </c>
       <c r="M17" s="105" t="n">
@@ -6104,7 +6155,7 @@
         <v>106165.175428303</v>
       </c>
       <c r="O17" s="105" t="n">
-        <f aca="false">N17-COMPARATIVO!F$31</f>
+        <f aca="false">N17-COMPARATIVO!F$34</f>
         <v>86644.8354283031</v>
       </c>
       <c r="P17" s="105" t="n">
@@ -6116,7 +6167,7 @@
         <v>94641.8443189086</v>
       </c>
       <c r="R17" s="105" t="n">
-        <f aca="false">Q17-COMPARATIVO!G$31</f>
+        <f aca="false">Q17-COMPARATIVO!G$34</f>
         <v>73292.9343189086</v>
       </c>
       <c r="S17" s="105" t="n">
@@ -6128,7 +6179,7 @@
         <v>81809.509993163</v>
       </c>
       <c r="U17" s="105" t="n">
-        <f aca="false">T17-COMPARATIVO!H$31</f>
+        <f aca="false">T17-COMPARATIVO!H$34</f>
         <v>66921.869993163</v>
       </c>
       <c r="V17" s="105" t="n">
@@ -6140,7 +6191,7 @@
         <v>106457.481820088</v>
       </c>
       <c r="X17" s="105" t="n">
-        <f aca="false">W17-COMPARATIVO!I$31</f>
+        <f aca="false">W17-COMPARATIVO!I$34</f>
         <v>85376.941820088</v>
       </c>
       <c r="Y17" s="105" t="n">
@@ -6152,7 +6203,7 @@
         <v>105175.8501087</v>
       </c>
       <c r="AA17" s="105" t="n">
-        <f aca="false">Z17-COMPARATIVO!J$31</f>
+        <f aca="false">Z17-COMPARATIVO!J$34</f>
         <v>83942.8501086998</v>
       </c>
       <c r="AB17" s="105" t="n">
@@ -6164,7 +6215,7 @@
         <v>106457.481820088</v>
       </c>
       <c r="AD17" s="105" t="n">
-        <f aca="false">AC17-COMPARATIVO!K$31</f>
+        <f aca="false">AC17-COMPARATIVO!K$34</f>
         <v>87067.481820088</v>
       </c>
       <c r="AE17" s="105" t="n">
@@ -6176,7 +6227,7 @@
         <v>86406.1670650719</v>
       </c>
       <c r="AG17" s="105" t="n">
-        <f aca="false">AF17-COMPARATIVO!L$31</f>
+        <f aca="false">AF17-COMPARATIVO!L$34</f>
         <v>66464.1670650719</v>
       </c>
     </row>
@@ -6197,7 +6248,7 @@
         <v>119518.831294506</v>
       </c>
       <c r="F18" s="105" t="n">
-        <f aca="false">E18-COMPARATIVO!C$31</f>
+        <f aca="false">E18-COMPARATIVO!C$34</f>
         <v>89720.1312945055</v>
       </c>
       <c r="G18" s="105" t="n">
@@ -6209,7 +6260,7 @@
         <v>119518.831294506</v>
       </c>
       <c r="I18" s="105" t="n">
-        <f aca="false">H18-COMPARATIVO!D$31</f>
+        <f aca="false">H18-COMPARATIVO!D$34</f>
         <v>90640.9312945055</v>
       </c>
       <c r="J18" s="105" t="n">
@@ -6221,7 +6272,7 @@
         <v>119190.661609024</v>
       </c>
       <c r="L18" s="105" t="n">
-        <f aca="false">K18-COMPARATIVO!E$31</f>
+        <f aca="false">K18-COMPARATIVO!E$34</f>
         <v>100670.321609024</v>
       </c>
       <c r="M18" s="105" t="n">
@@ -6233,7 +6284,7 @@
         <v>119190.661609024</v>
       </c>
       <c r="O18" s="105" t="n">
-        <f aca="false">N18-COMPARATIVO!F$31</f>
+        <f aca="false">N18-COMPARATIVO!F$34</f>
         <v>99670.321609024</v>
       </c>
       <c r="P18" s="105" t="n">
@@ -6245,7 +6296,7 @@
         <v>106253.524234856</v>
       </c>
       <c r="R18" s="105" t="n">
-        <f aca="false">Q18-COMPARATIVO!G$31</f>
+        <f aca="false">Q18-COMPARATIVO!G$34</f>
         <v>84904.6142348563</v>
       </c>
       <c r="S18" s="105" t="n">
@@ -6257,7 +6308,7 @@
         <v>91846.781043378</v>
       </c>
       <c r="U18" s="105" t="n">
-        <f aca="false">T18-COMPARATIVO!H$31</f>
+        <f aca="false">T18-COMPARATIVO!H$34</f>
         <v>76959.141043378</v>
       </c>
       <c r="V18" s="105" t="n">
@@ -6269,7 +6320,7 @@
         <v>119518.831294506</v>
       </c>
       <c r="X18" s="105" t="n">
-        <f aca="false">W18-COMPARATIVO!I$31</f>
+        <f aca="false">W18-COMPARATIVO!I$34</f>
         <v>98438.2912945055</v>
       </c>
       <c r="Y18" s="105" t="n">
@@ -6281,7 +6332,7 @@
         <v>118079.955212936</v>
       </c>
       <c r="AA18" s="105" t="n">
-        <f aca="false">Z18-COMPARATIVO!J$31</f>
+        <f aca="false">Z18-COMPARATIVO!J$34</f>
         <v>96846.9552129356</v>
       </c>
       <c r="AB18" s="105" t="n">
@@ -6293,7 +6344,7 @@
         <v>119518.831294506</v>
       </c>
       <c r="AD18" s="105" t="n">
-        <f aca="false">AC18-COMPARATIVO!K$31</f>
+        <f aca="false">AC18-COMPARATIVO!K$34</f>
         <v>100128.831294506</v>
       </c>
       <c r="AE18" s="105" t="n">
@@ -6305,7 +6356,7 @@
         <v>97007.4054701762</v>
       </c>
       <c r="AG18" s="105" t="n">
-        <f aca="false">AF18-COMPARATIVO!L$31</f>
+        <f aca="false">AF18-COMPARATIVO!L$34</f>
         <v>77065.4054701762</v>
       </c>
     </row>
@@ -6326,7 +6377,7 @@
         <v>133431.584834413</v>
       </c>
       <c r="F19" s="105" t="n">
-        <f aca="false">E19-COMPARATIVO!C$31</f>
+        <f aca="false">E19-COMPARATIVO!C$34</f>
         <v>103632.884834413</v>
       </c>
       <c r="G19" s="105" t="n">
@@ -6338,7 +6389,7 @@
         <v>133431.584834413</v>
       </c>
       <c r="I19" s="105" t="n">
-        <f aca="false">H19-COMPARATIVO!D$31</f>
+        <f aca="false">H19-COMPARATIVO!D$34</f>
         <v>104553.684834413</v>
       </c>
       <c r="J19" s="105" t="n">
@@ -6350,7 +6401,7 @@
         <v>133065.214106435</v>
       </c>
       <c r="L19" s="105" t="n">
-        <f aca="false">K19-COMPARATIVO!E$31</f>
+        <f aca="false">K19-COMPARATIVO!E$34</f>
         <v>114544.874106435</v>
       </c>
       <c r="M19" s="105" t="n">
@@ -6362,7 +6413,7 @@
         <v>133065.214106435</v>
       </c>
       <c r="O19" s="105" t="n">
-        <f aca="false">N19-COMPARATIVO!F$31</f>
+        <f aca="false">N19-COMPARATIVO!F$34</f>
         <v>113544.874106435</v>
       </c>
       <c r="P19" s="105" t="n">
@@ -6374,7 +6425,7 @@
         <v>118622.111506125</v>
       </c>
       <c r="R19" s="105" t="n">
-        <f aca="false">Q19-COMPARATIVO!G$31</f>
+        <f aca="false">Q19-COMPARATIVO!G$34</f>
         <v>97273.201506125</v>
       </c>
       <c r="S19" s="105" t="n">
@@ -6386,7 +6437,7 @@
         <v>102538.331607001</v>
       </c>
       <c r="U19" s="105" t="n">
-        <f aca="false">T19-COMPARATIVO!H$31</f>
+        <f aca="false">T19-COMPARATIVO!H$34</f>
         <v>87650.6916070012</v>
       </c>
       <c r="V19" s="105" t="n">
@@ -6398,7 +6449,7 @@
         <v>133431.584834413</v>
       </c>
       <c r="X19" s="105" t="n">
-        <f aca="false">W19-COMPARATIVO!I$31</f>
+        <f aca="false">W19-COMPARATIVO!I$34</f>
         <v>112351.044834413</v>
       </c>
       <c r="Y19" s="105" t="n">
@@ -6410,7 +6461,7 @@
         <v>131825.214408391</v>
       </c>
       <c r="AA19" s="105" t="n">
-        <f aca="false">Z19-COMPARATIVO!J$31</f>
+        <f aca="false">Z19-COMPARATIVO!J$34</f>
         <v>110592.214408391</v>
       </c>
       <c r="AB19" s="105" t="n">
@@ -6422,7 +6473,7 @@
         <v>133431.584834413</v>
       </c>
       <c r="AD19" s="105" t="n">
-        <f aca="false">AC19-COMPARATIVO!K$31</f>
+        <f aca="false">AC19-COMPARATIVO!K$34</f>
         <v>114041.584834413</v>
       </c>
       <c r="AE19" s="105" t="n">
@@ -6434,7 +6485,7 @@
         <v>108299.685600717</v>
       </c>
       <c r="AG19" s="105" t="n">
-        <f aca="false">AF19-COMPARATIVO!L$31</f>
+        <f aca="false">AF19-COMPARATIVO!L$34</f>
         <v>88357.6856007172</v>
       </c>
     </row>
@@ -6455,7 +6506,7 @@
         <v>148251.241213819</v>
       </c>
       <c r="F20" s="105" t="n">
-        <f aca="false">E20-COMPARATIVO!C$31</f>
+        <f aca="false">E20-COMPARATIVO!C$34</f>
         <v>118452.541213819</v>
       </c>
       <c r="G20" s="105" t="n">
@@ -6467,7 +6518,7 @@
         <v>148251.241213819</v>
       </c>
       <c r="I20" s="105" t="n">
-        <f aca="false">H20-COMPARATIVO!D$31</f>
+        <f aca="false">H20-COMPARATIVO!D$34</f>
         <v>119373.341213819</v>
       </c>
       <c r="J20" s="105" t="n">
@@ -6479,7 +6530,7 @@
         <v>147844.17930839</v>
       </c>
       <c r="L20" s="105" t="n">
-        <f aca="false">K20-COMPARATIVO!E$31</f>
+        <f aca="false">K20-COMPARATIVO!E$34</f>
         <v>129323.83930839</v>
       </c>
       <c r="M20" s="105" t="n">
@@ -6491,7 +6542,7 @@
         <v>147844.17930839</v>
       </c>
       <c r="O20" s="105" t="n">
-        <f aca="false">N20-COMPARATIVO!F$31</f>
+        <f aca="false">N20-COMPARATIVO!F$34</f>
         <v>128323.83930839</v>
       </c>
       <c r="P20" s="105" t="n">
@@ -6503,7 +6554,7 @@
         <v>131796.945138671</v>
       </c>
       <c r="R20" s="105" t="n">
-        <f aca="false">Q20-COMPARATIVO!G$31</f>
+        <f aca="false">Q20-COMPARATIVO!G$34</f>
         <v>110448.035138671</v>
       </c>
       <c r="S20" s="105" t="n">
@@ -6515,7 +6566,7 @@
         <v>113926.810894114</v>
       </c>
       <c r="U20" s="105" t="n">
-        <f aca="false">T20-COMPARATIVO!H$31</f>
+        <f aca="false">T20-COMPARATIVO!H$34</f>
         <v>99039.1708941142</v>
       </c>
       <c r="V20" s="105" t="n">
@@ -6527,7 +6578,7 @@
         <v>148251.241213819</v>
       </c>
       <c r="X20" s="105" t="n">
-        <f aca="false">W20-COMPARATIVO!I$31</f>
+        <f aca="false">W20-COMPARATIVO!I$34</f>
         <v>127170.701213819</v>
       </c>
       <c r="Y20" s="105" t="n">
@@ -6539,7 +6590,7 @@
         <v>146466.458324502</v>
       </c>
       <c r="AA20" s="105" t="n">
-        <f aca="false">Z20-COMPARATIVO!J$31</f>
+        <f aca="false">Z20-COMPARATIVO!J$34</f>
         <v>125233.458324502</v>
       </c>
       <c r="AB20" s="105" t="n">
@@ -6551,7 +6602,7 @@
         <v>148251.241213819</v>
       </c>
       <c r="AD20" s="105" t="n">
-        <f aca="false">AC20-COMPARATIVO!K$31</f>
+        <f aca="false">AC20-COMPARATIVO!K$34</f>
         <v>128861.241213819</v>
       </c>
       <c r="AE20" s="105" t="n">
@@ -6563,7 +6614,7 @@
         <v>120328.053011568</v>
       </c>
       <c r="AG20" s="105" t="n">
-        <f aca="false">AF20-COMPARATIVO!L$31</f>
+        <f aca="false">AF20-COMPARATIVO!L$34</f>
         <v>100386.053011568</v>
       </c>
     </row>
@@ -6584,7 +6635,7 @@
         <v>164036.916894317</v>
       </c>
       <c r="F21" s="105" t="n">
-        <f aca="false">E21-COMPARATIVO!C$31</f>
+        <f aca="false">E21-COMPARATIVO!C$34</f>
         <v>134238.216894317</v>
       </c>
       <c r="G21" s="105" t="n">
@@ -6596,7 +6647,7 @@
         <v>164036.916894317</v>
       </c>
       <c r="I21" s="105" t="n">
-        <f aca="false">H21-COMPARATIVO!D$31</f>
+        <f aca="false">H21-COMPARATIVO!D$34</f>
         <v>135159.016894317</v>
       </c>
       <c r="J21" s="105" t="n">
@@ -6608,7 +6659,7 @@
         <v>163586.511357035</v>
       </c>
       <c r="L21" s="105" t="n">
-        <f aca="false">K21-COMPARATIVO!E$31</f>
+        <f aca="false">K21-COMPARATIVO!E$34</f>
         <v>145066.171357035</v>
       </c>
       <c r="M21" s="105" t="n">
@@ -6620,7 +6671,7 @@
         <v>163586.511357035</v>
       </c>
       <c r="O21" s="105" t="n">
-        <f aca="false">N21-COMPARATIVO!F$31</f>
+        <f aca="false">N21-COMPARATIVO!F$34</f>
         <v>144066.171357035</v>
       </c>
       <c r="P21" s="105" t="n">
@@ -6632,7 +6683,7 @@
         <v>145830.580301555</v>
       </c>
       <c r="R21" s="105" t="n">
-        <f aca="false">Q21-COMPARATIVO!G$31</f>
+        <f aca="false">Q21-COMPARATIVO!G$34</f>
         <v>124481.670301555</v>
       </c>
       <c r="S21" s="105" t="n">
@@ -6644,7 +6695,7 @@
         <v>126057.648203558</v>
       </c>
       <c r="U21" s="105" t="n">
-        <f aca="false">T21-COMPARATIVO!H$31</f>
+        <f aca="false">T21-COMPARATIVO!H$34</f>
         <v>111170.008203558</v>
       </c>
       <c r="V21" s="105" t="n">
@@ -6656,7 +6707,7 @@
         <v>164036.916894317</v>
       </c>
       <c r="X21" s="105" t="n">
-        <f aca="false">W21-COMPARATIVO!I$31</f>
+        <f aca="false">W21-COMPARATIVO!I$34</f>
         <v>142956.376894317</v>
       </c>
       <c r="Y21" s="105" t="n">
@@ -6668,7 +6719,7 @@
         <v>162062.091725285</v>
       </c>
       <c r="AA21" s="105" t="n">
-        <f aca="false">Z21-COMPARATIVO!J$31</f>
+        <f aca="false">Z21-COMPARATIVO!J$34</f>
         <v>140829.091725285</v>
       </c>
       <c r="AB21" s="105" t="n">
@@ -6680,7 +6731,7 @@
         <v>164036.916894317</v>
       </c>
       <c r="AD21" s="105" t="n">
-        <f aca="false">AC21-COMPARATIVO!K$31</f>
+        <f aca="false">AC21-COMPARATIVO!K$34</f>
         <v>144646.916894317</v>
       </c>
       <c r="AE21" s="105" t="n">
@@ -6692,7 +6743,7 @@
         <v>133140.489552094</v>
       </c>
       <c r="AG21" s="105" t="n">
-        <f aca="false">AF21-COMPARATIVO!L$31</f>
+        <f aca="false">AF21-COMPARATIVO!L$34</f>
         <v>113198.489552094</v>
       </c>
     </row>
@@ -6713,7 +6764,7 @@
         <v>180851.581844048</v>
       </c>
       <c r="F22" s="105" t="n">
-        <f aca="false">E22-COMPARATIVO!C$31</f>
+        <f aca="false">E22-COMPARATIVO!C$34</f>
         <v>151052.881844048</v>
       </c>
       <c r="G22" s="105" t="n">
@@ -6725,7 +6776,7 @@
         <v>180851.581844048</v>
       </c>
       <c r="I22" s="105" t="n">
-        <f aca="false">H22-COMPARATIVO!D$31</f>
+        <f aca="false">H22-COMPARATIVO!D$34</f>
         <v>151973.681844048</v>
       </c>
       <c r="J22" s="105" t="n">
@@ -6737,7 +6788,7 @@
         <v>180355.00732027</v>
       </c>
       <c r="L22" s="105" t="n">
-        <f aca="false">K22-COMPARATIVO!E$31</f>
+        <f aca="false">K22-COMPARATIVO!E$34</f>
         <v>161834.66732027</v>
       </c>
       <c r="M22" s="105" t="n">
@@ -6749,7 +6800,7 @@
         <v>180355.00732027</v>
       </c>
       <c r="O22" s="105" t="n">
-        <f aca="false">N22-COMPARATIVO!F$31</f>
+        <f aca="false">N22-COMPARATIVO!F$34</f>
         <v>160834.66732027</v>
       </c>
       <c r="P22" s="105" t="n">
@@ -6761,7 +6812,7 @@
         <v>160778.997972532</v>
       </c>
       <c r="R22" s="105" t="n">
-        <f aca="false">Q22-COMPARATIVO!G$31</f>
+        <f aca="false">Q22-COMPARATIVO!G$34</f>
         <v>139430.087972532</v>
       </c>
       <c r="S22" s="105" t="n">
@@ -6773,7 +6824,7 @@
         <v>138979.234143017</v>
       </c>
       <c r="U22" s="105" t="n">
-        <f aca="false">T22-COMPARATIVO!H$31</f>
+        <f aca="false">T22-COMPARATIVO!H$34</f>
         <v>124091.594143017</v>
       </c>
       <c r="V22" s="105" t="n">
@@ -6785,7 +6836,7 @@
         <v>180851.581844048</v>
       </c>
       <c r="X22" s="105" t="n">
-        <f aca="false">W22-COMPARATIVO!I$31</f>
+        <f aca="false">W22-COMPARATIVO!I$34</f>
         <v>159771.041844048</v>
       </c>
       <c r="Y22" s="105" t="n">
@@ -6797,7 +6848,7 @@
         <v>178674.326489298</v>
       </c>
       <c r="AA22" s="105" t="n">
-        <f aca="false">Z22-COMPARATIVO!J$31</f>
+        <f aca="false">Z22-COMPARATIVO!J$34</f>
         <v>157441.326489298</v>
       </c>
       <c r="AB22" s="105" t="n">
@@ -6809,7 +6860,7 @@
         <v>180851.581844048</v>
       </c>
       <c r="AD22" s="105" t="n">
-        <f aca="false">AC22-COMPARATIVO!K$31</f>
+        <f aca="false">AC22-COMPARATIVO!K$34</f>
         <v>161461.581844048</v>
       </c>
       <c r="AE22" s="105" t="n">
@@ -6821,7 +6872,7 @@
         <v>146788.104768515</v>
       </c>
       <c r="AG22" s="105" t="n">
-        <f aca="false">AF22-COMPARATIVO!L$31</f>
+        <f aca="false">AF22-COMPARATIVO!L$34</f>
         <v>126846.104768515</v>
       </c>
     </row>
@@ -6842,7 +6893,7 @@
         <v>198762.310728528</v>
       </c>
       <c r="F23" s="105" t="n">
-        <f aca="false">E23-COMPARATIVO!C$31</f>
+        <f aca="false">E23-COMPARATIVO!C$34</f>
         <v>168963.610728528</v>
       </c>
       <c r="G23" s="105" t="n">
@@ -6854,7 +6905,7 @@
         <v>198762.310728528</v>
       </c>
       <c r="I23" s="105" t="n">
-        <f aca="false">H23-COMPARATIVO!D$31</f>
+        <f aca="false">H23-COMPARATIVO!D$34</f>
         <v>169884.410728528</v>
       </c>
       <c r="J23" s="105" t="n">
@@ -6866,7 +6917,7 @@
         <v>198216.557692869</v>
       </c>
       <c r="L23" s="105" t="n">
-        <f aca="false">K23-COMPARATIVO!E$31</f>
+        <f aca="false">K23-COMPARATIVO!E$34</f>
         <v>179696.217692869</v>
       </c>
       <c r="M23" s="105" t="n">
@@ -6878,7 +6929,7 @@
         <v>198216.557692869</v>
       </c>
       <c r="O23" s="105" t="n">
-        <f aca="false">N23-COMPARATIVO!F$31</f>
+        <f aca="false">N23-COMPARATIVO!F$34</f>
         <v>178696.217692869</v>
       </c>
       <c r="P23" s="105" t="n">
@@ -6890,7 +6941,7 @@
         <v>176701.828249391</v>
       </c>
       <c r="R23" s="105" t="n">
-        <f aca="false">Q23-COMPARATIVO!G$31</f>
+        <f aca="false">Q23-COMPARATIVO!G$34</f>
         <v>155352.918249391</v>
       </c>
       <c r="S23" s="105" t="n">
@@ -6902,7 +6953,7 @@
         <v>152743.11366194</v>
       </c>
       <c r="U23" s="105" t="n">
-        <f aca="false">T23-COMPARATIVO!H$31</f>
+        <f aca="false">T23-COMPARATIVO!H$34</f>
         <v>137855.47366194</v>
       </c>
       <c r="V23" s="105" t="n">
@@ -6914,7 +6965,7 @@
         <v>198762.310728528</v>
       </c>
       <c r="X23" s="105" t="n">
-        <f aca="false">W23-COMPARATIVO!I$31</f>
+        <f aca="false">W23-COMPARATIVO!I$34</f>
         <v>177681.770728528</v>
       </c>
       <c r="Y23" s="105" t="n">
@@ -6926,7 +6977,7 @@
         <v>196369.429776403</v>
       </c>
       <c r="AA23" s="105" t="n">
-        <f aca="false">Z23-COMPARATIVO!J$31</f>
+        <f aca="false">Z23-COMPARATIVO!J$34</f>
         <v>175136.429776403</v>
       </c>
       <c r="AB23" s="105" t="n">
@@ -6938,7 +6989,7 @@
         <v>198762.310728528</v>
       </c>
       <c r="AD23" s="105" t="n">
-        <f aca="false">AC23-COMPARATIVO!K$31</f>
+        <f aca="false">AC23-COMPARATIVO!K$34</f>
         <v>179372.310728528</v>
       </c>
       <c r="AE23" s="105" t="n">
@@ -6950,7 +7001,7 @@
         <v>161325.339782818</v>
       </c>
       <c r="AG23" s="105" t="n">
-        <f aca="false">AF23-COMPARATIVO!L$31</f>
+        <f aca="false">AF23-COMPARATIVO!L$34</f>
         <v>141383.339782818</v>
       </c>
     </row>
@@ -6971,7 +7022,7 @@
         <v>217840.550475342</v>
       </c>
       <c r="F24" s="105" t="n">
-        <f aca="false">E24-COMPARATIVO!C$31</f>
+        <f aca="false">E24-COMPARATIVO!C$34</f>
         <v>188041.850475342</v>
       </c>
       <c r="G24" s="105" t="n">
@@ -6983,7 +7034,7 @@
         <v>217840.550475342</v>
       </c>
       <c r="I24" s="105" t="n">
-        <f aca="false">H24-COMPARATIVO!D$31</f>
+        <f aca="false">H24-COMPARATIVO!D$34</f>
         <v>188962.650475342</v>
       </c>
       <c r="J24" s="105" t="n">
@@ -6995,7 +7046,7 @@
         <v>217242.413226506</v>
       </c>
       <c r="L24" s="105" t="n">
-        <f aca="false">K24-COMPARATIVO!E$31</f>
+        <f aca="false">K24-COMPARATIVO!E$34</f>
         <v>198722.073226506</v>
       </c>
       <c r="M24" s="105" t="n">
@@ -7007,7 +7058,7 @@
         <v>217242.413226506</v>
       </c>
       <c r="O24" s="105" t="n">
-        <f aca="false">N24-COMPARATIVO!F$31</f>
+        <f aca="false">N24-COMPARATIVO!F$34</f>
         <v>197722.073226506</v>
       </c>
       <c r="P24" s="105" t="n">
@@ -7019,7 +7070,7 @@
         <v>193662.588217847</v>
       </c>
       <c r="R24" s="105" t="n">
-        <f aca="false">Q24-COMPARATIVO!G$31</f>
+        <f aca="false">Q24-COMPARATIVO!G$34</f>
         <v>172313.678217847</v>
       </c>
       <c r="S24" s="105" t="n">
@@ -7031,7 +7082,7 @@
         <v>167404.191667305</v>
       </c>
       <c r="U24" s="105" t="n">
-        <f aca="false">T24-COMPARATIVO!H$31</f>
+        <f aca="false">T24-COMPARATIVO!H$34</f>
         <v>152516.551667305</v>
       </c>
       <c r="V24" s="105" t="n">
@@ -7043,7 +7094,7 @@
         <v>217840.550475342</v>
       </c>
       <c r="X24" s="105" t="n">
-        <f aca="false">W24-COMPARATIVO!I$31</f>
+        <f aca="false">W24-COMPARATIVO!I$34</f>
         <v>196760.010475342</v>
       </c>
       <c r="Y24" s="105" t="n">
@@ -7055,7 +7106,7 @@
         <v>215217.988371278</v>
       </c>
       <c r="AA24" s="105" t="n">
-        <f aca="false">Z24-COMPARATIVO!J$31</f>
+        <f aca="false">Z24-COMPARATIVO!J$34</f>
         <v>193984.988371278</v>
       </c>
       <c r="AB24" s="105" t="n">
@@ -7067,7 +7118,7 @@
         <v>217840.550475342</v>
       </c>
       <c r="AD24" s="105" t="n">
-        <f aca="false">AC24-COMPARATIVO!K$31</f>
+        <f aca="false">AC24-COMPARATIVO!K$34</f>
         <v>198450.550475342</v>
       </c>
       <c r="AE24" s="105" t="n">
@@ -7079,7 +7130,7 @@
         <v>176810.184461529</v>
       </c>
       <c r="AG24" s="105" t="n">
-        <f aca="false">AF24-COMPARATIVO!L$31</f>
+        <f aca="false">AF24-COMPARATIVO!L$34</f>
         <v>156868.184461529</v>
       </c>
     </row>
@@ -7100,7 +7151,7 @@
         <v>238162.405280052</v>
       </c>
       <c r="F25" s="108" t="n">
-        <f aca="false">E25-COMPARATIVO!C$31</f>
+        <f aca="false">E25-COMPARATIVO!C$34</f>
         <v>208363.705280052</v>
       </c>
       <c r="G25" s="108" t="n">
@@ -7112,7 +7163,7 @@
         <v>238162.405280052</v>
       </c>
       <c r="I25" s="108" t="n">
-        <f aca="false">H25-COMPARATIVO!D$31</f>
+        <f aca="false">H25-COMPARATIVO!D$34</f>
         <v>209284.505280052</v>
       </c>
       <c r="J25" s="108" t="n">
@@ -7124,7 +7175,7 @@
         <v>237508.469153103</v>
       </c>
       <c r="L25" s="108" t="n">
-        <f aca="false">K25-COMPARATIVO!E$31</f>
+        <f aca="false">K25-COMPARATIVO!E$34</f>
         <v>218988.129153103</v>
       </c>
       <c r="M25" s="108" t="n">
@@ -7136,7 +7187,7 @@
         <v>237508.469153103</v>
       </c>
       <c r="O25" s="108" t="n">
-        <f aca="false">N25-COMPARATIVO!F$31</f>
+        <f aca="false">N25-COMPARATIVO!F$34</f>
         <v>217988.129153103</v>
       </c>
       <c r="P25" s="108" t="n">
@@ -7148,7 +7199,7 @@
         <v>211728.935324847</v>
       </c>
       <c r="R25" s="108" t="n">
-        <f aca="false">Q25-COMPARATIVO!G$31</f>
+        <f aca="false">Q25-COMPARATIVO!G$34</f>
         <v>190380.025324847</v>
       </c>
       <c r="S25" s="108" t="n">
@@ -7160,7 +7211,7 @@
         <v>183020.952042449</v>
       </c>
       <c r="U25" s="108" t="n">
-        <f aca="false">T25-COMPARATIVO!H$31</f>
+        <f aca="false">T25-COMPARATIVO!H$34</f>
         <v>168133.312042449</v>
       </c>
       <c r="V25" s="108" t="n">
@@ -7172,7 +7223,7 @@
         <v>238162.405280052</v>
       </c>
       <c r="X25" s="108" t="n">
-        <f aca="false">W25-COMPARATIVO!I$31</f>
+        <f aca="false">W25-COMPARATIVO!I$34</f>
         <v>217081.865280052</v>
       </c>
       <c r="Y25" s="108" t="n">
@@ -7184,7 +7235,7 @@
         <v>235295.19025816</v>
       </c>
       <c r="AA25" s="108" t="n">
-        <f aca="false">Z25-COMPARATIVO!J$31</f>
+        <f aca="false">Z25-COMPARATIVO!J$34</f>
         <v>214062.19025816</v>
       </c>
       <c r="AB25" s="108" t="n">
@@ -7196,7 +7247,7 @@
         <v>238162.405280052</v>
       </c>
       <c r="AD25" s="108" t="n">
-        <f aca="false">AC25-COMPARATIVO!K$31</f>
+        <f aca="false">AC25-COMPARATIVO!K$34</f>
         <v>218772.405280052</v>
       </c>
       <c r="AE25" s="108" t="n">
@@ -7208,28 +7259,28 @@
         <v>193304.408740621</v>
       </c>
       <c r="AG25" s="108" t="n">
-        <f aca="false">AF25-COMPARATIVO!L$31</f>
+        <f aca="false">AF25-COMPARATIVO!L$34</f>
         <v>173362.408740621</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>864</v>
+        <v>881</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>866</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>867</v>
+        <v>884</v>
       </c>
     </row>
   </sheetData>
@@ -7263,23 +7314,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>868</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>869</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>870</v>
+        <v>887</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>871</v>
+        <v>888</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7287,25 +7338,25 @@
         <v>268</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>872</v>
+        <v>889</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>873</v>
+        <v>890</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>877</v>
+        <v>894</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>878</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7731,32 +7782,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>879</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>880</v>
+        <v>897</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>883</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7764,12 +7815,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -7800,32 +7851,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>888</v>
+        <v>905</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>891</v>
+        <v>908</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -7835,10 +7886,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>894</v>
+        <v>911</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E6" s="110"/>
     </row>
@@ -7847,10 +7898,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>896</v>
+        <v>913</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E7" s="110"/>
     </row>
@@ -7859,10 +7910,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>897</v>
+        <v>914</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E8" s="110"/>
     </row>
@@ -7871,17 +7922,17 @@
         <v>4</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>898</v>
+        <v>915</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E9" s="110"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
       <c r="C10" s="7" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -7891,10 +7942,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="111" t="s">
-        <v>900</v>
+        <v>917</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E11" s="110"/>
     </row>
@@ -7903,10 +7954,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E12" s="110"/>
     </row>
@@ -7915,10 +7966,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>902</v>
+        <v>919</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E13" s="110"/>
     </row>
@@ -7927,10 +7978,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>903</v>
+        <v>920</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E14" s="110"/>
     </row>
@@ -7939,10 +7990,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>904</v>
+        <v>921</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E15" s="110"/>
     </row>
@@ -7951,10 +8002,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>905</v>
+        <v>922</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E16" s="110"/>
     </row>
@@ -7963,10 +8014,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>906</v>
+        <v>923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E17" s="110"/>
     </row>
@@ -7975,10 +8026,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E19" s="110"/>
     </row>
@@ -7987,10 +8038,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E20" s="110"/>
     </row>
@@ -7999,10 +8050,10 @@
         <v>14</v>
       </c>
       <c r="C21" s="109" t="s">
-        <v>909</v>
+        <v>926</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E21" s="110"/>
     </row>
@@ -8011,10 +8062,10 @@
         <v>15</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>910</v>
+        <v>927</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E22" s="110"/>
     </row>
@@ -8023,10 +8074,10 @@
         <v>16</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>911</v>
+        <v>928</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E23" s="110"/>
     </row>
@@ -8035,10 +8086,10 @@
         <v>17</v>
       </c>
       <c r="C24" s="109" t="s">
+        <v>929</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>912</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>895</v>
       </c>
       <c r="E24" s="110"/>
     </row>
@@ -8047,17 +8098,17 @@
         <v>18</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>913</v>
+        <v>930</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E25" s="110"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="8"/>
       <c r="C26" s="7" t="s">
-        <v>914</v>
+        <v>931</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -8067,10 +8118,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E27" s="110"/>
     </row>
@@ -8079,10 +8130,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>916</v>
+        <v>933</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E28" s="110"/>
     </row>
@@ -8091,10 +8142,10 @@
         <v>21</v>
       </c>
       <c r="C29" s="109" t="s">
-        <v>917</v>
+        <v>934</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E29" s="110"/>
     </row>
@@ -8103,10 +8154,10 @@
         <v>22</v>
       </c>
       <c r="C30" s="109" t="s">
-        <v>918</v>
+        <v>935</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E30" s="110"/>
     </row>
@@ -8115,10 +8166,10 @@
         <v>23</v>
       </c>
       <c r="C31" s="109" t="s">
-        <v>919</v>
+        <v>936</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E31" s="110"/>
     </row>
@@ -8127,17 +8178,17 @@
         <v>24</v>
       </c>
       <c r="C32" s="111" t="s">
-        <v>920</v>
+        <v>937</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E32" s="110"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8"/>
       <c r="C34" s="7" t="s">
-        <v>921</v>
+        <v>938</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -8147,10 +8198,10 @@
         <v>25</v>
       </c>
       <c r="C35" s="109" t="s">
-        <v>922</v>
+        <v>939</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E35" s="110"/>
     </row>
@@ -8159,10 +8210,10 @@
         <v>26</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>923</v>
+        <v>940</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E36" s="110"/>
     </row>
@@ -8171,10 +8222,10 @@
         <v>27</v>
       </c>
       <c r="C37" s="109" t="s">
-        <v>924</v>
+        <v>941</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E37" s="110"/>
     </row>
@@ -8183,10 +8234,10 @@
         <v>28</v>
       </c>
       <c r="C38" s="109" t="s">
-        <v>925</v>
+        <v>942</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E38" s="110"/>
     </row>
@@ -8195,17 +8246,17 @@
         <v>29</v>
       </c>
       <c r="C39" s="111" t="s">
-        <v>926</v>
+        <v>943</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E39" s="110"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="8"/>
       <c r="C41" s="7" t="s">
-        <v>927</v>
+        <v>944</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -8215,10 +8266,10 @@
         <v>30</v>
       </c>
       <c r="C42" s="111" t="s">
-        <v>928</v>
+        <v>945</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E42" s="110"/>
     </row>
@@ -8227,10 +8278,10 @@
         <v>31</v>
       </c>
       <c r="C43" s="109" t="s">
-        <v>929</v>
+        <v>946</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E43" s="110"/>
     </row>
@@ -8239,10 +8290,10 @@
         <v>32</v>
       </c>
       <c r="C44" s="109" t="s">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E44" s="110"/>
     </row>
@@ -8251,17 +8302,17 @@
         <v>33</v>
       </c>
       <c r="C45" s="109" t="s">
-        <v>931</v>
+        <v>948</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E45" s="110"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="8"/>
       <c r="C47" s="7" t="s">
-        <v>932</v>
+        <v>949</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -8271,10 +8322,10 @@
         <v>34</v>
       </c>
       <c r="C48" s="109" t="s">
-        <v>933</v>
+        <v>950</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E48" s="110"/>
     </row>
@@ -8283,10 +8334,10 @@
         <v>35</v>
       </c>
       <c r="C49" s="109" t="s">
-        <v>934</v>
+        <v>951</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E49" s="110"/>
     </row>
@@ -8295,10 +8346,10 @@
         <v>36</v>
       </c>
       <c r="C50" s="109" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E50" s="110"/>
     </row>
@@ -8307,10 +8358,10 @@
         <v>37</v>
       </c>
       <c r="C51" s="109" t="s">
-        <v>936</v>
+        <v>953</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E51" s="110"/>
     </row>
@@ -8319,10 +8370,10 @@
         <v>38</v>
       </c>
       <c r="C52" s="109" t="s">
-        <v>937</v>
+        <v>954</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E52" s="110"/>
     </row>
@@ -8331,10 +8382,10 @@
         <v>39</v>
       </c>
       <c r="C53" s="109" t="s">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E53" s="110"/>
     </row>
@@ -8343,10 +8394,10 @@
         <v>40</v>
       </c>
       <c r="C54" s="109" t="s">
-        <v>939</v>
+        <v>956</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E54" s="110"/>
     </row>
@@ -8355,10 +8406,10 @@
         <v>41</v>
       </c>
       <c r="C55" s="109" t="s">
-        <v>940</v>
+        <v>957</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E55" s="110"/>
     </row>
@@ -8367,10 +8418,10 @@
         <v>42</v>
       </c>
       <c r="C56" s="109" t="s">
-        <v>941</v>
+        <v>958</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E56" s="110"/>
     </row>
@@ -8379,10 +8430,10 @@
         <v>43</v>
       </c>
       <c r="C57" s="109" t="s">
-        <v>942</v>
+        <v>959</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E57" s="110"/>
     </row>
@@ -8391,10 +8442,10 @@
         <v>44</v>
       </c>
       <c r="C58" s="109" t="s">
-        <v>943</v>
+        <v>960</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E58" s="110"/>
     </row>
@@ -8403,10 +8454,10 @@
         <v>45</v>
       </c>
       <c r="C59" s="109" t="s">
-        <v>944</v>
+        <v>961</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E59" s="110"/>
     </row>
@@ -8415,17 +8466,17 @@
         <v>46</v>
       </c>
       <c r="C60" s="109" t="s">
-        <v>945</v>
+        <v>962</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E60" s="110"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="8"/>
       <c r="C62" s="7" t="s">
-        <v>946</v>
+        <v>963</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -8435,10 +8486,10 @@
         <v>47</v>
       </c>
       <c r="C63" s="111" t="s">
-        <v>947</v>
+        <v>964</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E63" s="110"/>
     </row>
@@ -8447,10 +8498,10 @@
         <v>48</v>
       </c>
       <c r="C64" s="111" t="s">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E64" s="110"/>
     </row>
@@ -8459,10 +8510,10 @@
         <v>49</v>
       </c>
       <c r="C65" s="111" t="s">
-        <v>949</v>
+        <v>966</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E65" s="110"/>
     </row>
@@ -8471,10 +8522,10 @@
         <v>50</v>
       </c>
       <c r="C66" s="111" t="s">
-        <v>950</v>
+        <v>967</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E66" s="110"/>
     </row>
@@ -8483,10 +8534,10 @@
         <v>51</v>
       </c>
       <c r="C67" s="111" t="s">
-        <v>951</v>
+        <v>968</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E67" s="110"/>
     </row>
@@ -8495,10 +8546,10 @@
         <v>52</v>
       </c>
       <c r="C68" s="111" t="s">
-        <v>952</v>
+        <v>969</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E68" s="110"/>
     </row>
@@ -8507,10 +8558,10 @@
         <v>53</v>
       </c>
       <c r="C69" s="111" t="s">
-        <v>953</v>
+        <v>970</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E69" s="110"/>
     </row>
@@ -8519,10 +8570,10 @@
         <v>54</v>
       </c>
       <c r="C70" s="111" t="s">
-        <v>954</v>
+        <v>971</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E70" s="110"/>
     </row>
@@ -8531,17 +8582,17 @@
         <v>55</v>
       </c>
       <c r="C71" s="111" t="s">
-        <v>955</v>
+        <v>972</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E71" s="110"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="8"/>
       <c r="C73" s="7" t="s">
-        <v>956</v>
+        <v>973</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
@@ -8551,10 +8602,10 @@
         <v>56</v>
       </c>
       <c r="C74" s="111" t="s">
-        <v>957</v>
+        <v>974</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E74" s="110"/>
     </row>
@@ -8563,10 +8614,10 @@
         <v>57</v>
       </c>
       <c r="C75" s="111" t="s">
-        <v>958</v>
+        <v>975</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E75" s="110"/>
     </row>
@@ -8575,10 +8626,10 @@
         <v>58</v>
       </c>
       <c r="C76" s="111" t="s">
-        <v>959</v>
+        <v>976</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E76" s="110"/>
     </row>
@@ -8587,10 +8638,10 @@
         <v>59</v>
       </c>
       <c r="C77" s="111" t="s">
-        <v>960</v>
+        <v>977</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E77" s="110"/>
     </row>
@@ -8599,10 +8650,10 @@
         <v>60</v>
       </c>
       <c r="C78" s="111" t="s">
-        <v>961</v>
+        <v>978</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E78" s="110"/>
     </row>
@@ -8611,10 +8662,10 @@
         <v>61</v>
       </c>
       <c r="C79" s="111" t="s">
-        <v>962</v>
+        <v>979</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E79" s="110"/>
     </row>
@@ -8623,17 +8674,17 @@
         <v>62</v>
       </c>
       <c r="C80" s="111" t="s">
-        <v>963</v>
+        <v>980</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E80" s="110"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="8"/>
       <c r="C82" s="7" t="s">
-        <v>964</v>
+        <v>981</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
@@ -8643,10 +8694,10 @@
         <v>63</v>
       </c>
       <c r="C83" s="111" t="s">
-        <v>965</v>
+        <v>982</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E83" s="110"/>
     </row>
@@ -8655,10 +8706,10 @@
         <v>64</v>
       </c>
       <c r="C84" s="111" t="s">
-        <v>966</v>
+        <v>983</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E84" s="110"/>
     </row>
@@ -8667,10 +8718,10 @@
         <v>65</v>
       </c>
       <c r="C85" s="111" t="s">
-        <v>967</v>
+        <v>984</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E85" s="110"/>
     </row>
@@ -8679,10 +8730,10 @@
         <v>66</v>
       </c>
       <c r="C86" s="111" t="s">
-        <v>968</v>
+        <v>985</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E86" s="110"/>
     </row>
@@ -8691,10 +8742,10 @@
         <v>67</v>
       </c>
       <c r="C87" s="111" t="s">
-        <v>969</v>
+        <v>986</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="E87" s="110"/>
     </row>
@@ -8726,370 +8777,370 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>970</v>
+        <v>987</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>971</v>
+        <v>988</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>972</v>
+        <v>989</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>973</v>
+        <v>990</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>974</v>
+        <v>991</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>975</v>
+        <v>992</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>976</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>977</v>
+        <v>994</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="66" t="s">
-        <v>978</v>
+      <c r="F5" s="68" t="s">
+        <v>995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>979</v>
+        <v>996</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="66" t="s">
-        <v>980</v>
+      <c r="F6" s="68" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>981</v>
+        <v>998</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="66" t="s">
-        <v>982</v>
+      <c r="F7" s="68" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="48" t="s">
-        <v>983</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="66" t="s">
-        <v>984</v>
+      <c r="F8" s="68" t="s">
+        <v>1001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="66" t="s">
-        <v>985</v>
+      <c r="F9" s="68" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="66" t="s">
-        <v>986</v>
+      <c r="F10" s="68" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="66" t="s">
-        <v>988</v>
+      <c r="F11" s="68" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>989</v>
+        <v>1006</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="66" t="s">
-        <v>990</v>
+      <c r="F12" s="68" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="66" t="s">
-        <v>992</v>
+      <c r="F13" s="68" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="66" t="s">
-        <v>993</v>
+      <c r="F14" s="68" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="66" t="s">
-        <v>995</v>
+      <c r="F15" s="68" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>996</v>
+        <v>1013</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="66" t="s">
-        <v>997</v>
+      <c r="F16" s="68" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="66" t="s">
-        <v>998</v>
+      <c r="F17" s="68" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>999</v>
+        <v>1016</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="66" t="s">
-        <v>1000</v>
+      <c r="F18" s="68" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>1001</v>
+        <v>1018</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="66" t="s">
-        <v>1002</v>
+      <c r="F19" s="68" t="s">
+        <v>1019</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>1003</v>
+        <v>1020</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="66" t="s">
-        <v>1004</v>
+      <c r="F20" s="68" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>1005</v>
+        <v>1022</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="66" t="s">
-        <v>1006</v>
+      <c r="F21" s="68" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>1007</v>
+        <v>1024</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="66" t="s">
-        <v>1008</v>
+      <c r="F22" s="68" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>1009</v>
+        <v>1026</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="66" t="s">
-        <v>1010</v>
+      <c r="F23" s="68" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>1011</v>
+        <v>1028</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="66" t="s">
-        <v>1012</v>
+      <c r="F24" s="68" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>1013</v>
+        <v>1030</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="66" t="s">
-        <v>1014</v>
+      <c r="F25" s="68" t="s">
+        <v>1031</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>1015</v>
+        <v>1032</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="66" t="s">
-        <v>1016</v>
+      <c r="F26" s="68" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>1017</v>
+        <v>1034</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="66" t="s">
-        <v>1018</v>
+      <c r="F27" s="68" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="48" t="s">
-        <v>1019</v>
+        <v>1036</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="66" t="s">
-        <v>1020</v>
+      <c r="F28" s="68" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>1021</v>
+        <v>1038</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="66" t="s">
-        <v>1022</v>
+      <c r="F29" s="68" t="s">
+        <v>1039</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>1023</v>
+        <v>1040</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="66" t="s">
-        <v>1024</v>
+      <c r="F30" s="68" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>1025</v>
+        <v>1042</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="66" t="s">
-        <v>1026</v>
+      <c r="F31" s="68" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="66" t="s">
-        <v>1028</v>
+      <c r="F32" s="68" t="s">
+        <v>1045</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1029</v>
+        <v>1046</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
-      <c r="F33" s="66" t="s">
-        <v>1030</v>
+      <c r="F33" s="68" t="s">
+        <v>1047</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1031</v>
+        <v>1048</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="66" t="s">
-        <v>1032</v>
+      <c r="F34" s="68" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="66" t="s">
-        <v>1033</v>
+      <c r="F35" s="68" t="s">
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
@@ -12278,7 +12329,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -12354,7 +12405,7 @@
       <c r="F5" s="65" t="s">
         <v>466</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>467</v>
       </c>
       <c r="H5" s="65" t="s">
@@ -12375,11 +12426,11 @@
       <c r="M5" s="65" t="s">
         <v>471</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="67" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="64" t="s">
         <v>473</v>
       </c>
@@ -12389,2619 +12440,2696 @@
       <c r="D6" s="65" t="s">
         <v>474</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="65" t="s">
         <v>475</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="65" t="s">
         <v>475</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="65" t="s">
+        <v>476</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>477</v>
+      </c>
+      <c r="I6" s="65" t="s">
         <v>475</v>
       </c>
-      <c r="H6" s="65" t="s">
-        <v>476</v>
-      </c>
-      <c r="I6" s="67" t="s">
-        <v>475</v>
-      </c>
-      <c r="J6" s="67" t="s">
+      <c r="J6" s="65" t="s">
+        <v>478</v>
+      </c>
+      <c r="K6" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="K6" s="65" t="s">
-        <v>476</v>
-      </c>
       <c r="L6" s="65" t="s">
-        <v>478</v>
-      </c>
-      <c r="M6" s="65"/>
+        <v>479</v>
+      </c>
+      <c r="M6" s="65" t="s">
+        <v>480</v>
+      </c>
       <c r="N6" s="68" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="64" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G7" s="65" t="s">
+        <v>485</v>
+      </c>
+      <c r="H7" s="65" t="s">
+        <v>486</v>
+      </c>
+      <c r="I7" s="65" t="s">
         <v>484</v>
-      </c>
-      <c r="H7" s="65" t="s">
-        <v>485</v>
-      </c>
-      <c r="I7" s="65" t="s">
-        <v>486</v>
       </c>
       <c r="J7" s="65" t="s">
         <v>487</v>
       </c>
       <c r="K7" s="65" t="s">
+        <v>486</v>
+      </c>
+      <c r="L7" s="65" t="s">
         <v>488</v>
       </c>
-      <c r="L7" s="65" t="s">
+      <c r="M7" s="65" t="s">
         <v>489</v>
       </c>
-      <c r="M7" s="65" t="s">
+      <c r="N7" s="68" t="s">
         <v>490</v>
       </c>
-      <c r="N7" s="68" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="69" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="69" t="s">
+      <c r="C8" s="70" t="s">
         <v>492</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="D8" s="70" t="s">
+        <v>492</v>
+      </c>
+      <c r="E8" s="66" t="s">
         <v>493</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="F8" s="66" t="s">
         <v>493</v>
       </c>
-      <c r="E8" s="70" t="s">
-        <v>494</v>
-      </c>
-      <c r="F8" s="70" t="s">
-        <v>494</v>
-      </c>
-      <c r="G8" s="70" t="s">
-        <v>494</v>
+      <c r="G8" s="66" t="s">
+        <v>493</v>
       </c>
       <c r="H8" s="70" t="s">
         <v>494</v>
       </c>
-      <c r="I8" s="70" t="s">
-        <v>494</v>
-      </c>
-      <c r="J8" s="70" t="s">
-        <v>494</v>
+      <c r="I8" s="66" t="s">
+        <v>493</v>
+      </c>
+      <c r="J8" s="66" t="s">
+        <v>495</v>
       </c>
       <c r="K8" s="70" t="s">
         <v>494</v>
       </c>
       <c r="L8" s="70" t="s">
-        <v>494</v>
-      </c>
-      <c r="M8" s="70" t="s">
-        <v>495</v>
-      </c>
-      <c r="N8" s="68" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="64" t="s">
+      <c r="M8" s="70"/>
+      <c r="N8" s="67" t="s">
         <v>497</v>
       </c>
-      <c r="C9" s="71" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="69" t="s">
+        <v>498</v>
+      </c>
+      <c r="C9" s="70" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>500</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>501</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>501</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>502</v>
+      </c>
+      <c r="H9" s="70" t="s">
+        <v>503</v>
+      </c>
+      <c r="I9" s="70" t="s">
+        <v>504</v>
+      </c>
+      <c r="J9" s="70" t="s">
+        <v>505</v>
+      </c>
+      <c r="K9" s="70" t="s">
+        <v>506</v>
+      </c>
+      <c r="L9" s="70" t="s">
+        <v>507</v>
+      </c>
+      <c r="M9" s="70" t="s">
+        <v>508</v>
+      </c>
+      <c r="N9" s="67" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="64" t="s">
+        <v>510</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>511</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>511</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="F10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="H10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="I10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="J10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="K10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="L10" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="M10" s="71" t="s">
+        <v>513</v>
+      </c>
+      <c r="N10" s="67" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="69" t="s">
+        <v>515</v>
+      </c>
+      <c r="C11" s="72" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="71" t="n">
+      <c r="D11" s="72" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="71" t="n">
+      <c r="E11" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="71" t="n">
+      <c r="F11" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="71" t="n">
+      <c r="G11" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="71" t="n">
+      <c r="H11" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="71" t="n">
+      <c r="I11" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="71" t="n">
+      <c r="J11" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="K9" s="71" t="n">
+      <c r="K11" s="72" t="n">
         <v>11</v>
       </c>
-      <c r="L9" s="71" t="n">
+      <c r="L11" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="72"/>
-      <c r="N9" s="66" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="64" t="s">
-        <v>499</v>
-      </c>
-      <c r="C10" s="71" t="n">
-        <v>615</v>
-      </c>
-      <c r="D10" s="71" t="n">
-        <v>605</v>
-      </c>
-      <c r="E10" s="71" t="n">
-        <v>620</v>
-      </c>
-      <c r="F10" s="71" t="n">
-        <v>620</v>
-      </c>
-      <c r="G10" s="71" t="n">
-        <v>535</v>
-      </c>
-      <c r="H10" s="71" t="n">
-        <v>585</v>
-      </c>
-      <c r="I10" s="71" t="n">
-        <v>650</v>
-      </c>
-      <c r="J10" s="71" t="n">
-        <v>590</v>
-      </c>
-      <c r="K10" s="71" t="n">
-        <v>620</v>
-      </c>
-      <c r="L10" s="71" t="n">
-        <v>615</v>
-      </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="66" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="64" t="s">
-        <v>501</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>502</v>
-      </c>
-      <c r="D11" s="65" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>504</v>
-      </c>
-      <c r="F11" s="65" t="s">
-        <v>504</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>505</v>
-      </c>
-      <c r="H11" s="65" t="s">
-        <v>506</v>
-      </c>
-      <c r="I11" s="65" t="s">
-        <v>507</v>
-      </c>
-      <c r="J11" s="65" t="s">
-        <v>508</v>
-      </c>
-      <c r="K11" s="65" t="s">
-        <v>509</v>
-      </c>
-      <c r="L11" s="65" t="s">
-        <v>510</v>
-      </c>
-      <c r="M11" s="65"/>
+      <c r="M11" s="73"/>
       <c r="N11" s="68" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="69" t="s">
-        <v>512</v>
-      </c>
-      <c r="C12" s="73" t="n">
-        <f aca="false">C9*C10/1000</f>
-        <v>7.38</v>
-      </c>
-      <c r="D12" s="73" t="n">
-        <f aca="false">D9*D10/1000</f>
-        <v>7.26</v>
-      </c>
-      <c r="E12" s="73" t="n">
-        <f aca="false">E9*E10/1000</f>
-        <v>6.2</v>
-      </c>
-      <c r="F12" s="73" t="n">
-        <f aca="false">F9*F10/1000</f>
-        <v>6.2</v>
-      </c>
-      <c r="G12" s="73" t="n">
-        <f aca="false">G9*G10/1000</f>
-        <v>5.35</v>
-      </c>
-      <c r="H12" s="73" t="n">
-        <f aca="false">H9*H10/1000</f>
-        <v>4.68</v>
-      </c>
-      <c r="I12" s="73" t="n">
-        <f aca="false">I9*I10/1000</f>
-        <v>6.5</v>
-      </c>
-      <c r="J12" s="73" t="n">
-        <f aca="false">J9*J10/1000</f>
-        <v>5.9</v>
-      </c>
-      <c r="K12" s="73" t="n">
-        <f aca="false">K9*K10/1000</f>
-        <v>6.82</v>
-      </c>
-      <c r="L12" s="73" t="n">
-        <f aca="false">L9*L10/1000</f>
-        <v>4.92</v>
+        <v>517</v>
+      </c>
+      <c r="C12" s="72" t="n">
+        <v>615</v>
+      </c>
+      <c r="D12" s="72" t="n">
+        <v>605</v>
+      </c>
+      <c r="E12" s="72" t="n">
+        <v>620</v>
+      </c>
+      <c r="F12" s="72" t="n">
+        <v>620</v>
+      </c>
+      <c r="G12" s="72" t="n">
+        <v>535</v>
+      </c>
+      <c r="H12" s="72" t="n">
+        <v>585</v>
+      </c>
+      <c r="I12" s="72" t="n">
+        <v>650</v>
+      </c>
+      <c r="J12" s="72" t="n">
+        <v>590</v>
+      </c>
+      <c r="K12" s="72" t="n">
+        <v>620</v>
+      </c>
+      <c r="L12" s="72" t="n">
+        <v>615</v>
       </c>
       <c r="M12" s="73"/>
-      <c r="N12" s="66" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>515</v>
-      </c>
-      <c r="D13" s="65" t="s">
-        <v>515</v>
-      </c>
-      <c r="E13" s="65" t="s">
-        <v>516</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>517</v>
-      </c>
-      <c r="G13" s="65" t="s">
+      <c r="N12" s="68" t="s">
         <v>518</v>
       </c>
-      <c r="H13" s="65" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="69" t="s">
         <v>519</v>
       </c>
-      <c r="I13" s="65" t="s">
+      <c r="C13" s="70" t="s">
         <v>520</v>
       </c>
-      <c r="J13" s="65" t="s">
+      <c r="D13" s="70" t="s">
         <v>521</v>
       </c>
-      <c r="K13" s="65" t="s">
+      <c r="E13" s="70" t="s">
         <v>522</v>
       </c>
-      <c r="L13" s="65" t="s">
+      <c r="F13" s="70" t="s">
+        <v>522</v>
+      </c>
+      <c r="G13" s="70" t="s">
         <v>523</v>
       </c>
-      <c r="M13" s="65"/>
-      <c r="N13" s="68" t="s">
+      <c r="H13" s="70" t="s">
         <v>524</v>
+      </c>
+      <c r="I13" s="70" t="s">
+        <v>525</v>
+      </c>
+      <c r="J13" s="70" t="s">
+        <v>526</v>
+      </c>
+      <c r="K13" s="70" t="s">
+        <v>527</v>
+      </c>
+      <c r="L13" s="70" t="s">
+        <v>528</v>
+      </c>
+      <c r="M13" s="70"/>
+      <c r="N13" s="67" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="64" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C14" s="74" t="n">
+        <f aca="false">C11*C12/1000</f>
+        <v>7.38</v>
+      </c>
+      <c r="D14" s="74" t="n">
+        <f aca="false">D11*D12/1000</f>
+        <v>7.26</v>
+      </c>
+      <c r="E14" s="74" t="n">
+        <f aca="false">E11*E12/1000</f>
+        <v>6.2</v>
+      </c>
+      <c r="F14" s="74" t="n">
+        <f aca="false">F11*F12/1000</f>
+        <v>6.2</v>
+      </c>
+      <c r="G14" s="74" t="n">
+        <f aca="false">G11*G12/1000</f>
+        <v>5.35</v>
+      </c>
+      <c r="H14" s="74" t="n">
+        <f aca="false">H11*H12/1000</f>
+        <v>4.68</v>
+      </c>
+      <c r="I14" s="74" t="n">
+        <f aca="false">I11*I12/1000</f>
+        <v>6.5</v>
+      </c>
+      <c r="J14" s="74" t="n">
+        <f aca="false">J11*J12/1000</f>
+        <v>5.9</v>
+      </c>
+      <c r="K14" s="74" t="n">
+        <f aca="false">K11*K12/1000</f>
+        <v>6.82</v>
+      </c>
+      <c r="L14" s="74" t="n">
+        <f aca="false">L11*L12/1000</f>
+        <v>4.92</v>
+      </c>
+      <c r="M14" s="74"/>
+      <c r="N14" s="68" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="69" t="s">
+        <v>532</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>533</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>533</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>534</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>535</v>
+      </c>
+      <c r="G15" s="70" t="s">
+        <v>536</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>537</v>
+      </c>
+      <c r="I15" s="70" t="s">
+        <v>538</v>
+      </c>
+      <c r="J15" s="70" t="s">
+        <v>539</v>
+      </c>
+      <c r="K15" s="70" t="s">
+        <v>540</v>
+      </c>
+      <c r="L15" s="70" t="s">
+        <v>541</v>
+      </c>
+      <c r="M15" s="70"/>
+      <c r="N15" s="67" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="69" t="s">
+        <v>543</v>
+      </c>
+      <c r="C16" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="74" t="n">
+      <c r="D16" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="74" t="n">
+      <c r="E16" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="74" t="n">
+      <c r="F16" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="74" t="n">
+      <c r="G16" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="74" t="n">
+      <c r="H16" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="74" t="n">
+      <c r="I16" s="75" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="74" t="n">
+      <c r="J16" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="K14" s="74" t="n">
+      <c r="K16" s="75" t="n">
         <v>7.5</v>
       </c>
-      <c r="L14" s="74" t="n">
+      <c r="L16" s="75" t="n">
         <v>5</v>
-      </c>
-      <c r="M14" s="75"/>
-      <c r="N14" s="66" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="64" t="s">
-        <v>527</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="D15" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="E15" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="F15" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="G15" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="H15" s="65" t="s">
-        <v>530</v>
-      </c>
-      <c r="I15" s="65" t="s">
-        <v>531</v>
-      </c>
-      <c r="J15" s="65" t="s">
-        <v>531</v>
-      </c>
-      <c r="K15" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="L15" s="65" t="s">
-        <v>532</v>
-      </c>
-      <c r="M15" s="65"/>
-      <c r="N15" s="68" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="C16" s="76" t="n">
-        <f aca="false">IFERROR(C12/C14,0)</f>
-        <v>1.23</v>
-      </c>
-      <c r="D16" s="76" t="n">
-        <f aca="false">IFERROR(D12/D14,0)</f>
-        <v>1.21</v>
-      </c>
-      <c r="E16" s="76" t="n">
-        <f aca="false">IFERROR(E12/E14,0)</f>
-        <v>1.24</v>
-      </c>
-      <c r="F16" s="76" t="n">
-        <f aca="false">IFERROR(F12/F14,0)</f>
-        <v>1.24</v>
-      </c>
-      <c r="G16" s="76" t="n">
-        <f aca="false">IFERROR(G12/G14,0)</f>
-        <v>1.3375</v>
-      </c>
-      <c r="H16" s="76" t="n">
-        <f aca="false">IFERROR(H12/H14,0)</f>
-        <v>1.56</v>
-      </c>
-      <c r="I16" s="76" t="n">
-        <f aca="false">IFERROR(I12/I14,0)</f>
-        <v>0.722222222222222</v>
-      </c>
-      <c r="J16" s="76" t="n">
-        <f aca="false">IFERROR(J12/J14,0)</f>
-        <v>1.18</v>
-      </c>
-      <c r="K16" s="76" t="n">
-        <f aca="false">IFERROR(K12/K14,0)</f>
-        <v>0.909333333333333</v>
-      </c>
-      <c r="L16" s="76" t="n">
-        <f aca="false">IFERROR(L12/L14,0)</f>
-        <v>0.984</v>
       </c>
       <c r="M16" s="76"/>
       <c r="N16" s="68" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="64" t="s">
-        <v>536</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="D17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="E17" s="77" t="s">
-        <v>538</v>
-      </c>
-      <c r="F17" s="77" t="s">
-        <v>538</v>
-      </c>
-      <c r="G17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="H17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="I17" s="77" t="s">
-        <v>538</v>
-      </c>
-      <c r="J17" s="77" t="s">
-        <v>538</v>
-      </c>
-      <c r="K17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="L17" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="M17" s="77"/>
-      <c r="N17" s="68" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="69" t="s">
+        <v>545</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>546</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>547</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>546</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>548</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>549</v>
+      </c>
+      <c r="J17" s="70" t="s">
+        <v>549</v>
+      </c>
+      <c r="K17" s="70" t="s">
+        <v>546</v>
+      </c>
+      <c r="L17" s="70" t="s">
+        <v>550</v>
+      </c>
+      <c r="M17" s="70"/>
+      <c r="N17" s="67" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="64" t="s">
-        <v>540</v>
-      </c>
-      <c r="C18" s="65" t="s">
-        <v>541</v>
-      </c>
-      <c r="D18" s="65" t="s">
-        <v>541</v>
-      </c>
-      <c r="E18" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="G18" s="65" t="s">
-        <v>543</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>543</v>
-      </c>
-      <c r="I18" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="J18" s="65" t="s">
-        <v>544</v>
-      </c>
-      <c r="K18" s="65" t="s">
-        <v>543</v>
-      </c>
-      <c r="L18" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="M18" s="65"/>
-      <c r="N18" s="68" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="64" t="s">
-        <v>546</v>
-      </c>
-      <c r="C19" s="75" t="n">
-        <f aca="false">C9*C10*0.00452</f>
+        <v>552</v>
+      </c>
+      <c r="C18" s="77" t="n">
+        <f aca="false">IFERROR(C14/C16,0)</f>
+        <v>1.23</v>
+      </c>
+      <c r="D18" s="77" t="n">
+        <f aca="false">IFERROR(D14/D16,0)</f>
+        <v>1.21</v>
+      </c>
+      <c r="E18" s="77" t="n">
+        <f aca="false">IFERROR(E14/E16,0)</f>
+        <v>1.24</v>
+      </c>
+      <c r="F18" s="77" t="n">
+        <f aca="false">IFERROR(F14/F16,0)</f>
+        <v>1.24</v>
+      </c>
+      <c r="G18" s="77" t="n">
+        <f aca="false">IFERROR(G14/G16,0)</f>
+        <v>1.3375</v>
+      </c>
+      <c r="H18" s="77" t="n">
+        <f aca="false">IFERROR(H14/H16,0)</f>
+        <v>1.56</v>
+      </c>
+      <c r="I18" s="77" t="n">
+        <f aca="false">IFERROR(I14/I16,0)</f>
+        <v>0.722222222222222</v>
+      </c>
+      <c r="J18" s="77" t="n">
+        <f aca="false">IFERROR(J14/J16,0)</f>
+        <v>1.18</v>
+      </c>
+      <c r="K18" s="77" t="n">
+        <f aca="false">IFERROR(K14/K16,0)</f>
+        <v>0.909333333333333</v>
+      </c>
+      <c r="L18" s="77" t="n">
+        <f aca="false">IFERROR(L14/L16,0)</f>
+        <v>0.984</v>
+      </c>
+      <c r="M18" s="77"/>
+      <c r="N18" s="67" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="69" t="s">
+        <v>554</v>
+      </c>
+      <c r="C19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="D19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="E19" s="78" t="s">
+        <v>556</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>556</v>
+      </c>
+      <c r="G19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="I19" s="78" t="s">
+        <v>556</v>
+      </c>
+      <c r="J19" s="78" t="s">
+        <v>556</v>
+      </c>
+      <c r="K19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="L19" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="M19" s="78"/>
+      <c r="N19" s="67" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="69" t="s">
+        <v>558</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>559</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>559</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="G20" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="J20" s="70" t="s">
+        <v>562</v>
+      </c>
+      <c r="K20" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="L20" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="M20" s="70"/>
+      <c r="N20" s="67" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="69" t="s">
+        <v>564</v>
+      </c>
+      <c r="C21" s="76" t="n">
+        <f aca="false">C11*C12*0.00452</f>
         <v>33.3576</v>
       </c>
-      <c r="D19" s="75" t="n">
-        <f aca="false">D9*D10*0.00452</f>
+      <c r="D21" s="76" t="n">
+        <f aca="false">D11*D12*0.00452</f>
         <v>32.8152</v>
       </c>
-      <c r="E19" s="75" t="n">
-        <f aca="false">E9*E10*0.00452</f>
+      <c r="E21" s="76" t="n">
+        <f aca="false">E11*E12*0.00452</f>
         <v>28.024</v>
       </c>
-      <c r="F19" s="75" t="n">
-        <f aca="false">F9*F10*0.00452</f>
+      <c r="F21" s="76" t="n">
+        <f aca="false">F11*F12*0.00452</f>
         <v>28.024</v>
       </c>
-      <c r="G19" s="75" t="n">
-        <f aca="false">G9*G10*0.00452</f>
+      <c r="G21" s="76" t="n">
+        <f aca="false">G11*G12*0.00452</f>
         <v>24.182</v>
       </c>
-      <c r="H19" s="75" t="n">
+      <c r="H21" s="76" t="n">
         <v>21.12</v>
       </c>
-      <c r="I19" s="75" t="n">
-        <f aca="false">I9*I10*0.00452</f>
+      <c r="I21" s="76" t="n">
+        <f aca="false">I11*I12*0.00452</f>
         <v>29.38</v>
       </c>
-      <c r="J19" s="75" t="n">
+      <c r="J21" s="76" t="n">
         <v>28</v>
       </c>
-      <c r="K19" s="75" t="n">
+      <c r="K21" s="76" t="n">
         <v>30.58</v>
       </c>
-      <c r="L19" s="75" t="n">
+      <c r="L21" s="76" t="n">
         <v>25.93</v>
       </c>
-      <c r="M19" s="75"/>
-      <c r="N19" s="66" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="64" t="s">
-        <v>548</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="D20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="E20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="F20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="G20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="H20" s="65" t="s">
-        <v>549</v>
-      </c>
-      <c r="I20" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="J20" s="65" t="s">
-        <v>550</v>
-      </c>
-      <c r="K20" s="65" t="s">
-        <v>549</v>
-      </c>
-      <c r="L20" s="65" t="s">
-        <v>551</v>
-      </c>
-      <c r="M20" s="65"/>
-      <c r="N20" s="66" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="64" t="s">
-        <v>553</v>
-      </c>
-      <c r="C21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="D21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="E21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="F21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="G21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="H21" s="65" t="s">
-        <v>554</v>
-      </c>
-      <c r="I21" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="J21" s="65" t="s">
-        <v>555</v>
-      </c>
-      <c r="K21" s="65" t="s">
-        <v>554</v>
-      </c>
-      <c r="L21" s="65" t="s">
-        <v>556</v>
-      </c>
-      <c r="M21" s="65"/>
-      <c r="N21" s="66" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="64" t="s">
-        <v>558</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="D22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="E22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="F22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>559</v>
-      </c>
-      <c r="I22" s="65" t="s">
-        <v>542</v>
-      </c>
-      <c r="J22" s="65" t="s">
+      <c r="M21" s="76"/>
+      <c r="N21" s="68" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="69" t="s">
+        <v>566</v>
+      </c>
+      <c r="C22" s="66" t="s">
         <v>560</v>
       </c>
-      <c r="K22" s="65" t="s">
-        <v>559</v>
-      </c>
-      <c r="L22" s="65" t="s">
-        <v>561</v>
-      </c>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="64" t="s">
-        <v>563</v>
-      </c>
-      <c r="C23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="D23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="E23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="F23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="G23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="H23" s="67" t="s">
-        <v>565</v>
-      </c>
-      <c r="I23" s="65" t="s">
-        <v>564</v>
-      </c>
-      <c r="J23" s="65" t="s">
-        <v>566</v>
-      </c>
-      <c r="K23" s="67" t="s">
-        <v>565</v>
-      </c>
-      <c r="L23" s="65" t="s">
+      <c r="D22" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="E22" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="F22" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="G22" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="H22" s="70" t="s">
         <v>567</v>
       </c>
-      <c r="M23" s="65"/>
+      <c r="I22" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="J22" s="70" t="s">
+        <v>568</v>
+      </c>
+      <c r="K22" s="70" t="s">
+        <v>567</v>
+      </c>
+      <c r="L22" s="70" t="s">
+        <v>569</v>
+      </c>
+      <c r="M22" s="70"/>
+      <c r="N22" s="68" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="69" t="s">
+        <v>571</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="F23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="G23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="H23" s="70" t="s">
+        <v>572</v>
+      </c>
+      <c r="I23" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="J23" s="70" t="s">
+        <v>573</v>
+      </c>
+      <c r="K23" s="70" t="s">
+        <v>572</v>
+      </c>
+      <c r="L23" s="70" t="s">
+        <v>574</v>
+      </c>
+      <c r="M23" s="70"/>
       <c r="N23" s="68" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="64" t="s">
-        <v>569</v>
-      </c>
-      <c r="C24" s="65" t="s">
-        <v>570</v>
-      </c>
-      <c r="D24" s="65" t="s">
-        <v>570</v>
-      </c>
-      <c r="E24" s="65" t="s">
-        <v>571</v>
-      </c>
-      <c r="F24" s="65" t="s">
-        <v>571</v>
-      </c>
-      <c r="G24" s="65" t="s">
-        <v>572</v>
-      </c>
-      <c r="H24" s="65" t="s">
-        <v>573</v>
-      </c>
-      <c r="I24" s="65" t="s">
-        <v>574</v>
-      </c>
-      <c r="J24" s="65" t="s">
         <v>575</v>
       </c>
-      <c r="K24" s="65" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="69" t="s">
         <v>576</v>
       </c>
-      <c r="L24" s="65" t="s">
+      <c r="C24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="F24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="G24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="H24" s="70" t="s">
         <v>577</v>
       </c>
-      <c r="M24" s="65"/>
-      <c r="N24" s="66" t="s">
+      <c r="I24" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="J24" s="70" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
+      <c r="K24" s="70" t="s">
+        <v>577</v>
+      </c>
+      <c r="L24" s="70" t="s">
         <v>579</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="64" t="s">
+      <c r="M24" s="70"/>
+      <c r="N24" s="68" t="s">
         <v>580</v>
       </c>
-      <c r="C26" s="78" t="n">
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="69" t="s">
+        <v>581</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="D25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="E25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="F25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="G25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="H25" s="66" t="s">
+        <v>583</v>
+      </c>
+      <c r="I25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="J25" s="70" t="s">
+        <v>584</v>
+      </c>
+      <c r="K25" s="66" t="s">
+        <v>583</v>
+      </c>
+      <c r="L25" s="70" t="s">
+        <v>585</v>
+      </c>
+      <c r="M25" s="70"/>
+      <c r="N25" s="67" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="69" t="s">
+        <v>587</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>588</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>588</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>589</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>589</v>
+      </c>
+      <c r="G26" s="70" t="s">
+        <v>590</v>
+      </c>
+      <c r="H26" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="I26" s="70" t="s">
+        <v>592</v>
+      </c>
+      <c r="J26" s="70" t="s">
+        <v>593</v>
+      </c>
+      <c r="K26" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="L26" s="70" t="s">
+        <v>595</v>
+      </c>
+      <c r="M26" s="70"/>
+      <c r="N26" s="68" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="69" t="s">
+        <v>598</v>
+      </c>
+      <c r="C29" s="79" t="n">
         <v>18228.7</v>
       </c>
-      <c r="D26" s="78" t="n">
+      <c r="D29" s="79" t="n">
         <v>17307.9</v>
       </c>
-      <c r="E26" s="78" t="n">
+      <c r="E29" s="79" t="n">
         <v>14220.34</v>
       </c>
-      <c r="F26" s="78" t="n">
+      <c r="F29" s="79" t="n">
         <v>15220.34</v>
       </c>
-      <c r="G26" s="78" t="n">
+      <c r="G29" s="79" t="n">
         <v>11158.91</v>
       </c>
-      <c r="H26" s="78" t="n">
+      <c r="H29" s="79" t="n">
         <v>12387.64</v>
       </c>
-      <c r="I26" s="78" t="n">
+      <c r="I29" s="79" t="n">
         <v>16780.54</v>
       </c>
-      <c r="J26" s="78" t="n">
+      <c r="J29" s="79" t="n">
         <v>18733</v>
       </c>
-      <c r="K26" s="78" t="n">
+      <c r="K29" s="79" t="n">
         <v>16890</v>
       </c>
-      <c r="L26" s="78" t="n">
+      <c r="L29" s="79" t="n">
         <v>17442</v>
       </c>
-      <c r="M26" s="79"/>
-      <c r="N26" s="66" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="64" t="s">
-        <v>582</v>
-      </c>
-      <c r="C27" s="78" t="n">
+      <c r="M29" s="80"/>
+      <c r="N29" s="68" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="69" t="s">
+        <v>600</v>
+      </c>
+      <c r="C30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="78" t="n">
+      <c r="D30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="78" t="n">
+      <c r="E30" s="79" t="n">
         <v>1800</v>
       </c>
-      <c r="F27" s="78" t="n">
+      <c r="F30" s="79" t="n">
         <v>1800</v>
       </c>
-      <c r="G27" s="78" t="n">
+      <c r="G30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="78" t="n">
+      <c r="H30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="78" t="n">
+      <c r="I30" s="79" t="n">
         <v>1800</v>
       </c>
-      <c r="J27" s="78" t="n">
+      <c r="J30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="78" t="n">
+      <c r="K30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="78" t="n">
+      <c r="L30" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="79"/>
-      <c r="N27" s="68" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="64" t="s">
-        <v>584</v>
-      </c>
-      <c r="C28" s="78" t="n">
+      <c r="M30" s="80"/>
+      <c r="N30" s="67" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="69" t="s">
+        <v>602</v>
+      </c>
+      <c r="C31" s="79" t="n">
         <v>790</v>
       </c>
-      <c r="D28" s="78" t="n">
+      <c r="D31" s="79" t="n">
         <v>790</v>
       </c>
-      <c r="E28" s="78" t="n">
+      <c r="E31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="78" t="n">
+      <c r="F31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="78" t="n">
+      <c r="G31" s="79" t="n">
         <v>790</v>
       </c>
-      <c r="H28" s="78" t="n">
+      <c r="H31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="78" t="n">
+      <c r="I31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="78" t="n">
+      <c r="J31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="78" t="n">
+      <c r="K31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="78" t="n">
+      <c r="L31" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="79"/>
-      <c r="N28" s="66" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="64" t="s">
-        <v>586</v>
-      </c>
-      <c r="C29" s="79" t="n">
-        <f aca="false">6900/10*C9</f>
+      <c r="M31" s="80"/>
+      <c r="N31" s="68" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="69" t="s">
+        <v>604</v>
+      </c>
+      <c r="C32" s="80" t="n">
+        <f aca="false">6900/10*C11</f>
         <v>8280</v>
       </c>
-      <c r="D29" s="79" t="n">
-        <f aca="false">6900/10*D9</f>
+      <c r="D32" s="80" t="n">
+        <f aca="false">6900/10*D11</f>
         <v>8280</v>
       </c>
-      <c r="E29" s="78" t="n">
+      <c r="E32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="78" t="n">
+      <c r="F32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="78" t="n">
+      <c r="G32" s="79" t="n">
         <v>6900</v>
       </c>
-      <c r="H29" s="78" t="n">
+      <c r="H32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="78" t="n">
+      <c r="I32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="78" t="n">
+      <c r="J32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="78" t="n">
+      <c r="K32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="78" t="n">
+      <c r="L32" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="79"/>
-      <c r="N29" s="68" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="64" t="s">
-        <v>588</v>
-      </c>
-      <c r="C30" s="79" t="n">
+      <c r="M32" s="80"/>
+      <c r="N32" s="67" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="69" t="s">
+        <v>606</v>
+      </c>
+      <c r="C33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="D30" s="79" t="n">
+      <c r="D33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="E30" s="79" t="n">
+      <c r="E33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="F30" s="79" t="n">
+      <c r="F33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="G30" s="79" t="n">
+      <c r="G33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="H30" s="79" t="n">
+      <c r="H33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="I30" s="79" t="n">
+      <c r="I33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="J30" s="79" t="n">
+      <c r="J33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="K30" s="79" t="n">
+      <c r="K33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="L30" s="79" t="n">
+      <c r="L33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
         <v>2500</v>
       </c>
-      <c r="M30" s="79"/>
-      <c r="N30" s="68" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="69" t="s">
-        <v>590</v>
-      </c>
-      <c r="C31" s="80" t="n">
-        <f aca="false">SUM(C26:C30)</f>
+      <c r="M33" s="80"/>
+      <c r="N33" s="67" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="64" t="s">
+        <v>608</v>
+      </c>
+      <c r="C34" s="81" t="n">
+        <f aca="false">SUM(C29:C33)</f>
         <v>29798.7</v>
       </c>
-      <c r="D31" s="80" t="n">
-        <f aca="false">SUM(D26:D30)</f>
+      <c r="D34" s="81" t="n">
+        <f aca="false">SUM(D29:D33)</f>
         <v>28877.9</v>
       </c>
-      <c r="E31" s="80" t="n">
-        <f aca="false">SUM(E26:E30)</f>
+      <c r="E34" s="81" t="n">
+        <f aca="false">SUM(E29:E33)</f>
         <v>18520.34</v>
       </c>
-      <c r="F31" s="80" t="n">
-        <f aca="false">SUM(F26:F30)</f>
+      <c r="F34" s="81" t="n">
+        <f aca="false">SUM(F29:F33)</f>
         <v>19520.34</v>
       </c>
-      <c r="G31" s="80" t="n">
-        <f aca="false">SUM(G26:G30)</f>
+      <c r="G34" s="81" t="n">
+        <f aca="false">SUM(G29:G33)</f>
         <v>21348.91</v>
       </c>
-      <c r="H31" s="80" t="n">
-        <f aca="false">SUM(H26:H30)</f>
+      <c r="H34" s="81" t="n">
+        <f aca="false">SUM(H29:H33)</f>
         <v>14887.64</v>
       </c>
-      <c r="I31" s="80" t="n">
-        <f aca="false">SUM(I26:I30)</f>
+      <c r="I34" s="81" t="n">
+        <f aca="false">SUM(I29:I33)</f>
         <v>21080.54</v>
       </c>
-      <c r="J31" s="80" t="n">
-        <f aca="false">SUM(J26:J30)</f>
+      <c r="J34" s="81" t="n">
+        <f aca="false">SUM(J29:J33)</f>
         <v>21233</v>
       </c>
-      <c r="K31" s="80" t="n">
-        <f aca="false">SUM(K26:K30)</f>
+      <c r="K34" s="81" t="n">
+        <f aca="false">SUM(K29:K33)</f>
         <v>19390</v>
       </c>
-      <c r="L31" s="80" t="n">
-        <f aca="false">SUM(L26:L30)</f>
+      <c r="L34" s="81" t="n">
+        <f aca="false">SUM(L29:L33)</f>
         <v>19942</v>
       </c>
-      <c r="M31" s="80"/>
-      <c r="N31" s="66" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="69" t="s">
-        <v>592</v>
-      </c>
-      <c r="C32" s="81" t="n">
-        <f aca="false">IFERROR(C31/(C12*1000),0)</f>
+      <c r="M34" s="81"/>
+      <c r="N34" s="68" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="64" t="s">
+        <v>610</v>
+      </c>
+      <c r="C35" s="82" t="n">
+        <f aca="false">IFERROR(C34/(C14*1000),0)</f>
         <v>4.03776422764228</v>
       </c>
-      <c r="D32" s="81" t="n">
-        <f aca="false">IFERROR(D31/(D12*1000),0)</f>
+      <c r="D35" s="82" t="n">
+        <f aca="false">IFERROR(D34/(D14*1000),0)</f>
         <v>3.97767217630854</v>
       </c>
-      <c r="E32" s="81" t="n">
-        <f aca="false">IFERROR(E31/(E12*1000),0)</f>
+      <c r="E35" s="82" t="n">
+        <f aca="false">IFERROR(E34/(E14*1000),0)</f>
         <v>2.98715161290323</v>
       </c>
-      <c r="F32" s="81" t="n">
-        <f aca="false">IFERROR(F31/(F12*1000),0)</f>
+      <c r="F35" s="82" t="n">
+        <f aca="false">IFERROR(F34/(F14*1000),0)</f>
         <v>3.14844193548387</v>
       </c>
-      <c r="G32" s="81" t="n">
-        <f aca="false">IFERROR(G31/(G12*1000),0)</f>
+      <c r="G35" s="82" t="n">
+        <f aca="false">IFERROR(G34/(G14*1000),0)</f>
         <v>3.99045046728972</v>
       </c>
-      <c r="H32" s="81" t="n">
-        <f aca="false">IFERROR(H31/(H12*1000),0)</f>
+      <c r="H35" s="82" t="n">
+        <f aca="false">IFERROR(H34/(H14*1000),0)</f>
         <v>3.18111965811966</v>
       </c>
-      <c r="I32" s="81" t="n">
-        <f aca="false">IFERROR(I31/(I12*1000),0)</f>
+      <c r="I35" s="82" t="n">
+        <f aca="false">IFERROR(I34/(I14*1000),0)</f>
         <v>3.24316</v>
       </c>
-      <c r="J32" s="81" t="n">
-        <f aca="false">IFERROR(J31/(J12*1000),0)</f>
+      <c r="J35" s="82" t="n">
+        <f aca="false">IFERROR(J34/(J14*1000),0)</f>
         <v>3.59881355932203</v>
       </c>
-      <c r="K32" s="81" t="n">
-        <f aca="false">IFERROR(K31/(K12*1000),0)</f>
+      <c r="K35" s="82" t="n">
+        <f aca="false">IFERROR(K34/(K14*1000),0)</f>
         <v>2.84310850439883</v>
       </c>
-      <c r="L32" s="81" t="n">
-        <f aca="false">IFERROR(L31/(L12*1000),0)</f>
+      <c r="L35" s="82" t="n">
+        <f aca="false">IFERROR(L34/(L14*1000),0)</f>
         <v>4.05325203252033</v>
       </c>
-      <c r="M32" s="81"/>
-      <c r="N32" s="66" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="64" t="s">
-        <v>594</v>
-      </c>
-      <c r="C33" s="82" t="n">
-        <f aca="false">IFERROR(C26/(C12*1000),0)</f>
+      <c r="M35" s="82"/>
+      <c r="N35" s="68" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="69" t="s">
+        <v>612</v>
+      </c>
+      <c r="C36" s="83" t="n">
+        <f aca="false">IFERROR(C29/(C14*1000),0)</f>
         <v>2.4700135501355</v>
       </c>
-      <c r="D33" s="82" t="n">
-        <f aca="false">IFERROR(D26/(D12*1000),0)</f>
+      <c r="D36" s="83" t="n">
+        <f aca="false">IFERROR(D29/(D14*1000),0)</f>
         <v>2.38400826446281</v>
       </c>
-      <c r="E33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="F33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="G33" s="82" t="n">
-        <f aca="false">IFERROR(G26/(G12*1000),0)</f>
+      <c r="E36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="F36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="G36" s="83" t="n">
+        <f aca="false">IFERROR(G29/(G14*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
-      <c r="H33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="I33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="J33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="K33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="L33" s="82" t="s">
-        <v>595</v>
-      </c>
-      <c r="M33" s="82"/>
-      <c r="N33" s="66" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="64" t="s">
-        <v>598</v>
-      </c>
-      <c r="C36" s="72" t="n">
-        <f aca="false">C12*GERACAO!$I$17</f>
+      <c r="H36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="I36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="J36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="K36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="L36" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="M36" s="83"/>
+      <c r="N36" s="68" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="69" t="s">
+        <v>616</v>
+      </c>
+      <c r="C39" s="73" t="n">
+        <f aca="false">C14*GERACAO!$I$17</f>
         <v>9330.3051831</v>
       </c>
-      <c r="D36" s="72" t="n">
-        <f aca="false">D12*GERACAO!$I$17</f>
+      <c r="D39" s="73" t="n">
+        <f aca="false">D14*GERACAO!$I$17</f>
         <v>9178.5929037</v>
       </c>
-      <c r="E36" s="72" t="n">
-        <f aca="false">E12*GERACAO!$I$17</f>
+      <c r="E39" s="73" t="n">
+        <f aca="false">E14*GERACAO!$I$17</f>
         <v>7838.467769</v>
       </c>
-      <c r="F36" s="72" t="n">
-        <f aca="false">F12*GERACAO!$I$17</f>
+      <c r="F39" s="73" t="n">
+        <f aca="false">F14*GERACAO!$I$17</f>
         <v>7838.467769</v>
       </c>
-      <c r="G36" s="72" t="n">
-        <f aca="false">G12*GERACAO!$I$17</f>
+      <c r="G39" s="73" t="n">
+        <f aca="false">G14*GERACAO!$I$17</f>
         <v>6763.83912325</v>
       </c>
-      <c r="H36" s="72" t="n">
-        <f aca="false">H12*GERACAO!$I$17</f>
+      <c r="H39" s="73" t="n">
+        <f aca="false">H14*GERACAO!$I$17</f>
         <v>5916.7788966</v>
       </c>
-      <c r="I36" s="72" t="n">
-        <f aca="false">I12*GERACAO!$I$17</f>
+      <c r="I39" s="73" t="n">
+        <f aca="false">I14*GERACAO!$I$17</f>
         <v>8217.7484675</v>
       </c>
-      <c r="J36" s="72" t="n">
-        <f aca="false">J12*GERACAO!$I$17</f>
+      <c r="J39" s="73" t="n">
+        <f aca="false">J14*GERACAO!$I$17</f>
         <v>7459.1870705</v>
       </c>
-      <c r="K36" s="72" t="n">
-        <f aca="false">K12*GERACAO!$I$17</f>
+      <c r="K39" s="73" t="n">
+        <f aca="false">K14*GERACAO!$I$17</f>
         <v>8622.3145459</v>
       </c>
-      <c r="L36" s="72" t="n">
-        <f aca="false">L12*GERACAO!$I$17</f>
+      <c r="L39" s="73" t="n">
+        <f aca="false">L14*GERACAO!$I$17</f>
         <v>6220.2034554</v>
       </c>
-      <c r="M36" s="72"/>
-      <c r="N36" s="66" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="64" t="s">
-        <v>600</v>
-      </c>
-      <c r="C37" s="72" t="n">
-        <f aca="false">C36/12</f>
-        <v>777.525431925</v>
-      </c>
-      <c r="D37" s="72" t="n">
-        <f aca="false">D36/12</f>
-        <v>764.882741975</v>
-      </c>
-      <c r="E37" s="72" t="n">
-        <f aca="false">E36/12</f>
-        <v>653.205647416667</v>
-      </c>
-      <c r="F37" s="72" t="n">
-        <f aca="false">F36/12</f>
-        <v>653.205647416667</v>
-      </c>
-      <c r="G37" s="72" t="n">
-        <f aca="false">G36/12</f>
-        <v>563.653260270833</v>
-      </c>
-      <c r="H37" s="72" t="n">
-        <f aca="false">H36/12</f>
-        <v>493.06490805</v>
-      </c>
-      <c r="I37" s="72" t="n">
-        <f aca="false">I36/12</f>
-        <v>684.812372291667</v>
-      </c>
-      <c r="J37" s="72" t="n">
-        <f aca="false">J36/12</f>
-        <v>621.598922541667</v>
-      </c>
-      <c r="K37" s="72" t="n">
-        <f aca="false">K36/12</f>
-        <v>718.526212158333</v>
-      </c>
-      <c r="L37" s="72" t="n">
-        <f aca="false">L36/12</f>
-        <v>518.35028795</v>
-      </c>
-      <c r="M37" s="72"/>
-      <c r="N37" s="66"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="64" t="s">
-        <v>601</v>
-      </c>
-      <c r="C38" s="72" t="n">
-        <f aca="false">C36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>8503.5692808</v>
-      </c>
-      <c r="D38" s="72" t="n">
-        <f aca="false">D36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>8365.2998616</v>
-      </c>
-      <c r="E38" s="72" t="n">
-        <f aca="false">E36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>7143.919992</v>
-      </c>
-      <c r="F38" s="72" t="n">
-        <f aca="false">F36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>7143.919992</v>
-      </c>
-      <c r="G38" s="72" t="n">
-        <f aca="false">G36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>6164.511606</v>
-      </c>
-      <c r="H38" s="72" t="n">
-        <f aca="false">H36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>5392.5073488</v>
-      </c>
-      <c r="I38" s="72" t="n">
-        <f aca="false">I36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>7489.59354</v>
-      </c>
-      <c r="J38" s="72" t="n">
-        <f aca="false">J36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>6798.246444</v>
-      </c>
-      <c r="K38" s="72" t="n">
-        <f aca="false">K36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>7858.3119912</v>
-      </c>
-      <c r="L38" s="72" t="n">
-        <f aca="false">L36/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>5669.0461872</v>
-      </c>
-      <c r="M38" s="72"/>
-      <c r="N38" s="66" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="64" t="s">
-        <v>603</v>
-      </c>
-      <c r="C39" s="71" t="n">
-        <v>10554</v>
-      </c>
-      <c r="D39" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="71" t="n">
-        <v>8400</v>
-      </c>
-      <c r="F39" s="71" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G39" s="71" t="n">
-        <v>6151</v>
-      </c>
-      <c r="H39" s="71" t="n">
-        <v>6367.5</v>
-      </c>
-      <c r="I39" s="71" t="n">
-        <v>8400</v>
-      </c>
-      <c r="J39" s="71" t="n">
-        <v>7329.96</v>
-      </c>
-      <c r="K39" s="71" t="n">
-        <v>9279.13</v>
-      </c>
-      <c r="L39" s="71" t="n">
-        <v>6385.01</v>
-      </c>
-      <c r="M39" s="72"/>
-      <c r="N39" s="66" t="s">
-        <v>604</v>
+      <c r="M39" s="73"/>
+      <c r="N39" s="68" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="69" t="s">
-        <v>605</v>
-      </c>
-      <c r="C40" s="83" t="n">
-        <f aca="false">IFERROR(C36/C39-1,0)</f>
+        <v>618</v>
+      </c>
+      <c r="C40" s="73" t="n">
+        <f aca="false">C39/12</f>
+        <v>777.525431925</v>
+      </c>
+      <c r="D40" s="73" t="n">
+        <f aca="false">D39/12</f>
+        <v>764.882741975</v>
+      </c>
+      <c r="E40" s="73" t="n">
+        <f aca="false">E39/12</f>
+        <v>653.205647416667</v>
+      </c>
+      <c r="F40" s="73" t="n">
+        <f aca="false">F39/12</f>
+        <v>653.205647416667</v>
+      </c>
+      <c r="G40" s="73" t="n">
+        <f aca="false">G39/12</f>
+        <v>563.653260270833</v>
+      </c>
+      <c r="H40" s="73" t="n">
+        <f aca="false">H39/12</f>
+        <v>493.06490805</v>
+      </c>
+      <c r="I40" s="73" t="n">
+        <f aca="false">I39/12</f>
+        <v>684.812372291667</v>
+      </c>
+      <c r="J40" s="73" t="n">
+        <f aca="false">J39/12</f>
+        <v>621.598922541667</v>
+      </c>
+      <c r="K40" s="73" t="n">
+        <f aca="false">K39/12</f>
+        <v>718.526212158333</v>
+      </c>
+      <c r="L40" s="73" t="n">
+        <f aca="false">L39/12</f>
+        <v>518.35028795</v>
+      </c>
+      <c r="M40" s="73"/>
+      <c r="N40" s="68"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="69" t="s">
+        <v>619</v>
+      </c>
+      <c r="C41" s="73" t="n">
+        <f aca="false">C39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>8503.5692808</v>
+      </c>
+      <c r="D41" s="73" t="n">
+        <f aca="false">D39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>8365.2998616</v>
+      </c>
+      <c r="E41" s="73" t="n">
+        <f aca="false">E39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7143.919992</v>
+      </c>
+      <c r="F41" s="73" t="n">
+        <f aca="false">F39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7143.919992</v>
+      </c>
+      <c r="G41" s="73" t="n">
+        <f aca="false">G39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>6164.511606</v>
+      </c>
+      <c r="H41" s="73" t="n">
+        <f aca="false">H39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>5392.5073488</v>
+      </c>
+      <c r="I41" s="73" t="n">
+        <f aca="false">I39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7489.59354</v>
+      </c>
+      <c r="J41" s="73" t="n">
+        <f aca="false">J39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>6798.246444</v>
+      </c>
+      <c r="K41" s="73" t="n">
+        <f aca="false">K39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>7858.3119912</v>
+      </c>
+      <c r="L41" s="73" t="n">
+        <f aca="false">L39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
+        <v>5669.0461872</v>
+      </c>
+      <c r="M41" s="73"/>
+      <c r="N41" s="68" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="69" t="s">
+        <v>621</v>
+      </c>
+      <c r="C42" s="72" t="n">
+        <v>10554</v>
+      </c>
+      <c r="D42" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="72" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F42" s="72" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G42" s="72" t="n">
+        <v>6151</v>
+      </c>
+      <c r="H42" s="72" t="n">
+        <v>6367.5</v>
+      </c>
+      <c r="I42" s="72" t="n">
+        <v>8400</v>
+      </c>
+      <c r="J42" s="72" t="n">
+        <v>7329.96</v>
+      </c>
+      <c r="K42" s="72" t="n">
+        <v>9279.13</v>
+      </c>
+      <c r="L42" s="72" t="n">
+        <v>6385.01</v>
+      </c>
+      <c r="M42" s="73"/>
+      <c r="N42" s="68" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="64" t="s">
+        <v>623</v>
+      </c>
+      <c r="C43" s="84" t="n">
+        <f aca="false">IFERROR(C39/C42-1,0)</f>
         <v>-0.115946069442865</v>
       </c>
-      <c r="D40" s="83" t="n">
-        <f aca="false">IFERROR(D36/D39-1,0)</f>
+      <c r="D43" s="84" t="n">
+        <f aca="false">IFERROR(D39/D42-1,0)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="83" t="n">
-        <f aca="false">IFERROR(E36/E39-1,0)</f>
+      <c r="E43" s="84" t="n">
+        <f aca="false">IFERROR(E39/E42-1,0)</f>
         <v>-0.0668490751190475</v>
       </c>
-      <c r="F40" s="83" t="n">
-        <f aca="false">IFERROR(F36/F39-1,0)</f>
+      <c r="F43" s="84" t="n">
+        <f aca="false">IFERROR(F39/F42-1,0)</f>
         <v>-0.0668490751190475</v>
       </c>
-      <c r="G40" s="83" t="n">
-        <f aca="false">IFERROR(G36/G39-1,0)</f>
+      <c r="G43" s="84" t="n">
+        <f aca="false">IFERROR(G39/G42-1,0)</f>
         <v>0.0996324375304829</v>
       </c>
-      <c r="H40" s="83" t="n">
-        <f aca="false">IFERROR(H36/H39-1,0)</f>
+      <c r="H43" s="84" t="n">
+        <f aca="false">IFERROR(H39/H42-1,0)</f>
         <v>-0.0707846255830389</v>
       </c>
-      <c r="I40" s="83" t="n">
-        <f aca="false">IFERROR(I36/I39-1,0)</f>
+      <c r="I43" s="84" t="n">
+        <f aca="false">IFERROR(I39/I42-1,0)</f>
         <v>-0.0216966110119046</v>
       </c>
-      <c r="J40" s="83" t="n">
-        <f aca="false">IFERROR(J36/J39-1,0)</f>
+      <c r="J43" s="84" t="n">
+        <f aca="false">IFERROR(J39/J42-1,0)</f>
         <v>0.0176299830421995</v>
       </c>
-      <c r="K40" s="83" t="n">
-        <f aca="false">IFERROR(K36/K39-1,0)</f>
+      <c r="K43" s="84" t="n">
+        <f aca="false">IFERROR(K39/K42-1,0)</f>
         <v>-0.0707841633967838</v>
       </c>
-      <c r="L40" s="83" t="n">
-        <f aca="false">IFERROR(L36/L39-1,0)</f>
+      <c r="L43" s="84" t="n">
+        <f aca="false">IFERROR(L39/L42-1,0)</f>
         <v>-0.0258114779146783</v>
       </c>
-      <c r="M40" s="83"/>
-      <c r="N40" s="68" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C41" s="72" t="n">
-        <f aca="false">C12*GERACAO!$J$17</f>
+      <c r="M43" s="84"/>
+      <c r="N43" s="67" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="69" t="s">
+        <v>625</v>
+      </c>
+      <c r="C44" s="73" t="n">
+        <f aca="false">C14*GERACAO!$J$17</f>
         <v>10488.7105362</v>
       </c>
-      <c r="D41" s="72" t="n">
-        <f aca="false">D12*GERACAO!$J$17</f>
+      <c r="D44" s="73" t="n">
+        <f aca="false">D14*GERACAO!$J$17</f>
         <v>10318.1623974</v>
       </c>
-      <c r="E41" s="72" t="n">
-        <f aca="false">E12*GERACAO!$J$17</f>
+      <c r="E44" s="73" t="n">
+        <f aca="false">E14*GERACAO!$J$17</f>
         <v>8811.653838</v>
       </c>
-      <c r="F41" s="72" t="n">
-        <f aca="false">F12*GERACAO!$J$17</f>
+      <c r="F44" s="73" t="n">
+        <f aca="false">F14*GERACAO!$J$17</f>
         <v>8811.653838</v>
       </c>
-      <c r="G41" s="72" t="n">
-        <f aca="false">G12*GERACAO!$J$17</f>
+      <c r="G44" s="73" t="n">
+        <f aca="false">G14*GERACAO!$J$17</f>
         <v>7603.6045215</v>
       </c>
-      <c r="H41" s="72" t="n">
-        <f aca="false">H12*GERACAO!$J$17</f>
+      <c r="H44" s="73" t="n">
+        <f aca="false">H14*GERACAO!$J$17</f>
         <v>6651.3774132</v>
       </c>
-      <c r="I41" s="72" t="n">
-        <f aca="false">I12*GERACAO!$J$17</f>
+      <c r="I44" s="73" t="n">
+        <f aca="false">I14*GERACAO!$J$17</f>
         <v>9238.024185</v>
       </c>
-      <c r="J41" s="72" t="n">
-        <f aca="false">J12*GERACAO!$J$17</f>
+      <c r="J44" s="73" t="n">
+        <f aca="false">J14*GERACAO!$J$17</f>
         <v>8385.283491</v>
       </c>
-      <c r="K41" s="72" t="n">
-        <f aca="false">K12*GERACAO!$J$17</f>
+      <c r="K44" s="73" t="n">
+        <f aca="false">K14*GERACAO!$J$17</f>
         <v>9692.8192218</v>
       </c>
-      <c r="L41" s="72" t="n">
-        <f aca="false">L12*GERACAO!$J$17</f>
+      <c r="L44" s="73" t="n">
+        <f aca="false">L14*GERACAO!$J$17</f>
         <v>6992.4736908</v>
       </c>
-      <c r="M41" s="72"/>
-      <c r="N41" s="66" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="64" t="s">
-        <v>610</v>
-      </c>
-      <c r="C44" s="84" t="n">
-        <f aca="false">IFERROR(C36/(BYD!$F$33*12),0)</f>
+      <c r="M44" s="73"/>
+      <c r="N44" s="68" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="69" t="s">
+        <v>628</v>
+      </c>
+      <c r="C47" s="85" t="n">
+        <f aca="false">IFERROR(C39/(BYD!$F$33*12),0)</f>
         <v>2.03896529350962</v>
       </c>
-      <c r="D44" s="84" t="n">
-        <f aca="false">IFERROR(D36/(BYD!$F$33*12),0)</f>
+      <c r="D47" s="85" t="n">
+        <f aca="false">IFERROR(D39/(BYD!$F$33*12),0)</f>
         <v>2.00581138629808</v>
       </c>
-      <c r="E44" s="84" t="n">
-        <f aca="false">IFERROR(E36/(BYD!$F$33*12),0)</f>
+      <c r="E47" s="85" t="n">
+        <f aca="false">IFERROR(E39/(BYD!$F$33*12),0)</f>
         <v>1.71295187259615</v>
       </c>
-      <c r="F44" s="84" t="n">
-        <f aca="false">IFERROR(F36/(BYD!$F$33*12),0)</f>
+      <c r="F47" s="85" t="n">
+        <f aca="false">IFERROR(F39/(BYD!$F$33*12),0)</f>
         <v>1.71295187259615</v>
       </c>
-      <c r="G44" s="84" t="n">
-        <f aca="false">IFERROR(G36/(BYD!$F$33*12),0)</f>
+      <c r="G47" s="85" t="n">
+        <f aca="false">IFERROR(G39/(BYD!$F$33*12),0)</f>
         <v>1.47811169651442</v>
       </c>
-      <c r="H44" s="84" t="n">
-        <f aca="false">IFERROR(H36/(BYD!$F$33*12),0)</f>
+      <c r="H47" s="85" t="n">
+        <f aca="false">IFERROR(H39/(BYD!$F$33*12),0)</f>
         <v>1.29300238125</v>
       </c>
-      <c r="I44" s="84" t="n">
-        <f aca="false">IFERROR(I36/(BYD!$F$33*12),0)</f>
+      <c r="I47" s="85" t="n">
+        <f aca="false">IFERROR(I39/(BYD!$F$33*12),0)</f>
         <v>1.795836640625</v>
       </c>
-      <c r="J44" s="84" t="n">
-        <f aca="false">IFERROR(J36/(BYD!$F$33*12),0)</f>
+      <c r="J47" s="85" t="n">
+        <f aca="false">IFERROR(J39/(BYD!$F$33*12),0)</f>
         <v>1.63006710456731</v>
       </c>
-      <c r="K44" s="84" t="n">
-        <f aca="false">IFERROR(K36/(BYD!$F$33*12),0)</f>
+      <c r="K47" s="85" t="n">
+        <f aca="false">IFERROR(K39/(BYD!$F$33*12),0)</f>
         <v>1.88424705985577</v>
       </c>
-      <c r="L44" s="84" t="n">
-        <f aca="false">IFERROR(L36/(BYD!$F$33*12),0)</f>
+      <c r="L47" s="85" t="n">
+        <f aca="false">IFERROR(L39/(BYD!$F$33*12),0)</f>
         <v>1.35931019567308</v>
       </c>
-      <c r="M44" s="84"/>
-      <c r="N44" s="66" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="64" t="s">
-        <v>612</v>
-      </c>
-      <c r="C45" s="84" t="n">
-        <f aca="false">IFERROR(C36/(BYD!$F$34*12),0)</f>
-        <v>1.32476728548084</v>
-      </c>
-      <c r="D45" s="84" t="n">
-        <f aca="false">IFERROR(D36/(BYD!$F$34*12),0)</f>
-        <v>1.3032263540096</v>
-      </c>
-      <c r="E45" s="84" t="n">
-        <f aca="false">IFERROR(E36/(BYD!$F$34*12),0)</f>
-        <v>1.11294812601371</v>
-      </c>
-      <c r="F45" s="84" t="n">
-        <f aca="false">IFERROR(F36/(BYD!$F$34*12),0)</f>
-        <v>1.11294812601371</v>
-      </c>
-      <c r="G45" s="84" t="n">
-        <f aca="false">IFERROR(G36/(BYD!$F$34*12),0)</f>
-        <v>0.960366528092475</v>
-      </c>
-      <c r="H45" s="84" t="n">
-        <f aca="false">IFERROR(H36/(BYD!$F$34*12),0)</f>
-        <v>0.840096327378091</v>
-      </c>
-      <c r="I45" s="84" t="n">
-        <f aca="false">IFERROR(I36/(BYD!$F$34*12),0)</f>
-        <v>1.16680045469179</v>
-      </c>
-      <c r="J45" s="84" t="n">
-        <f aca="false">IFERROR(J36/(BYD!$F$34*12),0)</f>
-        <v>1.05909579733563</v>
-      </c>
-      <c r="K45" s="84" t="n">
-        <f aca="false">IFERROR(K36/(BYD!$F$34*12),0)</f>
-        <v>1.22424293861508</v>
-      </c>
-      <c r="L45" s="84" t="n">
-        <f aca="false">IFERROR(L36/(BYD!$F$34*12),0)</f>
-        <v>0.883178190320557</v>
-      </c>
-      <c r="M45" s="84"/>
-      <c r="N45" s="66"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="69" t="s">
-        <v>613</v>
-      </c>
-      <c r="C46" s="85" t="n">
-        <f aca="false">IFERROR(C36/(BYD!$F$35*12),0)</f>
-        <v>1.15197155259203</v>
-      </c>
-      <c r="D46" s="85" t="n">
-        <f aca="false">IFERROR(D36/(BYD!$F$35*12),0)</f>
-        <v>1.13324030783444</v>
-      </c>
-      <c r="E46" s="85" t="n">
-        <f aca="false">IFERROR(E36/(BYD!$F$35*12),0)</f>
-        <v>0.967780979142357</v>
-      </c>
-      <c r="F46" s="85" t="n">
-        <f aca="false">IFERROR(F36/(BYD!$F$35*12),0)</f>
-        <v>0.967780979142357</v>
-      </c>
-      <c r="G46" s="85" t="n">
-        <f aca="false">IFERROR(G36/(BYD!$F$35*12),0)</f>
-        <v>0.835101328776066</v>
-      </c>
-      <c r="H46" s="85" t="n">
-        <f aca="false">IFERROR(H36/(BYD!$F$35*12),0)</f>
-        <v>0.730518545546166</v>
-      </c>
-      <c r="I46" s="85" t="n">
-        <f aca="false">IFERROR(I36/(BYD!$F$35*12),0)</f>
-        <v>1.01460909103634</v>
-      </c>
-      <c r="J46" s="85" t="n">
-        <f aca="false">IFERROR(J36/(BYD!$F$35*12),0)</f>
-        <v>0.920952867248371</v>
-      </c>
-      <c r="K46" s="85" t="n">
-        <f aca="false">IFERROR(K36/(BYD!$F$35*12),0)</f>
-        <v>1.06455907705659</v>
-      </c>
-      <c r="L46" s="85" t="n">
-        <f aca="false">IFERROR(L36/(BYD!$F$35*12),0)</f>
-        <v>0.767981035061354</v>
-      </c>
-      <c r="M46" s="85"/>
-      <c r="N46" s="66" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="64" t="s">
-        <v>615</v>
-      </c>
-      <c r="C47" s="72" t="n">
-        <f aca="false">C36-BYD!$G$35</f>
-        <v>1230.88192728605</v>
-      </c>
-      <c r="D47" s="72" t="n">
-        <f aca="false">D36-BYD!$G$35</f>
-        <v>1079.16964788605</v>
-      </c>
-      <c r="E47" s="72" t="n">
-        <f aca="false">E36-BYD!$G$35</f>
-        <v>-260.955486813953</v>
-      </c>
-      <c r="F47" s="72" t="n">
-        <f aca="false">F36-BYD!$G$35</f>
-        <v>-260.955486813953</v>
-      </c>
-      <c r="G47" s="72" t="n">
-        <f aca="false">G36-BYD!$G$35</f>
-        <v>-1335.58413256395</v>
-      </c>
-      <c r="H47" s="72" t="n">
-        <f aca="false">H36-BYD!$G$35</f>
-        <v>-2182.64435921395</v>
-      </c>
-      <c r="I47" s="72" t="n">
-        <f aca="false">I36-BYD!$G$35</f>
-        <v>118.325211686048</v>
-      </c>
-      <c r="J47" s="72" t="n">
-        <f aca="false">J36-BYD!$G$35</f>
-        <v>-640.236185313953</v>
-      </c>
-      <c r="K47" s="72" t="n">
-        <f aca="false">K36-BYD!$G$35</f>
-        <v>522.891290086047</v>
-      </c>
-      <c r="L47" s="72" t="n">
-        <f aca="false">L36-BYD!$G$35</f>
-        <v>-1879.21980041395</v>
-      </c>
-      <c r="M47" s="72"/>
-      <c r="N47" s="66" t="s">
-        <v>616</v>
+      <c r="M47" s="85"/>
+      <c r="N47" s="68" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="69" t="s">
-        <v>617</v>
-      </c>
-      <c r="C48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C36)/GERACAO!$I$17*1000/C10,0),0)</f>
+        <v>630</v>
+      </c>
+      <c r="C48" s="85" t="n">
+        <f aca="false">IFERROR(C39/(BYD!$F$34*12),0)</f>
+        <v>1.32476728548084</v>
+      </c>
+      <c r="D48" s="85" t="n">
+        <f aca="false">IFERROR(D39/(BYD!$F$34*12),0)</f>
+        <v>1.3032263540096</v>
+      </c>
+      <c r="E48" s="85" t="n">
+        <f aca="false">IFERROR(E39/(BYD!$F$34*12),0)</f>
+        <v>1.11294812601371</v>
+      </c>
+      <c r="F48" s="85" t="n">
+        <f aca="false">IFERROR(F39/(BYD!$F$34*12),0)</f>
+        <v>1.11294812601371</v>
+      </c>
+      <c r="G48" s="85" t="n">
+        <f aca="false">IFERROR(G39/(BYD!$F$34*12),0)</f>
+        <v>0.960366528092475</v>
+      </c>
+      <c r="H48" s="85" t="n">
+        <f aca="false">IFERROR(H39/(BYD!$F$34*12),0)</f>
+        <v>0.840096327378091</v>
+      </c>
+      <c r="I48" s="85" t="n">
+        <f aca="false">IFERROR(I39/(BYD!$F$34*12),0)</f>
+        <v>1.16680045469179</v>
+      </c>
+      <c r="J48" s="85" t="n">
+        <f aca="false">IFERROR(J39/(BYD!$F$34*12),0)</f>
+        <v>1.05909579733563</v>
+      </c>
+      <c r="K48" s="85" t="n">
+        <f aca="false">IFERROR(K39/(BYD!$F$34*12),0)</f>
+        <v>1.22424293861508</v>
+      </c>
+      <c r="L48" s="85" t="n">
+        <f aca="false">IFERROR(L39/(BYD!$F$34*12),0)</f>
+        <v>0.883178190320557</v>
+      </c>
+      <c r="M48" s="85"/>
+      <c r="N48" s="68"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="64" t="s">
+        <v>631</v>
+      </c>
+      <c r="C49" s="86" t="n">
+        <f aca="false">IFERROR(C39/(BYD!$F$35*12),0)</f>
+        <v>1.15197155259203</v>
+      </c>
+      <c r="D49" s="86" t="n">
+        <f aca="false">IFERROR(D39/(BYD!$F$35*12),0)</f>
+        <v>1.13324030783444</v>
+      </c>
+      <c r="E49" s="86" t="n">
+        <f aca="false">IFERROR(E39/(BYD!$F$35*12),0)</f>
+        <v>0.967780979142357</v>
+      </c>
+      <c r="F49" s="86" t="n">
+        <f aca="false">IFERROR(F39/(BYD!$F$35*12),0)</f>
+        <v>0.967780979142357</v>
+      </c>
+      <c r="G49" s="86" t="n">
+        <f aca="false">IFERROR(G39/(BYD!$F$35*12),0)</f>
+        <v>0.835101328776066</v>
+      </c>
+      <c r="H49" s="86" t="n">
+        <f aca="false">IFERROR(H39/(BYD!$F$35*12),0)</f>
+        <v>0.730518545546166</v>
+      </c>
+      <c r="I49" s="86" t="n">
+        <f aca="false">IFERROR(I39/(BYD!$F$35*12),0)</f>
+        <v>1.01460909103634</v>
+      </c>
+      <c r="J49" s="86" t="n">
+        <f aca="false">IFERROR(J39/(BYD!$F$35*12),0)</f>
+        <v>0.920952867248371</v>
+      </c>
+      <c r="K49" s="86" t="n">
+        <f aca="false">IFERROR(K39/(BYD!$F$35*12),0)</f>
+        <v>1.06455907705659</v>
+      </c>
+      <c r="L49" s="86" t="n">
+        <f aca="false">IFERROR(L39/(BYD!$F$35*12),0)</f>
+        <v>0.767981035061354</v>
+      </c>
+      <c r="M49" s="86"/>
+      <c r="N49" s="68" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="69" t="s">
+        <v>633</v>
+      </c>
+      <c r="C50" s="73" t="n">
+        <f aca="false">C39-BYD!$G$35</f>
+        <v>1230.88192728605</v>
+      </c>
+      <c r="D50" s="73" t="n">
+        <f aca="false">D39-BYD!$G$35</f>
+        <v>1079.16964788605</v>
+      </c>
+      <c r="E50" s="73" t="n">
+        <f aca="false">E39-BYD!$G$35</f>
+        <v>-260.955486813953</v>
+      </c>
+      <c r="F50" s="73" t="n">
+        <f aca="false">F39-BYD!$G$35</f>
+        <v>-260.955486813953</v>
+      </c>
+      <c r="G50" s="73" t="n">
+        <f aca="false">G39-BYD!$G$35</f>
+        <v>-1335.58413256395</v>
+      </c>
+      <c r="H50" s="73" t="n">
+        <f aca="false">H39-BYD!$G$35</f>
+        <v>-2182.64435921395</v>
+      </c>
+      <c r="I50" s="73" t="n">
+        <f aca="false">I39-BYD!$G$35</f>
+        <v>118.325211686048</v>
+      </c>
+      <c r="J50" s="73" t="n">
+        <f aca="false">J39-BYD!$G$35</f>
+        <v>-640.236185313953</v>
+      </c>
+      <c r="K50" s="73" t="n">
+        <f aca="false">K39-BYD!$G$35</f>
+        <v>522.891290086047</v>
+      </c>
+      <c r="L50" s="73" t="n">
+        <f aca="false">L39-BYD!$G$35</f>
+        <v>-1879.21980041395</v>
+      </c>
+      <c r="M50" s="73"/>
+      <c r="N50" s="68" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="64" t="s">
+        <v>635</v>
+      </c>
+      <c r="C51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C39)/GERACAO!$I$17*1000/C12,0),0)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-D36)/GERACAO!$I$17*1000/D10,0),0)</f>
+      <c r="D51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-D39)/GERACAO!$I$17*1000/D12,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-E36)/GERACAO!$I$17*1000/E10,0),0)</f>
+      <c r="E51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-E39)/GERACAO!$I$17*1000/E12,0),0)</f>
         <v>1</v>
       </c>
-      <c r="F48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-F36)/GERACAO!$I$17*1000/F10,0),0)</f>
+      <c r="F51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-F39)/GERACAO!$I$17*1000/F12,0),0)</f>
         <v>1</v>
       </c>
-      <c r="G48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-G36)/GERACAO!$I$17*1000/G10,0),0)</f>
+      <c r="G51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-G39)/GERACAO!$I$17*1000/G12,0),0)</f>
         <v>2</v>
       </c>
-      <c r="H48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-H36)/GERACAO!$I$17*1000/H10,0),0)</f>
+      <c r="H51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-H39)/GERACAO!$I$17*1000/H12,0),0)</f>
         <v>3</v>
       </c>
-      <c r="I48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-I36)/GERACAO!$I$17*1000/I10,0),0)</f>
+      <c r="I51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-I39)/GERACAO!$I$17*1000/I12,0),0)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-J36)/GERACAO!$I$17*1000/J10,0),0)</f>
+      <c r="J51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-J39)/GERACAO!$I$17*1000/J12,0),0)</f>
         <v>1</v>
       </c>
-      <c r="K48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-K36)/GERACAO!$I$17*1000/K10,0),0)</f>
+      <c r="K51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-K39)/GERACAO!$I$17*1000/K12,0),0)</f>
         <v>0</v>
       </c>
-      <c r="L48" s="86" t="n">
-        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-L36)/GERACAO!$I$17*1000/L10,0),0)</f>
+      <c r="L51" s="87" t="n">
+        <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-L39)/GERACAO!$I$17*1000/L12,0),0)</f>
         <v>3</v>
       </c>
-      <c r="M48" s="86"/>
-      <c r="N48" s="66"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="69" t="s">
-        <v>618</v>
-      </c>
-      <c r="C49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="D49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/D10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="E49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/E10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="F49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/F10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="G49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/G10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="H49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/H10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="I49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/I10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="J49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/J10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/K10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="L49" s="87" t="n">
-        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/L10,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="M49" s="87"/>
-      <c r="N49" s="66" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="64" t="s">
-        <v>620</v>
-      </c>
-      <c r="C50" s="65" t="str">
-        <f aca="false">C14&amp;" kW = "&amp;TEXT(C14*1000/220,"0")&amp;" A"</f>
-        <v>6 kW = 27 A</v>
-      </c>
-      <c r="D50" s="65" t="str">
-        <f aca="false">D14&amp;" kW = "&amp;TEXT(D14*1000/220,"0")&amp;" A"</f>
-        <v>6 kW = 27 A</v>
-      </c>
-      <c r="E50" s="65" t="str">
-        <f aca="false">E14&amp;" kW = "&amp;TEXT(E14*1000/220,"0")&amp;" A"</f>
-        <v>5 kW = 23 A</v>
-      </c>
-      <c r="F50" s="65" t="str">
-        <f aca="false">F14&amp;" kW = "&amp;TEXT(F14*1000/220,"0")&amp;" A"</f>
-        <v>5 kW = 23 A</v>
-      </c>
-      <c r="G50" s="65" t="str">
-        <f aca="false">G14&amp;" kW = "&amp;TEXT(G14*1000/220,"0")&amp;" A"</f>
-        <v>4 kW = 18 A</v>
-      </c>
-      <c r="H50" s="65" t="str">
-        <f aca="false">H14&amp;" kW = "&amp;TEXT(H14*1000/220,"0")&amp;" A"</f>
-        <v>3 kW = 14 A</v>
-      </c>
-      <c r="I50" s="65" t="str">
-        <f aca="false">I14&amp;" kW = "&amp;TEXT(I14*1000/220,"0")&amp;" A"</f>
-        <v>9 kW = 41 A</v>
-      </c>
-      <c r="J50" s="65" t="str">
-        <f aca="false">J14&amp;" kW = "&amp;TEXT(J14*1000/220,"0")&amp;" A"</f>
-        <v>5 kW = 23 A</v>
-      </c>
-      <c r="K50" s="65" t="str">
-        <f aca="false">K14&amp;" kW = "&amp;TEXT(K14*1000/220,"0")&amp;" A"</f>
-        <v>7.5 kW = 34 A</v>
-      </c>
-      <c r="L50" s="65" t="str">
-        <f aca="false">L14&amp;" kW = "&amp;TEXT(L14*1000/220,"0")&amp;" A"</f>
-        <v>5 kW = 23 A</v>
-      </c>
-      <c r="M50" s="65"/>
-      <c r="N50" s="68" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
+      <c r="M51" s="87"/>
+      <c r="N51" s="68"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="64" t="s">
-        <v>623</v>
-      </c>
-      <c r="C52" s="79" t="n">
+        <v>636</v>
+      </c>
+      <c r="C52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="D52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/D12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/E12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="F52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/F12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="G52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/G12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="H52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/H12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="I52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/I12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="J52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/J12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/K12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="L52" s="88" t="n">
+        <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/L12,0),0)</f>
+        <v>4</v>
+      </c>
+      <c r="M52" s="88"/>
+      <c r="N52" s="68" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="69" t="s">
+        <v>638</v>
+      </c>
+      <c r="C53" s="70" t="str">
+        <f aca="false">C16&amp;" kW = "&amp;TEXT(C16*1000/220,"0")&amp;" A"</f>
+        <v>6 kW = 27 A</v>
+      </c>
+      <c r="D53" s="70" t="str">
+        <f aca="false">D16&amp;" kW = "&amp;TEXT(D16*1000/220,"0")&amp;" A"</f>
+        <v>6 kW = 27 A</v>
+      </c>
+      <c r="E53" s="70" t="str">
+        <f aca="false">E16&amp;" kW = "&amp;TEXT(E16*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="F53" s="70" t="str">
+        <f aca="false">F16&amp;" kW = "&amp;TEXT(F16*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="G53" s="70" t="str">
+        <f aca="false">G16&amp;" kW = "&amp;TEXT(G16*1000/220,"0")&amp;" A"</f>
+        <v>4 kW = 18 A</v>
+      </c>
+      <c r="H53" s="70" t="str">
+        <f aca="false">H16&amp;" kW = "&amp;TEXT(H16*1000/220,"0")&amp;" A"</f>
+        <v>3 kW = 14 A</v>
+      </c>
+      <c r="I53" s="70" t="str">
+        <f aca="false">I16&amp;" kW = "&amp;TEXT(I16*1000/220,"0")&amp;" A"</f>
+        <v>9 kW = 41 A</v>
+      </c>
+      <c r="J53" s="70" t="str">
+        <f aca="false">J16&amp;" kW = "&amp;TEXT(J16*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="K53" s="70" t="str">
+        <f aca="false">K16&amp;" kW = "&amp;TEXT(K16*1000/220,"0")&amp;" A"</f>
+        <v>7.5 kW = 34 A</v>
+      </c>
+      <c r="L53" s="70" t="str">
+        <f aca="false">L16&amp;" kW = "&amp;TEXT(L16*1000/220,"0")&amp;" A"</f>
+        <v>5 kW = 23 A</v>
+      </c>
+      <c r="M53" s="70"/>
+      <c r="N53" s="67" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="69" t="s">
+        <v>641</v>
+      </c>
+      <c r="C56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="D52" s="79" t="n">
+      <c r="D56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="E52" s="79" t="n">
+      <c r="E56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="F52" s="79" t="n">
+      <c r="F56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="G52" s="79" t="n">
+      <c r="G56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="H52" s="79" t="n">
+      <c r="H56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="I52" s="79" t="n">
+      <c r="I56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="J52" s="79" t="n">
+      <c r="J56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="K52" s="79" t="n">
+      <c r="K56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="L52" s="79" t="n">
+      <c r="L56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
         <v>410.62787654321</v>
       </c>
-      <c r="M52" s="79"/>
-      <c r="N52" s="66" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="64" t="s">
-        <v>625</v>
-      </c>
-      <c r="C53" s="79" t="n">
+      <c r="M56" s="80"/>
+      <c r="N56" s="68" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="69" t="s">
+        <v>643</v>
+      </c>
+      <c r="C57" s="80" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="D53" s="79" t="n">
+      <c r="D57" s="80" t="n">
         <f aca="false">ECONOMIA!D8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="E53" s="79" t="n">
+      <c r="E57" s="80" t="n">
         <f aca="false">ECONOMIA!E8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="F53" s="79" t="n">
+      <c r="F57" s="80" t="n">
         <f aca="false">ECONOMIA!F8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="G53" s="79" t="n">
+      <c r="G57" s="80" t="n">
         <f aca="false">ECONOMIA!G8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="H53" s="79" t="n">
+      <c r="H57" s="80" t="n">
         <f aca="false">ECONOMIA!H8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="I53" s="79" t="n">
+      <c r="I57" s="80" t="n">
         <f aca="false">ECONOMIA!I8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="J53" s="79" t="n">
+      <c r="J57" s="80" t="n">
         <f aca="false">ECONOMIA!J8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="K53" s="79" t="n">
+      <c r="K57" s="80" t="n">
         <f aca="false">ECONOMIA!K8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="L53" s="79" t="n">
+      <c r="L57" s="80" t="n">
         <f aca="false">ECONOMIA!L8/12</f>
         <v>710.553156093023</v>
       </c>
-      <c r="M53" s="79"/>
-      <c r="N53" s="66" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="69" t="s">
-        <v>627</v>
-      </c>
-      <c r="C54" s="88" t="n">
+      <c r="M57" s="80"/>
+      <c r="N57" s="68" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="64" t="s">
+        <v>645</v>
+      </c>
+      <c r="C58" s="89" t="n">
         <f aca="false">ECONOMIA!C19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="D54" s="88" t="n">
+      <c r="D58" s="89" t="n">
         <f aca="false">ECONOMIA!D19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="E54" s="88" t="n">
+      <c r="E58" s="89" t="n">
         <f aca="false">ECONOMIA!E19</f>
         <v>164.294054390772</v>
       </c>
-      <c r="F54" s="88" t="n">
+      <c r="F58" s="89" t="n">
         <f aca="false">ECONOMIA!F19</f>
         <v>164.294054390772</v>
       </c>
-      <c r="G54" s="88" t="n">
+      <c r="G58" s="89" t="n">
         <f aca="false">ECONOMIA!G19</f>
         <v>219.515548258055</v>
       </c>
-      <c r="H54" s="88" t="n">
+      <c r="H58" s="89" t="n">
         <f aca="false">ECONOMIA!H19</f>
         <v>281.009977650472</v>
       </c>
-      <c r="I54" s="88" t="n">
+      <c r="I58" s="89" t="n">
         <f aca="false">ECONOMIA!I19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="J54" s="88" t="n">
+      <c r="J58" s="89" t="n">
         <f aca="false">ECONOMIA!J19</f>
         <v>169.035046518012</v>
       </c>
-      <c r="K54" s="88" t="n">
+      <c r="K58" s="89" t="n">
         <f aca="false">ECONOMIA!K19</f>
         <v>162.893279261767</v>
       </c>
-      <c r="L54" s="88" t="n">
+      <c r="L58" s="89" t="n">
         <f aca="false">ECONOMIA!L19</f>
         <v>258.982122345726</v>
       </c>
-      <c r="M54" s="88"/>
-      <c r="N54" s="68" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="64" t="s">
-        <v>629</v>
-      </c>
-      <c r="C55" s="79" t="n">
+      <c r="M58" s="89"/>
+      <c r="N58" s="67" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="C59" s="80" t="n">
         <f aca="false">ECONOMIA!C26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="D55" s="79" t="n">
+      <c r="D59" s="80" t="n">
         <f aca="false">ECONOMIA!D26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="E55" s="79" t="n">
+      <c r="E59" s="80" t="n">
         <f aca="false">ECONOMIA!E26</f>
         <v>6105.10922042702</v>
       </c>
-      <c r="F55" s="79" t="n">
+      <c r="F59" s="80" t="n">
         <f aca="false">ECONOMIA!F26</f>
         <v>6105.10922042702</v>
       </c>
-      <c r="G55" s="79" t="n">
+      <c r="G59" s="80" t="n">
         <f aca="false">ECONOMIA!G26</f>
         <v>5442.45129401962</v>
       </c>
-      <c r="H55" s="79" t="n">
+      <c r="H59" s="80" t="n">
         <f aca="false">ECONOMIA!H26</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="I55" s="79" t="n">
+      <c r="I59" s="80" t="n">
         <f aca="false">ECONOMIA!I26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="J55" s="79" t="n">
+      <c r="J59" s="80" t="n">
         <f aca="false">ECONOMIA!J26</f>
         <v>6048.21731490014</v>
       </c>
-      <c r="K55" s="79" t="n">
+      <c r="K59" s="80" t="n">
         <f aca="false">ECONOMIA!K26</f>
         <v>6121.91852197507</v>
       </c>
-      <c r="L55" s="79" t="n">
+      <c r="L59" s="80" t="n">
         <f aca="false">ECONOMIA!L26</f>
         <v>4968.85240496757</v>
       </c>
-      <c r="M55" s="79"/>
-      <c r="N55" s="66"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="69" t="s">
-        <v>630</v>
-      </c>
-      <c r="C56" s="88" t="n">
-        <f aca="false">C55/12</f>
+      <c r="M59" s="80"/>
+      <c r="N59" s="68"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="64" t="s">
+        <v>648</v>
+      </c>
+      <c r="C60" s="89" t="n">
+        <f aca="false">C59/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="D56" s="88" t="n">
-        <f aca="false">D55/12</f>
+      <c r="D60" s="89" t="n">
+        <f aca="false">D59/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="E56" s="88" t="n">
-        <f aca="false">E55/12</f>
+      <c r="E60" s="89" t="n">
+        <f aca="false">E59/12</f>
         <v>508.759101702252</v>
       </c>
-      <c r="F56" s="88" t="n">
-        <f aca="false">F55/12</f>
+      <c r="F60" s="89" t="n">
+        <f aca="false">F59/12</f>
         <v>508.759101702252</v>
       </c>
-      <c r="G56" s="88" t="n">
-        <f aca="false">G55/12</f>
+      <c r="G60" s="89" t="n">
+        <f aca="false">G59/12</f>
         <v>453.537607834968</v>
       </c>
-      <c r="H56" s="88" t="n">
-        <f aca="false">H55/12</f>
+      <c r="H60" s="89" t="n">
+        <f aca="false">H59/12</f>
         <v>392.043178442552</v>
       </c>
-      <c r="I56" s="88" t="n">
-        <f aca="false">I55/12</f>
+      <c r="I60" s="89" t="n">
+        <f aca="false">I59/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="J56" s="88" t="n">
-        <f aca="false">J55/12</f>
+      <c r="J60" s="89" t="n">
+        <f aca="false">J59/12</f>
         <v>504.018109575012</v>
       </c>
-      <c r="K56" s="88" t="n">
-        <f aca="false">K55/12</f>
+      <c r="K60" s="89" t="n">
+        <f aca="false">K59/12</f>
         <v>510.159876831256</v>
       </c>
-      <c r="L56" s="88" t="n">
-        <f aca="false">L55/12</f>
+      <c r="L60" s="89" t="n">
+        <f aca="false">L59/12</f>
         <v>414.071033747298</v>
       </c>
-      <c r="M56" s="88"/>
-      <c r="N56" s="66"/>
-    </row>
-    <row r="57" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="69" t="s">
-        <v>631</v>
-      </c>
-      <c r="C57" s="89" t="n">
-        <f aca="false">IFERROR(C31/C55,0)</f>
+      <c r="M60" s="89"/>
+      <c r="N60" s="68"/>
+    </row>
+    <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="64" t="s">
+        <v>649</v>
+      </c>
+      <c r="C61" s="90" t="n">
+        <f aca="false">IFERROR(C34/C59,0)</f>
         <v>4.86754273076902</v>
       </c>
-      <c r="D57" s="89" t="n">
-        <f aca="false">IFERROR(D31/D55,0)</f>
+      <c r="D61" s="90" t="n">
+        <f aca="false">IFERROR(D34/D59,0)</f>
         <v>4.71713236566947</v>
       </c>
-      <c r="E57" s="89" t="n">
-        <f aca="false">IFERROR(E31/E55,0)</f>
+      <c r="E61" s="90" t="n">
+        <f aca="false">IFERROR(E34/E59,0)</f>
         <v>3.03358045389802</v>
       </c>
-      <c r="F57" s="89" t="n">
-        <f aca="false">IFERROR(F31/F55,0)</f>
+      <c r="F61" s="90" t="n">
+        <f aca="false">IFERROR(F34/F59,0)</f>
         <v>3.19737768731264</v>
       </c>
-      <c r="G57" s="89" t="n">
-        <f aca="false">IFERROR(G31/G55,0)</f>
+      <c r="G61" s="90" t="n">
+        <f aca="false">IFERROR(G34/G59,0)</f>
         <v>3.92266441106401</v>
       </c>
-      <c r="H57" s="89" t="n">
-        <f aca="false">IFERROR(H31/H55,0)</f>
+      <c r="H61" s="90" t="n">
+        <f aca="false">IFERROR(H34/H59,0)</f>
         <v>3.1645408844895</v>
       </c>
-      <c r="I57" s="89" t="n">
-        <f aca="false">IFERROR(I31/I55,0)</f>
+      <c r="I61" s="90" t="n">
+        <f aca="false">IFERROR(I34/I59,0)</f>
         <v>3.44345321231079</v>
       </c>
-      <c r="J57" s="89" t="n">
-        <f aca="false">IFERROR(J31/J55,0)</f>
+      <c r="J61" s="90" t="n">
+        <f aca="false">IFERROR(J34/J59,0)</f>
         <v>3.51062121192161</v>
       </c>
-      <c r="K57" s="89" t="n">
-        <f aca="false">IFERROR(K31/K55,0)</f>
+      <c r="K61" s="90" t="n">
+        <f aca="false">IFERROR(K34/K59,0)</f>
         <v>3.16730775334533</v>
       </c>
-      <c r="L57" s="89" t="n">
-        <f aca="false">IFERROR(L31/L55,0)</f>
+      <c r="L61" s="90" t="n">
+        <f aca="false">IFERROR(L34/L59,0)</f>
         <v>4.01340156130682</v>
       </c>
-      <c r="M57" s="89"/>
-      <c r="N57" s="66" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="64" t="s">
-        <v>633</v>
-      </c>
-      <c r="C58" s="90" t="n">
+      <c r="M61" s="90"/>
+      <c r="N61" s="68" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="69" t="s">
+        <v>651</v>
+      </c>
+      <c r="C62" s="91" t="n">
         <f aca="false">PROJECAO!E10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="D58" s="90" t="n">
+      <c r="D62" s="91" t="n">
         <f aca="false">PROJECAO!H10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="E58" s="90" t="n">
+      <c r="E62" s="91" t="n">
         <f aca="false">PROJECAO!K10</f>
         <v>34773.1378668975</v>
       </c>
-      <c r="F58" s="90" t="n">
+      <c r="F62" s="91" t="n">
         <f aca="false">PROJECAO!N10</f>
         <v>34773.1378668975</v>
       </c>
-      <c r="G58" s="90" t="n">
+      <c r="G62" s="91" t="n">
         <f aca="false">PROJECAO!Q10</f>
         <v>30998.8081044653</v>
       </c>
-      <c r="H58" s="90" t="n">
+      <c r="H62" s="91" t="n">
         <f aca="false">PROJECAO!T10</f>
         <v>26795.7299400571</v>
       </c>
-      <c r="I58" s="90" t="n">
+      <c r="I62" s="91" t="n">
         <f aca="false">PROJECAO!W10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="J58" s="90" t="n">
+      <c r="J62" s="91" t="n">
         <f aca="false">PROJECAO!Z10</f>
         <v>34449.0961498751</v>
       </c>
-      <c r="K58" s="90" t="n">
+      <c r="K62" s="91" t="n">
         <f aca="false">PROJECAO!AC10</f>
         <v>34868.8793416317</v>
       </c>
-      <c r="L58" s="90" t="n">
+      <c r="L62" s="91" t="n">
         <f aca="false">PROJECAO!AF10</f>
         <v>28301.310178054</v>
       </c>
-      <c r="M58" s="90"/>
-      <c r="N58" s="66"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="64" t="s">
-        <v>634</v>
-      </c>
-      <c r="C59" s="90" t="n">
+      <c r="M62" s="91"/>
+      <c r="N62" s="68"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="69" t="s">
+        <v>652</v>
+      </c>
+      <c r="C63" s="91" t="n">
         <f aca="false">PROJECAO!E15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="D59" s="90" t="n">
+      <c r="D63" s="91" t="n">
         <f aca="false">PROJECAO!H15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="E59" s="90" t="n">
+      <c r="E63" s="91" t="n">
         <f aca="false">PROJECAO!K15</f>
         <v>82456.7440682698</v>
       </c>
-      <c r="F59" s="90" t="n">
+      <c r="F63" s="91" t="n">
         <f aca="false">PROJECAO!N15</f>
         <v>82456.7440682698</v>
       </c>
-      <c r="G59" s="90" t="n">
+      <c r="G63" s="91" t="n">
         <f aca="false">PROJECAO!Q15</f>
         <v>73506.7624922213</v>
       </c>
-      <c r="H59" s="90" t="n">
+      <c r="H63" s="91" t="n">
         <f aca="false">PROJECAO!T15</f>
         <v>63540.0996667917</v>
       </c>
-      <c r="I59" s="90" t="n">
+      <c r="I63" s="91" t="n">
         <f aca="false">PROJECAO!W15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="J59" s="90" t="n">
+      <c r="J63" s="91" t="n">
         <f aca="false">PROJECAO!Z15</f>
         <v>81688.351378768</v>
       </c>
-      <c r="K59" s="90" t="n">
+      <c r="K63" s="91" t="n">
         <f aca="false">PROJECAO!AC15</f>
         <v>82683.773630833</v>
       </c>
-      <c r="L59" s="90" t="n">
+      <c r="L63" s="91" t="n">
         <f aca="false">PROJECAO!AF15</f>
         <v>67110.2475445575</v>
       </c>
-      <c r="M59" s="90"/>
-      <c r="N59" s="66"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="64" t="s">
-        <v>635</v>
-      </c>
-      <c r="C60" s="90" t="n">
+      <c r="M63" s="91"/>
+      <c r="N63" s="68"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="69" t="s">
+        <v>653</v>
+      </c>
+      <c r="C64" s="91" t="n">
         <f aca="false">PROJECAO!E25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="D60" s="90" t="n">
+      <c r="D64" s="91" t="n">
         <f aca="false">PROJECAO!H25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="E60" s="90" t="n">
+      <c r="E64" s="91" t="n">
         <f aca="false">PROJECAO!K25</f>
         <v>237508.469153103</v>
       </c>
-      <c r="F60" s="90" t="n">
+      <c r="F64" s="91" t="n">
         <f aca="false">PROJECAO!N25</f>
         <v>237508.469153103</v>
       </c>
-      <c r="G60" s="90" t="n">
+      <c r="G64" s="91" t="n">
         <f aca="false">PROJECAO!Q25</f>
         <v>211728.935324847</v>
       </c>
-      <c r="H60" s="90" t="n">
+      <c r="H64" s="91" t="n">
         <f aca="false">PROJECAO!T25</f>
         <v>183020.952042449</v>
       </c>
-      <c r="I60" s="90" t="n">
+      <c r="I64" s="91" t="n">
         <f aca="false">PROJECAO!W25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="J60" s="90" t="n">
+      <c r="J64" s="91" t="n">
         <f aca="false">PROJECAO!Z25</f>
         <v>235295.19025816</v>
       </c>
-      <c r="K60" s="90" t="n">
+      <c r="K64" s="91" t="n">
         <f aca="false">PROJECAO!AC25</f>
         <v>238162.405280052</v>
       </c>
-      <c r="L60" s="90" t="n">
+      <c r="L64" s="91" t="n">
         <f aca="false">PROJECAO!AF25</f>
         <v>193304.408740621</v>
       </c>
-      <c r="M60" s="90"/>
-      <c r="N60" s="66"/>
-    </row>
-    <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="69" t="s">
-        <v>636</v>
-      </c>
-      <c r="C61" s="91" t="n">
-        <f aca="false">C60-C31</f>
+      <c r="M64" s="91"/>
+      <c r="N64" s="68"/>
+    </row>
+    <row r="65" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="64" t="s">
+        <v>654</v>
+      </c>
+      <c r="C65" s="92" t="n">
+        <f aca="false">C64-C34</f>
         <v>208363.705280052</v>
       </c>
-      <c r="D61" s="91" t="n">
-        <f aca="false">D60-D31</f>
+      <c r="D65" s="92" t="n">
+        <f aca="false">D64-D34</f>
         <v>209284.505280052</v>
       </c>
-      <c r="E61" s="91" t="n">
-        <f aca="false">E60-E31</f>
+      <c r="E65" s="92" t="n">
+        <f aca="false">E64-E34</f>
         <v>218988.129153103</v>
       </c>
-      <c r="F61" s="91" t="n">
-        <f aca="false">F60-F31</f>
+      <c r="F65" s="92" t="n">
+        <f aca="false">F64-F34</f>
         <v>217988.129153103</v>
       </c>
-      <c r="G61" s="91" t="n">
-        <f aca="false">G60-G31</f>
+      <c r="G65" s="92" t="n">
+        <f aca="false">G64-G34</f>
         <v>190380.025324847</v>
       </c>
-      <c r="H61" s="91" t="n">
-        <f aca="false">H60-H31</f>
+      <c r="H65" s="92" t="n">
+        <f aca="false">H64-H34</f>
         <v>168133.312042449</v>
       </c>
-      <c r="I61" s="91" t="n">
-        <f aca="false">I60-I31</f>
+      <c r="I65" s="92" t="n">
+        <f aca="false">I64-I34</f>
         <v>217081.865280052</v>
       </c>
-      <c r="J61" s="91" t="n">
-        <f aca="false">J60-J31</f>
+      <c r="J65" s="92" t="n">
+        <f aca="false">J64-J34</f>
         <v>214062.19025816</v>
       </c>
-      <c r="K61" s="91" t="n">
-        <f aca="false">K60-K31</f>
+      <c r="K65" s="92" t="n">
+        <f aca="false">K64-K34</f>
         <v>218772.405280052</v>
       </c>
-      <c r="L61" s="91" t="n">
-        <f aca="false">L60-L31</f>
+      <c r="L65" s="92" t="n">
+        <f aca="false">L64-L34</f>
         <v>173362.408740621</v>
       </c>
-      <c r="M61" s="91"/>
-      <c r="N61" s="66" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="64" t="s">
-        <v>638</v>
-      </c>
-      <c r="C62" s="84" t="n">
-        <f aca="false">IFERROR(C61/C31,0)</f>
+      <c r="M65" s="92"/>
+      <c r="N65" s="68" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="69" t="s">
+        <v>656</v>
+      </c>
+      <c r="C66" s="85" t="n">
+        <f aca="false">IFERROR(C65/C34,0)</f>
         <v>6.99237568350472</v>
       </c>
-      <c r="D62" s="84" t="n">
-        <f aca="false">IFERROR(D61/D31,0)</f>
+      <c r="D66" s="85" t="n">
+        <f aca="false">IFERROR(D65/D34,0)</f>
         <v>7.24722037544461</v>
       </c>
-      <c r="E62" s="84" t="n">
-        <f aca="false">IFERROR(E61/E31,0)</f>
+      <c r="E66" s="85" t="n">
+        <f aca="false">IFERROR(E65/E34,0)</f>
         <v>11.8241959463543</v>
       </c>
-      <c r="F62" s="84" t="n">
-        <f aca="false">IFERROR(F61/F31,0)</f>
+      <c r="F66" s="85" t="n">
+        <f aca="false">IFERROR(F65/F34,0)</f>
         <v>11.1672301380561</v>
       </c>
-      <c r="G62" s="84" t="n">
-        <f aca="false">IFERROR(G61/G31,0)</f>
+      <c r="G66" s="85" t="n">
+        <f aca="false">IFERROR(G65/G34,0)</f>
         <v>8.91755248042393</v>
       </c>
-      <c r="H62" s="84" t="n">
-        <f aca="false">IFERROR(H61/H31,0)</f>
+      <c r="H66" s="85" t="n">
+        <f aca="false">IFERROR(H65/H34,0)</f>
         <v>11.2934831875602</v>
       </c>
-      <c r="I62" s="84" t="n">
-        <f aca="false">IFERROR(I61/I31,0)</f>
+      <c r="I66" s="85" t="n">
+        <f aca="false">IFERROR(I65/I34,0)</f>
         <v>10.2977374052113</v>
       </c>
-      <c r="J62" s="84" t="n">
-        <f aca="false">IFERROR(J61/J31,0)</f>
+      <c r="J66" s="85" t="n">
+        <f aca="false">IFERROR(J65/J34,0)</f>
         <v>10.0815800997579</v>
       </c>
-      <c r="K62" s="84" t="n">
-        <f aca="false">IFERROR(K61/K31,0)</f>
+      <c r="K66" s="85" t="n">
+        <f aca="false">IFERROR(K65/K34,0)</f>
         <v>11.2827439546185</v>
       </c>
-      <c r="L62" s="84" t="n">
-        <f aca="false">IFERROR(L61/L31,0)</f>
+      <c r="L66" s="85" t="n">
+        <f aca="false">IFERROR(L65/L34,0)</f>
         <v>8.69333109721298</v>
       </c>
-      <c r="M62" s="84"/>
-      <c r="N62" s="66"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="64" t="s">
-        <v>640</v>
-      </c>
-      <c r="C65" s="75" t="n">
-        <f aca="false">C14*1.35</f>
+      <c r="M66" s="85"/>
+      <c r="N66" s="68"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="69" t="s">
+        <v>658</v>
+      </c>
+      <c r="C69" s="76" t="n">
+        <f aca="false">C16*1.35</f>
         <v>8.1</v>
       </c>
-      <c r="D65" s="75" t="n">
-        <f aca="false">D14*1.35</f>
+      <c r="D69" s="76" t="n">
+        <f aca="false">D16*1.35</f>
         <v>8.1</v>
       </c>
-      <c r="E65" s="75" t="n">
-        <f aca="false">E14*1.35</f>
+      <c r="E69" s="76" t="n">
+        <f aca="false">E16*1.35</f>
         <v>6.75</v>
       </c>
-      <c r="F65" s="75" t="n">
-        <f aca="false">F14*1.35</f>
+      <c r="F69" s="76" t="n">
+        <f aca="false">F16*1.35</f>
         <v>6.75</v>
       </c>
-      <c r="G65" s="75" t="n">
-        <f aca="false">G14*1.35</f>
+      <c r="G69" s="76" t="n">
+        <f aca="false">G16*1.35</f>
         <v>5.4</v>
       </c>
-      <c r="H65" s="75" t="n">
-        <f aca="false">H14*1.35</f>
+      <c r="H69" s="76" t="n">
+        <f aca="false">H16*1.35</f>
         <v>4.05</v>
       </c>
-      <c r="I65" s="75" t="n">
-        <f aca="false">I14*1.35</f>
+      <c r="I69" s="76" t="n">
+        <f aca="false">I16*1.35</f>
         <v>12.15</v>
       </c>
-      <c r="J65" s="75" t="n">
-        <f aca="false">J14*1.35</f>
+      <c r="J69" s="76" t="n">
+        <f aca="false">J16*1.35</f>
         <v>6.75</v>
       </c>
-      <c r="K65" s="75" t="n">
-        <f aca="false">K14*1.35</f>
+      <c r="K69" s="76" t="n">
+        <f aca="false">K16*1.35</f>
         <v>10.125</v>
       </c>
-      <c r="L65" s="75" t="n">
-        <f aca="false">L14*1.35</f>
+      <c r="L69" s="76" t="n">
+        <f aca="false">L16*1.35</f>
         <v>6.75</v>
       </c>
-      <c r="M65" s="75"/>
-      <c r="N65" s="66"/>
-    </row>
-    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="69" t="s">
-        <v>641</v>
-      </c>
-      <c r="C66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((C65-C12)*1000/C10,0))</f>
+      <c r="M69" s="76"/>
+      <c r="N69" s="68"/>
+    </row>
+    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="C70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((C69-C14)*1000/C12,0))</f>
         <v>1</v>
       </c>
-      <c r="D66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((D65-D12)*1000/D10,0))</f>
+      <c r="D70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((D69-D14)*1000/D12,0))</f>
         <v>1</v>
       </c>
-      <c r="E66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((E65-E12)*1000/E10,0))</f>
+      <c r="E70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((E69-E14)*1000/E12,0))</f>
         <v>0</v>
       </c>
-      <c r="F66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((F65-F12)*1000/F10,0))</f>
+      <c r="F70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((F69-F14)*1000/F12,0))</f>
         <v>0</v>
       </c>
-      <c r="G66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((G65-G12)*1000/G10,0))</f>
+      <c r="G70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((G69-G14)*1000/G12,0))</f>
         <v>0</v>
       </c>
-      <c r="H66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((H65-H12)*1000/H10,0))</f>
+      <c r="H70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((H69-H14)*1000/H12,0))</f>
         <v>0</v>
       </c>
-      <c r="I66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((I65-I12)*1000/I10,0))</f>
+      <c r="I70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((I69-I14)*1000/I12,0))</f>
         <v>8</v>
       </c>
-      <c r="J66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((J65-J12)*1000/J10,0))</f>
+      <c r="J70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((J69-J14)*1000/J12,0))</f>
         <v>1</v>
       </c>
-      <c r="K66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((K65-K12)*1000/K10,0))</f>
+      <c r="K70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((K69-K14)*1000/K12,0))</f>
         <v>5</v>
       </c>
-      <c r="L66" s="86" t="n">
-        <f aca="false">MAX(0,ROUNDDOWN((L65-L12)*1000/L10,0))</f>
+      <c r="L70" s="87" t="n">
+        <f aca="false">MAX(0,ROUNDDOWN((L69-L14)*1000/L12,0))</f>
         <v>2</v>
       </c>
-      <c r="M66" s="86"/>
-      <c r="N66" s="68" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="64" t="s">
-        <v>643</v>
-      </c>
-      <c r="C67" s="72" t="n">
-        <f aca="false">C66*C10/1000*GERACAO!$I$17</f>
+      <c r="M70" s="87"/>
+      <c r="N70" s="67" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="69" t="s">
+        <v>661</v>
+      </c>
+      <c r="C71" s="73" t="n">
+        <f aca="false">C70*C12/1000*GERACAO!$I$17</f>
         <v>777.525431925</v>
       </c>
-      <c r="D67" s="72" t="n">
-        <f aca="false">D66*D10/1000*GERACAO!$I$17</f>
+      <c r="D71" s="73" t="n">
+        <f aca="false">D70*D12/1000*GERACAO!$I$17</f>
         <v>764.882741975</v>
       </c>
-      <c r="E67" s="72" t="n">
-        <f aca="false">E66*E10/1000*GERACAO!$I$17</f>
+      <c r="E71" s="73" t="n">
+        <f aca="false">E70*E12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="F67" s="72" t="n">
-        <f aca="false">F66*F10/1000*GERACAO!$I$17</f>
+      <c r="F71" s="73" t="n">
+        <f aca="false">F70*F12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="G67" s="72" t="n">
-        <f aca="false">G66*G10/1000*GERACAO!$I$17</f>
+      <c r="G71" s="73" t="n">
+        <f aca="false">G70*G12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="H67" s="72" t="n">
-        <f aca="false">H66*H10/1000*GERACAO!$I$17</f>
+      <c r="H71" s="73" t="n">
+        <f aca="false">H70*H12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="I67" s="72" t="n">
-        <f aca="false">I66*I10/1000*GERACAO!$I$17</f>
+      <c r="I71" s="73" t="n">
+        <f aca="false">I70*I12/1000*GERACAO!$I$17</f>
         <v>6574.198774</v>
       </c>
-      <c r="J67" s="72" t="n">
-        <f aca="false">J66*J10/1000*GERACAO!$I$17</f>
+      <c r="J71" s="73" t="n">
+        <f aca="false">J70*J12/1000*GERACAO!$I$17</f>
         <v>745.91870705</v>
       </c>
-      <c r="K67" s="72" t="n">
-        <f aca="false">K66*K10/1000*GERACAO!$I$17</f>
+      <c r="K71" s="73" t="n">
+        <f aca="false">K70*K12/1000*GERACAO!$I$17</f>
         <v>3919.2338845</v>
       </c>
-      <c r="L67" s="72" t="n">
-        <f aca="false">L66*L10/1000*GERACAO!$I$17</f>
+      <c r="L71" s="73" t="n">
+        <f aca="false">L70*L12/1000*GERACAO!$I$17</f>
         <v>1555.05086385</v>
       </c>
-      <c r="M67" s="72"/>
-      <c r="N67" s="66"/>
-    </row>
-    <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="69" t="s">
-        <v>644</v>
-      </c>
-      <c r="C68" s="92" t="str">
-        <f aca="false">IF(C16&gt;1.35,"JA SOBRECARREGADO",IF(C16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="M71" s="73"/>
+      <c r="N71" s="68"/>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="C72" s="65" t="str">
+        <f aca="false">IF(C18&gt;1.35,"JA SOBRECARREGADO",IF(C18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="D68" s="92" t="str">
-        <f aca="false">IF(D16&gt;1.35,"JA SOBRECARREGADO",IF(D16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="D72" s="65" t="str">
+        <f aca="false">IF(D18&gt;1.35,"JA SOBRECARREGADO",IF(D18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="E68" s="92" t="str">
-        <f aca="false">IF(E16&gt;1.35,"JA SOBRECARREGADO",IF(E16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="E72" s="65" t="str">
+        <f aca="false">IF(E18&gt;1.35,"JA SOBRECARREGADO",IF(E18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="F68" s="92" t="str">
-        <f aca="false">IF(F16&gt;1.35,"JA SOBRECARREGADO",IF(F16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="F72" s="65" t="str">
+        <f aca="false">IF(F18&gt;1.35,"JA SOBRECARREGADO",IF(F18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="G68" s="92" t="str">
-        <f aca="false">IF(G16&gt;1.35,"JA SOBRECARREGADO",IF(G16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="G72" s="65" t="str">
+        <f aca="false">IF(G18&gt;1.35,"JA SOBRECARREGADO",IF(G18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="H68" s="92" t="str">
-        <f aca="false">IF(H16&gt;1.35,"JA SOBRECARREGADO",IF(H16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="H72" s="65" t="str">
+        <f aca="false">IF(H18&gt;1.35,"JA SOBRECARREGADO",IF(H18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>JA SOBRECARREGADO</v>
       </c>
-      <c r="I68" s="92" t="str">
-        <f aca="false">IF(I16&gt;1.35,"JA SOBRECARREGADO",IF(I16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="I72" s="65" t="str">
+        <f aca="false">IF(I18&gt;1.35,"JA SOBRECARREGADO",IF(I18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="J68" s="92" t="str">
-        <f aca="false">IF(J16&gt;1.35,"JA SOBRECARREGADO",IF(J16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="J72" s="65" t="str">
+        <f aca="false">IF(J18&gt;1.35,"JA SOBRECARREGADO",IF(J18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K68" s="92" t="str">
-        <f aca="false">IF(K16&gt;1.35,"JA SOBRECARREGADO",IF(K16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="K72" s="65" t="str">
+        <f aca="false">IF(K18&gt;1.35,"JA SOBRECARREGADO",IF(K18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="L68" s="92" t="str">
-        <f aca="false">IF(L16&gt;1.35,"JA SOBRECARREGADO",IF(L16&lt;1.1,"SUBAPROVEITADO","OK"))</f>
+      <c r="L72" s="65" t="str">
+        <f aca="false">IF(L18&gt;1.35,"JA SOBRECARREGADO",IF(L18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="M68" s="92"/>
-      <c r="N68" s="66" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="21" t="s">
-        <v>647</v>
-      </c>
-      <c r="C71" s="35" t="n">
-        <f aca="false">F26-E26</f>
+      <c r="M72" s="65"/>
+      <c r="N72" s="68" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="C75" s="35" t="n">
+        <f aca="false">F29-E29</f>
         <v>1000</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="C72" s="29" t="n">
-        <f aca="false">IFERROR(F57-E57,0)</f>
-        <v>0.163797233414615</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="C73" s="93" t="n">
-        <f aca="false">F61-E61</f>
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="5" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>652</v>
+        <v>666</v>
+      </c>
+      <c r="C76" s="29" t="n">
+        <f aca="false">IFERROR(F61-E61,0)</f>
+        <v>0.163797233414615</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="4"/>
+        <v>667</v>
+      </c>
+      <c r="C77" s="93" t="n">
+        <f aca="false">F65-E65</f>
+        <v>-1000</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="5" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>656</v>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="5" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="4" t="s">
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -15031,12 +15159,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15044,312 +15172,312 @@
         <v>451</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="F5" s="94" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="F8" s="94" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="F10" s="94" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="F13" s="95" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="F14" s="94" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="D17" s="96" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="F20" s="94" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -15363,7 +15491,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -15377,7 +15505,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -15391,7 +15519,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>738</v>
+        <v>755</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -15405,7 +15533,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>739</v>
+        <v>756</v>
       </c>
       <c r="C28" s="47" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -15422,78 +15550,78 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="C30" s="44" t="str">
-        <f aca="false">COMPARATIVO!C11</f>
-        <v>JA Solar bifacial N-type</v>
-      </c>
-      <c r="D30" s="44" t="str">
-        <f aca="false">COMPARATIVO!D11</f>
-        <v>Astronergy bifacial N-type</v>
-      </c>
-      <c r="E30" s="44" t="str">
-        <f aca="false">COMPARATIVO!G11</f>
-        <v>Maxeon bifacial PERC</v>
+        <v>757</v>
+      </c>
+      <c r="C30" s="44" t="n">
+        <f aca="false">COMPARATIVO!C14</f>
+        <v>7.38</v>
+      </c>
+      <c r="D30" s="44" t="n">
+        <f aca="false">COMPARATIVO!D14</f>
+        <v>7.26</v>
+      </c>
+      <c r="E30" s="44" t="n">
+        <f aca="false">COMPARATIVO!G14</f>
+        <v>5.35</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="C31" s="97" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
-        <v>0</v>
+        <v>2.4700135501355</v>
       </c>
       <c r="D31" s="97" t="n">
         <f aca="false">IFERROR(D28/(D30*1000),0)</f>
-        <v>0</v>
+        <v>2.38400826446281</v>
       </c>
       <c r="E31" s="97" t="n">
         <f aca="false">IFERROR(E28/(E30*1000),0)</f>
-        <v>0</v>
+        <v>2.08577757009346</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
       <c r="C34" s="98" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -15502,32 +15630,32 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="C39" s="12" t="n">
-        <f aca="false">COMPARATIVO!C28-COMPARATIVO!D28</f>
-        <v>0</v>
+        <f aca="false">COMPARATIVO!C39-COMPARATIVO!D39</f>
+        <v>151.712279400001</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
-        <v>0</v>
+        <v>154.969542038719</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="C41" s="99" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
-        <v>0</v>
+        <v>5.94181274517766</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -15557,58 +15685,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>754</v>
+        <v>771</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>755</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>756</v>
+        <v>773</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>757</v>
+        <v>774</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>760</v>
+        <v>777</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>761</v>
+        <v>778</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>762</v>
+        <v>779</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>763</v>
+        <v>780</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -15651,62 +15779,62 @@
         <v>8099.42325581395</v>
       </c>
       <c r="M5" s="100"/>
-      <c r="N5" s="66" t="s">
-        <v>770</v>
+      <c r="N5" s="68" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
       <c r="C6" s="36" t="n">
-        <f aca="false">COMPARATIVO!C36</f>
+        <f aca="false">COMPARATIVO!C39</f>
         <v>9330.3051831</v>
       </c>
       <c r="D6" s="36" t="n">
-        <f aca="false">COMPARATIVO!D36</f>
+        <f aca="false">COMPARATIVO!D39</f>
         <v>9178.5929037</v>
       </c>
       <c r="E6" s="36" t="n">
-        <f aca="false">COMPARATIVO!E36</f>
+        <f aca="false">COMPARATIVO!E39</f>
         <v>7838.467769</v>
       </c>
       <c r="F6" s="36" t="n">
-        <f aca="false">COMPARATIVO!F36</f>
+        <f aca="false">COMPARATIVO!F39</f>
         <v>7838.467769</v>
       </c>
       <c r="G6" s="36" t="n">
-        <f aca="false">COMPARATIVO!G36</f>
+        <f aca="false">COMPARATIVO!G39</f>
         <v>6763.83912325</v>
       </c>
       <c r="H6" s="36" t="n">
-        <f aca="false">COMPARATIVO!H36</f>
+        <f aca="false">COMPARATIVO!H39</f>
         <v>5916.7788966</v>
       </c>
       <c r="I6" s="36" t="n">
-        <f aca="false">COMPARATIVO!I36</f>
+        <f aca="false">COMPARATIVO!I39</f>
         <v>8217.7484675</v>
       </c>
       <c r="J6" s="36" t="n">
-        <f aca="false">COMPARATIVO!J36</f>
+        <f aca="false">COMPARATIVO!J39</f>
         <v>7459.1870705</v>
       </c>
       <c r="K6" s="36" t="n">
-        <f aca="false">COMPARATIVO!K36</f>
+        <f aca="false">COMPARATIVO!K39</f>
         <v>8622.3145459</v>
       </c>
       <c r="L6" s="36" t="n">
-        <f aca="false">COMPARATIVO!L36</f>
+        <f aca="false">COMPARATIVO!L39</f>
         <v>6220.2034554</v>
       </c>
       <c r="M6" s="100"/>
-      <c r="N6" s="66" t="s">
-        <v>772</v>
+      <c r="N6" s="68" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="C7" s="101" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -15749,13 +15877,13 @@
         <v>1.02147</v>
       </c>
       <c r="M7" s="100"/>
-      <c r="N7" s="66" t="s">
-        <v>774</v>
+      <c r="N7" s="68" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
       <c r="C8" s="102" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -15798,13 +15926,13 @@
         <v>8526.63787311628</v>
       </c>
       <c r="M8" s="100"/>
-      <c r="N8" s="66" t="s">
-        <v>776</v>
+      <c r="N8" s="68" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -15847,13 +15975,13 @@
         <v>1866.06103662</v>
       </c>
       <c r="M9" s="100"/>
-      <c r="N9" s="66" t="s">
-        <v>778</v>
+      <c r="N9" s="68" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">C6-C9</f>
@@ -15896,13 +16024,13 @@
         <v>4354.14241878</v>
       </c>
       <c r="M10" s="100"/>
-      <c r="N10" s="66" t="s">
-        <v>780</v>
+      <c r="N10" s="68" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -15945,13 +16073,13 @@
         <v>600</v>
       </c>
       <c r="M11" s="100"/>
-      <c r="N11" s="66" t="s">
-        <v>782</v>
+      <c r="N11" s="68" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -15994,13 +16122,13 @@
         <v>4354.14241878</v>
       </c>
       <c r="M12" s="100"/>
-      <c r="N12" s="66" t="s">
-        <v>784</v>
+      <c r="N12" s="68" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">C10-C12</f>
@@ -16043,13 +16171,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="100"/>
-      <c r="N13" s="66" t="s">
-        <v>786</v>
+      <c r="N13" s="68" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -16092,13 +16220,13 @@
         <v>1879.21980041395</v>
       </c>
       <c r="M14" s="100"/>
-      <c r="N14" s="66" t="s">
-        <v>788</v>
+      <c r="N14" s="68" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
       <c r="C15" s="101" t="n">
         <f aca="false">C14*C7</f>
@@ -16141,11 +16269,11 @@
         <v>1919.56664952884</v>
       </c>
       <c r="M15" s="100"/>
-      <c r="N15" s="66"/>
+      <c r="N15" s="68"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="C16" s="101" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -16188,13 +16316,13 @@
         <v>934.898818619864</v>
       </c>
       <c r="M16" s="100"/>
-      <c r="N16" s="66" t="s">
-        <v>791</v>
+      <c r="N16" s="68" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="C17" s="101" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -16237,13 +16365,13 @@
         <v>253.32</v>
       </c>
       <c r="M17" s="100"/>
-      <c r="N17" s="66" t="s">
-        <v>793</v>
+      <c r="N17" s="68" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -16286,13 +16414,13 @@
         <v>3107.78546814871</v>
       </c>
       <c r="M18" s="100"/>
-      <c r="N18" s="66" t="s">
-        <v>795</v>
+      <c r="N18" s="68" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">C18/12</f>
@@ -16335,13 +16463,13 @@
         <v>258.982122345726</v>
       </c>
       <c r="M19" s="100"/>
-      <c r="N19" s="66" t="s">
-        <v>797</v>
+      <c r="N19" s="68" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="C20" s="37" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -16384,11 +16512,11 @@
         <v>0.635520410929228</v>
       </c>
       <c r="M20" s="100"/>
-      <c r="N20" s="66"/>
+      <c r="N20" s="68"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="C21" s="101" t="n">
         <f aca="false">C8-C18</f>
@@ -16431,11 +16559,11 @@
         <v>5418.85240496757</v>
       </c>
       <c r="M21" s="100"/>
-      <c r="N21" s="66"/>
+      <c r="N21" s="68"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="C22" s="101" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -16478,13 +16606,13 @@
         <v>300</v>
       </c>
       <c r="M22" s="100"/>
-      <c r="N22" s="66" t="s">
-        <v>801</v>
+      <c r="N22" s="68" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="C23" s="101" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -16527,13 +16655,13 @@
         <v>150</v>
       </c>
       <c r="M23" s="100"/>
-      <c r="N23" s="66" t="s">
-        <v>803</v>
+      <c r="N23" s="68" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="C24" s="101" t="n">
         <f aca="false">0</f>
@@ -16576,13 +16704,13 @@
         <v>0</v>
       </c>
       <c r="M24" s="100"/>
-      <c r="N24" s="66" t="s">
-        <v>805</v>
+      <c r="N24" s="68" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="C25" s="101" t="n">
         <f aca="false">C22+C23</f>
@@ -16625,11 +16753,11 @@
         <v>450</v>
       </c>
       <c r="M25" s="100"/>
-      <c r="N25" s="66"/>
+      <c r="N25" s="68"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="C26" s="103" t="n">
         <f aca="false">C21-C25</f>
@@ -16672,13 +16800,13 @@
         <v>4968.85240496757</v>
       </c>
       <c r="M26" s="100"/>
-      <c r="N26" s="66" t="s">
-        <v>808</v>
+      <c r="N26" s="68" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -16695,122 +16823,122 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4576</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>811</v>
+        <v>828</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>7042.97674418605</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
         <v>2466.97674418605</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.539112050739958</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>818</v>
+        <v>835</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4927.56672</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>819</v>
+        <v>836</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>820</v>
+        <v>837</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7447.50945488372</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2519.94273488372</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>823</v>
+        <v>840</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>824</v>
+        <v>841</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>529.696418232558</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>1990.24631665116</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="1072">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">RONMA SOLAR bifacial N-type 144 cel</t>
   </si>
   <si>
-    <t xml:space="preserve">Nao informado (650 W)</t>
+    <t xml:space="preserve">ZNShine ZXNR-MD132-650 N-type (Tier 1 BNEF)</t>
   </si>
   <si>
     <t xml:space="preserve">Longi ou DAH Solar (Tier 1 de verdade)</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">AUXSOL 3 kW mono 220V 1 MPPT</t>
   </si>
   <si>
-    <t xml:space="preserve">4x MICROINVERSOR 2,25 kW = 9,0 kW AC</t>
+    <t xml:space="preserve">4x DEYE SUN-S225G4-EU-Q0 2,25 kW = 9,0 kW AC</t>
   </si>
   <si>
     <t xml:space="preserve">2x microinversor 2,5 kW = 5,0 kW AC - Solis ou Growatt</t>
@@ -1703,6 +1703,9 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">4 por micro = 16 canais (10 usados, 6 livres)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 por modulo (10 MPPTs)</t>
   </si>
   <si>
@@ -1760,6 +1763,9 @@
     <t xml:space="preserve">25 anos eficiencia / 15 anos defeito</t>
   </si>
   <si>
+    <t xml:space="preserve">nao declarada pelo vendedor - exigir por escrito (N-type costuma dar 12/25 a 30 anos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 anos produto / 25 anos eficiencia</t>
   </si>
   <si>
@@ -1775,6 +1781,9 @@
     <t xml:space="preserve">10 a 25 anos</t>
   </si>
   <si>
+    <t xml:space="preserve">nao declarada pelo vendedor - a Deye pratica 10 anos, exigir por escrito</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 a 10 anos</t>
   </si>
   <si>
@@ -2037,6 +2046,33 @@
   </si>
   <si>
     <t xml:space="preserve">ALERTA: os inversores de 5 kW da SunWash (C e D) nao aceitam nenhum modulo a mais. Sun Coast v2 (+5) e a opcao com microinversores tem folga real - mas nos micros o limite verdadeiro e o numero de CANAIS livres, nao a potencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITE REAL de expansao (canais e estrutura)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 modulo (limite de potencia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - inversor no limite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - inversor sobrecarregado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MODULOS - canais livres nos 4 micros Deye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 modulo; para 12 precisa de um 3o micro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 modulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 a 3 modulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A linha acima calcula pela POTENCIA do inversor. Em microinversor o limite verdadeiro e o numero de CANAIS livres. Os 4 micros Deye SUN-S225G4-EU-Q0 tem 4 MPPTs cada = 16 canais para 10 modulos, ou seja 6 canais livres: da para ir a 10,4 kWp sem comprar inversor nenhum.</t>
   </si>
   <si>
     <t xml:space="preserve">Geracao extra possivel sem trocar inversor (kWh/ano)</t>
@@ -2888,7 +2924,34 @@
     <t xml:space="preserve">1-bis) PERGUNTAS ESPECIFICAS DA PROPOSTA COM MICROINVERSORES (opcao G)</t>
   </si>
   <si>
-    <t xml:space="preserve">QUAL A MARCA E O MODELO DOS 4 MICROINVERSORES? Deye, Hoymiles, APsystems e Sungrow tem rede no Brasil. Marca desconhecida em microinversor e pior que em inversor string, porque sao 4 equipamentos DEBAIXO dos modulos: trocar um exige desmontar placa.</t>
+    <t xml:space="preserve">RESPONDIDO: os microinversores sao DEYE SUN-S225G4-EU-Q0, 2,25 kW monofasico. A Deye e um dos maiores fabricantes do mundo e tem rede de assistencia estabelecida no Brasil. Isso resolve a principal duvida que havia sobre esta proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSEQUENCIA 1 - CORRENTE: o sufixo Q0 indica 4 MPPTs por micro, e a linha G4 da Deye foi projetada para modulos de 600 a 700 W, com corrente por MPPT na casa de 20 A. Isso e folgado para os ~16 A de um modulo de 650 W. Ou seja: nesta proposta o risco de corte de corrente por MPPT NAO existe - diferente das propostas com inversor string e modulos de 605 a 620 W, onde a verificacao continua obrigatoria. CONFIRMAR na ficha tecnica do SUN-S225G4-EU-Q0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSEQUENCIA 2 - EXPANSAO: 4 micros x 4 MPPTs = 16 canais para 10 modulos = 6 CANAIS LIVRES. Da para chegar a 16 modulos (10,4 kWp) sem comprar inversor, com DC/AC de 1,16. E a unica proposta do conjunto com folga real de expansao - e voce tem um consumo subindo 39% ao ano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERGUNTA QUE SOBROU: QUANTO CUSTA COM 3 MICROS EM VEZ DE 4? Tres micros dao 12 canais (10 usados, 2 livres) e 6,75 kW AC em vez de 9,0 kW. Duas vantagens: preco menor, e potencia homologada de 31 A em vez de 41 A, o que pode reduzir o custo do padrao de entrada. Vale so se voce NAO pretende passar de ~7,8 kWp no futuro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXIGIR A GARANTIA DA DEYE POR ESCRITO. A Deye pratica 10 anos de fabrica nos microinversores, com extensao opcional, mas o Yuri nao declarou nada. Sem estar no papel, nao vale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPONDIDO: o modulo e ZNShine ZXNR-MD132-650, N-type, 650 W. A ZNShine e fabricante listada como Tier 1 pela Bloomberg NEF e atua desde os anos 1990. Com isso, os DOIS equipamentos desta proposta estao identificados e sao de fabricantes credenciados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESCLARECIMENTO IMPORTANTE SOBRE 'TIER 1': o selo Tier 1 da Bloomberg NEF mede BANCABILIDADE, ou seja, que bancos financiaram projetos com aquele fabricante. NAO e certificado de qualidade nem de eficiencia, e nao substitui o registro INMETRO. Exigir o INMETRO do modelo ZXNR-MD132-650 do mesmo jeito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESCLARECIMENTO SOBRE 'MONO': significa monocristalino, e nao monofacial. Se o modulo e bifacial ou nao precisa ser lido na ficha tecnica. Em telhado ceramico com modulo assentado proximo a telha o ganho bifacial e pequeno (1% a 2%), portanto isso quase nao muda a estimativa de geracao desta planilha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGORA SO FALTA PAPEL NESTA PROPOSTA: razao social e CNPJ da SunWash, garantias de modulo/inversor/instalacao por escrito em anos, escopo item a item, esclarecimento dos R$ 1.800 da regiao, e o tipo de telha considerado. Nenhuma pendencia tecnica restou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTO A PESAR COM HONESTIDADE: a Deye domina o mercado brasileiro em inversor string e hibrido, mas a linha de MICROINVERSORES dela e mais recente no Brasil e tem menos historico de campo aqui do que os micros da Hoymiles ou APsystems. Nao e impedimento - e um dado a considerar, e reforca a exigencia da garantia por escrito.</t>
   </si>
   <si>
     <t xml:space="preserve">QUAL A MARCA DO MODULO DE 650 W? O orcamento nao informa. 650 W e formato grande (cerca de 2,6 m2 por placa): confirmar que cabe na agua Sudeste e que o peso por m2 e compativel com o telhado.</t>
@@ -4577,110 +4640,110 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="AA4" s="17" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="AC4" s="17" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7265,22 +7328,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -7314,23 +7377,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7338,25 +7401,25 @@
         <v>268</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7782,32 +7845,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7815,12 +7878,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>
@@ -7839,7 +7902,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -7851,32 +7914,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -7886,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E6" s="110"/>
     </row>
@@ -7898,10 +7961,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E7" s="110"/>
     </row>
@@ -7910,10 +7973,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E8" s="110"/>
     </row>
@@ -7922,17 +7985,17 @@
         <v>4</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E9" s="110"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
       <c r="C10" s="7" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -7942,10 +8005,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="111" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E11" s="110"/>
     </row>
@@ -7954,10 +8017,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E12" s="110"/>
     </row>
@@ -7966,10 +8029,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E13" s="110"/>
     </row>
@@ -7978,10 +8041,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E14" s="110"/>
     </row>
@@ -7990,10 +8053,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E15" s="110"/>
     </row>
@@ -8002,10 +8065,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E16" s="110"/>
     </row>
@@ -8014,10 +8077,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E17" s="110"/>
     </row>
@@ -8026,10 +8089,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="109" t="s">
+        <v>936</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>924</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>912</v>
       </c>
       <c r="E19" s="110"/>
     </row>
@@ -8038,10 +8101,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E20" s="110"/>
     </row>
@@ -8050,10 +8113,10 @@
         <v>14</v>
       </c>
       <c r="C21" s="109" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E21" s="110"/>
     </row>
@@ -8062,10 +8125,10 @@
         <v>15</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E22" s="110"/>
     </row>
@@ -8074,10 +8137,10 @@
         <v>16</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E23" s="110"/>
     </row>
@@ -8086,10 +8149,10 @@
         <v>17</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E24" s="110"/>
     </row>
@@ -8098,66 +8161,66 @@
         <v>18</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E25" s="110"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="8"/>
       <c r="C26" s="7" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="109" t="s">
-        <v>932</v>
+      <c r="C27" s="111" t="s">
+        <v>944</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E27" s="110"/>
     </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="109" t="s">
-        <v>933</v>
+      <c r="C28" s="111" t="s">
+        <v>945</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E28" s="110"/>
     </row>
-    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="109" t="s">
-        <v>934</v>
+      <c r="C29" s="111" t="s">
+        <v>946</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E29" s="110"/>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="109" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E30" s="110"/>
     </row>
@@ -8166,274 +8229,274 @@
         <v>23</v>
       </c>
       <c r="C31" s="109" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E31" s="110"/>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="111" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E32" s="110"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8"/>
-      <c r="C34" s="7" t="s">
-        <v>938</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C33" s="111" t="s">
+        <v>950</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E33" s="110"/>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C34" s="111" t="s">
+        <v>951</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E34" s="110"/>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C35" s="109" t="s">
-        <v>939</v>
+        <v>952</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E35" s="110"/>
     </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>940</v>
+        <v>953</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E36" s="110"/>
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C37" s="109" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E37" s="110"/>
     </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C38" s="109" t="s">
-        <v>942</v>
+        <v>955</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E38" s="110"/>
     </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="C39" s="111" t="s">
-        <v>943</v>
+        <v>31</v>
+      </c>
+      <c r="C39" s="109" t="s">
+        <v>956</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E39" s="110"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8"/>
-      <c r="C41" s="7" t="s">
-        <v>944</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-    </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C42" s="111" t="s">
-        <v>945</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E42" s="110"/>
-    </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="C43" s="109" t="s">
-        <v>946</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E43" s="110"/>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C40" s="109" t="s">
+        <v>957</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E40" s="110"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C41" s="111" t="s">
+        <v>958</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E41" s="110"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="8"/>
+      <c r="C43" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" s="109" t="s">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E44" s="110"/>
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C45" s="109" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E45" s="110"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="8"/>
-      <c r="C47" s="7" t="s">
-        <v>949</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="109" t="s">
+        <v>962</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E46" s="110"/>
+    </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C47" s="109" t="s">
+        <v>963</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E47" s="110"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="C48" s="109" t="s">
-        <v>950</v>
+        <v>38</v>
+      </c>
+      <c r="C48" s="111" t="s">
+        <v>964</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E48" s="110"/>
     </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C49" s="109" t="s">
-        <v>951</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E49" s="110"/>
-    </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="C50" s="109" t="s">
-        <v>952</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E50" s="110"/>
-    </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="8"/>
+      <c r="C50" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="C51" s="109" t="s">
-        <v>953</v>
+        <v>39</v>
+      </c>
+      <c r="C51" s="111" t="s">
+        <v>966</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E51" s="110"/>
     </row>
-    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C52" s="109" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E52" s="110"/>
     </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C53" s="109" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E53" s="110"/>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C54" s="109" t="s">
-        <v>956</v>
+        <v>969</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E54" s="110"/>
     </row>
-    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="C55" s="109" t="s">
-        <v>957</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E55" s="110"/>
-    </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="C56" s="109" t="s">
-        <v>958</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E56" s="110"/>
-    </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="8"/>
+      <c r="C56" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="n">
         <v>43</v>
       </c>
       <c r="C57" s="109" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E57" s="110"/>
     </row>
@@ -8442,10 +8505,10 @@
         <v>44</v>
       </c>
       <c r="C58" s="109" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E58" s="110"/>
     </row>
@@ -8454,300 +8517,408 @@
         <v>45</v>
       </c>
       <c r="C59" s="109" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E59" s="110"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="n">
         <v>46</v>
       </c>
       <c r="C60" s="109" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E60" s="110"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="8"/>
-      <c r="C62" s="7" t="s">
-        <v>963</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C61" s="109" t="s">
+        <v>975</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E61" s="110"/>
+    </row>
+    <row r="62" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C62" s="109" t="s">
+        <v>976</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E62" s="110"/>
+    </row>
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="C63" s="111" t="s">
-        <v>964</v>
+        <v>49</v>
+      </c>
+      <c r="C63" s="109" t="s">
+        <v>977</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E63" s="110"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="C64" s="111" t="s">
-        <v>965</v>
+        <v>50</v>
+      </c>
+      <c r="C64" s="109" t="s">
+        <v>978</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E64" s="110"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C65" s="111" t="s">
-        <v>966</v>
+        <v>51</v>
+      </c>
+      <c r="C65" s="109" t="s">
+        <v>979</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E65" s="110"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C66" s="111" t="s">
-        <v>967</v>
+        <v>52</v>
+      </c>
+      <c r="C66" s="109" t="s">
+        <v>980</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E66" s="110"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="C67" s="111" t="s">
-        <v>968</v>
+        <v>53</v>
+      </c>
+      <c r="C67" s="109" t="s">
+        <v>981</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E67" s="110"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="C68" s="111" t="s">
-        <v>969</v>
+        <v>54</v>
+      </c>
+      <c r="C68" s="109" t="s">
+        <v>982</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E68" s="110"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="C69" s="111" t="s">
-        <v>970</v>
+        <v>55</v>
+      </c>
+      <c r="C69" s="109" t="s">
+        <v>983</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E69" s="110"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="C70" s="111" t="s">
-        <v>971</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E70" s="110"/>
-    </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="C71" s="111" t="s">
-        <v>972</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E71" s="110"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="7" t="s">
+        <v>984</v>
+      </c>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C72" s="111" t="s">
+        <v>985</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E72" s="110"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="8"/>
-      <c r="C73" s="7" t="s">
-        <v>973</v>
-      </c>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
+      <c r="B73" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="C73" s="111" t="s">
+        <v>986</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E73" s="110"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C74" s="111" t="s">
-        <v>974</v>
+        <v>987</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E74" s="110"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C75" s="111" t="s">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E75" s="110"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C76" s="111" t="s">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E76" s="110"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C77" s="111" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E77" s="110"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C78" s="111" t="s">
-        <v>978</v>
+        <v>991</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E78" s="110"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C79" s="111" t="s">
-        <v>979</v>
+        <v>992</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E79" s="110"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C80" s="111" t="s">
-        <v>980</v>
+        <v>993</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E80" s="110"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="8"/>
       <c r="C82" s="7" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C83" s="111" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E83" s="110"/>
     </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C84" s="111" t="s">
-        <v>983</v>
+        <v>996</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E84" s="110"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C85" s="111" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E85" s="110"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C86" s="111" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E86" s="110"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C87" s="111" t="s">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E87" s="110"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C88" s="111" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E88" s="110"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="C89" s="111" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E89" s="110"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="8"/>
+      <c r="C91" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="C92" s="111" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E92" s="110"/>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="C93" s="111" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E93" s="110"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="C94" s="111" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E94" s="110"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="C95" s="111" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E95" s="110"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="C96" s="111" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="E96" s="110"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8777,73 +8948,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>990</v>
+        <v>1011</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>993</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="68" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="68" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="68" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="48" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="68" t="s">
-        <v>1001</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8854,7 +9025,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="68" t="s">
-        <v>1002</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8865,40 +9036,40 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="68" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="68" t="s">
-        <v>1005</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>1006</v>
+        <v>1027</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="68" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>1008</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="68" t="s">
-        <v>1009</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8909,29 +9080,29 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="68" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>1011</v>
+        <v>1032</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="68" t="s">
-        <v>1012</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>1013</v>
+        <v>1034</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="68" t="s">
-        <v>1014</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8942,205 +9113,205 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="68" t="s">
-        <v>1015</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>1016</v>
+        <v>1037</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="68" t="s">
-        <v>1017</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="68" t="s">
-        <v>1019</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="68" t="s">
-        <v>1021</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="68" t="s">
-        <v>1023</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>1024</v>
+        <v>1045</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="68" t="s">
-        <v>1025</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>1026</v>
+        <v>1047</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="68" t="s">
-        <v>1027</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>1028</v>
+        <v>1049</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="68" t="s">
-        <v>1029</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>1030</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="68" t="s">
-        <v>1031</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>1032</v>
+        <v>1053</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="68" t="s">
-        <v>1033</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>1034</v>
+        <v>1055</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="68" t="s">
-        <v>1035</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="48" t="s">
-        <v>1036</v>
+        <v>1057</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="68" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>1038</v>
+        <v>1059</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="68" t="s">
-        <v>1039</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>1040</v>
+        <v>1061</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="68" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>1042</v>
+        <v>1063</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="68" t="s">
-        <v>1043</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1044</v>
+        <v>1065</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="68" t="s">
-        <v>1045</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="68" t="s">
-        <v>1047</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="68" t="s">
-        <v>1049</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="68" t="s">
-        <v>1050</v>
+        <v>1071</v>
       </c>
     </row>
   </sheetData>
@@ -12329,7 +12500,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -12903,22 +13074,22 @@
         <v>549</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K17" s="70" t="s">
         <v>546</v>
       </c>
       <c r="L17" s="70" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M17" s="70"/>
       <c r="N17" s="67" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="64" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C18" s="77" t="n">
         <f aca="false">IFERROR(C14/C16,0)</f>
@@ -12962,90 +13133,90 @@
       </c>
       <c r="M18" s="77"/>
       <c r="N18" s="67" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="69" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C19" s="78" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D19" s="78" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E19" s="78" t="s">
+        <v>557</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>557</v>
+      </c>
+      <c r="G19" s="78" t="s">
         <v>556</v>
       </c>
-      <c r="F19" s="78" t="s">
+      <c r="H19" s="78" t="s">
         <v>556</v>
       </c>
-      <c r="G19" s="78" t="s">
-        <v>555</v>
-      </c>
-      <c r="H19" s="78" t="s">
-        <v>555</v>
-      </c>
       <c r="I19" s="78" t="s">
+        <v>557</v>
+      </c>
+      <c r="J19" s="78" t="s">
+        <v>557</v>
+      </c>
+      <c r="K19" s="78" t="s">
         <v>556</v>
       </c>
-      <c r="J19" s="78" t="s">
+      <c r="L19" s="78" t="s">
         <v>556</v>
-      </c>
-      <c r="K19" s="78" t="s">
-        <v>555</v>
-      </c>
-      <c r="L19" s="78" t="s">
-        <v>555</v>
       </c>
       <c r="M19" s="78"/>
       <c r="N19" s="67" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="69" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C20" s="70" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D20" s="70" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E20" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F20" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G20" s="70" t="s">
+        <v>562</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>562</v>
+      </c>
+      <c r="I20" s="66" t="s">
         <v>561</v>
       </c>
-      <c r="H20" s="70" t="s">
+      <c r="J20" s="70" t="s">
+        <v>563</v>
+      </c>
+      <c r="K20" s="70" t="s">
+        <v>562</v>
+      </c>
+      <c r="L20" s="66" t="s">
         <v>561</v>
-      </c>
-      <c r="I20" s="66" t="s">
-        <v>560</v>
-      </c>
-      <c r="J20" s="70" t="s">
-        <v>562</v>
-      </c>
-      <c r="K20" s="70" t="s">
-        <v>561</v>
-      </c>
-      <c r="L20" s="66" t="s">
-        <v>560</v>
       </c>
       <c r="M20" s="70"/>
       <c r="N20" s="67" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="69" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C21" s="76" t="n">
         <f aca="false">C11*C12*0.00452</f>
@@ -13085,207 +13256,207 @@
       </c>
       <c r="M21" s="76"/>
       <c r="N21" s="68" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="69" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C22" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D22" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E22" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F22" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H22" s="70" t="s">
-        <v>567</v>
-      </c>
-      <c r="I22" s="66" t="s">
-        <v>560</v>
+        <v>568</v>
+      </c>
+      <c r="I22" s="70" t="s">
+        <v>569</v>
       </c>
       <c r="J22" s="70" t="s">
+        <v>570</v>
+      </c>
+      <c r="K22" s="70" t="s">
         <v>568</v>
       </c>
-      <c r="K22" s="70" t="s">
-        <v>567</v>
-      </c>
       <c r="L22" s="70" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M22" s="70"/>
       <c r="N22" s="68" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="69" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E23" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G23" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H23" s="70" t="s">
-        <v>572</v>
-      </c>
-      <c r="I23" s="66" t="s">
-        <v>560</v>
+        <v>574</v>
+      </c>
+      <c r="I23" s="70" t="s">
+        <v>575</v>
       </c>
       <c r="J23" s="70" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K23" s="70" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L23" s="70" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M23" s="70"/>
       <c r="N23" s="68" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="69" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H24" s="70" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="I24" s="66" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J24" s="70" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K24" s="70" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L24" s="70" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M24" s="70"/>
       <c r="N24" s="68" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="69" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H25" s="66" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="I25" s="66" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="J25" s="70" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="K25" s="66" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L25" s="70" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M25" s="70"/>
       <c r="N25" s="67" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="69" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C26" s="70" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D26" s="70" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E26" s="70" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F26" s="70" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="G26" s="70" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="H26" s="70" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J26" s="70" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K26" s="70" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L26" s="70" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M26" s="70"/>
       <c r="N26" s="68" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -13302,7 +13473,7 @@
     </row>
     <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="69" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C29" s="79" t="n">
         <v>18228.7</v>
@@ -13336,12 +13507,12 @@
       </c>
       <c r="M29" s="80"/>
       <c r="N29" s="68" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="69" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C30" s="79" t="n">
         <v>0</v>
@@ -13375,12 +13546,12 @@
       </c>
       <c r="M30" s="80"/>
       <c r="N30" s="67" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="69" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C31" s="79" t="n">
         <v>790</v>
@@ -13414,12 +13585,12 @@
       </c>
       <c r="M31" s="80"/>
       <c r="N31" s="68" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="69" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C32" s="80" t="n">
         <f aca="false">6900/10*C11</f>
@@ -13455,12 +13626,12 @@
       </c>
       <c r="M32" s="80"/>
       <c r="N32" s="67" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="69" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C33" s="80" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -13504,12 +13675,12 @@
       </c>
       <c r="M33" s="80"/>
       <c r="N33" s="67" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="64" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C34" s="81" t="n">
         <f aca="false">SUM(C29:C33)</f>
@@ -13553,12 +13724,12 @@
       </c>
       <c r="M34" s="81"/>
       <c r="N34" s="68" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="64" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C35" s="82" t="n">
         <f aca="false">IFERROR(C34/(C14*1000),0)</f>
@@ -13602,12 +13773,12 @@
       </c>
       <c r="M35" s="82"/>
       <c r="N35" s="68" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="69" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C36" s="83" t="n">
         <f aca="false">IFERROR(C29/(C14*1000),0)</f>
@@ -13618,38 +13789,38 @@
         <v>2.38400826446281</v>
       </c>
       <c r="E36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G36" s="83" t="n">
         <f aca="false">IFERROR(G29/(G14*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
       <c r="H36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="J36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="L36" s="83" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M36" s="83"/>
       <c r="N36" s="68" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -13666,7 +13837,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="69" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C39" s="73" t="n">
         <f aca="false">C14*GERACAO!$I$17</f>
@@ -13710,12 +13881,12 @@
       </c>
       <c r="M39" s="73"/>
       <c r="N39" s="68" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="69" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C40" s="73" t="n">
         <f aca="false">C39/12</f>
@@ -13762,7 +13933,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="69" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C41" s="73" t="n">
         <f aca="false">C39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -13806,12 +13977,12 @@
       </c>
       <c r="M41" s="73"/>
       <c r="N41" s="68" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="69" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C42" s="72" t="n">
         <v>10554</v>
@@ -13845,12 +14016,12 @@
       </c>
       <c r="M42" s="73"/>
       <c r="N42" s="68" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="64" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C43" s="84" t="n">
         <f aca="false">IFERROR(C39/C42-1,0)</f>
@@ -13894,12 +14065,12 @@
       </c>
       <c r="M43" s="84"/>
       <c r="N43" s="67" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="69" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C44" s="73" t="n">
         <f aca="false">C14*GERACAO!$J$17</f>
@@ -13943,12 +14114,12 @@
       </c>
       <c r="M44" s="73"/>
       <c r="N44" s="68" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -13965,7 +14136,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="69" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C47" s="85" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$33*12),0)</f>
@@ -14009,12 +14180,12 @@
       </c>
       <c r="M47" s="85"/>
       <c r="N47" s="68" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="69" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C48" s="85" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$34*12),0)</f>
@@ -14061,7 +14232,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="64" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C49" s="86" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$35*12),0)</f>
@@ -14105,12 +14276,12 @@
       </c>
       <c r="M49" s="86"/>
       <c r="N49" s="68" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="69" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C50" s="73" t="n">
         <f aca="false">C39-BYD!$G$35</f>
@@ -14154,12 +14325,12 @@
       </c>
       <c r="M50" s="73"/>
       <c r="N50" s="68" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="64" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C51" s="87" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C39)/GERACAO!$I$17*1000/C12,0),0)</f>
@@ -14206,7 +14377,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="64" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C52" s="88" t="n">
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C12,0),0)</f>
@@ -14250,12 +14421,12 @@
       </c>
       <c r="M52" s="88"/>
       <c r="N52" s="68" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="69" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C53" s="70" t="str">
         <f aca="false">C16&amp;" kW = "&amp;TEXT(C16*1000/220,"0")&amp;" A"</f>
@@ -14299,12 +14470,12 @@
       </c>
       <c r="M53" s="70"/>
       <c r="N53" s="67" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="7" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -14321,7 +14492,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="69" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C56" s="80" t="n">
         <f aca="false">CONTA!$C$54</f>
@@ -14365,12 +14536,12 @@
       </c>
       <c r="M56" s="80"/>
       <c r="N56" s="68" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="69" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C57" s="80" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
@@ -14414,12 +14585,12 @@
       </c>
       <c r="M57" s="80"/>
       <c r="N57" s="68" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="64" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C58" s="89" t="n">
         <f aca="false">ECONOMIA!C19</f>
@@ -14463,12 +14634,12 @@
       </c>
       <c r="M58" s="89"/>
       <c r="N58" s="67" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="69" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C59" s="80" t="n">
         <f aca="false">ECONOMIA!C26</f>
@@ -14515,7 +14686,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="64" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C60" s="89" t="n">
         <f aca="false">C59/12</f>
@@ -14562,7 +14733,7 @@
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="64" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C61" s="90" t="n">
         <f aca="false">IFERROR(C34/C59,0)</f>
@@ -14606,12 +14777,12 @@
       </c>
       <c r="M61" s="90"/>
       <c r="N61" s="68" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="69" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C62" s="91" t="n">
         <f aca="false">PROJECAO!E10</f>
@@ -14658,7 +14829,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="69" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C63" s="91" t="n">
         <f aca="false">PROJECAO!E15</f>
@@ -14705,7 +14876,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="69" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C64" s="91" t="n">
         <f aca="false">PROJECAO!E25</f>
@@ -14752,7 +14923,7 @@
     </row>
     <row r="65" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="64" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C65" s="92" t="n">
         <f aca="false">C64-C34</f>
@@ -14796,12 +14967,12 @@
       </c>
       <c r="M65" s="92"/>
       <c r="N65" s="68" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="69" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C66" s="85" t="n">
         <f aca="false">IFERROR(C65/C34,0)</f>
@@ -14848,7 +15019,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="7" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -14865,7 +15036,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="69" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C69" s="76" t="n">
         <f aca="false">C16*1.35</f>
@@ -14912,7 +15083,7 @@
     </row>
     <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="64" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C70" s="87" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((C69-C14)*1000/C12,0))</f>
@@ -14956,180 +15127,219 @@
       </c>
       <c r="M70" s="87"/>
       <c r="N70" s="67" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="69" t="s">
-        <v>661</v>
-      </c>
-      <c r="C71" s="73" t="n">
+        <v>664</v>
+      </c>
+      <c r="C71" s="70" t="s">
+        <v>665</v>
+      </c>
+      <c r="D71" s="70" t="s">
+        <v>665</v>
+      </c>
+      <c r="E71" s="70" t="s">
+        <v>666</v>
+      </c>
+      <c r="F71" s="70" t="s">
+        <v>666</v>
+      </c>
+      <c r="G71" s="70" t="s">
+        <v>666</v>
+      </c>
+      <c r="H71" s="70" t="s">
+        <v>667</v>
+      </c>
+      <c r="I71" s="70" t="s">
+        <v>668</v>
+      </c>
+      <c r="J71" s="70" t="s">
+        <v>669</v>
+      </c>
+      <c r="K71" s="70" t="s">
+        <v>670</v>
+      </c>
+      <c r="L71" s="70" t="s">
+        <v>671</v>
+      </c>
+      <c r="M71" s="70"/>
+      <c r="N71" s="68" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="69" t="s">
+        <v>673</v>
+      </c>
+      <c r="C72" s="73" t="n">
         <f aca="false">C70*C12/1000*GERACAO!$I$17</f>
         <v>777.525431925</v>
       </c>
-      <c r="D71" s="73" t="n">
+      <c r="D72" s="73" t="n">
         <f aca="false">D70*D12/1000*GERACAO!$I$17</f>
         <v>764.882741975</v>
       </c>
-      <c r="E71" s="73" t="n">
+      <c r="E72" s="73" t="n">
         <f aca="false">E70*E12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="F71" s="73" t="n">
+      <c r="F72" s="73" t="n">
         <f aca="false">F70*F12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="G71" s="73" t="n">
+      <c r="G72" s="73" t="n">
         <f aca="false">G70*G12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="H71" s="73" t="n">
+      <c r="H72" s="73" t="n">
         <f aca="false">H70*H12/1000*GERACAO!$I$17</f>
         <v>0</v>
       </c>
-      <c r="I71" s="73" t="n">
+      <c r="I72" s="73" t="n">
         <f aca="false">I70*I12/1000*GERACAO!$I$17</f>
         <v>6574.198774</v>
       </c>
-      <c r="J71" s="73" t="n">
+      <c r="J72" s="73" t="n">
         <f aca="false">J70*J12/1000*GERACAO!$I$17</f>
         <v>745.91870705</v>
       </c>
-      <c r="K71" s="73" t="n">
+      <c r="K72" s="73" t="n">
         <f aca="false">K70*K12/1000*GERACAO!$I$17</f>
         <v>3919.2338845</v>
       </c>
-      <c r="L71" s="73" t="n">
+      <c r="L72" s="73" t="n">
         <f aca="false">L70*L12/1000*GERACAO!$I$17</f>
         <v>1555.05086385</v>
       </c>
-      <c r="M71" s="73"/>
-      <c r="N71" s="68"/>
-    </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="64" t="s">
-        <v>662</v>
-      </c>
-      <c r="C72" s="65" t="str">
+      <c r="M72" s="73"/>
+      <c r="N72" s="68"/>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="64" t="s">
+        <v>674</v>
+      </c>
+      <c r="C73" s="65" t="str">
         <f aca="false">IF(C18&gt;1.35,"JA SOBRECARREGADO",IF(C18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="D72" s="65" t="str">
+      <c r="D73" s="65" t="str">
         <f aca="false">IF(D18&gt;1.35,"JA SOBRECARREGADO",IF(D18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="E72" s="65" t="str">
+      <c r="E73" s="65" t="str">
         <f aca="false">IF(E18&gt;1.35,"JA SOBRECARREGADO",IF(E18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="F72" s="65" t="str">
+      <c r="F73" s="65" t="str">
         <f aca="false">IF(F18&gt;1.35,"JA SOBRECARREGADO",IF(F18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="G72" s="65" t="str">
+      <c r="G73" s="65" t="str">
         <f aca="false">IF(G18&gt;1.35,"JA SOBRECARREGADO",IF(G18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="H72" s="65" t="str">
+      <c r="H73" s="65" t="str">
         <f aca="false">IF(H18&gt;1.35,"JA SOBRECARREGADO",IF(H18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>JA SOBRECARREGADO</v>
       </c>
-      <c r="I72" s="65" t="str">
+      <c r="I73" s="65" t="str">
         <f aca="false">IF(I18&gt;1.35,"JA SOBRECARREGADO",IF(I18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="J72" s="65" t="str">
+      <c r="J73" s="65" t="str">
         <f aca="false">IF(J18&gt;1.35,"JA SOBRECARREGADO",IF(J18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K72" s="65" t="str">
+      <c r="K73" s="65" t="str">
         <f aca="false">IF(K18&gt;1.35,"JA SOBRECARREGADO",IF(K18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="L72" s="65" t="str">
+      <c r="L73" s="65" t="str">
         <f aca="false">IF(L18&gt;1.35,"JA SOBRECARREGADO",IF(L18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
         <v>SUBAPROVEITADO</v>
       </c>
-      <c r="M72" s="65"/>
-      <c r="N72" s="68" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
+      <c r="M73" s="65"/>
+      <c r="N73" s="68" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="21" t="s">
-        <v>665</v>
-      </c>
-      <c r="C75" s="35" t="n">
+      <c r="B75" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+      <c r="N75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="C76" s="35" t="n">
         <f aca="false">F29-E29</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="C76" s="29" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C77" s="29" t="n">
         <f aca="false">IFERROR(F61-E61,0)</f>
         <v>0.163797233414615</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="C77" s="93" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="C78" s="93" t="n">
         <f aca="false">F65-E65</f>
         <v>-1000</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="5" t="s">
-        <v>668</v>
-      </c>
-    </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="4" t="s">
-        <v>669</v>
+      <c r="B80" s="5" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="4"/>
+      <c r="B83" s="4" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="5" t="s">
-        <v>672</v>
-      </c>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="4" t="s">
-        <v>673</v>
+      <c r="B85" s="5" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="4" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -15159,12 +15369,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15172,33 +15382,33 @@
         <v>451</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="F5" s="94" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15206,278 +15416,278 @@
         <v>532</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="F8" s="94" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="F10" s="94" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="F13" s="95" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F14" s="94" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="D17" s="96" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="F20" s="94" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -15491,7 +15701,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -15505,7 +15715,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -15519,7 +15729,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -15533,7 +15743,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="C28" s="47" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -15550,7 +15760,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="C30" s="44" t="n">
         <f aca="false">COMPARATIVO!C14</f>
@@ -15567,7 +15777,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="C31" s="97" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
@@ -15584,44 +15794,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="C34" s="98" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -15630,7 +15840,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">COMPARATIVO!C39-COMPARATIVO!D39</f>
@@ -15639,7 +15849,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
@@ -15648,14 +15858,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="C41" s="99" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
         <v>5.94181274517766</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -15685,58 +15895,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -15780,12 +15990,12 @@
       </c>
       <c r="M5" s="100"/>
       <c r="N5" s="68" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COMPARATIVO!C39</f>
@@ -15829,12 +16039,12 @@
       </c>
       <c r="M6" s="100"/>
       <c r="N6" s="68" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="C7" s="101" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -15878,12 +16088,12 @@
       </c>
       <c r="M7" s="100"/>
       <c r="N7" s="68" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="C8" s="102" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -15927,12 +16137,12 @@
       </c>
       <c r="M8" s="100"/>
       <c r="N8" s="68" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -15976,12 +16186,12 @@
       </c>
       <c r="M9" s="100"/>
       <c r="N9" s="68" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">C6-C9</f>
@@ -16025,12 +16235,12 @@
       </c>
       <c r="M10" s="100"/>
       <c r="N10" s="68" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -16074,12 +16284,12 @@
       </c>
       <c r="M11" s="100"/>
       <c r="N11" s="68" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -16123,12 +16333,12 @@
       </c>
       <c r="M12" s="100"/>
       <c r="N12" s="68" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">C10-C12</f>
@@ -16172,12 +16382,12 @@
       </c>
       <c r="M13" s="100"/>
       <c r="N13" s="68" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -16221,12 +16431,12 @@
       </c>
       <c r="M14" s="100"/>
       <c r="N14" s="68" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C15" s="101" t="n">
         <f aca="false">C14*C7</f>
@@ -16273,7 +16483,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="C16" s="101" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -16317,12 +16527,12 @@
       </c>
       <c r="M16" s="100"/>
       <c r="N16" s="68" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C17" s="101" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -16366,12 +16576,12 @@
       </c>
       <c r="M17" s="100"/>
       <c r="N17" s="68" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="C18" s="47" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -16415,12 +16625,12 @@
       </c>
       <c r="M18" s="100"/>
       <c r="N18" s="68" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">C18/12</f>
@@ -16464,12 +16674,12 @@
       </c>
       <c r="M19" s="100"/>
       <c r="N19" s="68" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="C20" s="37" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -16516,7 +16726,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C21" s="101" t="n">
         <f aca="false">C8-C18</f>
@@ -16563,7 +16773,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="C22" s="101" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -16607,12 +16817,12 @@
       </c>
       <c r="M22" s="100"/>
       <c r="N22" s="68" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="C23" s="101" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -16656,12 +16866,12 @@
       </c>
       <c r="M23" s="100"/>
       <c r="N23" s="68" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="C24" s="101" t="n">
         <f aca="false">0</f>
@@ -16705,12 +16915,12 @@
       </c>
       <c r="M24" s="100"/>
       <c r="N24" s="68" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="C25" s="101" t="n">
         <f aca="false">C22+C23</f>
@@ -16757,7 +16967,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="C26" s="103" t="n">
         <f aca="false">C21-C25</f>
@@ -16801,12 +17011,12 @@
       </c>
       <c r="M26" s="100"/>
       <c r="N26" s="68" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -16823,122 +17033,122 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4576</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>7042.97674418605</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
         <v>2466.97674418605</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.539112050739958</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4927.56672</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7447.50945488372</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2519.94273488372</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>529.696418232558</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>1990.24631665116</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="1271">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -1968,8 +1968,8 @@
   </si>
   <si>
     <t xml:space="preserve">J) AD BioSolar
-JA Solar 615W x8
-Huawei SUN2000-5KTL-L1</t>
+JA Solar 615W x10
+Huawei SUN2000-6KTL-L1</t>
   </si>
   <si>
     <t xml:space="preserve">SIMULACAO G12
@@ -2037,7 +2037,7 @@
     <t xml:space="preserve">nao informado (indicacao do Renato)</t>
   </si>
   <si>
-    <t xml:space="preserve">Adriano Melo</t>
+    <t xml:space="preserve">Adriano Melo (proposta) / Carlos (negociacao)</t>
   </si>
   <si>
     <t xml:space="preserve">Bruno</t>
@@ -2064,7 +2064,7 @@
     <t xml:space="preserve">(11) 99705-1311 (Renato)</t>
   </si>
   <si>
-    <t xml:space="preserve">(11) 97350-3103 / (11) 91408-8892</t>
+    <t xml:space="preserve">(11) 97350-3103 / Carlos (11) 91408-8892</t>
   </si>
   <si>
     <t xml:space="preserve">(11) 96861-7830</t>
@@ -2121,7 +2121,7 @@
     <t xml:space="preserve">Proposta 40438 de 11/08/2026 (val. 20/08)</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposta #01225 de 11/08/2026 (val. 26/08)</t>
+    <t xml:space="preserve">Proposta #01237 de 12/08/2026 (val. 27/08) - substitui a #01225</t>
   </si>
   <si>
     <t xml:space="preserve">SIMULACAO: opcao G escalada para 12 modulos</t>
@@ -2229,7 +2229,7 @@
     <t xml:space="preserve">AUXSOL 7,5 kW mono 220V 2 MPPT (100% over)</t>
   </si>
   <si>
-    <t xml:space="preserve">HUAWEI SUN2000-5KTL-L1 5.000 W (modelo EXATO informado)</t>
+    <t xml:space="preserve">HUAWEI SUN2000-6KTL-L1 6.000 W (modelo EXATO informado)</t>
   </si>
   <si>
     <t xml:space="preserve">4x DEYE SUN-S225G4-EU-Q0 = 9,0 kW AC (12 dos 16 canais)</t>
@@ -2418,7 +2418,7 @@
     <t xml:space="preserve">a vista, cartao 12x/21x COM juros ou financiamento 36x ate 120x</t>
   </si>
   <si>
-    <t xml:space="preserve">a vista ou financiamento em ate 60x</t>
+    <t xml:space="preserve">R$ 16.200 NEGOCIADO (o PDF traz R$ 21.289 - EXIGIR O DESCONTO POR ESCRITO)</t>
   </si>
   <si>
     <t xml:space="preserve">pedir preco e parcelamento para esta configuracao</t>
@@ -2433,7 +2433,7 @@
     <t xml:space="preserve">Preco BASE informado (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">A, B e E: valor do KIT/material. As demais: projeto completo, ja com instalacao - por isso as linhas de homologacao e instalacao ficam zeradas nelas.</t>
+    <t xml:space="preserve">A, B e E: valor do KIT/material. As demais: projeto completo, ja com instalacao. ALERTA na coluna J: o PDF da AD BioSolar traz R$ 21.289,00 e o valor de R$ 16.200,00 foi negociado verbalmente - um desconto de R$ 5.089 (24%) que PRECISA constar em proposta assinada, senao pode evaporar na hora de fechar.</t>
   </si>
   <si>
     <t xml:space="preserve">Acrescimo regional a confirmar (R$)</t>
@@ -2502,7 +2502,7 @@
     <t xml:space="preserve">Geracao PROMETIDA pelo vendedor (kWh/ano)</t>
   </si>
   <si>
-    <t xml:space="preserve">A: 10.554. C, D e G: 700 kWh/mes x 12. E: 6.151. F: 6.367,50. H: 7.329,96. I: 9.279,13. J: 6.385,01. B: nao informada.</t>
+    <t xml:space="preserve">A: 10.554. C, D e G: 700 kWh/mes x 12. E: 6.151. F: 6.367,50. H: 7.329,96. I: 9.279,13. J: 7.981,26. B: nao informada.</t>
   </si>
   <si>
     <t xml:space="preserve">DESVIO DA PROMESSA</t>
@@ -3024,7 +3024,7 @@
     <t xml:space="preserve">I) Sun Coast v2 TCL 620W x11 AUXSOL 7,5 kW</t>
   </si>
   <si>
-    <t xml:space="preserve">J) AD BioSolar JA Solar 615W x8 Huawei SUN2000-5KTL-L1</t>
+    <t xml:space="preserve">J) AD BioSolar JA Solar 615W x10 Huawei SUN2000-6KTL-L1</t>
   </si>
   <si>
     <t xml:space="preserve">SIMULACAO G12 MICRO 12x650W 4x Deye 2,25 kW</t>
@@ -3492,10 +3492,13 @@
     <t xml:space="preserve">ESSA MESMA VERIFICACAO VALE PARA AS OPCOES A, B, C, D e I, que usam modulos de 605 a 620 W. Exigir de cada fornecedor o PROJETO DE STRING por escrito: quantos modulos em serie por MPPT, tensao minima e maxima nas temperaturas extremas, e a corrente por MPPT comparada ao limite do inversor. Fornecedor que nao souber responder isso nao fez projeto - fez lista de compras.</t>
   </si>
   <si>
-    <t xml:space="preserve">AD BIOSOLAR: 4,92 kWp COBRE SO 77% DO CENARIO 3, porque dimensionaram com 460 kWh/mes. Pedir a versao com 11 ou 12 modulos. O SUN2000-5KTL-L1 aceita ate cerca de 6,75 kWp (DC/AC 1,35), ou seja, cabem mais 2 a 3 modulos sem trocar inversor - e o preco marginal do modulo e baixo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD BIOSOLAR E A MAIS CARA POR Wp entre todas as turnkey (R$ 4,05/Wp com o padrao). Equipamento e otimo, mas o sistema e pequeno. Pedir preco para 11 modulos antes de comparar.</t>
+    <t xml:space="preserve">AD BIOSOLAR CORRIGIU A PROPOSTA (#01237 de 12/08): subiu de 8 para 10 modulos e de 4,92 para 6,15 kWp, trocou o inversor do SUN2000-5KTL-L1 para o 6KTL-L1 de 6 kW, e passou a dimensionar com 650 kWh/mes em vez de 460. Com o valor negociado de R$ 16.200 ela sai a R$ 2,63/Wp - deixou de ser a mais cara e passou a ser uma das mais baratas, com o melhor equipamento do conjunto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O DESCONTO DE R$ 5.089 PRECISA ESTAR NO PAPEL. O PDF #01237 traz R$ 21.289,00; o valor de R$ 16.200,00 veio da negociacao. Sao 24% de desconto. Exigir proposta reemitida com o valor final, ou o desconto pode nao existir na assinatura.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFICACAO OBRIGATORIA NA AD BIOSOLAR: 10 modulos JA Solar de 615 W em um SUN2000-6KTL-L1 de 2 MPPTs dao 5 modulos por string. Confirmar na ficha tecnica do inversor a corrente maxima de entrada por MPPT e comparar com o Impp do modulo (~16 A). Se a do inversor for menor, perde-se geracao nas melhores horas. Pedir tambem a tensao da string nas temperaturas extremas.</t>
   </si>
   <si>
     <t xml:space="preserve">NUMEROS DE MARKETING DA AD BIOSOLAR: 'Economia total em 25 anos R$ 419.713,53', 'ROI 24,06 vezes' e 'TIR 35,81%' usam reajuste de energia de 10% ao ano composto por 25 anos. Ignore. Alem disso a 'conta COM sistema de R$ 75,31/mes' vale para 460 kWh/mes SEM o carro - com o BYD o meu modelo da cerca de R$ 259/mes nessa potencia.</t>
@@ -5530,15 +5533,15 @@
       </c>
       <c r="AE6" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
-        <v>4968.85240496758</v>
+        <v>5988.72947711613</v>
       </c>
       <c r="AF6" s="116" t="n">
         <f aca="false">AE6</f>
-        <v>4968.85240496758</v>
+        <v>5988.72947711613</v>
       </c>
       <c r="AG6" s="116" t="n">
         <f aca="false">AF6-COMPARATIVO!L$34</f>
-        <v>-14973.1475950324</v>
+        <v>-12711.2705228839</v>
       </c>
       <c r="AH6" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
@@ -5683,15 +5686,15 @@
       </c>
       <c r="AE7" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
-        <v>5292.74704898539</v>
+        <v>6379.10480808194</v>
       </c>
       <c r="AF7" s="116" t="n">
         <f aca="false">AF6+AE7</f>
-        <v>10261.599453953</v>
+        <v>12367.8342851981</v>
       </c>
       <c r="AG7" s="116" t="n">
         <f aca="false">AF7-COMPARATIVO!L$34</f>
-        <v>-9680.40054604704</v>
+        <v>-6332.16571480193</v>
       </c>
       <c r="AH7" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
@@ -5836,15 +5839,15 @@
       </c>
       <c r="AE8" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
-        <v>5637.7547653735</v>
+        <v>6794.92675499676</v>
       </c>
       <c r="AF8" s="116" t="n">
         <f aca="false">AF7+AE8</f>
-        <v>15899.3542193265</v>
+        <v>19162.7610401948</v>
       </c>
       <c r="AG8" s="116" t="n">
         <f aca="false">AF8-COMPARATIVO!L$34</f>
-        <v>-4042.64578067354</v>
+        <v>462.761040194833</v>
       </c>
       <c r="AH8" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
@@ -5989,15 +5992,15 @@
       </c>
       <c r="AE9" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
-        <v>6005.25180975437</v>
+        <v>7237.85405552123</v>
       </c>
       <c r="AF9" s="116" t="n">
         <f aca="false">AF8+AE9</f>
-        <v>21904.6060290808</v>
+        <v>26400.6150957161</v>
       </c>
       <c r="AG9" s="116" t="n">
         <f aca="false">AF9-COMPARATIVO!L$34</f>
-        <v>1962.60602908083</v>
+        <v>7700.61509571606</v>
       </c>
       <c r="AH9" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
@@ -6142,15 +6145,15 @@
       </c>
       <c r="AE10" s="119" t="n">
         <f aca="false">ECONOMIA!L$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
-        <v>6396.70414897321</v>
+        <v>7709.65357213038</v>
       </c>
       <c r="AF10" s="119" t="n">
         <f aca="false">AF9+AE10</f>
-        <v>28301.310178054</v>
+        <v>34110.2686678464</v>
       </c>
       <c r="AG10" s="119" t="n">
         <f aca="false">AF10-COMPARATIVO!L$34</f>
-        <v>8359.31017805405</v>
+        <v>15410.2686678464</v>
       </c>
       <c r="AH10" s="119" t="n">
         <f aca="false">ECONOMIA!M$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
@@ -6295,15 +6298,15 @@
       </c>
       <c r="AE11" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
-        <v>6813.67330892403</v>
+        <v>8212.2073402297</v>
       </c>
       <c r="AF11" s="116" t="n">
         <f aca="false">AF10+AE11</f>
-        <v>35114.9834869781</v>
+        <v>42322.4760080761</v>
       </c>
       <c r="AG11" s="116" t="n">
         <f aca="false">AF11-COMPARATIVO!L$34</f>
-        <v>15172.9834869781</v>
+        <v>23622.4760080761</v>
       </c>
       <c r="AH11" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
@@ -6448,15 +6451,15 @@
       </c>
       <c r="AE12" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
-        <v>7257.82260356625</v>
+        <v>8747.52007570258</v>
       </c>
       <c r="AF12" s="116" t="n">
         <f aca="false">AF11+AE12</f>
-        <v>42372.8060905443</v>
+        <v>51069.9960837787</v>
       </c>
       <c r="AG12" s="116" t="n">
         <f aca="false">AF12-COMPARATIVO!L$34</f>
-        <v>22430.8060905443</v>
+        <v>32369.9960837787</v>
       </c>
       <c r="AH12" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
@@ -6601,15 +6604,15 @@
       </c>
       <c r="AE13" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
-        <v>7730.92376997971</v>
+        <v>9317.72717183725</v>
       </c>
       <c r="AF13" s="116" t="n">
         <f aca="false">AF12+AE13</f>
-        <v>50103.729860524</v>
+        <v>60387.723255616</v>
       </c>
       <c r="AG13" s="116" t="n">
         <f aca="false">AF13-COMPARATIVO!L$34</f>
-        <v>30161.729860524</v>
+        <v>41687.723255616</v>
       </c>
       <c r="AH13" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
@@ -6754,15 +6757,15 @@
       </c>
       <c r="AE14" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
-        <v>8234.86403592584</v>
+        <v>9925.10321753346</v>
       </c>
       <c r="AF14" s="116" t="n">
         <f aca="false">AF13+AE14</f>
-        <v>58338.5938964499</v>
+        <v>70312.8264731494</v>
       </c>
       <c r="AG14" s="116" t="n">
         <f aca="false">AF14-COMPARATIVO!L$34</f>
-        <v>38396.5938964499</v>
+        <v>51612.8264731494</v>
       </c>
       <c r="AH14" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
@@ -6907,15 +6910,15 @@
       </c>
       <c r="AE15" s="119" t="n">
         <f aca="false">ECONOMIA!L$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
-        <v>8771.65364810767</v>
+        <v>10572.0710707684</v>
       </c>
       <c r="AF15" s="119" t="n">
         <f aca="false">AF14+AE15</f>
-        <v>67110.2475445575</v>
+        <v>80884.8975439178</v>
       </c>
       <c r="AG15" s="119" t="n">
         <f aca="false">AF15-COMPARATIVO!L$34</f>
-        <v>47168.2475445575</v>
+        <v>62184.8975439178</v>
       </c>
       <c r="AH15" s="119" t="n">
         <f aca="false">ECONOMIA!M$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
@@ -7060,15 +7063,15 @@
       </c>
       <c r="AE16" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
-        <v>9343.43389115957</v>
+        <v>11261.2115235164</v>
       </c>
       <c r="AF16" s="116" t="n">
         <f aca="false">AF15+AE16</f>
-        <v>76453.6814357171</v>
+        <v>92146.1090674342</v>
       </c>
       <c r="AG16" s="116" t="n">
         <f aca="false">AF16-COMPARATIVO!L$34</f>
-        <v>56511.6814357171</v>
+        <v>73446.1090674342</v>
       </c>
       <c r="AH16" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
@@ -7213,15 +7216,15 @@
       </c>
       <c r="AE17" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
-        <v>9952.48562935481</v>
+        <v>11995.2735966768</v>
       </c>
       <c r="AF17" s="116" t="n">
         <f aca="false">AF16+AE17</f>
-        <v>86406.1670650719</v>
+        <v>104141.382664111</v>
       </c>
       <c r="AG17" s="116" t="n">
         <f aca="false">AF17-COMPARATIVO!L$34</f>
-        <v>66464.1670650719</v>
+        <v>85441.3826641111</v>
       </c>
       <c r="AH17" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
@@ -7366,15 +7369,15 @@
       </c>
       <c r="AE18" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
-        <v>10601.2384051043</v>
+        <v>12777.1855060762</v>
       </c>
       <c r="AF18" s="116" t="n">
         <f aca="false">AF17+AE18</f>
-        <v>97007.4054701762</v>
+        <v>116918.568170187</v>
       </c>
       <c r="AG18" s="116" t="n">
         <f aca="false">AF18-COMPARATIVO!L$34</f>
-        <v>77065.4054701762</v>
+        <v>98218.5681701873</v>
       </c>
       <c r="AH18" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
@@ -7519,15 +7522,15 @@
       </c>
       <c r="AE19" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
-        <v>11292.280130541</v>
+        <v>13610.0663432898</v>
       </c>
       <c r="AF19" s="116" t="n">
         <f aca="false">AF18+AE19</f>
-        <v>108299.685600717</v>
+        <v>130528.634513477</v>
       </c>
       <c r="AG19" s="116" t="n">
         <f aca="false">AF19-COMPARATIVO!L$34</f>
-        <v>88357.6856007173</v>
+        <v>111828.634513477</v>
       </c>
       <c r="AH19" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
@@ -7672,15 +7675,15 @@
       </c>
       <c r="AE20" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
-        <v>12028.3674108503</v>
+        <v>14497.2385178771</v>
       </c>
       <c r="AF20" s="116" t="n">
         <f aca="false">AF19+AE20</f>
-        <v>120328.053011568</v>
+        <v>145025.873031354</v>
       </c>
       <c r="AG20" s="116" t="n">
         <f aca="false">AF20-COMPARATIVO!L$34</f>
-        <v>100386.053011568</v>
+        <v>126325.873031354</v>
       </c>
       <c r="AH20" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
@@ -7825,15 +7828,15 @@
       </c>
       <c r="AE21" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
-        <v>12812.4365405266</v>
+        <v>15442.241010665</v>
       </c>
       <c r="AF21" s="116" t="n">
         <f aca="false">AF20+AE21</f>
-        <v>133140.489552094</v>
+        <v>160468.114042019</v>
       </c>
       <c r="AG21" s="116" t="n">
         <f aca="false">AF21-COMPARATIVO!L$34</f>
-        <v>113198.489552094</v>
+        <v>141768.114042019</v>
       </c>
       <c r="AH21" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
@@ -7978,15 +7981,15 @@
       </c>
       <c r="AE22" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
-        <v>13647.6152164209</v>
+        <v>16448.8434909452</v>
       </c>
       <c r="AF22" s="116" t="n">
         <f aca="false">AF21+AE22</f>
-        <v>146788.104768515</v>
+        <v>176916.957532964</v>
       </c>
       <c r="AG22" s="116" t="n">
         <f aca="false">AF22-COMPARATIVO!L$34</f>
-        <v>126846.104768515</v>
+        <v>158216.957532964</v>
       </c>
       <c r="AH22" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
@@ -8131,15 +8134,15 @@
       </c>
       <c r="AE23" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
-        <v>14537.2350143032</v>
+        <v>17521.0613539024</v>
       </c>
       <c r="AF23" s="116" t="n">
         <f aca="false">AF22+AE23</f>
-        <v>161325.339782818</v>
+        <v>194438.018886867</v>
       </c>
       <c r="AG23" s="116" t="n">
         <f aca="false">AF23-COMPARATIVO!L$34</f>
-        <v>141383.339782818</v>
+        <v>175738.018886867</v>
       </c>
       <c r="AH23" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
@@ -8284,15 +8287,15 @@
       </c>
       <c r="AE24" s="116" t="n">
         <f aca="false">ECONOMIA!L$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
-        <v>15484.8446787106</v>
+        <v>18663.1717382566</v>
       </c>
       <c r="AF24" s="116" t="n">
         <f aca="false">AF23+AE24</f>
-        <v>176810.184461529</v>
+        <v>213101.190625123</v>
       </c>
       <c r="AG24" s="116" t="n">
         <f aca="false">AF24-COMPARATIVO!L$34</f>
-        <v>156868.184461529</v>
+        <v>194401.190625123</v>
       </c>
       <c r="AH24" s="116" t="n">
         <f aca="false">ECONOMIA!M$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
@@ -8437,15 +8440,15 @@
       </c>
       <c r="AE25" s="119" t="n">
         <f aca="false">ECONOMIA!L$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
-        <v>16494.2242790924</v>
+        <v>19879.7305880148</v>
       </c>
       <c r="AF25" s="119" t="n">
         <f aca="false">AF24+AE25</f>
-        <v>193304.408740621</v>
+        <v>232980.921213138</v>
       </c>
       <c r="AG25" s="119" t="n">
         <f aca="false">AF25-COMPARATIVO!L$34</f>
-        <v>173362.408740621</v>
+        <v>214280.921213138</v>
       </c>
       <c r="AH25" s="119" t="n">
         <f aca="false">ECONOMIA!M$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
@@ -9048,7 +9051,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9182,11 +9185,11 @@
       </c>
       <c r="E13" s="121"/>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="122" t="s">
         <v>1130</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -9230,19 +9233,19 @@
       </c>
       <c r="E17" s="121"/>
     </row>
-    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="n">
+    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C18" s="120" t="s">
         <v>1134</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>1122</v>
       </c>
-      <c r="E19" s="121"/>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="121"/>
+    </row>
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="n">
         <v>13</v>
       </c>
@@ -9266,7 +9269,7 @@
       </c>
       <c r="E21" s="121"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="n">
         <v>15</v>
       </c>
@@ -9290,7 +9293,7 @@
       </c>
       <c r="E23" s="121"/>
     </row>
-    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="n">
         <v>17</v>
       </c>
@@ -9314,27 +9317,27 @@
       </c>
       <c r="E25" s="121"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8"/>
-      <c r="C26" s="7" t="s">
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="120" t="s">
         <v>1141</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C27" s="122" t="s">
+      <c r="D26" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E26" s="121"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="8"/>
+      <c r="C27" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E27" s="121"/>
-    </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="n">
         <v>20</v>
       </c>
@@ -9346,7 +9349,7 @@
       </c>
       <c r="E28" s="121"/>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="n">
         <v>21</v>
       </c>
@@ -9358,11 +9361,11 @@
       </c>
       <c r="E29" s="121"/>
     </row>
-    <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="120" t="s">
+      <c r="C30" s="122" t="s">
         <v>1145</v>
       </c>
       <c r="D30" s="9" t="s">
@@ -9370,7 +9373,7 @@
       </c>
       <c r="E30" s="121"/>
     </row>
-    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="n">
         <v>23</v>
       </c>
@@ -9382,11 +9385,11 @@
       </c>
       <c r="E31" s="121"/>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="120" t="s">
         <v>1147</v>
       </c>
       <c r="D32" s="9" t="s">
@@ -9394,7 +9397,7 @@
       </c>
       <c r="E32" s="121"/>
     </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="n">
         <v>25</v>
       </c>
@@ -9418,11 +9421,11 @@
       </c>
       <c r="E34" s="121"/>
     </row>
-    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C35" s="120" t="s">
+      <c r="C35" s="122" t="s">
         <v>1150</v>
       </c>
       <c r="D35" s="9" t="s">
@@ -9430,7 +9433,7 @@
       </c>
       <c r="E35" s="121"/>
     </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="n">
         <v>28</v>
       </c>
@@ -9442,7 +9445,7 @@
       </c>
       <c r="E36" s="121"/>
     </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="n">
         <v>29</v>
       </c>
@@ -9454,7 +9457,7 @@
       </c>
       <c r="E37" s="121"/>
     </row>
-    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="n">
         <v>30</v>
       </c>
@@ -9466,7 +9469,7 @@
       </c>
       <c r="E38" s="121"/>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="n">
         <v>31</v>
       </c>
@@ -9490,11 +9493,11 @@
       </c>
       <c r="E40" s="121"/>
     </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="C41" s="122" t="s">
+      <c r="C41" s="120" t="s">
         <v>1156</v>
       </c>
       <c r="D41" s="9" t="s">
@@ -9502,25 +9505,25 @@
       </c>
       <c r="E41" s="121"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8"/>
-      <c r="C43" s="7" t="s">
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C42" s="122" t="s">
         <v>1157</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-    </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="C44" s="120" t="s">
+      <c r="D42" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E42" s="121"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="8"/>
+      <c r="C44" s="7" t="s">
         <v>1158</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E44" s="121"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="n">
@@ -9558,11 +9561,11 @@
       </c>
       <c r="E47" s="121"/>
     </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="C48" s="122" t="s">
+      <c r="C48" s="120" t="s">
         <v>1162</v>
       </c>
       <c r="D48" s="9" t="s">
@@ -9570,31 +9573,31 @@
       </c>
       <c r="E48" s="121"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8"/>
-      <c r="C50" s="7" t="s">
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C49" s="122" t="s">
         <v>1163</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-    </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="C51" s="122" t="s">
+      <c r="D49" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E49" s="121"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="8"/>
+      <c r="C51" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E51" s="121"/>
-    </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C52" s="120" t="s">
+      <c r="C52" s="122" t="s">
         <v>1165</v>
       </c>
       <c r="D52" s="9" t="s">
@@ -9626,27 +9629,27 @@
       </c>
       <c r="E54" s="121"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="8"/>
-      <c r="C56" s="7" t="s">
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C55" s="120" t="s">
         <v>1168</v>
       </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-    </row>
-    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="C57" s="120" t="s">
+      <c r="D55" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E55" s="121"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="8"/>
+      <c r="C57" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E57" s="121"/>
-    </row>
-    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="n">
         <v>44</v>
       </c>
@@ -9682,7 +9685,7 @@
       </c>
       <c r="E60" s="121"/>
     </row>
-    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="n">
         <v>47</v>
       </c>
@@ -9718,7 +9721,7 @@
       </c>
       <c r="E63" s="121"/>
     </row>
-    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="n">
         <v>50</v>
       </c>
@@ -9778,7 +9781,7 @@
       </c>
       <c r="E68" s="121"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="n">
         <v>55</v>
       </c>
@@ -9790,25 +9793,25 @@
       </c>
       <c r="E69" s="121"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="8"/>
-      <c r="C71" s="7" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C70" s="120" t="s">
         <v>1182</v>
       </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+      <c r="D70" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E70" s="121"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C72" s="122" t="s">
+      <c r="B72" s="8"/>
+      <c r="C72" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="D72" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E72" s="121"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="n">
@@ -9906,25 +9909,25 @@
       </c>
       <c r="E80" s="121"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="8"/>
-      <c r="C82" s="7" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="C81" s="122" t="s">
         <v>1192</v>
       </c>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
+      <c r="D81" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E81" s="121"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="C83" s="122" t="s">
+      <c r="B83" s="8"/>
+      <c r="C83" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="D83" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E83" s="121"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="n">
@@ -9998,27 +10001,27 @@
       </c>
       <c r="E89" s="121"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="8"/>
-      <c r="C91" s="7" t="s">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="C90" s="122" t="s">
         <v>1200</v>
       </c>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+      <c r="D90" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E90" s="121"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="C92" s="122" t="s">
+      <c r="B92" s="8"/>
+      <c r="C92" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E92" s="121"/>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="n">
         <v>73</v>
       </c>
@@ -10030,7 +10033,7 @@
       </c>
       <c r="E93" s="121"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="n">
         <v>74</v>
       </c>
@@ -10065,6 +10068,18 @@
         <v>1122</v>
       </c>
       <c r="E96" s="121"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="C97" s="122" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E97" s="121"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10094,73 +10109,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="80" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="80" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="80" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="51" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="80" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10171,7 +10186,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="80" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10182,40 +10197,40 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="80" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="80" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="80" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="80" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,29 +10241,29 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="80" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="80" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="80" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10259,194 +10274,194 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="80" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="80" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="80" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="80" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="80" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="80" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="80" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="80" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="80" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="80" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="80" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="51" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="80" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="80" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="80" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="80" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="80" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="80" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="80" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10457,7 +10472,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="80" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -15406,7 +15421,7 @@
         <v>11</v>
       </c>
       <c r="L11" s="84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M11" s="84" t="n">
         <v>12</v>
@@ -15551,7 +15566,7 @@
       </c>
       <c r="L14" s="86" t="n">
         <f aca="false">L11*L12/1000</f>
-        <v>4.92</v>
+        <v>6.15</v>
       </c>
       <c r="M14" s="86" t="n">
         <f aca="false">M11*M12/1000</f>
@@ -15643,7 +15658,7 @@
         <v>7.5</v>
       </c>
       <c r="L16" s="87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" s="87" t="n">
         <v>9</v>
@@ -15743,7 +15758,7 @@
       </c>
       <c r="L18" s="89" t="n">
         <f aca="false">IFERROR(L14/L16,0)</f>
-        <v>0.984</v>
+        <v>1.025</v>
       </c>
       <c r="M18" s="89" t="n">
         <f aca="false">IFERROR(M14/M16,0)</f>
@@ -15886,7 +15901,7 @@
         <v>30.58</v>
       </c>
       <c r="L21" s="88" t="n">
-        <v>25.93</v>
+        <v>32.41</v>
       </c>
       <c r="M21" s="88" t="n">
         <f aca="false">M11*M12*0.00452</f>
@@ -16145,7 +16160,7 @@
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="81" t="s">
         <v>790</v>
       </c>
@@ -16177,7 +16192,7 @@
         <v>16890</v>
       </c>
       <c r="L29" s="91" t="n">
-        <v>17442</v>
+        <v>16200</v>
       </c>
       <c r="M29" s="92" t="n">
         <f aca="false">I29+2*ENTRADAS!$C$54</f>
@@ -16428,7 +16443,7 @@
       </c>
       <c r="L34" s="93" t="n">
         <f aca="false">SUM(L29:L33)</f>
-        <v>19942</v>
+        <v>18700</v>
       </c>
       <c r="M34" s="93" t="n">
         <f aca="false">SUM(M29:M33)</f>
@@ -16485,7 +16500,7 @@
       </c>
       <c r="L35" s="94" t="n">
         <f aca="false">IFERROR(L34/(L14*1000),0)</f>
-        <v>4.05325203252033</v>
+        <v>3.04065040650407</v>
       </c>
       <c r="M35" s="94" t="n">
         <f aca="false">IFERROR(M34/(M14*1000),0)</f>
@@ -16609,7 +16624,7 @@
       </c>
       <c r="L39" s="85" t="n">
         <f aca="false">L14*GERACAO!$I$17</f>
-        <v>6220.2034554</v>
+        <v>7775.25431925</v>
       </c>
       <c r="M39" s="85" t="n">
         <f aca="false">M14*GERACAO!$I$17</f>
@@ -16666,7 +16681,7 @@
       </c>
       <c r="L40" s="85" t="n">
         <f aca="false">L39/12</f>
-        <v>518.35028795</v>
+        <v>647.9378599375</v>
       </c>
       <c r="M40" s="85" t="n">
         <f aca="false">M39/12</f>
@@ -16721,7 +16736,7 @@
       </c>
       <c r="L41" s="85" t="n">
         <f aca="false">L39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
-        <v>5669.0461872</v>
+        <v>7086.307734</v>
       </c>
       <c r="M41" s="85" t="n">
         <f aca="false">M39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -16768,7 +16783,7 @@
         <v>9279.13</v>
       </c>
       <c r="L42" s="84" t="n">
-        <v>6385.01</v>
+        <v>7981.26</v>
       </c>
       <c r="M42" s="84" t="n">
         <v>0</v>
@@ -16823,7 +16838,7 @@
       </c>
       <c r="L43" s="96" t="n">
         <f aca="false">IFERROR(L39/L42-1,0)</f>
-        <v>-0.0258114779146783</v>
+        <v>-0.0258111727659541</v>
       </c>
       <c r="M43" s="96" t="n">
         <f aca="false">IFERROR(M39/M42-1,0)</f>
@@ -16880,7 +16895,7 @@
       </c>
       <c r="L44" s="85" t="n">
         <f aca="false">L14*GERACAO!$J$17</f>
-        <v>6992.4736908</v>
+        <v>8740.5921135</v>
       </c>
       <c r="M44" s="85" t="n">
         <f aca="false">M14*GERACAO!$J$17</f>
@@ -16956,7 +16971,7 @@
       </c>
       <c r="L47" s="97" t="n">
         <f aca="false">IFERROR(L39/(BYD!$F$33*12),0)</f>
-        <v>1.47330975403937</v>
+        <v>1.84163719254921</v>
       </c>
       <c r="M47" s="97" t="n">
         <f aca="false">IFERROR(M39/(BYD!$F$33*12),0)</f>
@@ -17013,7 +17028,7 @@
       </c>
       <c r="L48" s="97" t="n">
         <f aca="false">IFERROR(L39/(BYD!$F$34*12),0)</f>
-        <v>0.898623338225131</v>
+        <v>1.12327917278141</v>
       </c>
       <c r="M48" s="97" t="n">
         <f aca="false">IFERROR(M39/(BYD!$F$34*12),0)</f>
@@ -17068,7 +17083,7 @@
       </c>
       <c r="L49" s="98" t="n">
         <f aca="false">IFERROR(L39/(BYD!$F$35*12),0)</f>
-        <v>0.781411598456636</v>
+        <v>0.976764498070795</v>
       </c>
       <c r="M49" s="98" t="n">
         <f aca="false">IFERROR(M39/(BYD!$F$35*12),0)</f>
@@ -17125,7 +17140,7 @@
       </c>
       <c r="L50" s="85" t="n">
         <f aca="false">L39-BYD!$G$35</f>
-        <v>-1740.01042891591</v>
+        <v>-184.959565065905</v>
       </c>
       <c r="M50" s="85" t="n">
         <f aca="false">M39-BYD!$G$35</f>
@@ -17182,7 +17197,7 @@
       </c>
       <c r="L51" s="99" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-L39)/GERACAO!$I$17*1000/L12,0),0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M51" s="99" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-M39)/GERACAO!$I$17*1000/M12,0),0)</f>
@@ -17294,7 +17309,7 @@
       </c>
       <c r="L53" s="82" t="str">
         <f aca="false">L16&amp;" kW = "&amp;TEXT(L16*1000/220,"0")&amp;" A"</f>
-        <v>5 kW = 23 A</v>
+        <v>6 kW = 27 A</v>
       </c>
       <c r="M53" s="82" t="str">
         <f aca="false">M16&amp;" kW = "&amp;TEXT(M16*1000/220,"0")&amp;" A"</f>
@@ -17484,7 +17499,7 @@
       </c>
       <c r="L58" s="101" t="n">
         <f aca="false">ECONOMIA!L19</f>
-        <v>247.132272620383</v>
+        <v>162.142516608004</v>
       </c>
       <c r="M58" s="101" t="n">
         <f aca="false">ECONOMIA!M19</f>
@@ -17541,7 +17556,7 @@
       </c>
       <c r="L59" s="92" t="n">
         <f aca="false">ECONOMIA!L26</f>
-        <v>4968.85240496758</v>
+        <v>5988.72947711613</v>
       </c>
       <c r="M59" s="92" t="n">
         <f aca="false">ECONOMIA!M26</f>
@@ -17596,7 +17611,7 @@
       </c>
       <c r="L60" s="101" t="n">
         <f aca="false">L59/12</f>
-        <v>414.071033747298</v>
+        <v>499.060789759677</v>
       </c>
       <c r="M60" s="101" t="n">
         <f aca="false">M59/12</f>
@@ -17651,7 +17666,7 @@
       </c>
       <c r="L61" s="102" t="n">
         <f aca="false">IFERROR(L34/L59,0)</f>
-        <v>4.01340156130682</v>
+        <v>3.12253209490521</v>
       </c>
       <c r="M61" s="102" t="n">
         <f aca="false">IFERROR(M34/M59,0)</f>
@@ -17708,7 +17723,7 @@
       </c>
       <c r="L62" s="103" t="n">
         <f aca="false">PROJECAO!AF10</f>
-        <v>28301.310178054</v>
+        <v>34110.2686678464</v>
       </c>
       <c r="M62" s="103" t="n">
         <f aca="false">PROJECAO!AI10</f>
@@ -17763,7 +17778,7 @@
       </c>
       <c r="L63" s="103" t="n">
         <f aca="false">PROJECAO!AF15</f>
-        <v>67110.2475445575</v>
+        <v>80884.8975439178</v>
       </c>
       <c r="M63" s="103" t="n">
         <f aca="false">PROJECAO!AI15</f>
@@ -17818,7 +17833,7 @@
       </c>
       <c r="L64" s="103" t="n">
         <f aca="false">PROJECAO!AF25</f>
-        <v>193304.408740621</v>
+        <v>232980.921213138</v>
       </c>
       <c r="M64" s="103" t="n">
         <f aca="false">PROJECAO!AI25</f>
@@ -17873,7 +17888,7 @@
       </c>
       <c r="L65" s="104" t="n">
         <f aca="false">L64-L34</f>
-        <v>173362.408740621</v>
+        <v>214280.921213138</v>
       </c>
       <c r="M65" s="104" t="n">
         <f aca="false">M64-M34</f>
@@ -17930,7 +17945,7 @@
       </c>
       <c r="L66" s="97" t="n">
         <f aca="false">IFERROR(L65/L34,0)</f>
-        <v>8.69333109721298</v>
+        <v>11.4588727921464</v>
       </c>
       <c r="M66" s="97" t="n">
         <f aca="false">IFERROR(M65/M34,0)</f>
@@ -18004,7 +18019,7 @@
       </c>
       <c r="L69" s="88" t="n">
         <f aca="false">L16*1.35</f>
-        <v>6.75</v>
+        <v>8.1</v>
       </c>
       <c r="M69" s="88" t="n">
         <f aca="false">M16*1.35</f>
@@ -18059,7 +18074,7 @@
       </c>
       <c r="L70" s="99" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((L69-L14)*1000/L12,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M70" s="99" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((M69-M14)*1000/M12,0))</f>
@@ -18161,7 +18176,7 @@
       </c>
       <c r="L72" s="85" t="n">
         <f aca="false">L70*L12/1000*GERACAO!$I$17</f>
-        <v>1555.05086385</v>
+        <v>2332.576295775</v>
       </c>
       <c r="M72" s="85" t="n">
         <f aca="false">M70*M12/1000*GERACAO!$I$17</f>
@@ -19017,7 +19032,7 @@
       </c>
       <c r="L6" s="39" t="n">
         <f aca="false">COMPARATIVO!L39</f>
-        <v>6220.2034554</v>
+        <v>7775.25431925</v>
       </c>
       <c r="M6" s="39" t="n">
         <f aca="false">COMPARATIVO!M39</f>
@@ -19188,7 +19203,7 @@
       </c>
       <c r="L9" s="39" t="n">
         <f aca="false">MIN(L5,L6)*ENTRADAS!$C$37</f>
-        <v>1866.06103662</v>
+        <v>2332.576295775</v>
       </c>
       <c r="M9" s="39" t="n">
         <f aca="false">MIN(M5,M6)*ENTRADAS!$C$37</f>
@@ -19245,7 +19260,7 @@
       </c>
       <c r="L10" s="39" t="n">
         <f aca="false">L6-L9</f>
-        <v>4354.14241878</v>
+        <v>5442.678023475</v>
       </c>
       <c r="M10" s="39" t="n">
         <f aca="false">M6-M9</f>
@@ -19359,7 +19374,7 @@
       </c>
       <c r="L12" s="39" t="n">
         <f aca="false">MAX(0,MIN(L10,L5-L9-L11))</f>
-        <v>4354.14241878</v>
+        <v>5027.63758854091</v>
       </c>
       <c r="M12" s="39" t="n">
         <f aca="false">MAX(0,MIN(M10,M5-M9-M11))</f>
@@ -19416,7 +19431,7 @@
       </c>
       <c r="L13" s="39" t="n">
         <f aca="false">L10-L12</f>
-        <v>0</v>
+        <v>415.040434934095</v>
       </c>
       <c r="M13" s="39" t="n">
         <f aca="false">M10-M12</f>
@@ -19473,7 +19488,7 @@
       </c>
       <c r="L14" s="39" t="n">
         <f aca="false">MAX(L11,L5-L9-L12)</f>
-        <v>1740.01042891591</v>
+        <v>600</v>
       </c>
       <c r="M14" s="39" t="n">
         <f aca="false">MAX(M11,M5-M9-M12)</f>
@@ -19530,7 +19545,7 @@
       </c>
       <c r="L15" s="112" t="n">
         <f aca="false">L14*L7</f>
-        <v>1777.36845282473</v>
+        <v>612.882</v>
       </c>
       <c r="M15" s="112" t="n">
         <f aca="false">M14*M7</f>
@@ -19585,7 +19600,7 @@
       </c>
       <c r="L16" s="112" t="n">
         <f aca="false">L12*ENTRADAS!$C$25</f>
-        <v>934.898818619864</v>
+        <v>1079.50819929604</v>
       </c>
       <c r="M16" s="112" t="n">
         <f aca="false">M12*ENTRADAS!$C$25</f>
@@ -19699,7 +19714,7 @@
       </c>
       <c r="L18" s="50" t="n">
         <f aca="false">L15+L16+L17</f>
-        <v>2965.5872714446</v>
+        <v>1945.71019929604</v>
       </c>
       <c r="M18" s="50" t="n">
         <f aca="false">M15+M16+M17</f>
@@ -19756,7 +19771,7 @@
       </c>
       <c r="L19" s="50" t="n">
         <f aca="false">L18/12</f>
-        <v>247.132272620383</v>
+        <v>162.142516608004</v>
       </c>
       <c r="M19" s="50" t="n">
         <f aca="false">M18/12</f>
@@ -19813,7 +19828,7 @@
       </c>
       <c r="L20" s="40" t="n">
         <f aca="false">IFERROR(1-L18/L8,0)</f>
-        <v>0.646298693067392</v>
+        <v>0.767937957169651</v>
       </c>
       <c r="M20" s="40" t="n">
         <f aca="false">IFERROR(1-M18/M8,0)</f>
@@ -19868,7 +19883,7 @@
       </c>
       <c r="L21" s="112" t="n">
         <f aca="false">L8-L18</f>
-        <v>5418.85240496758</v>
+        <v>6438.72947711613</v>
       </c>
       <c r="M21" s="112" t="n">
         <f aca="false">M8-M18</f>
@@ -20149,7 +20164,7 @@
       </c>
       <c r="L26" s="114" t="n">
         <f aca="false">L21-L25</f>
-        <v>4968.85240496758</v>
+        <v>5988.72947711613</v>
       </c>
       <c r="M26" s="114" t="n">
         <f aca="false">M21-M25</f>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1282">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -2112,7 +2112,7 @@
     <t xml:space="preserve">Proposta 40436 de 11/08/2026 (val. 20/08)</t>
   </si>
   <si>
-    <t xml:space="preserve">WhatsApp 10/08/2026 17:45</t>
+    <t xml:space="preserve">Proposta 6695731 de 12/08/2026 - VALIDADE 17/08 (5 dias)</t>
   </si>
   <si>
     <t xml:space="preserve">Proposta 0664/2026 de 11/08/2026 (val. 10 dias)</t>
@@ -2181,18 +2181,21 @@
     <t xml:space="preserve">RONMA SOLAR bifacial N-type 144 cel</t>
   </si>
   <si>
+    <t xml:space="preserve">ZNShine 650W qt.10 (pag.5) x RISEN 660W qt.16 (tabela) - CONTRADICAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longi ou DAH Solar (Tier 1 de verdade)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCL Solar bifacial N-type 132 cel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA Solar bifacial N-type 132 cel - TIER 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZNShine ZXNR-MD132-650 N-type (Tier 1 BNEF)</t>
   </si>
   <si>
-    <t xml:space="preserve">Longi ou DAH Solar (Tier 1 de verdade)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCL Solar bifacial N-type 132 cel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA Solar bifacial N-type 132 cel - TIER 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALERTA: Maxeon do William e PERC, uma geracao atras. TCL e RONMA tem pouquissima rede de assistencia no Brasil. JA Solar, Longi e DAH sao Tier 1 com representacao aqui.</t>
   </si>
   <si>
@@ -2307,6 +2310,9 @@
     <t xml:space="preserve">Colonial</t>
   </si>
   <si>
+    <t xml:space="preserve">estrutura apropriada ao telhado (tipo nao especificado)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ceramico / colonial</t>
   </si>
   <si>
@@ -2325,7 +2331,7 @@
     <t xml:space="preserve">25 anos eficiencia / 15 anos defeito</t>
   </si>
   <si>
-    <t xml:space="preserve">nao declarada pelo vendedor - exigir por escrito (N-type costuma dar 12/25 a 30 anos)</t>
+    <t xml:space="preserve">12 anos defeito / 25 anos eficiencia</t>
   </si>
   <si>
     <t xml:space="preserve">12 anos produto / 25 anos eficiencia</t>
@@ -2346,7 +2352,7 @@
     <t xml:space="preserve">10 a 25 anos</t>
   </si>
   <si>
-    <t xml:space="preserve">nao declarada pelo vendedor - a Deye pratica 10 anos, exigir por escrito</t>
+    <t xml:space="preserve">12 anos</t>
   </si>
   <si>
     <t xml:space="preserve">7 a 10 anos</t>
@@ -2367,6 +2373,9 @@
     <t xml:space="preserve">12 meses</t>
   </si>
   <si>
+    <t xml:space="preserve">vistoria, projeto eletrico, ART, licencas, gestao de obra, frete e documentacao</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 ano instalacao + SEGURO ALL RISK 1 ano + GARANTIA DE PERFORMANCE EM CONTRATO</t>
   </si>
   <si>
@@ -2385,12 +2394,12 @@
     <t xml:space="preserve">padrao de entrada, obras civis, telhado, eletrodutos, ART estrutural</t>
   </si>
   <si>
+    <t xml:space="preserve">alvenaria, reforco estrutural e alteracoes na rede pedidas pela concessionaria</t>
+  </si>
+  <si>
     <t xml:space="preserve">obras civis, reformas no telhado/laje e no PADRAO DE ENTRADA</t>
   </si>
   <si>
-    <t xml:space="preserve">alvenaria, reforco estrutural e alteracoes na rede pedidas pela concessionaria</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALERTA: Sun Coast, Sfero e AD BioSolar excluem por escrito a adequacao do padrao. E honesto declarar, mas o custo e seu. Quem nao declarou exclusao tambem nao incluiu - so nao avisou.</t>
   </si>
   <si>
@@ -2457,7 +2466,7 @@
     <t xml:space="preserve">Adequacao do padrao mono -&gt; bifasico (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">ALERTA: NENHUM dos orcamentos incluiu. Necessario para qualquer inversor de 220 V. Editavel em ENTRADAS!C28.</t>
+    <t xml:space="preserve">ALERTA: so a proposta do Yuri (colunas G, e as simulacoes) lista 'PADRAO DE ENTRADA' e 'TROCA DE DISJUNTOR DO PADRAO' como inclusos - por isso zero nelas. MAS a pagina 8 da mesma proposta diz que a adequacao de entrada e responsabilidade do cliente. CONTRADICAO A RESOLVER POR ESCRITO: vale R$ 2.500.</t>
   </si>
   <si>
     <t xml:space="preserve">PRECO TOTAL INSTALADO (R$)</t>
@@ -3607,6 +3616,30 @@
   </si>
   <si>
     <t xml:space="preserve">AUXSOL DE 7,5 kW SIGNIFICA 7,5 kW DECLARADOS NA HOMOLOGACAO = 34 A em 220 V. Isso pode exigir padrao de entrada maior (e mais caro) do que 6,82 kWp precisaria. Perguntar se um inversor de 6 kW nao serviria, com preco menor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-septies) AS DUAS CONTRADICOES DA PROPOSTA FORMAL DO YURI (proposta 6695731)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRADICAO 1 - PADRAO DE ENTRADA. A pagina 5 lista como inclusos 'MAO DE OBRA + ENGENHARIA + HOMOLOGACAO + PADRAO DE ENTRADA + MATERIAL ELETRICO' e ainda 'TROCA DE DISJUNTOR DO PADRAO'. Mas a pagina 8, item 5, diz: 'E de responsabilidade do cliente todo o material e obra que tenha que ser realizada por motivos de adequacao de entrada'. Uma pagina inclui e a outra exclui. ISSO VALE CERCA DE R$ 2.500 - a planilha adotou como INCLUSO conforme a pagina 5, mas EXIJA a confirmacao por escrito. Se for excluido, some R$ 2.500 ao preco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRADICAO 2 - MODULO. A secao de caracteristicas tecnicas diz marca ZSHINE, 650 Wp, quantidade 10, totalizando os 6,50 kWp declarados e 25 m2 de area. Mas a tabela de equipamentos lista 'MODULOS BIFACIAL 660W RISEN' com quantidade 16. Sao tres divergencias ao mesmo tempo: marca (ZShine x Risen), potencia (650 x 660 W) e quantidade (10 x 16). Dezesseis modulos de 660 W dariam 10,56 kWp e precisariam de uns 43 m2, nao 25. Provavelmente a tabela ficou com sobra de outro orcamento - mas o CONTRATO e o que vale, entao exija a proposta corrigida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE POR ACASO FOREM MESMO 16 MODULOS pelo mesmo preco, seria 10,56 kWp a R$ 1,59/Wp - imbativel, e caberia exatamente nos 16 canais dos 4 micros Deye (DC/AC 1,17). Vale perguntar, mas nao contar com isso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANHOS REAIS DESTA PROPOSTA FORMAL em relacao ao orcamento de WhatsApp: garantias agora declaradas (modulo 12 anos de defeito e 25 de eficiencia, inversor 12 anos), escopo de servicos listado (vistoria tecnica, projeto eletrico, ART, licencas junto a concessionaria, gestao e fiscalizacao de obra, frete e documentacao), e a troca do disjuntor do padrao no escopo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDADE DE APENAS 5 DIAS: emitida em 12/08/2026 e valida ate 17/08/2026. Se for decidir, e nesta semana - ou peca revalidacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AINDA FALTAM NESTA PROPOSTA: razao social e CNPJ da SunWash (o PDF traz apenas 'YURI' e um WhatsApp), o tipo de telha considerado, o registro INMETRO do modulo e do micro, e o esclarecimento sobre os R$ 1.800 do acrescimo regional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSERVACAO SOBRE OS NUMEROS FINANCEIROS DELES: usaram consumo de 502 kWh/mes e tarifa de R$ 0,882/kWh (R$ 442,67 / 502 kWh). Sua tarifa real e R$ 1,0215. A tabela de anos vai de 2023 a 2030, o que indica planilha-modelo nao atualizada. Ignore a analise financeira deles e use a aba COMPARATIVO.</t>
   </si>
   <si>
     <t xml:space="preserve">1-ter) DEMAIS BLOQUEADORES</t>
@@ -5291,128 +5324,128 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="AA4" s="17" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="AC4" s="17" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="AH4" s="17" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="AI4" s="17" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="AJ4" s="17" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="AM4" s="17" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5505,7 +5538,7 @@
       </c>
       <c r="X6" s="116" t="n">
         <f aca="false">W6-COMPARATIVO!I$34</f>
-        <v>-15079.8964560775</v>
+        <v>-12579.8964560775</v>
       </c>
       <c r="Y6" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
@@ -5553,7 +5586,7 @@
       </c>
       <c r="AJ6" s="116" t="n">
         <f aca="false">AI6-COMPARATIVO!M$34</f>
-        <v>-16879.8964560775</v>
+        <v>-14379.8964560775</v>
       </c>
       <c r="AK6" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
@@ -5565,7 +5598,7 @@
       </c>
       <c r="AM6" s="116" t="n">
         <f aca="false">AL6-COMPARATIVO!N$34</f>
-        <v>-18679.8964560775</v>
+        <v>-16179.8964560775</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,7 +5691,7 @@
       </c>
       <c r="X7" s="116" t="n">
         <f aca="false">W7-COMPARATIVO!I$34</f>
-        <v>-8688.10096274443</v>
+        <v>-6188.10096274443</v>
       </c>
       <c r="Y7" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
@@ -5706,7 +5739,7 @@
       </c>
       <c r="AJ7" s="116" t="n">
         <f aca="false">AI7-COMPARATIVO!M$34</f>
-        <v>-10488.1009627444</v>
+        <v>-7988.10096274443</v>
       </c>
       <c r="AK7" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
@@ -5718,7 +5751,7 @@
       </c>
       <c r="AM7" s="116" t="n">
         <f aca="false">AL7-COMPARATIVO!N$34</f>
-        <v>-12288.1009627444</v>
+        <v>-9788.10096274443</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5811,7 +5844,7 @@
       </c>
       <c r="X8" s="116" t="n">
         <f aca="false">W8-COMPARATIVO!I$34</f>
-        <v>-1879.65628017843</v>
+        <v>620.343719821569</v>
       </c>
       <c r="Y8" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
@@ -5859,7 +5892,7 @@
       </c>
       <c r="AJ8" s="116" t="n">
         <f aca="false">AI8-COMPARATIVO!M$34</f>
-        <v>-3679.65628017843</v>
+        <v>-1179.65628017843</v>
       </c>
       <c r="AK8" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
@@ -5871,7 +5904,7 @@
       </c>
       <c r="AM8" s="116" t="n">
         <f aca="false">AL8-COMPARATIVO!N$34</f>
-        <v>-5479.65628017843</v>
+        <v>-2979.65628017843</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5964,7 +5997,7 @@
       </c>
       <c r="X9" s="116" t="n">
         <f aca="false">W9-COMPARATIVO!I$34</f>
-        <v>5372.59686902063</v>
+        <v>7872.59686902063</v>
       </c>
       <c r="Y9" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
@@ -6012,7 +6045,7 @@
       </c>
       <c r="AJ9" s="116" t="n">
         <f aca="false">AI9-COMPARATIVO!M$34</f>
-        <v>3572.59686902063</v>
+        <v>6072.59686902063</v>
       </c>
       <c r="AK9" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
@@ -6024,7 +6057,7 @@
       </c>
       <c r="AM9" s="116" t="n">
         <f aca="false">AL9-COMPARATIVO!N$34</f>
-        <v>1772.59686902063</v>
+        <v>4272.59686902063</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6117,7 +6150,7 @@
       </c>
       <c r="X10" s="119" t="n">
         <f aca="false">W10-COMPARATIVO!I$34</f>
-        <v>13097.5881397502</v>
+        <v>15597.5881397502</v>
       </c>
       <c r="Y10" s="119" t="n">
         <f aca="false">ECONOMIA!J$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
@@ -6165,7 +6198,7 @@
       </c>
       <c r="AJ10" s="119" t="n">
         <f aca="false">AI10-COMPARATIVO!M$34</f>
-        <v>11297.5881397502</v>
+        <v>13797.5881397502</v>
       </c>
       <c r="AK10" s="119" t="n">
         <f aca="false">ECONOMIA!N$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
@@ -6177,7 +6210,7 @@
       </c>
       <c r="AM10" s="119" t="n">
         <f aca="false">AL10-COMPARATIVO!N$34</f>
-        <v>9497.58813975023</v>
+        <v>11997.5881397502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6270,7 +6303,7 @@
       </c>
       <c r="X11" s="116" t="n">
         <f aca="false">W11-COMPARATIVO!I$34</f>
-        <v>21326.1329664623</v>
+        <v>23826.1329664623</v>
       </c>
       <c r="Y11" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
@@ -6318,7 +6351,7 @@
       </c>
       <c r="AJ11" s="116" t="n">
         <f aca="false">AI11-COMPARATIVO!M$34</f>
-        <v>19526.1329664623</v>
+        <v>22026.1329664623</v>
       </c>
       <c r="AK11" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
@@ -6330,7 +6363,7 @@
       </c>
       <c r="AM11" s="116" t="n">
         <f aca="false">AL11-COMPARATIVO!N$34</f>
-        <v>17726.1329664623</v>
+        <v>20226.1329664623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6423,7 +6456,7 @@
       </c>
       <c r="X12" s="116" t="n">
         <f aca="false">W12-COMPARATIVO!I$34</f>
-        <v>30091.0554877037</v>
+        <v>32591.0554877037</v>
       </c>
       <c r="Y12" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
@@ -6471,7 +6504,7 @@
       </c>
       <c r="AJ12" s="116" t="n">
         <f aca="false">AI12-COMPARATIVO!M$34</f>
-        <v>28291.0554877037</v>
+        <v>30791.0554877037</v>
       </c>
       <c r="AK12" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
@@ -6483,7 +6516,7 @@
       </c>
       <c r="AM12" s="116" t="n">
         <f aca="false">AL12-COMPARATIVO!N$34</f>
-        <v>26491.0554877037</v>
+        <v>28991.0554877037</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6576,7 +6609,7 @@
       </c>
       <c r="X13" s="116" t="n">
         <f aca="false">W13-COMPARATIVO!I$34</f>
-        <v>39427.3194834922</v>
+        <v>41927.3194834922</v>
       </c>
       <c r="Y13" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
@@ -6624,7 +6657,7 @@
       </c>
       <c r="AJ13" s="116" t="n">
         <f aca="false">AI13-COMPARATIVO!M$34</f>
-        <v>37627.3194834922</v>
+        <v>40127.3194834922</v>
       </c>
       <c r="AK13" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
@@ -6636,7 +6669,7 @@
       </c>
       <c r="AM13" s="116" t="n">
         <f aca="false">AL13-COMPARATIVO!N$34</f>
-        <v>35827.3194834922</v>
+        <v>38327.3194834922</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6729,7 +6762,7 @@
       </c>
       <c r="X14" s="116" t="n">
         <f aca="false">W14-COMPARATIVO!I$34</f>
-        <v>49372.1678478461</v>
+        <v>51872.1678478461</v>
       </c>
       <c r="Y14" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
@@ -6777,7 +6810,7 @@
       </c>
       <c r="AJ14" s="116" t="n">
         <f aca="false">AI14-COMPARATIVO!M$34</f>
-        <v>47572.1678478461</v>
+        <v>50072.1678478461</v>
       </c>
       <c r="AK14" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
@@ -6789,7 +6822,7 @@
       </c>
       <c r="AM14" s="116" t="n">
         <f aca="false">AL14-COMPARATIVO!N$34</f>
-        <v>45772.1678478461</v>
+        <v>48272.1678478461</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6882,7 +6915,7 @@
       </c>
       <c r="X15" s="119" t="n">
         <f aca="false">W15-COMPARATIVO!I$34</f>
-        <v>59965.2711528304</v>
+        <v>62465.2711528304</v>
       </c>
       <c r="Y15" s="119" t="n">
         <f aca="false">ECONOMIA!J$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
@@ -6930,7 +6963,7 @@
       </c>
       <c r="AJ15" s="119" t="n">
         <f aca="false">AI15-COMPARATIVO!M$34</f>
-        <v>58165.2711528304</v>
+        <v>60665.2711528304</v>
       </c>
       <c r="AK15" s="119" t="n">
         <f aca="false">ECONOMIA!N$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
@@ -6942,7 +6975,7 @@
       </c>
       <c r="AM15" s="119" t="n">
         <f aca="false">AL15-COMPARATIVO!N$34</f>
-        <v>56365.2711528304</v>
+        <v>58865.2711528304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7035,7 +7068,7 @@
       </c>
       <c r="X16" s="116" t="n">
         <f aca="false">W16-COMPARATIVO!I$34</f>
-        <v>71248.8858967502</v>
+        <v>73748.8858967502</v>
       </c>
       <c r="Y16" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
@@ -7083,7 +7116,7 @@
       </c>
       <c r="AJ16" s="116" t="n">
         <f aca="false">AI16-COMPARATIVO!M$34</f>
-        <v>69448.8858967502</v>
+        <v>71948.8858967502</v>
       </c>
       <c r="AK16" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
@@ -7095,7 +7128,7 @@
       </c>
       <c r="AM16" s="116" t="n">
         <f aca="false">AL16-COMPARATIVO!N$34</f>
-        <v>67648.8858967502</v>
+        <v>70148.8858967502</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7188,7 +7221,7 @@
       </c>
       <c r="X17" s="116" t="n">
         <f aca="false">W17-COMPARATIVO!I$34</f>
-        <v>83268.0230677524</v>
+        <v>85768.0230677524</v>
       </c>
       <c r="Y17" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
@@ -7236,7 +7269,7 @@
       </c>
       <c r="AJ17" s="116" t="n">
         <f aca="false">AI17-COMPARATIVO!M$34</f>
-        <v>81468.0230677524</v>
+        <v>83968.0230677524</v>
       </c>
       <c r="AK17" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
@@ -7248,7 +7281,7 @@
       </c>
       <c r="AM17" s="116" t="n">
         <f aca="false">AL17-COMPARATIVO!N$34</f>
-        <v>79668.0230677524</v>
+        <v>82168.0230677524</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,7 +7374,7 @@
       </c>
       <c r="X18" s="116" t="n">
         <f aca="false">W18-COMPARATIVO!I$34</f>
-        <v>96070.6276952463</v>
+        <v>98570.6276952463</v>
       </c>
       <c r="Y18" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
@@ -7389,7 +7422,7 @@
       </c>
       <c r="AJ18" s="116" t="n">
         <f aca="false">AI18-COMPARATIVO!M$34</f>
-        <v>94270.6276952463</v>
+        <v>96770.6276952463</v>
       </c>
       <c r="AK18" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
@@ -7401,7 +7434,7 @@
       </c>
       <c r="AM18" s="116" t="n">
         <f aca="false">AL18-COMPARATIVO!N$34</f>
-        <v>92470.6276952463</v>
+        <v>94970.6276952463</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7494,7 +7527,7 @@
       </c>
       <c r="X19" s="116" t="n">
         <f aca="false">W19-COMPARATIVO!I$34</f>
-        <v>109707.770105383</v>
+        <v>112207.770105383</v>
       </c>
       <c r="Y19" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
@@ -7542,7 +7575,7 @@
       </c>
       <c r="AJ19" s="116" t="n">
         <f aca="false">AI19-COMPARATIVO!M$34</f>
-        <v>107907.770105383</v>
+        <v>110407.770105383</v>
       </c>
       <c r="AK19" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
@@ -7554,7 +7587,7 @@
       </c>
       <c r="AM19" s="116" t="n">
         <f aca="false">AL19-COMPARATIVO!N$34</f>
-        <v>106107.770105383</v>
+        <v>108607.770105383</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,7 +7680,7 @@
       </c>
       <c r="X20" s="116" t="n">
         <f aca="false">W20-COMPARATIVO!I$34</f>
-        <v>124233.849643525</v>
+        <v>126733.849643525</v>
       </c>
       <c r="Y20" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
@@ -7695,7 +7728,7 @@
       </c>
       <c r="AJ20" s="116" t="n">
         <f aca="false">AI20-COMPARATIVO!M$34</f>
-        <v>122433.849643525</v>
+        <v>124933.849643525</v>
       </c>
       <c r="AK20" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
@@ -7707,7 +7740,7 @@
       </c>
       <c r="AM20" s="116" t="n">
         <f aca="false">AL20-COMPARATIVO!N$34</f>
-        <v>120633.849643525</v>
+        <v>123133.849643525</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7800,7 +7833,7 @@
       </c>
       <c r="X21" s="116" t="n">
         <f aca="false">W21-COMPARATIVO!I$34</f>
-        <v>139706.811676361</v>
+        <v>142206.811676361</v>
       </c>
       <c r="Y21" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
@@ -7848,7 +7881,7 @@
       </c>
       <c r="AJ21" s="116" t="n">
         <f aca="false">AI21-COMPARATIVO!M$34</f>
-        <v>137906.811676361</v>
+        <v>140406.811676361</v>
       </c>
       <c r="AK21" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
@@ -7860,7 +7893,7 @@
       </c>
       <c r="AM21" s="116" t="n">
         <f aca="false">AL21-COMPARATIVO!N$34</f>
-        <v>136106.811676361</v>
+        <v>138606.811676361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,7 +7986,7 @@
       </c>
       <c r="X22" s="116" t="n">
         <f aca="false">W22-COMPARATIVO!I$34</f>
-        <v>156188.378739307</v>
+        <v>158688.378739307</v>
       </c>
       <c r="Y22" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
@@ -8001,7 +8034,7 @@
       </c>
       <c r="AJ22" s="116" t="n">
         <f aca="false">AI22-COMPARATIVO!M$34</f>
-        <v>154388.378739307</v>
+        <v>156888.378739307</v>
       </c>
       <c r="AK22" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
@@ -8013,7 +8046,7 @@
       </c>
       <c r="AM22" s="116" t="n">
         <f aca="false">AL22-COMPARATIVO!N$34</f>
-        <v>152588.378739307</v>
+        <v>155088.378739307</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8106,7 +8139,7 @@
       </c>
       <c r="X23" s="116" t="n">
         <f aca="false">W23-COMPARATIVO!I$34</f>
-        <v>173744.296751251</v>
+        <v>176244.296751251</v>
       </c>
       <c r="Y23" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
@@ -8154,7 +8187,7 @@
       </c>
       <c r="AJ23" s="116" t="n">
         <f aca="false">AI23-COMPARATIVO!M$34</f>
-        <v>171944.296751251</v>
+        <v>174444.296751251</v>
       </c>
       <c r="AK23" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
@@ -8166,7 +8199,7 @@
       </c>
       <c r="AM23" s="116" t="n">
         <f aca="false">AL23-COMPARATIVO!N$34</f>
-        <v>170144.296751251</v>
+        <v>172644.296751251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8259,7 +8292,7 @@
       </c>
       <c r="X24" s="116" t="n">
         <f aca="false">W24-COMPARATIVO!I$34</f>
-        <v>192444.597278804</v>
+        <v>194944.597278804</v>
       </c>
       <c r="Y24" s="116" t="n">
         <f aca="false">ECONOMIA!J$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
@@ -8307,7 +8340,7 @@
       </c>
       <c r="AJ24" s="116" t="n">
         <f aca="false">AI24-COMPARATIVO!M$34</f>
-        <v>190644.597278804</v>
+        <v>193144.597278804</v>
       </c>
       <c r="AK24" s="116" t="n">
         <f aca="false">ECONOMIA!N$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
@@ -8319,7 +8352,7 @@
       </c>
       <c r="AM24" s="116" t="n">
         <f aca="false">AL24-COMPARATIVO!N$34</f>
-        <v>188844.597278804</v>
+        <v>191344.597278804</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8412,7 +8445,7 @@
       </c>
       <c r="X25" s="119" t="n">
         <f aca="false">W25-COMPARATIVO!I$34</f>
-        <v>212363.876896246</v>
+        <v>214863.876896246</v>
       </c>
       <c r="Y25" s="119" t="n">
         <f aca="false">ECONOMIA!J$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
@@ -8460,7 +8493,7 @@
       </c>
       <c r="AJ25" s="119" t="n">
         <f aca="false">AI25-COMPARATIVO!M$34</f>
-        <v>210563.876896246</v>
+        <v>213063.876896246</v>
       </c>
       <c r="AK25" s="119" t="n">
         <f aca="false">ECONOMIA!N$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
@@ -8472,27 +8505,27 @@
       </c>
       <c r="AM25" s="119" t="n">
         <f aca="false">AL25-COMPARATIVO!N$34</f>
-        <v>208763.876896246</v>
+        <v>211263.876896246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -8526,23 +8559,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8550,25 +8583,25 @@
         <v>292</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8994,32 +9027,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9027,12 +9060,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -9051,7 +9084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9063,32 +9096,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -9098,10 +9131,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="120" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E6" s="121"/>
     </row>
@@ -9110,10 +9143,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="120" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E7" s="121"/>
     </row>
@@ -9122,10 +9155,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="120" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E8" s="121"/>
     </row>
@@ -9134,17 +9167,17 @@
         <v>4</v>
       </c>
       <c r="C9" s="120" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>1125</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>1122</v>
       </c>
       <c r="E9" s="121"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
       <c r="C10" s="7" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -9154,10 +9187,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="122" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E11" s="121"/>
     </row>
@@ -9166,10 +9199,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="120" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E12" s="121"/>
     </row>
@@ -9178,10 +9211,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E13" s="121"/>
     </row>
@@ -9190,10 +9223,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="122" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E14" s="121"/>
     </row>
@@ -9202,10 +9235,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="120" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E15" s="121"/>
     </row>
@@ -9214,10 +9247,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="120" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E16" s="121"/>
     </row>
@@ -9226,10 +9259,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="120" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E17" s="121"/>
     </row>
@@ -9238,10 +9271,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="120" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E18" s="121"/>
     </row>
@@ -9250,10 +9283,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="120" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E20" s="121"/>
     </row>
@@ -9262,10 +9295,10 @@
         <v>14</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E21" s="121"/>
     </row>
@@ -9274,10 +9307,10 @@
         <v>15</v>
       </c>
       <c r="C22" s="120" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E22" s="121"/>
     </row>
@@ -9286,10 +9319,10 @@
         <v>16</v>
       </c>
       <c r="C23" s="120" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E23" s="121"/>
     </row>
@@ -9298,10 +9331,10 @@
         <v>17</v>
       </c>
       <c r="C24" s="120" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E24" s="121"/>
     </row>
@@ -9310,10 +9343,10 @@
         <v>18</v>
       </c>
       <c r="C25" s="120" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E25" s="121"/>
     </row>
@@ -9322,17 +9355,17 @@
         <v>19</v>
       </c>
       <c r="C26" s="120" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E26" s="121"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="8"/>
       <c r="C27" s="7" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -9342,10 +9375,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="122" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E28" s="121"/>
     </row>
@@ -9354,10 +9387,10 @@
         <v>21</v>
       </c>
       <c r="C29" s="122" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E29" s="121"/>
     </row>
@@ -9366,10 +9399,10 @@
         <v>22</v>
       </c>
       <c r="C30" s="122" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E30" s="121"/>
     </row>
@@ -9378,10 +9411,10 @@
         <v>23</v>
       </c>
       <c r="C31" s="120" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E31" s="121"/>
     </row>
@@ -9390,10 +9423,10 @@
         <v>24</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E32" s="121"/>
     </row>
@@ -9402,10 +9435,10 @@
         <v>25</v>
       </c>
       <c r="C33" s="122" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E33" s="121"/>
     </row>
@@ -9414,10 +9447,10 @@
         <v>26</v>
       </c>
       <c r="C34" s="122" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E34" s="121"/>
     </row>
@@ -9426,10 +9459,10 @@
         <v>27</v>
       </c>
       <c r="C35" s="122" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E35" s="121"/>
     </row>
@@ -9438,10 +9471,10 @@
         <v>28</v>
       </c>
       <c r="C36" s="120" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E36" s="121"/>
     </row>
@@ -9450,10 +9483,10 @@
         <v>29</v>
       </c>
       <c r="C37" s="120" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E37" s="121"/>
     </row>
@@ -9462,10 +9495,10 @@
         <v>30</v>
       </c>
       <c r="C38" s="120" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E38" s="121"/>
     </row>
@@ -9474,10 +9507,10 @@
         <v>31</v>
       </c>
       <c r="C39" s="120" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E39" s="121"/>
     </row>
@@ -9486,10 +9519,10 @@
         <v>32</v>
       </c>
       <c r="C40" s="120" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E40" s="121"/>
     </row>
@@ -9498,10 +9531,10 @@
         <v>33</v>
       </c>
       <c r="C41" s="120" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E41" s="121"/>
     </row>
@@ -9510,17 +9543,17 @@
         <v>34</v>
       </c>
       <c r="C42" s="122" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E42" s="121"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="8"/>
       <c r="C44" s="7" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
@@ -9530,10 +9563,10 @@
         <v>35</v>
       </c>
       <c r="C45" s="120" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E45" s="121"/>
     </row>
@@ -9542,10 +9575,10 @@
         <v>36</v>
       </c>
       <c r="C46" s="120" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E46" s="121"/>
     </row>
@@ -9554,10 +9587,10 @@
         <v>37</v>
       </c>
       <c r="C47" s="120" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E47" s="121"/>
     </row>
@@ -9566,10 +9599,10 @@
         <v>38</v>
       </c>
       <c r="C48" s="120" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E48" s="121"/>
     </row>
@@ -9578,17 +9611,17 @@
         <v>39</v>
       </c>
       <c r="C49" s="122" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E49" s="121"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="8"/>
       <c r="C51" s="7" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
@@ -9598,10 +9631,10 @@
         <v>40</v>
       </c>
       <c r="C52" s="122" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E52" s="121"/>
     </row>
@@ -9610,10 +9643,10 @@
         <v>41</v>
       </c>
       <c r="C53" s="120" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E53" s="121"/>
     </row>
@@ -9622,10 +9655,10 @@
         <v>42</v>
       </c>
       <c r="C54" s="120" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E54" s="121"/>
     </row>
@@ -9634,254 +9667,254 @@
         <v>43</v>
       </c>
       <c r="C55" s="120" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E55" s="121"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="8"/>
       <c r="C57" s="7" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="n">
         <v>44</v>
       </c>
       <c r="C58" s="120" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E58" s="121"/>
     </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="n">
         <v>45</v>
       </c>
       <c r="C59" s="120" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E59" s="121"/>
     </row>
-    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="C60" s="120" t="s">
-        <v>1172</v>
+      <c r="C60" s="122" t="s">
+        <v>1175</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E60" s="121"/>
     </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="C61" s="120" t="s">
-        <v>1173</v>
+      <c r="C61" s="122" t="s">
+        <v>1176</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E61" s="121"/>
     </row>
-    <row r="62" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="n">
         <v>48</v>
       </c>
       <c r="C62" s="120" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E62" s="121"/>
     </row>
-    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="n">
         <v>49</v>
       </c>
       <c r="C63" s="120" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E63" s="121"/>
     </row>
-    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C64" s="120" t="s">
-        <v>1176</v>
+      <c r="C64" s="122" t="s">
+        <v>1179</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E64" s="121"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="4" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="8"/>
+      <c r="C66" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="C65" s="120" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E65" s="121"/>
-    </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="C66" s="120" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E66" s="121"/>
-    </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="4" t="n">
-        <v>53</v>
-      </c>
       <c r="C67" s="120" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E67" s="121"/>
     </row>
     <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C68" s="120" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E68" s="121"/>
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C69" s="120" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E69" s="121"/>
+    </row>
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="C70" s="120" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E70" s="121"/>
+    </row>
+    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="C69" s="120" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E69" s="121"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4" t="n">
+      <c r="C71" s="120" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E71" s="121"/>
+    </row>
+    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="C70" s="120" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E70" s="121"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="8"/>
-      <c r="C72" s="7" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="120" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E72" s="121"/>
+    </row>
+    <row r="73" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="C73" s="122" t="s">
-        <v>1184</v>
+      <c r="C73" s="120" t="s">
+        <v>1187</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E73" s="121"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="C74" s="122" t="s">
-        <v>1185</v>
+      <c r="C74" s="120" t="s">
+        <v>1188</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E74" s="121"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="C75" s="122" t="s">
-        <v>1186</v>
+      <c r="C75" s="120" t="s">
+        <v>1189</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E75" s="121"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C76" s="122" t="s">
-        <v>1187</v>
+      <c r="C76" s="120" t="s">
+        <v>1190</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E76" s="121"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="C77" s="122" t="s">
-        <v>1188</v>
+      <c r="C77" s="120" t="s">
+        <v>1191</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E77" s="121"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="C78" s="122" t="s">
-        <v>1189</v>
+      <c r="C78" s="120" t="s">
+        <v>1192</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E78" s="121"/>
     </row>
@@ -9889,55 +9922,55 @@
       <c r="B79" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="C79" s="122" t="s">
-        <v>1190</v>
+      <c r="C79" s="120" t="s">
+        <v>1193</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E79" s="121"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="4" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="8"/>
+      <c r="C81" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="C80" s="122" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E80" s="121"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="4" t="n">
+      <c r="C82" s="122" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E82" s="121"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="C81" s="122" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E81" s="121"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="8"/>
-      <c r="C83" s="7" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
+      <c r="C83" s="122" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E83" s="121"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="n">
         <v>66</v>
       </c>
       <c r="C84" s="122" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E84" s="121"/>
     </row>
@@ -9946,10 +9979,10 @@
         <v>67</v>
       </c>
       <c r="C85" s="122" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E85" s="121"/>
     </row>
@@ -9958,10 +9991,10 @@
         <v>68</v>
       </c>
       <c r="C86" s="122" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E86" s="121"/>
     </row>
@@ -9970,10 +10003,10 @@
         <v>69</v>
       </c>
       <c r="C87" s="122" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E87" s="121"/>
     </row>
@@ -9982,10 +10015,10 @@
         <v>70</v>
       </c>
       <c r="C88" s="122" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E88" s="121"/>
     </row>
@@ -9994,10 +10027,10 @@
         <v>71</v>
       </c>
       <c r="C89" s="122" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E89" s="121"/>
     </row>
@@ -10006,17 +10039,17 @@
         <v>72</v>
       </c>
       <c r="C90" s="122" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E90" s="121"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="8"/>
       <c r="C92" s="7" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
@@ -10026,22 +10059,22 @@
         <v>73</v>
       </c>
       <c r="C93" s="122" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E93" s="121"/>
     </row>
-    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="n">
         <v>74</v>
       </c>
       <c r="C94" s="122" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E94" s="121"/>
     </row>
@@ -10050,10 +10083,10 @@
         <v>75</v>
       </c>
       <c r="C95" s="122" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E95" s="121"/>
     </row>
@@ -10062,10 +10095,10 @@
         <v>76</v>
       </c>
       <c r="C96" s="122" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E96" s="121"/>
     </row>
@@ -10074,12 +10107,104 @@
         <v>77</v>
       </c>
       <c r="C97" s="122" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E97" s="121"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="C98" s="122" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E98" s="121"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="C99" s="122" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E99" s="121"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="8"/>
+      <c r="C101" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C102" s="122" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E102" s="121"/>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C103" s="122" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E103" s="121"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="C104" s="122" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E104" s="121"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="C105" s="122" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E105" s="121"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="C106" s="122" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E106" s="121"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10109,73 +10234,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1207</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1208</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1209</v>
+        <v>1220</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1210</v>
+        <v>1221</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1211</v>
+        <v>1222</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1212</v>
+        <v>1223</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1213</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>1214</v>
+        <v>1225</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="80" t="s">
-        <v>1215</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>1216</v>
+        <v>1227</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="80" t="s">
-        <v>1217</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="80" t="s">
-        <v>1219</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="51" t="s">
-        <v>1220</v>
+        <v>1231</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="80" t="s">
-        <v>1221</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10186,7 +10311,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="80" t="s">
-        <v>1222</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10197,282 +10322,282 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="80" t="s">
-        <v>1223</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>1224</v>
+        <v>1235</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="80" t="s">
-        <v>1225</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>1226</v>
+        <v>1237</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="80" t="s">
-        <v>1227</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>1228</v>
+        <v>1239</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="80" t="s">
-        <v>1229</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="80" t="s">
-        <v>1230</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>1231</v>
+        <v>1242</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="80" t="s">
-        <v>1232</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>1233</v>
+        <v>1244</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="80" t="s">
-        <v>1234</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="80" t="s">
-        <v>1235</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>1236</v>
+        <v>1247</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="80" t="s">
-        <v>1237</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>1238</v>
+        <v>1249</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="80" t="s">
-        <v>1239</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>1240</v>
+        <v>1251</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="80" t="s">
-        <v>1241</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>1242</v>
+        <v>1253</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="80" t="s">
-        <v>1243</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>1244</v>
+        <v>1255</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="80" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>1246</v>
+        <v>1257</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="80" t="s">
-        <v>1247</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>1248</v>
+        <v>1259</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="80" t="s">
-        <v>1249</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="80" t="s">
-        <v>1251</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>1252</v>
+        <v>1263</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="80" t="s">
-        <v>1253</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="80" t="s">
-        <v>1255</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="51" t="s">
-        <v>1256</v>
+        <v>1267</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="80" t="s">
-        <v>1257</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>1258</v>
+        <v>1269</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="80" t="s">
-        <v>1259</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>1260</v>
+        <v>1271</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="80" t="s">
-        <v>1261</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>1262</v>
+        <v>1273</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="80" t="s">
-        <v>1263</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1264</v>
+        <v>1275</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="80" t="s">
-        <v>1265</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1266</v>
+        <v>1277</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="80" t="s">
-        <v>1267</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="80" t="s">
-        <v>1269</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="18" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="80" t="s">
-        <v>1270</v>
+        <v>1281</v>
       </c>
     </row>
   </sheetData>
@@ -15479,7 +15604,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="81" t="s">
         <v>701</v>
       </c>
@@ -15514,19 +15639,19 @@
         <v>710</v>
       </c>
       <c r="M13" s="82" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="N13" s="82" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="O13" s="82"/>
       <c r="P13" s="79" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="76" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C14" s="86" t="n">
         <f aca="false">C11*C12/1000</f>
@@ -15578,57 +15703,57 @@
       </c>
       <c r="O14" s="86"/>
       <c r="P14" s="80" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="81" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F15" s="82" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G15" s="82" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H15" s="82" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I15" s="82" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="J15" s="82" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L15" s="82" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M15" s="82" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N15" s="82" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O15" s="82"/>
       <c r="P15" s="79" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="81" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C16" s="87" t="n">
         <v>6</v>
@@ -15668,57 +15793,57 @@
       </c>
       <c r="O16" s="88"/>
       <c r="P16" s="80" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="81" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C17" s="82" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D17" s="82" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E17" s="82" t="s">
+        <v>732</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>732</v>
+      </c>
+      <c r="G17" s="82" t="s">
         <v>731</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="H17" s="82" t="s">
+        <v>733</v>
+      </c>
+      <c r="I17" s="82" t="s">
+        <v>734</v>
+      </c>
+      <c r="J17" s="82" t="s">
+        <v>735</v>
+      </c>
+      <c r="K17" s="82" t="s">
         <v>731</v>
       </c>
-      <c r="G17" s="82" t="s">
-        <v>730</v>
-      </c>
-      <c r="H17" s="82" t="s">
-        <v>732</v>
-      </c>
-      <c r="I17" s="82" t="s">
-        <v>733</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>734</v>
-      </c>
-      <c r="K17" s="82" t="s">
-        <v>730</v>
-      </c>
       <c r="L17" s="82" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M17" s="82" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N17" s="82" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O17" s="82"/>
       <c r="P17" s="79" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="76" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C18" s="89" t="n">
         <f aca="false">IFERROR(C14/C16,0)</f>
@@ -15770,102 +15895,102 @@
       </c>
       <c r="O18" s="89"/>
       <c r="P18" s="79" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="81" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C19" s="90" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E19" s="90" t="s">
+        <v>744</v>
+      </c>
+      <c r="F19" s="90" t="s">
+        <v>744</v>
+      </c>
+      <c r="G19" s="90" t="s">
         <v>743</v>
       </c>
-      <c r="F19" s="90" t="s">
+      <c r="H19" s="90" t="s">
         <v>743</v>
       </c>
-      <c r="G19" s="90" t="s">
-        <v>742</v>
-      </c>
-      <c r="H19" s="90" t="s">
-        <v>742</v>
-      </c>
       <c r="I19" s="90" t="s">
+        <v>744</v>
+      </c>
+      <c r="J19" s="90" t="s">
+        <v>744</v>
+      </c>
+      <c r="K19" s="90" t="s">
         <v>743</v>
       </c>
-      <c r="J19" s="90" t="s">
+      <c r="L19" s="90" t="s">
         <v>743</v>
       </c>
-      <c r="K19" s="90" t="s">
-        <v>742</v>
-      </c>
-      <c r="L19" s="90" t="s">
-        <v>742</v>
-      </c>
       <c r="M19" s="90" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N19" s="90" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O19" s="90"/>
       <c r="P19" s="79" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="81" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C20" s="82" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E20" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F20" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G20" s="82" t="s">
+        <v>749</v>
+      </c>
+      <c r="H20" s="82" t="s">
+        <v>749</v>
+      </c>
+      <c r="I20" s="82" t="s">
+        <v>750</v>
+      </c>
+      <c r="J20" s="82" t="s">
+        <v>751</v>
+      </c>
+      <c r="K20" s="82" t="s">
+        <v>749</v>
+      </c>
+      <c r="L20" s="78" t="s">
         <v>748</v>
       </c>
-      <c r="H20" s="82" t="s">
+      <c r="M20" s="78" t="s">
         <v>748</v>
       </c>
-      <c r="I20" s="78" t="s">
-        <v>747</v>
-      </c>
-      <c r="J20" s="82" t="s">
-        <v>749</v>
-      </c>
-      <c r="K20" s="82" t="s">
+      <c r="N20" s="78" t="s">
         <v>748</v>
-      </c>
-      <c r="L20" s="78" t="s">
-        <v>747</v>
-      </c>
-      <c r="M20" s="78" t="s">
-        <v>747</v>
-      </c>
-      <c r="N20" s="78" t="s">
-        <v>747</v>
       </c>
       <c r="O20" s="82"/>
       <c r="P20" s="79" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="81" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C21" s="88" t="n">
         <f aca="false">C11*C12*0.00452</f>
@@ -15891,8 +16016,7 @@
         <v>21.12</v>
       </c>
       <c r="I21" s="88" t="n">
-        <f aca="false">I11*I12*0.00452</f>
-        <v>29.38</v>
+        <v>25</v>
       </c>
       <c r="J21" s="88" t="n">
         <v>28</v>
@@ -15913,237 +16037,237 @@
       </c>
       <c r="O21" s="88"/>
       <c r="P21" s="80" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="81" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C22" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D22" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E22" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F22" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G22" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H22" s="82" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="I22" s="82" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="J22" s="82" t="s">
+        <v>758</v>
+      </c>
+      <c r="K22" s="82" t="s">
         <v>756</v>
       </c>
-      <c r="K22" s="82" t="s">
-        <v>754</v>
-      </c>
       <c r="L22" s="82" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="M22" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N22" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="O22" s="82"/>
       <c r="P22" s="80" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="81" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C23" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D23" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E23" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F23" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G23" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H23" s="82" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I23" s="82" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J23" s="82" t="s">
+        <v>765</v>
+      </c>
+      <c r="K23" s="82" t="s">
         <v>763</v>
       </c>
-      <c r="K23" s="82" t="s">
-        <v>761</v>
-      </c>
       <c r="L23" s="82" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="M23" s="82" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N23" s="82" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="O23" s="82"/>
       <c r="P23" s="80" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="81" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F24" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G24" s="78" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H24" s="82" t="s">
-        <v>768</v>
-      </c>
-      <c r="I24" s="78" t="s">
-        <v>747</v>
+        <v>770</v>
+      </c>
+      <c r="I24" s="82" t="s">
+        <v>771</v>
       </c>
       <c r="J24" s="82" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="K24" s="82" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="L24" s="82" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="M24" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N24" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="O24" s="82"/>
       <c r="P24" s="80" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="81" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C25" s="78" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D25" s="78" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E25" s="78" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="F25" s="78" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G25" s="78" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="H25" s="78" t="s">
-        <v>774</v>
-      </c>
-      <c r="I25" s="78" t="s">
-        <v>773</v>
+        <v>777</v>
+      </c>
+      <c r="I25" s="82" t="s">
+        <v>778</v>
       </c>
       <c r="J25" s="82" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="K25" s="78" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="L25" s="82" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="M25" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N25" s="82" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="O25" s="82"/>
       <c r="P25" s="79" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="81" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C26" s="82" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D26" s="82" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E26" s="82" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="F26" s="82" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G26" s="82" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="H26" s="82" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="I26" s="82" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="J26" s="82" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="K26" s="82" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="L26" s="82" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="M26" s="82" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="N26" s="82" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="O26" s="82"/>
       <c r="P26" s="80" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -16162,7 +16286,7 @@
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="81" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C29" s="91" t="n">
         <v>18228.7</v>
@@ -16204,12 +16328,12 @@
       </c>
       <c r="O29" s="92"/>
       <c r="P29" s="80" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="81" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C30" s="91" t="n">
         <v>0</v>
@@ -16249,12 +16373,12 @@
       </c>
       <c r="O30" s="92"/>
       <c r="P30" s="79" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="81" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C31" s="91" t="n">
         <v>790</v>
@@ -16294,12 +16418,12 @@
       </c>
       <c r="O31" s="92"/>
       <c r="P31" s="80" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="81" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C32" s="92" t="n">
         <f aca="false">6900/10*C11</f>
@@ -16341,12 +16465,12 @@
       </c>
       <c r="O32" s="92"/>
       <c r="P32" s="79" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="81" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C33" s="92" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -16373,8 +16497,7 @@
         <v>2500</v>
       </c>
       <c r="I33" s="92" t="n">
-        <f aca="false">ENTRADAS!$C$28</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="J33" s="92" t="n">
         <f aca="false">ENTRADAS!$C$28</f>
@@ -16389,21 +16512,19 @@
         <v>2500</v>
       </c>
       <c r="M33" s="92" t="n">
-        <f aca="false">ENTRADAS!$C$28</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="N33" s="92" t="n">
-        <f aca="false">ENTRADAS!$C$28</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="O33" s="92"/>
       <c r="P33" s="79" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="76" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C34" s="93" t="n">
         <f aca="false">SUM(C29:C33)</f>
@@ -16431,7 +16552,7 @@
       </c>
       <c r="I34" s="93" t="n">
         <f aca="false">SUM(I29:I33)</f>
-        <v>21080.54</v>
+        <v>18580.54</v>
       </c>
       <c r="J34" s="93" t="n">
         <f aca="false">SUM(J29:J33)</f>
@@ -16447,20 +16568,20 @@
       </c>
       <c r="M34" s="93" t="n">
         <f aca="false">SUM(M29:M33)</f>
-        <v>22880.54</v>
+        <v>20380.54</v>
       </c>
       <c r="N34" s="93" t="n">
         <f aca="false">SUM(N29:N33)</f>
-        <v>24680.54</v>
+        <v>22180.54</v>
       </c>
       <c r="O34" s="93"/>
       <c r="P34" s="80" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="76" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C35" s="94" t="n">
         <f aca="false">IFERROR(C34/(C14*1000),0)</f>
@@ -16488,7 +16609,7 @@
       </c>
       <c r="I35" s="94" t="n">
         <f aca="false">IFERROR(I34/(I14*1000),0)</f>
-        <v>3.24316</v>
+        <v>2.85854461538462</v>
       </c>
       <c r="J35" s="94" t="n">
         <f aca="false">IFERROR(J34/(J14*1000),0)</f>
@@ -16504,20 +16625,20 @@
       </c>
       <c r="M35" s="94" t="n">
         <f aca="false">IFERROR(M34/(M14*1000),0)</f>
-        <v>2.93340256410256</v>
+        <v>2.61288974358974</v>
       </c>
       <c r="N35" s="94" t="n">
         <f aca="false">IFERROR(N34/(N14*1000),0)</f>
-        <v>2.71214725274725</v>
+        <v>2.43742197802198</v>
       </c>
       <c r="O35" s="94"/>
       <c r="P35" s="80" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="81" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C36" s="95" t="n">
         <f aca="false">IFERROR(C29/(C14*1000),0)</f>
@@ -16528,44 +16649,44 @@
         <v>2.38400826446281</v>
       </c>
       <c r="E36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="F36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="G36" s="95" t="n">
         <f aca="false">IFERROR(G29/(G14*1000),0)</f>
         <v>2.08577757009346</v>
       </c>
       <c r="H36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="I36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="J36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="L36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="N36" s="95" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="O36" s="95"/>
       <c r="P36" s="80" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -16584,7 +16705,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="81" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C39" s="85" t="n">
         <f aca="false">C14*GERACAO!$I$17</f>
@@ -16636,12 +16757,12 @@
       </c>
       <c r="O39" s="85"/>
       <c r="P39" s="80" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="81" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C40" s="85" t="n">
         <f aca="false">C39/12</f>
@@ -16696,7 +16817,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="81" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C41" s="85" t="n">
         <f aca="false">C39/ENTRADAS!$C$31*ENTRADAS!$C$32</f>
@@ -16748,12 +16869,12 @@
       </c>
       <c r="O41" s="85"/>
       <c r="P41" s="80" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="81" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C42" s="84" t="n">
         <v>10554</v>
@@ -16793,12 +16914,12 @@
       </c>
       <c r="O42" s="85"/>
       <c r="P42" s="80" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="76" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C43" s="96" t="n">
         <f aca="false">IFERROR(C39/C42-1,0)</f>
@@ -16850,12 +16971,12 @@
       </c>
       <c r="O43" s="96"/>
       <c r="P43" s="79" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="81" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C44" s="85" t="n">
         <f aca="false">C14*GERACAO!$J$17</f>
@@ -16907,12 +17028,12 @@
       </c>
       <c r="O44" s="85"/>
       <c r="P44" s="80" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -16931,7 +17052,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="81" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C47" s="97" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$33*12),0)</f>
@@ -16983,12 +17104,12 @@
       </c>
       <c r="O47" s="97"/>
       <c r="P47" s="80" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="81" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C48" s="97" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$34*12),0)</f>
@@ -17043,7 +17164,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="76" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C49" s="98" t="n">
         <f aca="false">IFERROR(C39/(BYD!$F$35*12),0)</f>
@@ -17095,12 +17216,12 @@
       </c>
       <c r="O49" s="98"/>
       <c r="P49" s="80" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="81" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C50" s="85" t="n">
         <f aca="false">C39-BYD!$G$35</f>
@@ -17152,12 +17273,12 @@
       </c>
       <c r="O50" s="85"/>
       <c r="P50" s="80" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="76" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C51" s="99" t="n">
         <f aca="false">IFERROR(ROUNDUP(MAX(0,BYD!$G$35-C39)/GERACAO!$I$17*1000/C12,0),0)</f>
@@ -17212,7 +17333,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="76" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C52" s="100" t="n">
         <f aca="false">IFERROR(ROUNDUP(BYD!$C$13*12/GERACAO!$I$17*1000/C12,0),0)</f>
@@ -17264,12 +17385,12 @@
       </c>
       <c r="O52" s="100"/>
       <c r="P52" s="80" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="81" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C53" s="82" t="str">
         <f aca="false">C16&amp;" kW = "&amp;TEXT(C16*1000/220,"0")&amp;" A"</f>
@@ -17321,12 +17442,12 @@
       </c>
       <c r="O53" s="82"/>
       <c r="P53" s="79" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="7" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -17345,7 +17466,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="81" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C56" s="92" t="n">
         <f aca="false">CONTA!$C$54</f>
@@ -17397,12 +17518,12 @@
       </c>
       <c r="O56" s="92"/>
       <c r="P56" s="80" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="81" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C57" s="92" t="n">
         <f aca="false">ECONOMIA!C8/12</f>
@@ -17454,12 +17575,12 @@
       </c>
       <c r="O57" s="92"/>
       <c r="P57" s="80" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="76" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C58" s="101" t="n">
         <f aca="false">ECONOMIA!C19</f>
@@ -17511,12 +17632,12 @@
       </c>
       <c r="O58" s="101"/>
       <c r="P58" s="79" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="81" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C59" s="92" t="n">
         <f aca="false">ECONOMIA!C26</f>
@@ -17571,7 +17692,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="76" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C60" s="101" t="n">
         <f aca="false">C59/12</f>
@@ -17626,7 +17747,7 @@
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="76" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C61" s="102" t="n">
         <f aca="false">IFERROR(C34/C59,0)</f>
@@ -17654,7 +17775,7 @@
       </c>
       <c r="I61" s="102" t="n">
         <f aca="false">IFERROR(I34/I59,0)</f>
-        <v>3.51304653337567</v>
+        <v>3.0964245524663</v>
       </c>
       <c r="J61" s="102" t="n">
         <f aca="false">IFERROR(J34/J59,0)</f>
@@ -17670,20 +17791,20 @@
       </c>
       <c r="M61" s="102" t="n">
         <f aca="false">IFERROR(M34/M59,0)</f>
-        <v>3.81301435963041</v>
+        <v>3.39639237872105</v>
       </c>
       <c r="N61" s="102" t="n">
         <f aca="false">IFERROR(N34/N59,0)</f>
-        <v>4.11298218588516</v>
+        <v>3.69636020497579</v>
       </c>
       <c r="O61" s="102"/>
       <c r="P61" s="80" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="81" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C62" s="103" t="n">
         <f aca="false">PROJECAO!E10</f>
@@ -17738,7 +17859,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="81" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C63" s="103" t="n">
         <f aca="false">PROJECAO!E15</f>
@@ -17793,7 +17914,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="81" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C64" s="103" t="n">
         <f aca="false">PROJECAO!E25</f>
@@ -17848,7 +17969,7 @@
     </row>
     <row r="65" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="76" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C65" s="104" t="n">
         <f aca="false">C64-C34</f>
@@ -17876,7 +17997,7 @@
       </c>
       <c r="I65" s="104" t="n">
         <f aca="false">I64-I34</f>
-        <v>212363.876896246</v>
+        <v>214863.876896246</v>
       </c>
       <c r="J65" s="104" t="n">
         <f aca="false">J64-J34</f>
@@ -17892,20 +18013,20 @@
       </c>
       <c r="M65" s="104" t="n">
         <f aca="false">M64-M34</f>
-        <v>210563.876896246</v>
+        <v>213063.876896246</v>
       </c>
       <c r="N65" s="104" t="n">
         <f aca="false">N64-N34</f>
-        <v>208763.876896246</v>
+        <v>211263.876896246</v>
       </c>
       <c r="O65" s="104"/>
       <c r="P65" s="80" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="81" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C66" s="97" t="n">
         <f aca="false">IFERROR(C65/C34,0)</f>
@@ -17933,7 +18054,7 @@
       </c>
       <c r="I66" s="97" t="n">
         <f aca="false">IFERROR(I65/I34,0)</f>
-        <v>10.0739296477341</v>
+        <v>11.5639199343101</v>
       </c>
       <c r="J66" s="97" t="n">
         <f aca="false">IFERROR(J65/J34,0)</f>
@@ -17949,18 +18070,18 @@
       </c>
       <c r="M66" s="97" t="n">
         <f aca="false">IFERROR(M65/M34,0)</f>
-        <v>9.20274944980519</v>
+        <v>10.4542802544116</v>
       </c>
       <c r="N66" s="97" t="n">
         <f aca="false">IFERROR(N65/N34,0)</f>
-        <v>8.45864299955534</v>
+        <v>9.52474001517752</v>
       </c>
       <c r="O66" s="97"/>
       <c r="P66" s="80"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="7" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -17979,7 +18100,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="81" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C69" s="88" t="n">
         <f aca="false">C16*1.35</f>
@@ -18034,7 +18155,7 @@
     </row>
     <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="76" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C70" s="99" t="n">
         <f aca="false">MAX(0,ROUNDDOWN((C69-C14)*1000/C12,0))</f>
@@ -18086,57 +18207,57 @@
       </c>
       <c r="O70" s="99"/>
       <c r="P70" s="79" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="81" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D71" s="82" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E71" s="82" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F71" s="82" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="G71" s="82" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="H71" s="82" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="I71" s="82" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="J71" s="82" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="K71" s="82" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="L71" s="82" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="M71" s="82" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="N71" s="82" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="O71" s="82"/>
       <c r="P71" s="80" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="81" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C72" s="85" t="n">
         <f aca="false">C70*C12/1000*GERACAO!$I$17</f>
@@ -18191,7 +18312,7 @@
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="76" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C73" s="77" t="str">
         <f aca="false">IF(C18&gt;1.35,"JA SOBRECARREGADO",IF(C18&lt;1.1,"SUBAPROVEITADO","OK"))</f>
@@ -18243,12 +18364,12 @@
       </c>
       <c r="O73" s="77"/>
       <c r="P73" s="80" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="7" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -18267,7 +18388,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="21" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C76" s="35" t="n">
         <f aca="false">F29-E29</f>
@@ -18276,7 +18397,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C77" s="29" t="n">
         <f aca="false">IFERROR(F61-E61,0)</f>
@@ -18285,7 +18406,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C78" s="105" t="n">
         <f aca="false">F65-E65</f>
@@ -18294,22 +18415,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="4" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18317,12 +18438,12 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
   </sheetData>
@@ -18352,12 +18473,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18365,312 +18486,312 @@
         <v>628</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="F5" s="106" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F6" s="106" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D7" s="54" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="F7" s="107" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="F8" s="106" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="F9" s="106" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="F10" s="106" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F11" s="107" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="F12" s="106" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D13" s="108" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="F13" s="107" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E14" s="54" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="F14" s="106" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C15" s="108" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E15" s="54" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F15" s="107" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E16" s="54" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="F16" s="106" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C17" s="108" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D17" s="108" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="F17" s="107" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D18" s="108" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E18" s="54" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="F18" s="107" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E19" s="54" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="F19" s="106" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E20" s="54" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="F20" s="106" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>17344.82</v>
@@ -18684,7 +18805,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>732.44</v>
@@ -18698,7 +18819,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>151.44</v>
@@ -18712,7 +18833,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0</v>
@@ -18726,7 +18847,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">SUM(C24:C27)</f>
@@ -18743,7 +18864,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C30" s="47" t="n">
         <f aca="false">COMPARATIVO!C14</f>
@@ -18760,7 +18881,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C31" s="109" t="n">
         <f aca="false">IFERROR(C28/(C30*1000),0)</f>
@@ -18777,44 +18898,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C34" s="110" t="n">
         <f aca="false">IFERROR(7690/E28,0)</f>
         <v>0.689135408386661</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">C28+790+6900/10*12</f>
         <v>27298.7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">C28-D28</f>
@@ -18823,7 +18944,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">COMPARATIVO!C39-COMPARATIVO!D39</f>
@@ -18832,7 +18953,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">C39*ENTRADAS!C18</f>
@@ -18841,14 +18962,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C41" s="36" t="n">
         <f aca="false">IFERROR(C38/C40,0)</f>
         <v>5.94181274517766</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
   </sheetData>
@@ -18878,64 +18999,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -18987,12 +19108,12 @@
       </c>
       <c r="O5" s="111"/>
       <c r="P5" s="80" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">COMPARATIVO!C39</f>
@@ -19044,12 +19165,12 @@
       </c>
       <c r="O6" s="111"/>
       <c r="P6" s="80" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C7" s="112" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -19101,12 +19222,12 @@
       </c>
       <c r="O7" s="111"/>
       <c r="P7" s="80" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="113" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
@@ -19158,12 +19279,12 @@
       </c>
       <c r="O8" s="111"/>
       <c r="P8" s="80" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -19215,12 +19336,12 @@
       </c>
       <c r="O9" s="111"/>
       <c r="P9" s="80" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">C6-C9</f>
@@ -19272,12 +19393,12 @@
       </c>
       <c r="O10" s="111"/>
       <c r="P10" s="80" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -19329,12 +19450,12 @@
       </c>
       <c r="O11" s="111"/>
       <c r="P11" s="80" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -19386,12 +19507,12 @@
       </c>
       <c r="O12" s="111"/>
       <c r="P12" s="80" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">C10-C12</f>
@@ -19443,12 +19564,12 @@
       </c>
       <c r="O13" s="111"/>
       <c r="P13" s="80" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -19500,12 +19621,12 @@
       </c>
       <c r="O14" s="111"/>
       <c r="P14" s="80" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C15" s="112" t="n">
         <f aca="false">C14*C7</f>
@@ -19560,7 +19681,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C16" s="112" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -19612,12 +19733,12 @@
       </c>
       <c r="O16" s="111"/>
       <c r="P16" s="80" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C17" s="112" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -19669,12 +19790,12 @@
       </c>
       <c r="O17" s="111"/>
       <c r="P17" s="80" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C18" s="50" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -19726,12 +19847,12 @@
       </c>
       <c r="O18" s="111"/>
       <c r="P18" s="80" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">C18/12</f>
@@ -19783,12 +19904,12 @@
       </c>
       <c r="O19" s="111"/>
       <c r="P19" s="80" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C20" s="40" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -19843,7 +19964,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C21" s="112" t="n">
         <f aca="false">C8-C18</f>
@@ -19898,7 +20019,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C22" s="112" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -19950,12 +20071,12 @@
       </c>
       <c r="O22" s="111"/>
       <c r="P22" s="80" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C23" s="112" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -20007,12 +20128,12 @@
       </c>
       <c r="O23" s="111"/>
       <c r="P23" s="80" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C24" s="112" t="n">
         <f aca="false">0</f>
@@ -20064,12 +20185,12 @@
       </c>
       <c r="O24" s="111"/>
       <c r="P24" s="80" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C25" s="112" t="n">
         <f aca="false">C22+C23</f>
@@ -20124,7 +20245,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C26" s="114" t="n">
         <f aca="false">C21-C25</f>
@@ -20176,12 +20297,12 @@
       </c>
       <c r="O26" s="111"/>
       <c r="P26" s="80" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -20200,31 +20321,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4221.92511679644</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>6921.92511679644</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
@@ -20236,86 +20357,86 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.639518685269514</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4565.88984905406</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7323.85884905406</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2757.969</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>579.72996</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>2178.23904</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1413">
   <si>
     <t xml:space="preserve">COMPARATIVO DE ORCAMENTOS - ENERGIA SOLAR + CARREGAMENTO DE BYD HIBRIDO</t>
   </si>
@@ -2652,7 +2652,7 @@
     <t xml:space="preserve">5 modulos</t>
   </si>
   <si>
-    <t xml:space="preserve">2 a 3 modulos</t>
+    <t xml:space="preserve">4 modulos - o 6KTL-L1 aceita ate 9.000 Wp</t>
   </si>
   <si>
     <t xml:space="preserve">0 - os 12 canais ficam cheios</t>
@@ -3213,6 +3213,174 @@
     <t xml:space="preserve">deste mesmo pedido deve ser sensivelmente menor. PECA O PRECO A VISTA (PIX) ANTES DE COMPARAR.</t>
   </si>
   <si>
+    <t xml:space="preserve">COMPARACAO DIRETA: YURI (R$ 16.780) x AD BIOSOLAR (R$ 16.200) - MESMO ESCOPO?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que esta incluido no preco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YURI / SunWash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comentario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preco anunciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 16.780,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 16.200,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferenca de apenas R$ 580 - mas nao sao a mesma coisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natureza do preco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATERIAL (pedido Route 66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURNKEY (projeto completo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O pedido do Yuri esta no CPF do cliente, nao no da empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modulos e inversor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x ZNShine 650 W + 3 micros Deye  x  10x JA Solar 615 W + Huawei 6 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estrutura de telhado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambos para telha colonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo CA, disjuntor, DPS, quadro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM (montagem eletrica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausentes no pedido Route 66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aterramento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vistoria tecnica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto eletrico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART do projeto e da instalacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem ART nao ha homologacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologacao junto a Enel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalacao e montagem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestao e fiscalizacao de obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frete ate a residencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAO - retirada em Jundiai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jundiai fica a ~60 km do Tucuruvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentacao do projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padrao de entrada mono -&gt; bifasico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS DOIS EXCLUEM. Somar cerca de R$ 2.500 nos dois casos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUSTO DE MATERIAL DA AD BIOSOLAR A PRECO DE VAREJO (para testar se R$ 16.200 fecha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modulo JA Solar JAM66-D45-615LB 615 W bifacial N-type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATIVA de varejo. Modulo vidro-vidro premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor Huawei SUN2000-6KTL-L1 6 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECO REAL de varejo no PIX (Meu Gerador, ago/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estrutura telha colonial + perfis para 10 modulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATIVA, mesma base do pedido Route 66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabos CC e CA, MC4, string box, DPS e disjuntor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATERIAL A PRECO DE VAREJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desconto tipico de distribuidor sobre o varejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATERIAL AO CUSTO PROVAVEL DA EMPRESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preco de venda da AD BioSolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOBRA PARA SERVICOS (projeto, ART, instalacao, homologacao, frete)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEITURA DESTE TESTE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se a AD BioSolar comprasse no varejo, o material sozinho custaria mais que o preco de venda dela - o negocio nao fecharia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprando com desconto tipico de distribuidor (20%), sobra algo em torno de R$ 3.500 para cobrir vistoria, projeto, ART,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instalacao de 10 modulos, homologacao, gestao de obra e frete. E APERTADO, MAS POSSIVEL para uma operacao enxuta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusao: os R$ 16.200 sao agressivos e plausiveis - nao sao impossiveis. Mas justamente por serem apertados, exija o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escopo por escrito e pergunte se a equipe de instalacao e propria ou terceirizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E O PONTO PRINCIPAL DA COMPARACAO: por R$ 580 A MENOS que o Yuri, a AD BioSolar entrega o mesmo material MAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projeto, ART, instalacao, homologacao, frete e montagem eletrica completa. Nao e uma disputa de preco - e de escopo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">MODELO DE ECONOMIA - ANO 1, PELAS REGRAS DA LEI 14.300/2022</t>
   </si>
   <si>
@@ -3723,7 +3891,16 @@
     <t xml:space="preserve">O DESCONTO DE R$ 5.089 PRECISA ESTAR NO PAPEL. O PDF #01237 traz R$ 21.289,00; o valor de R$ 16.200,00 veio da negociacao. Sao 24% de desconto. Exigir proposta reemitida com o valor final, ou o desconto pode nao existir na assinatura.</t>
   </si>
   <si>
-    <t xml:space="preserve">VERIFICACAO OBRIGATORIA NA AD BIOSOLAR: 10 modulos JA Solar de 615 W em um SUN2000-6KTL-L1 de 2 MPPTs dao 5 modulos por string. Confirmar na ficha tecnica do inversor a corrente maxima de entrada por MPPT e comparar com o Impp do modulo (~16 A). Se a do inversor for menor, perde-se geracao nas melhores horas. Pedir tambem a tensao da string nas temperaturas extremas.</t>
+    <t xml:space="preserve">CONFIRMADO POR FICHA TECNICA - INCOMPATIBILIDADE DE CORRENTE NA AD BIOSOLAR: o Huawei SUN2000-6KTL-L1 aceita no maximo 13,5 A por MPPT. O modulo JA Solar JAM66-D45-615LB tem Impp de 15,39 A e Isc de 16,1 A. A corrente do modulo excede a do inversor em cerca de 14%. Nao e problema de seguranca (o Isc cabe), mas o inversor nao consegue extrair toda a corrente nos momentos de maior irradiancia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIMENSAO REAL DESSA PERDA: o limite so passa a atuar quando a irradiancia no plano dos modulos ultrapassa cerca de 88% de 1.000 W/m2. No seu telhado Sudeste isso acontece em poucas horas do ano, entao a perda anual de energia deve ficar entre 1% e 3% - incomoda, mas nao inviabiliza. O que ela revela e mais grave que o numero: NINGUEM FEZ PROJETO DE STRING. Um projetista teria visto isso na primeira conferencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O QUE COBRAR DA AD BIOSOLAR: peca que expliquem essa diferenca e apresentem uma das saidas - (a) trocar por modulo de 144 meias-celulas com Impp em torno de 13,7 A, que casa com o inversor; (b) trocar o inversor por um modelo com corrente maior por MPPT; ou (c) assumir por escrito a perda estimada. Bonus: o 6KTL-L1 aceita ate 9.000 Wp, ou seja, ainda cabem 4 modulos de 615 W para expansao futura.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESSA MESMA CONTA VALE PARA AS OPCOES A e B (TecSolarSP, Huawei 6 kW com modulos de 615 e 605 W) e provavelmente para C, D e I. NAO se aplica a proposta do Yuri: o micro Deye SUN-M225G4-EU-Q0 aceita 18 A por MPPT e modulos de ate 790 W, com folga sobre os 15,39 A.</t>
   </si>
   <si>
     <t xml:space="preserve">NUMEROS DE MARKETING DA AD BIOSOLAR: 'Economia total em 25 anos R$ 419.713,53', 'ROI 24,06 vezes' e 'TIR 35,81%' usam reajuste de energia de 10% ao ano composto por 25 anos. Ignore. Alem disso a 'conta COM sistema de R$ 75,31/mes' vale para 460 kWh/mes SEM o carro - com o BYD o meu modelo da cerca de R$ 259/mes nessa potencia.</t>
@@ -4370,7 +4547,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4843,6 +5020,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5560,3208 +5745,3208 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1126</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1127</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1128</v>
+        <v>1184</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1129</v>
+        <v>1185</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1130</v>
+        <v>1186</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1131</v>
+        <v>1187</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1132</v>
+        <v>1188</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>1133</v>
+        <v>1189</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>1134</v>
+        <v>1190</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>1135</v>
+        <v>1191</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>1136</v>
+        <v>1192</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>1137</v>
+        <v>1193</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>1138</v>
+        <v>1194</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>1139</v>
+        <v>1195</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>1140</v>
+        <v>1196</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>1141</v>
+        <v>1197</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>1142</v>
+        <v>1198</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>1143</v>
+        <v>1199</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>1144</v>
+        <v>1200</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>1145</v>
+        <v>1201</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>1147</v>
+        <v>1203</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>1149</v>
+        <v>1205</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>1150</v>
+        <v>1206</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>1151</v>
+        <v>1207</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>1152</v>
+        <v>1208</v>
       </c>
       <c r="AA4" s="17" t="s">
-        <v>1153</v>
+        <v>1209</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>1154</v>
+        <v>1210</v>
       </c>
       <c r="AC4" s="17" t="s">
-        <v>1155</v>
+        <v>1211</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>1156</v>
+        <v>1212</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>1157</v>
+        <v>1213</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>1158</v>
+        <v>1214</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>1159</v>
+        <v>1215</v>
       </c>
       <c r="AH4" s="17" t="s">
-        <v>1160</v>
+        <v>1216</v>
       </c>
       <c r="AI4" s="17" t="s">
-        <v>1161</v>
+        <v>1217</v>
       </c>
       <c r="AJ4" s="17" t="s">
-        <v>1162</v>
+        <v>1218</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>1163</v>
+        <v>1219</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="AM4" s="17" t="s">
-        <v>1165</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="120" t="n">
+      <c r="B6" s="122" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(1-1)</f>
         <v>0.98</v>
       </c>
-      <c r="D6" s="121" t="n">
+      <c r="D6" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="E6" s="121" t="n">
+      <c r="E6" s="123" t="n">
         <f aca="false">D6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="F6" s="121" t="n">
+      <c r="F6" s="123" t="n">
         <f aca="false">E6-COMPARATIVO!C$34</f>
         <v>-23798.0564560775</v>
       </c>
-      <c r="G6" s="121" t="n">
+      <c r="G6" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="H6" s="121" t="n">
+      <c r="H6" s="123" t="n">
         <f aca="false">G6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="I6" s="121" t="n">
+      <c r="I6" s="123" t="n">
         <f aca="false">H6-COMPARATIVO!D$34</f>
         <v>-22877.2564560775</v>
       </c>
-      <c r="J6" s="121" t="n">
+      <c r="J6" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="K6" s="121" t="n">
+      <c r="K6" s="123" t="n">
         <f aca="false">J6</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="L6" s="121" t="n">
+      <c r="L6" s="123" t="n">
         <f aca="false">K6-COMPARATIVO!E$34</f>
         <v>-12527.5386639178</v>
       </c>
-      <c r="M6" s="121" t="n">
+      <c r="M6" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="N6" s="121" t="n">
+      <c r="N6" s="123" t="n">
         <f aca="false">M6</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="O6" s="121" t="n">
+      <c r="O6" s="123" t="n">
         <f aca="false">N6-COMPARATIVO!F$34</f>
         <v>-13527.5386639178</v>
       </c>
-      <c r="P6" s="121" t="n">
+      <c r="P6" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>5442.45129401962</v>
       </c>
-      <c r="Q6" s="121" t="n">
+      <c r="Q6" s="123" t="n">
         <f aca="false">P6</f>
         <v>5442.45129401962</v>
       </c>
-      <c r="R6" s="121" t="n">
+      <c r="R6" s="123" t="n">
         <f aca="false">Q6-COMPARATIVO!G$34</f>
         <v>-15906.4587059804</v>
       </c>
-      <c r="S6" s="121" t="n">
+      <c r="S6" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="T6" s="121" t="n">
+      <c r="T6" s="123" t="n">
         <f aca="false">S6</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="U6" s="121" t="n">
+      <c r="U6" s="123" t="n">
         <f aca="false">T6-COMPARATIVO!H$34</f>
         <v>-10183.1218586894</v>
       </c>
-      <c r="V6" s="121" t="n">
+      <c r="V6" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="W6" s="121" t="n">
+      <c r="W6" s="123" t="n">
         <f aca="false">V6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="X6" s="121" t="n">
+      <c r="X6" s="123" t="n">
         <f aca="false">W6-COMPARATIVO!I$34</f>
         <v>-21659.8364560775</v>
       </c>
-      <c r="Y6" s="121" t="n">
+      <c r="Y6" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>5968.37018228556</v>
       </c>
-      <c r="Z6" s="121" t="n">
+      <c r="Z6" s="123" t="n">
         <f aca="false">Y6</f>
         <v>5968.37018228556</v>
       </c>
-      <c r="AA6" s="121" t="n">
+      <c r="AA6" s="123" t="n">
         <f aca="false">Z6-COMPARATIVO!J$34</f>
         <v>-15264.6298177144</v>
       </c>
-      <c r="AB6" s="121" t="n">
+      <c r="AB6" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AC6" s="121" t="n">
+      <c r="AC6" s="123" t="n">
         <f aca="false">AB6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AD6" s="121" t="n">
+      <c r="AD6" s="123" t="n">
         <f aca="false">AC6-COMPARATIVO!K$34</f>
         <v>-13389.3564560775</v>
       </c>
-      <c r="AE6" s="121" t="n">
+      <c r="AE6" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>5988.72947711613</v>
       </c>
-      <c r="AF6" s="121" t="n">
+      <c r="AF6" s="123" t="n">
         <f aca="false">AE6</f>
         <v>5988.72947711613</v>
       </c>
-      <c r="AG6" s="121" t="n">
+      <c r="AG6" s="123" t="n">
         <f aca="false">AF6-COMPARATIVO!L$34</f>
         <v>-12711.2705228839</v>
       </c>
-      <c r="AH6" s="121" t="n">
+      <c r="AH6" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AI6" s="121" t="n">
+      <c r="AI6" s="123" t="n">
         <f aca="false">AH6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AJ6" s="121" t="n">
+      <c r="AJ6" s="123" t="n">
         <f aca="false">AI6-COMPARATIVO!M$34</f>
         <v>-23459.8364560775</v>
       </c>
-      <c r="AK6" s="121" t="n">
+      <c r="AK6" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C6/$C$6*(1+ENTRADAS!$C$27)^(1-1)</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AL6" s="121" t="n">
+      <c r="AL6" s="123" t="n">
         <f aca="false">AK6</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="AM6" s="121" t="n">
+      <c r="AM6" s="123" t="n">
         <f aca="false">AL6-COMPARATIVO!N$34</f>
         <v>-25259.8364560775</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="120" t="n">
+      <c r="B7" s="122" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(2-1)</f>
         <v>0.97559</v>
       </c>
-      <c r="D7" s="121" t="n">
+      <c r="D7" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="E7" s="121" t="n">
+      <c r="E7" s="123" t="n">
         <f aca="false">E6+D7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="F7" s="121" t="n">
+      <c r="F7" s="123" t="n">
         <f aca="false">E7-COMPARATIVO!C$34</f>
         <v>-17406.2609627444</v>
       </c>
-      <c r="G7" s="121" t="n">
+      <c r="G7" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="H7" s="121" t="n">
+      <c r="H7" s="123" t="n">
         <f aca="false">H6+G7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="I7" s="121" t="n">
+      <c r="I7" s="123" t="n">
         <f aca="false">H7-COMPARATIVO!D$34</f>
         <v>-16485.4609627444</v>
       </c>
-      <c r="J7" s="121" t="n">
+      <c r="J7" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6383.44209117476</v>
       </c>
-      <c r="K7" s="121" t="n">
+      <c r="K7" s="123" t="n">
         <f aca="false">K6+J7</f>
         <v>12376.243427257</v>
       </c>
-      <c r="L7" s="121" t="n">
+      <c r="L7" s="123" t="n">
         <f aca="false">K7-COMPARATIVO!E$34</f>
         <v>-6144.09657274299</v>
       </c>
-      <c r="M7" s="121" t="n">
+      <c r="M7" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6383.44209117476</v>
       </c>
-      <c r="N7" s="121" t="n">
+      <c r="N7" s="123" t="n">
         <f aca="false">N6+M7</f>
         <v>12376.243427257</v>
       </c>
-      <c r="O7" s="121" t="n">
+      <c r="O7" s="123" t="n">
         <f aca="false">N7-COMPARATIVO!F$34</f>
         <v>-7144.09657274299</v>
       </c>
-      <c r="P7" s="121" t="n">
+      <c r="P7" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>5797.21748162029</v>
       </c>
-      <c r="Q7" s="121" t="n">
+      <c r="Q7" s="123" t="n">
         <f aca="false">Q6+P7</f>
         <v>11239.6687756399</v>
       </c>
-      <c r="R7" s="121" t="n">
+      <c r="R7" s="123" t="n">
         <f aca="false">Q7-COMPARATIVO!G$34</f>
         <v>-10109.2412243601</v>
       </c>
-      <c r="S7" s="121" t="n">
+      <c r="S7" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>5011.18215635195</v>
       </c>
-      <c r="T7" s="121" t="n">
+      <c r="T7" s="123" t="n">
         <f aca="false">T6+S7</f>
         <v>9715.70029766257</v>
       </c>
-      <c r="U7" s="121" t="n">
+      <c r="U7" s="123" t="n">
         <f aca="false">T7-COMPARATIVO!H$34</f>
         <v>-5171.93970233743</v>
       </c>
-      <c r="V7" s="121" t="n">
+      <c r="V7" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="W7" s="121" t="n">
+      <c r="W7" s="123" t="n">
         <f aca="false">W6+V7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="X7" s="121" t="n">
+      <c r="X7" s="123" t="n">
         <f aca="false">W7-COMPARATIVO!I$34</f>
         <v>-15268.0409627444</v>
       </c>
-      <c r="Y7" s="121" t="n">
+      <c r="Y7" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6357.41839261784</v>
       </c>
-      <c r="Z7" s="121" t="n">
+      <c r="Z7" s="123" t="n">
         <f aca="false">Z6+Y7</f>
         <v>12325.7885749034</v>
       </c>
-      <c r="AA7" s="121" t="n">
+      <c r="AA7" s="123" t="n">
         <f aca="false">Z7-COMPARATIVO!J$34</f>
         <v>-8907.21142509661</v>
       </c>
-      <c r="AB7" s="121" t="n">
+      <c r="AB7" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="AC7" s="121" t="n">
+      <c r="AC7" s="123" t="n">
         <f aca="false">AC6+AB7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="AD7" s="121" t="n">
+      <c r="AD7" s="123" t="n">
         <f aca="false">AC7-COMPARATIVO!K$34</f>
         <v>-6997.56096274443</v>
       </c>
-      <c r="AE7" s="121" t="n">
+      <c r="AE7" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6379.10480808194</v>
       </c>
-      <c r="AF7" s="121" t="n">
+      <c r="AF7" s="123" t="n">
         <f aca="false">AF6+AE7</f>
         <v>12367.8342851981</v>
       </c>
-      <c r="AG7" s="121" t="n">
+      <c r="AG7" s="123" t="n">
         <f aca="false">AF7-COMPARATIVO!L$34</f>
         <v>-6332.16571480193</v>
       </c>
-      <c r="AH7" s="121" t="n">
+      <c r="AH7" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="AI7" s="121" t="n">
+      <c r="AI7" s="123" t="n">
         <f aca="false">AI6+AH7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="AJ7" s="121" t="n">
+      <c r="AJ7" s="123" t="n">
         <f aca="false">AI7-COMPARATIVO!M$34</f>
         <v>-17068.0409627444</v>
       </c>
-      <c r="AK7" s="121" t="n">
+      <c r="AK7" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C7/$C$6*(1+ENTRADAS!$C$27)^(2-1)</f>
         <v>6391.79549333308</v>
       </c>
-      <c r="AL7" s="121" t="n">
+      <c r="AL7" s="123" t="n">
         <f aca="false">AL6+AK7</f>
         <v>12392.4390372556</v>
       </c>
-      <c r="AM7" s="121" t="n">
+      <c r="AM7" s="123" t="n">
         <f aca="false">AL7-COMPARATIVO!N$34</f>
         <v>-18868.0409627444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="120" t="n">
+      <c r="B8" s="122" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(3-1)</f>
         <v>0.971199845</v>
       </c>
-      <c r="D8" s="121" t="n">
+      <c r="D8" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="E8" s="121" t="n">
+      <c r="E8" s="123" t="n">
         <f aca="false">E7+D8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="F8" s="121" t="n">
+      <c r="F8" s="123" t="n">
         <f aca="false">E8-COMPARATIVO!C$34</f>
         <v>-10597.8162801784</v>
       </c>
-      <c r="G8" s="121" t="n">
+      <c r="G8" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="H8" s="121" t="n">
+      <c r="H8" s="123" t="n">
         <f aca="false">H7+G8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="I8" s="121" t="n">
+      <c r="I8" s="123" t="n">
         <f aca="false">H8-COMPARATIVO!D$34</f>
         <v>-9677.01628017843</v>
       </c>
-      <c r="J8" s="121" t="n">
+      <c r="J8" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6799.54676388799</v>
       </c>
-      <c r="K8" s="121" t="n">
+      <c r="K8" s="123" t="n">
         <f aca="false">K7+J8</f>
         <v>19175.790191145</v>
       </c>
-      <c r="L8" s="121" t="n">
+      <c r="L8" s="123" t="n">
         <f aca="false">K8-COMPARATIVO!E$34</f>
         <v>655.450191144995</v>
       </c>
-      <c r="M8" s="121" t="n">
+      <c r="M8" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6799.54676388799</v>
       </c>
-      <c r="N8" s="121" t="n">
+      <c r="N8" s="123" t="n">
         <f aca="false">N7+M8</f>
         <v>19175.790191145</v>
       </c>
-      <c r="O8" s="121" t="n">
+      <c r="O8" s="123" t="n">
         <f aca="false">N8-COMPARATIVO!F$34</f>
         <v>-344.549808855005</v>
       </c>
-      <c r="P8" s="121" t="n">
+      <c r="P8" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6175.10910315971</v>
       </c>
-      <c r="Q8" s="121" t="n">
+      <c r="Q8" s="123" t="n">
         <f aca="false">Q7+P8</f>
         <v>17414.7778787996</v>
       </c>
-      <c r="R8" s="121" t="n">
+      <c r="R8" s="123" t="n">
         <f aca="false">Q8-COMPARATIVO!G$34</f>
         <v>-3934.13212120039</v>
       </c>
-      <c r="S8" s="121" t="n">
+      <c r="S8" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>5337.83606521376</v>
       </c>
-      <c r="T8" s="121" t="n">
+      <c r="T8" s="123" t="n">
         <f aca="false">T7+S8</f>
         <v>15053.5363628763</v>
       </c>
-      <c r="U8" s="121" t="n">
+      <c r="U8" s="123" t="n">
         <f aca="false">T8-COMPARATIVO!H$34</f>
         <v>165.89636287633</v>
       </c>
-      <c r="V8" s="121" t="n">
+      <c r="V8" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="W8" s="121" t="n">
+      <c r="W8" s="123" t="n">
         <f aca="false">W7+V8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="X8" s="121" t="n">
+      <c r="X8" s="123" t="n">
         <f aca="false">W8-COMPARATIVO!I$34</f>
         <v>-8459.59628017843</v>
       </c>
-      <c r="Y8" s="121" t="n">
+      <c r="Y8" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6771.82671054063</v>
       </c>
-      <c r="Z8" s="121" t="n">
+      <c r="Z8" s="123" t="n">
         <f aca="false">Z7+Y8</f>
         <v>19097.615285444</v>
       </c>
-      <c r="AA8" s="121" t="n">
+      <c r="AA8" s="123" t="n">
         <f aca="false">Z8-COMPARATIVO!J$34</f>
         <v>-2135.38471455597</v>
       </c>
-      <c r="AB8" s="121" t="n">
+      <c r="AB8" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="AC8" s="121" t="n">
+      <c r="AC8" s="123" t="n">
         <f aca="false">AC7+AB8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="AD8" s="121" t="n">
+      <c r="AD8" s="123" t="n">
         <f aca="false">AC8-COMPARATIVO!K$34</f>
         <v>-189.11628017843</v>
       </c>
-      <c r="AE8" s="121" t="n">
+      <c r="AE8" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6794.92675499676</v>
       </c>
-      <c r="AF8" s="121" t="n">
+      <c r="AF8" s="123" t="n">
         <f aca="false">AF7+AE8</f>
         <v>19162.7610401948</v>
       </c>
-      <c r="AG8" s="121" t="n">
+      <c r="AG8" s="123" t="n">
         <f aca="false">AF8-COMPARATIVO!L$34</f>
         <v>462.761040194833</v>
       </c>
-      <c r="AH8" s="121" t="n">
+      <c r="AH8" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="AI8" s="121" t="n">
+      <c r="AI8" s="123" t="n">
         <f aca="false">AI7+AH8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="AJ8" s="121" t="n">
+      <c r="AJ8" s="123" t="n">
         <f aca="false">AI8-COMPARATIVO!M$34</f>
         <v>-10259.5962801784</v>
       </c>
-      <c r="AK8" s="121" t="n">
+      <c r="AK8" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C8/$C$6*(1+ENTRADAS!$C$27)^(3-1)</f>
         <v>6808.444682566</v>
       </c>
-      <c r="AL8" s="121" t="n">
+      <c r="AL8" s="123" t="n">
         <f aca="false">AL7+AK8</f>
         <v>19200.8837198216</v>
       </c>
-      <c r="AM8" s="121" t="n">
+      <c r="AM8" s="123" t="n">
         <f aca="false">AL8-COMPARATIVO!N$34</f>
         <v>-12059.5962801784</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="120" t="n">
+      <c r="B9" s="122" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(4-1)</f>
         <v>0.9668294456975</v>
       </c>
-      <c r="D9" s="121" t="n">
+      <c r="D9" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="E9" s="121" t="n">
+      <c r="E9" s="123" t="n">
         <f aca="false">E8+D9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="F9" s="121" t="n">
+      <c r="F9" s="123" t="n">
         <f aca="false">E9-COMPARATIVO!C$34</f>
         <v>-3345.56313097937</v>
       </c>
-      <c r="G9" s="121" t="n">
+      <c r="G9" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="H9" s="121" t="n">
+      <c r="H9" s="123" t="n">
         <f aca="false">H8+G9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="I9" s="121" t="n">
+      <c r="I9" s="123" t="n">
         <f aca="false">H9-COMPARATIVO!D$34</f>
         <v>-2424.76313097937</v>
       </c>
-      <c r="J9" s="121" t="n">
+      <c r="J9" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7242.77521969203</v>
       </c>
-      <c r="K9" s="121" t="n">
+      <c r="K9" s="123" t="n">
         <f aca="false">K8+J9</f>
         <v>26418.565410837</v>
       </c>
-      <c r="L9" s="121" t="n">
+      <c r="L9" s="123" t="n">
         <f aca="false">K9-COMPARATIVO!E$34</f>
         <v>7898.22541083703</v>
       </c>
-      <c r="M9" s="121" t="n">
+      <c r="M9" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7242.77521969203</v>
       </c>
-      <c r="N9" s="121" t="n">
+      <c r="N9" s="123" t="n">
         <f aca="false">N8+M9</f>
         <v>26418.565410837</v>
       </c>
-      <c r="O9" s="121" t="n">
+      <c r="O9" s="123" t="n">
         <f aca="false">N9-COMPARATIVO!F$34</f>
         <v>6898.22541083703</v>
       </c>
-      <c r="P9" s="121" t="n">
+      <c r="P9" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>6577.63359004917</v>
       </c>
-      <c r="Q9" s="121" t="n">
+      <c r="Q9" s="123" t="n">
         <f aca="false">Q8+P9</f>
         <v>23992.4114688488</v>
       </c>
-      <c r="R9" s="121" t="n">
+      <c r="R9" s="123" t="n">
         <f aca="false">Q9-COMPARATIVO!G$34</f>
         <v>2643.50146884879</v>
       </c>
-      <c r="S9" s="121" t="n">
+      <c r="S9" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>5685.78290912472</v>
       </c>
-      <c r="T9" s="121" t="n">
+      <c r="T9" s="123" t="n">
         <f aca="false">T8+S9</f>
         <v>20739.319272001</v>
       </c>
-      <c r="U9" s="121" t="n">
+      <c r="U9" s="123" t="n">
         <f aca="false">T9-COMPARATIVO!H$34</f>
         <v>5851.67927200105</v>
       </c>
-      <c r="V9" s="121" t="n">
+      <c r="V9" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="W9" s="121" t="n">
+      <c r="W9" s="123" t="n">
         <f aca="false">W8+V9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="X9" s="121" t="n">
+      <c r="X9" s="123" t="n">
         <f aca="false">W9-COMPARATIVO!I$34</f>
         <v>-1207.34313097937</v>
       </c>
-      <c r="Y9" s="121" t="n">
+      <c r="Y9" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7213.24823466723</v>
       </c>
-      <c r="Z9" s="121" t="n">
+      <c r="Z9" s="123" t="n">
         <f aca="false">Z8+Y9</f>
         <v>26310.8635201113</v>
       </c>
-      <c r="AA9" s="121" t="n">
+      <c r="AA9" s="123" t="n">
         <f aca="false">Z9-COMPARATIVO!J$34</f>
         <v>5077.86352011126</v>
       </c>
-      <c r="AB9" s="121" t="n">
+      <c r="AB9" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="AC9" s="121" t="n">
+      <c r="AC9" s="123" t="n">
         <f aca="false">AC8+AB9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="AD9" s="121" t="n">
+      <c r="AD9" s="123" t="n">
         <f aca="false">AC9-COMPARATIVO!K$34</f>
         <v>7063.13686902063</v>
       </c>
-      <c r="AE9" s="121" t="n">
+      <c r="AE9" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7237.85405552123</v>
       </c>
-      <c r="AF9" s="121" t="n">
+      <c r="AF9" s="123" t="n">
         <f aca="false">AF8+AE9</f>
         <v>26400.6150957161</v>
       </c>
-      <c r="AG9" s="121" t="n">
+      <c r="AG9" s="123" t="n">
         <f aca="false">AF9-COMPARATIVO!L$34</f>
         <v>7700.61509571606</v>
       </c>
-      <c r="AH9" s="121" t="n">
+      <c r="AH9" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="AI9" s="121" t="n">
+      <c r="AI9" s="123" t="n">
         <f aca="false">AI8+AH9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="AJ9" s="121" t="n">
+      <c r="AJ9" s="123" t="n">
         <f aca="false">AI9-COMPARATIVO!M$34</f>
         <v>-3007.34313097937</v>
       </c>
-      <c r="AK9" s="121" t="n">
+      <c r="AK9" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C9/$C$6*(1+ENTRADAS!$C$27)^(4-1)</f>
         <v>7252.25314919906</v>
       </c>
-      <c r="AL9" s="121" t="n">
+      <c r="AL9" s="123" t="n">
         <f aca="false">AL8+AK9</f>
         <v>26453.1368690206</v>
       </c>
-      <c r="AM9" s="121" t="n">
+      <c r="AM9" s="123" t="n">
         <f aca="false">AL9-COMPARATIVO!N$34</f>
         <v>-4807.34313097937</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="122" t="n">
+      <c r="B10" s="124" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="123" t="n">
+      <c r="C10" s="125" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(5-1)</f>
         <v>0.962478713191861</v>
       </c>
-      <c r="D10" s="124" t="n">
+      <c r="D10" s="126" t="n">
         <f aca="false">ECONOMIA!C$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="E10" s="124" t="n">
+      <c r="E10" s="126" t="n">
         <f aca="false">E9+D10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="F10" s="124" t="n">
+      <c r="F10" s="126" t="n">
         <f aca="false">E10-COMPARATIVO!C$34</f>
         <v>4379.42813975023</v>
       </c>
-      <c r="G10" s="124" t="n">
+      <c r="G10" s="126" t="n">
         <f aca="false">ECONOMIA!D$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="H10" s="124" t="n">
+      <c r="H10" s="126" t="n">
         <f aca="false">H9+G10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="I10" s="124" t="n">
+      <c r="I10" s="126" t="n">
         <f aca="false">H10-COMPARATIVO!D$34</f>
         <v>5300.22813975023</v>
       </c>
-      <c r="J10" s="124" t="n">
+      <c r="J10" s="126" t="n">
         <f aca="false">ECONOMIA!E$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7714.89552238766</v>
       </c>
-      <c r="K10" s="124" t="n">
+      <c r="K10" s="126" t="n">
         <f aca="false">K9+J10</f>
         <v>34133.4609332247</v>
       </c>
-      <c r="L10" s="124" t="n">
+      <c r="L10" s="126" t="n">
         <f aca="false">K10-COMPARATIVO!E$34</f>
         <v>15613.1209332247</v>
       </c>
-      <c r="M10" s="124" t="n">
+      <c r="M10" s="126" t="n">
         <f aca="false">ECONOMIA!F$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7714.89552238766</v>
       </c>
-      <c r="N10" s="124" t="n">
+      <c r="N10" s="126" t="n">
         <f aca="false">N9+M10</f>
         <v>34133.4609332247</v>
       </c>
-      <c r="O10" s="124" t="n">
+      <c r="O10" s="126" t="n">
         <f aca="false">N10-COMPARATIVO!F$34</f>
         <v>14613.1209332247</v>
       </c>
-      <c r="P10" s="124" t="n">
+      <c r="P10" s="126" t="n">
         <f aca="false">ECONOMIA!G$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7006.39663561653</v>
       </c>
-      <c r="Q10" s="124" t="n">
+      <c r="Q10" s="126" t="n">
         <f aca="false">Q9+P10</f>
         <v>30998.8081044653</v>
       </c>
-      <c r="R10" s="124" t="n">
+      <c r="R10" s="126" t="n">
         <f aca="false">Q10-COMPARATIVO!G$34</f>
         <v>9649.89810446532</v>
       </c>
-      <c r="S10" s="124" t="n">
+      <c r="S10" s="126" t="n">
         <f aca="false">ECONOMIA!H$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>6056.41066805601</v>
       </c>
-      <c r="T10" s="124" t="n">
+      <c r="T10" s="126" t="n">
         <f aca="false">T9+S10</f>
         <v>26795.7299400571</v>
       </c>
-      <c r="U10" s="124" t="n">
+      <c r="U10" s="126" t="n">
         <f aca="false">T10-COMPARATIVO!H$34</f>
         <v>11908.0899400571</v>
       </c>
-      <c r="V10" s="124" t="n">
+      <c r="V10" s="126" t="n">
         <f aca="false">ECONOMIA!I$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="W10" s="124" t="n">
+      <c r="W10" s="126" t="n">
         <f aca="false">W9+V10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="X10" s="124" t="n">
+      <c r="X10" s="126" t="n">
         <f aca="false">W10-COMPARATIVO!I$34</f>
         <v>6517.64813975023</v>
       </c>
-      <c r="Y10" s="124" t="n">
+      <c r="Y10" s="126" t="n">
         <f aca="false">ECONOMIA!J$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7683.44382084401</v>
       </c>
-      <c r="Z10" s="124" t="n">
+      <c r="Z10" s="126" t="n">
         <f aca="false">Z9+Y10</f>
         <v>33994.3073409553</v>
       </c>
-      <c r="AA10" s="124" t="n">
+      <c r="AA10" s="126" t="n">
         <f aca="false">Z10-COMPARATIVO!J$34</f>
         <v>12761.3073409553</v>
       </c>
-      <c r="AB10" s="124" t="n">
+      <c r="AB10" s="126" t="n">
         <f aca="false">ECONOMIA!K$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="AC10" s="124" t="n">
+      <c r="AC10" s="126" t="n">
         <f aca="false">AC9+AB10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="AD10" s="124" t="n">
+      <c r="AD10" s="126" t="n">
         <f aca="false">AC10-COMPARATIVO!K$34</f>
         <v>14788.1281397502</v>
       </c>
-      <c r="AE10" s="124" t="n">
+      <c r="AE10" s="126" t="n">
         <f aca="false">ECONOMIA!L$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7709.65357213038</v>
       </c>
-      <c r="AF10" s="124" t="n">
+      <c r="AF10" s="126" t="n">
         <f aca="false">AF9+AE10</f>
         <v>34110.2686678464</v>
       </c>
-      <c r="AG10" s="124" t="n">
+      <c r="AG10" s="126" t="n">
         <f aca="false">AF10-COMPARATIVO!L$34</f>
         <v>15410.2686678464</v>
       </c>
-      <c r="AH10" s="124" t="n">
+      <c r="AH10" s="126" t="n">
         <f aca="false">ECONOMIA!M$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="AI10" s="124" t="n">
+      <c r="AI10" s="126" t="n">
         <f aca="false">AI9+AH10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="AJ10" s="124" t="n">
+      <c r="AJ10" s="126" t="n">
         <f aca="false">AI10-COMPARATIVO!M$34</f>
         <v>4717.64813975023</v>
       </c>
-      <c r="AK10" s="124" t="n">
+      <c r="AK10" s="126" t="n">
         <f aca="false">ECONOMIA!N$26*C10/$C$6*(1+ENTRADAS!$C$27)^(5-1)</f>
         <v>7724.9912707296</v>
       </c>
-      <c r="AL10" s="124" t="n">
+      <c r="AL10" s="126" t="n">
         <f aca="false">AL9+AK10</f>
         <v>34178.1281397502</v>
       </c>
-      <c r="AM10" s="124" t="n">
+      <c r="AM10" s="126" t="n">
         <f aca="false">AL10-COMPARATIVO!N$34</f>
         <v>2917.64813975023</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="120" t="n">
+      <c r="B11" s="122" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(6-1)</f>
         <v>0.958147558982498</v>
       </c>
-      <c r="D11" s="121" t="n">
+      <c r="D11" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="E11" s="121" t="n">
+      <c r="E11" s="123" t="n">
         <f aca="false">E10+D11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="F11" s="121" t="n">
+      <c r="F11" s="123" t="n">
         <f aca="false">E11-COMPARATIVO!C$34</f>
         <v>12607.9729664623</v>
       </c>
-      <c r="G11" s="121" t="n">
+      <c r="G11" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="H11" s="121" t="n">
+      <c r="H11" s="123" t="n">
         <f aca="false">H10+G11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="I11" s="121" t="n">
+      <c r="I11" s="123" t="n">
         <f aca="false">H11-COMPARATIVO!D$34</f>
         <v>13528.7729664623</v>
       </c>
-      <c r="J11" s="121" t="n">
+      <c r="J11" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8217.7909870145</v>
       </c>
-      <c r="K11" s="121" t="n">
+      <c r="K11" s="123" t="n">
         <f aca="false">K10+J11</f>
         <v>42351.2519202392</v>
       </c>
-      <c r="L11" s="121" t="n">
+      <c r="L11" s="123" t="n">
         <f aca="false">K11-COMPARATIVO!E$34</f>
         <v>23830.9119202392</v>
       </c>
-      <c r="M11" s="121" t="n">
+      <c r="M11" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8217.7909870145</v>
       </c>
-      <c r="N11" s="121" t="n">
+      <c r="N11" s="123" t="n">
         <f aca="false">N10+M11</f>
         <v>42351.2519202392</v>
       </c>
-      <c r="O11" s="121" t="n">
+      <c r="O11" s="123" t="n">
         <f aca="false">N11-COMPARATIVO!F$34</f>
         <v>22830.9119202392</v>
       </c>
-      <c r="P11" s="121" t="n">
+      <c r="P11" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>7463.10860030919</v>
       </c>
-      <c r="Q11" s="121" t="n">
+      <c r="Q11" s="123" t="n">
         <f aca="false">Q10+P11</f>
         <v>38461.9167047745</v>
       </c>
-      <c r="R11" s="121" t="n">
+      <c r="R11" s="123" t="n">
         <f aca="false">Q11-COMPARATIVO!G$34</f>
         <v>17113.0067047745</v>
       </c>
-      <c r="S11" s="121" t="n">
+      <c r="S11" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>6451.19779745324</v>
       </c>
-      <c r="T11" s="121" t="n">
+      <c r="T11" s="123" t="n">
         <f aca="false">T10+S11</f>
         <v>33246.9277375103</v>
       </c>
-      <c r="U11" s="121" t="n">
+      <c r="U11" s="123" t="n">
         <f aca="false">T11-COMPARATIVO!H$34</f>
         <v>18359.2877375103</v>
       </c>
-      <c r="V11" s="121" t="n">
+      <c r="V11" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="W11" s="121" t="n">
+      <c r="W11" s="123" t="n">
         <f aca="false">W10+V11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="X11" s="121" t="n">
+      <c r="X11" s="123" t="n">
         <f aca="false">W11-COMPARATIVO!I$34</f>
         <v>14746.1929664624</v>
       </c>
-      <c r="Y11" s="121" t="n">
+      <c r="Y11" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8184.28910630573</v>
       </c>
-      <c r="Z11" s="121" t="n">
+      <c r="Z11" s="123" t="n">
         <f aca="false">Z10+Y11</f>
         <v>42178.596447261</v>
       </c>
-      <c r="AA11" s="121" t="n">
+      <c r="AA11" s="123" t="n">
         <f aca="false">Z11-COMPARATIVO!J$34</f>
         <v>20945.596447261</v>
       </c>
-      <c r="AB11" s="121" t="n">
+      <c r="AB11" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="AC11" s="121" t="n">
+      <c r="AC11" s="123" t="n">
         <f aca="false">AC10+AB11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="AD11" s="121" t="n">
+      <c r="AD11" s="123" t="n">
         <f aca="false">AC11-COMPARATIVO!K$34</f>
         <v>23016.6729664624</v>
       </c>
-      <c r="AE11" s="121" t="n">
+      <c r="AE11" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8212.2073402297</v>
       </c>
-      <c r="AF11" s="121" t="n">
+      <c r="AF11" s="123" t="n">
         <f aca="false">AF10+AE11</f>
         <v>42322.4760080761</v>
       </c>
-      <c r="AG11" s="121" t="n">
+      <c r="AG11" s="123" t="n">
         <f aca="false">AF11-COMPARATIVO!L$34</f>
         <v>23622.4760080761</v>
       </c>
-      <c r="AH11" s="121" t="n">
+      <c r="AH11" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="AI11" s="121" t="n">
+      <c r="AI11" s="123" t="n">
         <f aca="false">AI10+AH11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="AJ11" s="121" t="n">
+      <c r="AJ11" s="123" t="n">
         <f aca="false">AI11-COMPARATIVO!M$34</f>
         <v>12946.1929664624</v>
       </c>
-      <c r="AK11" s="121" t="n">
+      <c r="AK11" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C11/$C$6*(1+ENTRADAS!$C$27)^(6-1)</f>
         <v>8228.54482671212</v>
       </c>
-      <c r="AL11" s="121" t="n">
+      <c r="AL11" s="123" t="n">
         <f aca="false">AL10+AK11</f>
         <v>42406.6729664624</v>
       </c>
-      <c r="AM11" s="121" t="n">
+      <c r="AM11" s="123" t="n">
         <f aca="false">AL11-COMPARATIVO!N$34</f>
         <v>11146.1929664624</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="120" t="n">
+      <c r="B12" s="122" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(7-1)</f>
         <v>0.953835894967077</v>
       </c>
-      <c r="D12" s="121" t="n">
+      <c r="D12" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="E12" s="121" t="n">
+      <c r="E12" s="123" t="n">
         <f aca="false">E11+D12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="F12" s="121" t="n">
+      <c r="F12" s="123" t="n">
         <f aca="false">E12-COMPARATIVO!C$34</f>
         <v>21372.8954877037</v>
       </c>
-      <c r="G12" s="121" t="n">
+      <c r="G12" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="H12" s="121" t="n">
+      <c r="H12" s="123" t="n">
         <f aca="false">H11+G12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="I12" s="121" t="n">
+      <c r="I12" s="123" t="n">
         <f aca="false">H12-COMPARATIVO!D$34</f>
         <v>22293.6954877037</v>
       </c>
-      <c r="J12" s="121" t="n">
+      <c r="J12" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8753.46769250304</v>
       </c>
-      <c r="K12" s="121" t="n">
+      <c r="K12" s="123" t="n">
         <f aca="false">K11+J12</f>
         <v>51104.7196127422</v>
       </c>
-      <c r="L12" s="121" t="n">
+      <c r="L12" s="123" t="n">
         <f aca="false">K12-COMPARATIVO!E$34</f>
         <v>32584.3796127422</v>
       </c>
-      <c r="M12" s="121" t="n">
+      <c r="M12" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8753.46769250304</v>
       </c>
-      <c r="N12" s="121" t="n">
+      <c r="N12" s="123" t="n">
         <f aca="false">N11+M12</f>
         <v>51104.7196127422</v>
       </c>
-      <c r="O12" s="121" t="n">
+      <c r="O12" s="123" t="n">
         <f aca="false">N12-COMPARATIVO!F$34</f>
         <v>31584.3796127422</v>
       </c>
-      <c r="P12" s="121" t="n">
+      <c r="P12" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>7949.59133442035</v>
       </c>
-      <c r="Q12" s="121" t="n">
+      <c r="Q12" s="123" t="n">
         <f aca="false">Q11+P12</f>
         <v>46411.5080391949</v>
       </c>
-      <c r="R12" s="121" t="n">
+      <c r="R12" s="123" t="n">
         <f aca="false">Q12-COMPARATIVO!G$34</f>
         <v>25062.5980391949</v>
       </c>
-      <c r="S12" s="121" t="n">
+      <c r="S12" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>6871.71912588023</v>
       </c>
-      <c r="T12" s="121" t="n">
+      <c r="T12" s="123" t="n">
         <f aca="false">T11+S12</f>
         <v>40118.6468633905</v>
       </c>
-      <c r="U12" s="121" t="n">
+      <c r="U12" s="123" t="n">
         <f aca="false">T12-COMPARATIVO!H$34</f>
         <v>25231.0068633905</v>
       </c>
-      <c r="V12" s="121" t="n">
+      <c r="V12" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="W12" s="121" t="n">
+      <c r="W12" s="123" t="n">
         <f aca="false">W11+V12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="X12" s="121" t="n">
+      <c r="X12" s="123" t="n">
         <f aca="false">W12-COMPARATIVO!I$34</f>
         <v>23511.1154877037</v>
       </c>
-      <c r="Y12" s="121" t="n">
+      <c r="Y12" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8717.78199170027</v>
       </c>
-      <c r="Z12" s="121" t="n">
+      <c r="Z12" s="123" t="n">
         <f aca="false">Z11+Y12</f>
         <v>50896.3784389613</v>
       </c>
-      <c r="AA12" s="121" t="n">
+      <c r="AA12" s="123" t="n">
         <f aca="false">Z12-COMPARATIVO!J$34</f>
         <v>29663.3784389613</v>
       </c>
-      <c r="AB12" s="121" t="n">
+      <c r="AB12" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="AC12" s="121" t="n">
+      <c r="AC12" s="123" t="n">
         <f aca="false">AC11+AB12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="AD12" s="121" t="n">
+      <c r="AD12" s="123" t="n">
         <f aca="false">AC12-COMPARATIVO!K$34</f>
         <v>31781.5954877037</v>
       </c>
-      <c r="AE12" s="121" t="n">
+      <c r="AE12" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8747.52007570258</v>
       </c>
-      <c r="AF12" s="121" t="n">
+      <c r="AF12" s="123" t="n">
         <f aca="false">AF11+AE12</f>
         <v>51069.9960837787</v>
       </c>
-      <c r="AG12" s="121" t="n">
+      <c r="AG12" s="123" t="n">
         <f aca="false">AF12-COMPARATIVO!L$34</f>
         <v>32369.9960837787</v>
       </c>
-      <c r="AH12" s="121" t="n">
+      <c r="AH12" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="AI12" s="121" t="n">
+      <c r="AI12" s="123" t="n">
         <f aca="false">AI11+AH12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="AJ12" s="121" t="n">
+      <c r="AJ12" s="123" t="n">
         <f aca="false">AI12-COMPARATIVO!M$34</f>
         <v>21711.1154877037</v>
       </c>
-      <c r="AK12" s="121" t="n">
+      <c r="AK12" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C12/$C$6*(1+ENTRADAS!$C$27)^(7-1)</f>
         <v>8764.92252124135</v>
       </c>
-      <c r="AL12" s="121" t="n">
+      <c r="AL12" s="123" t="n">
         <f aca="false">AL11+AK12</f>
         <v>51171.5954877037</v>
       </c>
-      <c r="AM12" s="121" t="n">
+      <c r="AM12" s="123" t="n">
         <f aca="false">AL12-COMPARATIVO!N$34</f>
         <v>19911.1154877037</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="120" t="n">
+      <c r="B13" s="122" t="n">
         <v>8</v>
       </c>
       <c r="C13" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(8-1)</f>
         <v>0.949543633439725</v>
       </c>
-      <c r="D13" s="121" t="n">
+      <c r="D13" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="E13" s="121" t="n">
+      <c r="E13" s="123" t="n">
         <f aca="false">E12+D13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="F13" s="121" t="n">
+      <c r="F13" s="123" t="n">
         <f aca="false">E13-COMPARATIVO!C$34</f>
         <v>30709.1594834922</v>
       </c>
-      <c r="G13" s="121" t="n">
+      <c r="G13" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="H13" s="121" t="n">
+      <c r="H13" s="123" t="n">
         <f aca="false">H12+G13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="I13" s="121" t="n">
+      <c r="I13" s="123" t="n">
         <f aca="false">H13-COMPARATIVO!D$34</f>
         <v>31629.9594834922</v>
       </c>
-      <c r="J13" s="121" t="n">
+      <c r="J13" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9324.06248403885</v>
       </c>
-      <c r="K13" s="121" t="n">
+      <c r="K13" s="123" t="n">
         <f aca="false">K12+J13</f>
         <v>60428.7820967811</v>
       </c>
-      <c r="L13" s="121" t="n">
+      <c r="L13" s="123" t="n">
         <f aca="false">K13-COMPARATIVO!E$34</f>
         <v>41908.4420967811</v>
       </c>
-      <c r="M13" s="121" t="n">
+      <c r="M13" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9324.06248403885</v>
       </c>
-      <c r="N13" s="121" t="n">
+      <c r="N13" s="123" t="n">
         <f aca="false">N12+M13</f>
         <v>60428.7820967811</v>
       </c>
-      <c r="O13" s="121" t="n">
+      <c r="O13" s="123" t="n">
         <f aca="false">N13-COMPARATIVO!F$34</f>
         <v>40908.4420967811</v>
       </c>
-      <c r="P13" s="121" t="n">
+      <c r="P13" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>8467.78544555454</v>
       </c>
-      <c r="Q13" s="121" t="n">
+      <c r="Q13" s="123" t="n">
         <f aca="false">Q12+P13</f>
         <v>54879.2934847494</v>
       </c>
-      <c r="R13" s="121" t="n">
+      <c r="R13" s="123" t="n">
         <f aca="false">Q13-COMPARATIVO!G$34</f>
         <v>33530.3834847494</v>
       </c>
-      <c r="S13" s="121" t="n">
+      <c r="S13" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>7319.65213710074</v>
       </c>
-      <c r="T13" s="121" t="n">
+      <c r="T13" s="123" t="n">
         <f aca="false">T12+S13</f>
         <v>47438.2990004913</v>
       </c>
-      <c r="U13" s="121" t="n">
+      <c r="U13" s="123" t="n">
         <f aca="false">T13-COMPARATIVO!H$34</f>
         <v>32550.6590004913</v>
       </c>
-      <c r="V13" s="121" t="n">
+      <c r="V13" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="W13" s="121" t="n">
+      <c r="W13" s="123" t="n">
         <f aca="false">W12+V13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="X13" s="121" t="n">
+      <c r="X13" s="123" t="n">
         <f aca="false">W13-COMPARATIVO!I$34</f>
         <v>32847.3794834922</v>
       </c>
-      <c r="Y13" s="121" t="n">
+      <c r="Y13" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9286.05061082925</v>
       </c>
-      <c r="Z13" s="121" t="n">
+      <c r="Z13" s="123" t="n">
         <f aca="false">Z12+Y13</f>
         <v>60182.4290497905</v>
       </c>
-      <c r="AA13" s="121" t="n">
+      <c r="AA13" s="123" t="n">
         <f aca="false">Z13-COMPARATIVO!J$34</f>
         <v>38949.4290497905</v>
       </c>
-      <c r="AB13" s="121" t="n">
+      <c r="AB13" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="AC13" s="121" t="n">
+      <c r="AC13" s="123" t="n">
         <f aca="false">AC12+AB13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="AD13" s="121" t="n">
+      <c r="AD13" s="123" t="n">
         <f aca="false">AC13-COMPARATIVO!K$34</f>
         <v>41117.8594834922</v>
       </c>
-      <c r="AE13" s="121" t="n">
+      <c r="AE13" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9317.72717183725</v>
       </c>
-      <c r="AF13" s="121" t="n">
+      <c r="AF13" s="123" t="n">
         <f aca="false">AF12+AE13</f>
         <v>60387.723255616</v>
       </c>
-      <c r="AG13" s="121" t="n">
+      <c r="AG13" s="123" t="n">
         <f aca="false">AF13-COMPARATIVO!L$34</f>
         <v>41687.723255616</v>
       </c>
-      <c r="AH13" s="121" t="n">
+      <c r="AH13" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="AI13" s="121" t="n">
+      <c r="AI13" s="123" t="n">
         <f aca="false">AI12+AH13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="AJ13" s="121" t="n">
+      <c r="AJ13" s="123" t="n">
         <f aca="false">AI13-COMPARATIVO!M$34</f>
         <v>31047.3794834922</v>
       </c>
-      <c r="AK13" s="121" t="n">
+      <c r="AK13" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C13/$C$6*(1+ENTRADAS!$C$27)^(8-1)</f>
         <v>9336.26399578846</v>
       </c>
-      <c r="AL13" s="121" t="n">
+      <c r="AL13" s="123" t="n">
         <f aca="false">AL12+AK13</f>
         <v>60507.8594834922</v>
       </c>
-      <c r="AM13" s="121" t="n">
+      <c r="AM13" s="123" t="n">
         <f aca="false">AL13-COMPARATIVO!N$34</f>
         <v>29247.3794834922</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="120" t="n">
+      <c r="B14" s="122" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(9-1)</f>
         <v>0.945270687089246</v>
       </c>
-      <c r="D14" s="121" t="n">
+      <c r="D14" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="E14" s="121" t="n">
+      <c r="E14" s="123" t="n">
         <f aca="false">E13+D14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="F14" s="121" t="n">
+      <c r="F14" s="123" t="n">
         <f aca="false">E14-COMPARATIVO!C$34</f>
         <v>40654.0078478461</v>
       </c>
-      <c r="G14" s="121" t="n">
+      <c r="G14" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="H14" s="121" t="n">
+      <c r="H14" s="123" t="n">
         <f aca="false">H13+G14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="I14" s="121" t="n">
+      <c r="I14" s="123" t="n">
         <f aca="false">H14-COMPARATIVO!D$34</f>
         <v>41574.8078478461</v>
       </c>
-      <c r="J14" s="121" t="n">
+      <c r="J14" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9931.85149706092</v>
       </c>
-      <c r="K14" s="121" t="n">
+      <c r="K14" s="123" t="n">
         <f aca="false">K13+J14</f>
         <v>70360.633593842</v>
       </c>
-      <c r="L14" s="121" t="n">
+      <c r="L14" s="123" t="n">
         <f aca="false">K14-COMPARATIVO!E$34</f>
         <v>51840.293593842</v>
       </c>
-      <c r="M14" s="121" t="n">
+      <c r="M14" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9931.85149706092</v>
       </c>
-      <c r="N14" s="121" t="n">
+      <c r="N14" s="123" t="n">
         <f aca="false">N13+M14</f>
         <v>70360.633593842</v>
       </c>
-      <c r="O14" s="121" t="n">
+      <c r="O14" s="123" t="n">
         <f aca="false">N14-COMPARATIVO!F$34</f>
         <v>50840.293593842</v>
       </c>
-      <c r="P14" s="121" t="n">
+      <c r="P14" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9019.75803982302</v>
       </c>
-      <c r="Q14" s="121" t="n">
+      <c r="Q14" s="123" t="n">
         <f aca="false">Q13+P14</f>
         <v>63899.0515245724</v>
       </c>
-      <c r="R14" s="121" t="n">
+      <c r="R14" s="123" t="n">
         <f aca="false">Q14-COMPARATIVO!G$34</f>
         <v>42550.1415245724</v>
       </c>
-      <c r="S14" s="121" t="n">
+      <c r="S14" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>7796.78366165765</v>
       </c>
-      <c r="T14" s="121" t="n">
+      <c r="T14" s="123" t="n">
         <f aca="false">T13+S14</f>
         <v>55235.0826621489</v>
       </c>
-      <c r="U14" s="121" t="n">
+      <c r="U14" s="123" t="n">
         <f aca="false">T14-COMPARATIVO!H$34</f>
         <v>40347.4426621489</v>
       </c>
-      <c r="V14" s="121" t="n">
+      <c r="V14" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="W14" s="121" t="n">
+      <c r="W14" s="123" t="n">
         <f aca="false">W13+V14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="X14" s="121" t="n">
+      <c r="X14" s="123" t="n">
         <f aca="false">W14-COMPARATIVO!I$34</f>
         <v>42792.2278478461</v>
       </c>
-      <c r="Y14" s="121" t="n">
+      <c r="Y14" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9891.36181989616</v>
       </c>
-      <c r="Z14" s="121" t="n">
+      <c r="Z14" s="123" t="n">
         <f aca="false">Z13+Y14</f>
         <v>70073.7908696867</v>
       </c>
-      <c r="AA14" s="121" t="n">
+      <c r="AA14" s="123" t="n">
         <f aca="false">Z14-COMPARATIVO!J$34</f>
         <v>48840.7908696867</v>
       </c>
-      <c r="AB14" s="121" t="n">
+      <c r="AB14" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="AC14" s="121" t="n">
+      <c r="AC14" s="123" t="n">
         <f aca="false">AC13+AB14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="AD14" s="121" t="n">
+      <c r="AD14" s="123" t="n">
         <f aca="false">AC14-COMPARATIVO!K$34</f>
         <v>51062.7078478461</v>
       </c>
-      <c r="AE14" s="121" t="n">
+      <c r="AE14" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9925.10321753346</v>
       </c>
-      <c r="AF14" s="121" t="n">
+      <c r="AF14" s="123" t="n">
         <f aca="false">AF13+AE14</f>
         <v>70312.8264731494</v>
       </c>
-      <c r="AG14" s="121" t="n">
+      <c r="AG14" s="123" t="n">
         <f aca="false">AF14-COMPARATIVO!L$34</f>
         <v>51612.8264731494</v>
       </c>
-      <c r="AH14" s="121" t="n">
+      <c r="AH14" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="AI14" s="121" t="n">
+      <c r="AI14" s="123" t="n">
         <f aca="false">AI13+AH14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="AJ14" s="121" t="n">
+      <c r="AJ14" s="123" t="n">
         <f aca="false">AI14-COMPARATIVO!M$34</f>
         <v>40992.2278478461</v>
       </c>
-      <c r="AK14" s="121" t="n">
+      <c r="AK14" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C14/$C$6*(1+ENTRADAS!$C$27)^(9-1)</f>
         <v>9944.84836435394</v>
       </c>
-      <c r="AL14" s="121" t="n">
+      <c r="AL14" s="123" t="n">
         <f aca="false">AL13+AK14</f>
         <v>70452.7078478461</v>
       </c>
-      <c r="AM14" s="121" t="n">
+      <c r="AM14" s="123" t="n">
         <f aca="false">AL14-COMPARATIVO!N$34</f>
         <v>39192.2278478461</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="122" t="n">
+      <c r="B15" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="123" t="n">
+      <c r="C15" s="125" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(10-1)</f>
         <v>0.941016968997345</v>
       </c>
-      <c r="D15" s="124" t="n">
+      <c r="D15" s="126" t="n">
         <f aca="false">ECONOMIA!C$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="E15" s="124" t="n">
+      <c r="E15" s="126" t="n">
         <f aca="false">E14+D15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="F15" s="124" t="n">
+      <c r="F15" s="126" t="n">
         <f aca="false">E15-COMPARATIVO!C$34</f>
         <v>51247.1111528305</v>
       </c>
-      <c r="G15" s="124" t="n">
+      <c r="G15" s="126" t="n">
         <f aca="false">ECONOMIA!D$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="H15" s="124" t="n">
+      <c r="H15" s="126" t="n">
         <f aca="false">H14+G15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="I15" s="124" t="n">
+      <c r="I15" s="126" t="n">
         <f aca="false">H15-COMPARATIVO!D$34</f>
         <v>52167.9111528304</v>
       </c>
-      <c r="J15" s="124" t="n">
+      <c r="J15" s="126" t="n">
         <f aca="false">ECONOMIA!E$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10579.2592368968</v>
       </c>
-      <c r="K15" s="124" t="n">
+      <c r="K15" s="126" t="n">
         <f aca="false">K14+J15</f>
         <v>80939.8928307388</v>
       </c>
-      <c r="L15" s="124" t="n">
+      <c r="L15" s="126" t="n">
         <f aca="false">K15-COMPARATIVO!E$34</f>
         <v>62419.5528307388</v>
       </c>
-      <c r="M15" s="124" t="n">
+      <c r="M15" s="126" t="n">
         <f aca="false">ECONOMIA!F$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10579.2592368968</v>
       </c>
-      <c r="N15" s="124" t="n">
+      <c r="N15" s="126" t="n">
         <f aca="false">N14+M15</f>
         <v>80939.8928307388</v>
       </c>
-      <c r="O15" s="124" t="n">
+      <c r="O15" s="126" t="n">
         <f aca="false">N15-COMPARATIVO!F$34</f>
         <v>61419.5528307388</v>
       </c>
-      <c r="P15" s="124" t="n">
+      <c r="P15" s="126" t="n">
         <f aca="false">ECONOMIA!G$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>9607.71096764888</v>
       </c>
-      <c r="Q15" s="124" t="n">
+      <c r="Q15" s="126" t="n">
         <f aca="false">Q14+P15</f>
         <v>73506.7624922213</v>
       </c>
-      <c r="R15" s="124" t="n">
+      <c r="R15" s="126" t="n">
         <f aca="false">Q15-COMPARATIVO!G$34</f>
         <v>52157.8524922213</v>
       </c>
-      <c r="S15" s="124" t="n">
+      <c r="S15" s="126" t="n">
         <f aca="false">ECONOMIA!H$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>8305.01700464281</v>
       </c>
-      <c r="T15" s="124" t="n">
+      <c r="T15" s="126" t="n">
         <f aca="false">T14+S15</f>
         <v>63540.0996667917</v>
       </c>
-      <c r="U15" s="124" t="n">
+      <c r="U15" s="126" t="n">
         <f aca="false">T15-COMPARATIVO!H$34</f>
         <v>48652.4596667917</v>
       </c>
-      <c r="V15" s="124" t="n">
+      <c r="V15" s="126" t="n">
         <f aca="false">ECONOMIA!I$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="W15" s="124" t="n">
+      <c r="W15" s="126" t="n">
         <f aca="false">W14+V15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="X15" s="124" t="n">
+      <c r="X15" s="126" t="n">
         <f aca="false">W15-COMPARATIVO!I$34</f>
         <v>53385.3311528305</v>
       </c>
-      <c r="Y15" s="124" t="n">
+      <c r="Y15" s="126" t="n">
         <f aca="false">ECONOMIA!J$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10536.1302401261</v>
       </c>
-      <c r="Z15" s="124" t="n">
+      <c r="Z15" s="126" t="n">
         <f aca="false">Z14+Y15</f>
         <v>80609.9211098128</v>
       </c>
-      <c r="AA15" s="124" t="n">
+      <c r="AA15" s="126" t="n">
         <f aca="false">Z15-COMPARATIVO!J$34</f>
         <v>59376.9211098128</v>
       </c>
-      <c r="AB15" s="124" t="n">
+      <c r="AB15" s="126" t="n">
         <f aca="false">ECONOMIA!K$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="AC15" s="124" t="n">
+      <c r="AC15" s="126" t="n">
         <f aca="false">AC14+AB15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="AD15" s="124" t="n">
+      <c r="AD15" s="126" t="n">
         <f aca="false">AC15-COMPARATIVO!K$34</f>
         <v>61655.8111528304</v>
       </c>
-      <c r="AE15" s="124" t="n">
+      <c r="AE15" s="126" t="n">
         <f aca="false">ECONOMIA!L$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10572.0710707684</v>
       </c>
-      <c r="AF15" s="124" t="n">
+      <c r="AF15" s="126" t="n">
         <f aca="false">AF14+AE15</f>
         <v>80884.8975439178</v>
       </c>
-      <c r="AG15" s="124" t="n">
+      <c r="AG15" s="126" t="n">
         <f aca="false">AF15-COMPARATIVO!L$34</f>
         <v>62184.8975439178</v>
       </c>
-      <c r="AH15" s="124" t="n">
+      <c r="AH15" s="126" t="n">
         <f aca="false">ECONOMIA!M$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="AI15" s="124" t="n">
+      <c r="AI15" s="126" t="n">
         <f aca="false">AI14+AH15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="AJ15" s="124" t="n">
+      <c r="AJ15" s="126" t="n">
         <f aca="false">AI15-COMPARATIVO!M$34</f>
         <v>51585.3311528305</v>
       </c>
-      <c r="AK15" s="124" t="n">
+      <c r="AK15" s="126" t="n">
         <f aca="false">ECONOMIA!N$26*C15/$C$6*(1+ENTRADAS!$C$27)^(10-1)</f>
         <v>10593.1033049843</v>
       </c>
-      <c r="AL15" s="124" t="n">
+      <c r="AL15" s="126" t="n">
         <f aca="false">AL14+AK15</f>
         <v>81045.8111528304</v>
       </c>
-      <c r="AM15" s="124" t="n">
+      <c r="AM15" s="126" t="n">
         <f aca="false">AL15-COMPARATIVO!N$34</f>
         <v>49785.3311528305</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="120" t="n">
+      <c r="B16" s="122" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(11-1)</f>
         <v>0.936782392636857</v>
       </c>
-      <c r="D16" s="121" t="n">
+      <c r="D16" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="E16" s="121" t="n">
+      <c r="E16" s="123" t="n">
         <f aca="false">E15+D16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="F16" s="121" t="n">
+      <c r="F16" s="123" t="n">
         <f aca="false">E16-COMPARATIVO!C$34</f>
         <v>62530.7258967502</v>
       </c>
-      <c r="G16" s="121" t="n">
+      <c r="G16" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="H16" s="121" t="n">
+      <c r="H16" s="123" t="n">
         <f aca="false">H15+G16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="I16" s="121" t="n">
+      <c r="I16" s="123" t="n">
         <f aca="false">H16-COMPARATIVO!D$34</f>
         <v>63451.5258967502</v>
       </c>
-      <c r="J16" s="121" t="n">
+      <c r="J16" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11268.868250254</v>
       </c>
-      <c r="K16" s="121" t="n">
+      <c r="K16" s="123" t="n">
         <f aca="false">K15+J16</f>
         <v>92208.7610809928</v>
       </c>
-      <c r="L16" s="121" t="n">
+      <c r="L16" s="123" t="n">
         <f aca="false">K16-COMPARATIVO!E$34</f>
         <v>73688.4210809928</v>
       </c>
-      <c r="M16" s="121" t="n">
+      <c r="M16" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11268.868250254</v>
       </c>
-      <c r="N16" s="121" t="n">
+      <c r="N16" s="123" t="n">
         <f aca="false">N15+M16</f>
         <v>92208.7610809928</v>
       </c>
-      <c r="O16" s="121" t="n">
+      <c r="O16" s="123" t="n">
         <f aca="false">N16-COMPARATIVO!F$34</f>
         <v>72688.4210809928</v>
       </c>
-      <c r="P16" s="121" t="n">
+      <c r="P16" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>10233.9896070751</v>
       </c>
-      <c r="Q16" s="121" t="n">
+      <c r="Q16" s="123" t="n">
         <f aca="false">Q15+P16</f>
         <v>83740.7520992964</v>
       </c>
-      <c r="R16" s="121" t="n">
+      <c r="R16" s="123" t="n">
         <f aca="false">Q16-COMPARATIVO!G$34</f>
         <v>62391.8420992964</v>
       </c>
-      <c r="S16" s="121" t="n">
+      <c r="S16" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>8846.37953809045</v>
       </c>
-      <c r="T16" s="121" t="n">
+      <c r="T16" s="123" t="n">
         <f aca="false">T15+S16</f>
         <v>72386.4792048822</v>
       </c>
-      <c r="U16" s="121" t="n">
+      <c r="U16" s="123" t="n">
         <f aca="false">T16-COMPARATIVO!H$34</f>
         <v>57498.8392048822</v>
       </c>
-      <c r="V16" s="121" t="n">
+      <c r="V16" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="W16" s="121" t="n">
+      <c r="W16" s="123" t="n">
         <f aca="false">W15+V16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="X16" s="121" t="n">
+      <c r="X16" s="123" t="n">
         <f aca="false">W16-COMPARATIVO!I$34</f>
         <v>64668.9458967502</v>
       </c>
-      <c r="Y16" s="121" t="n">
+      <c r="Y16" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11222.9278898287</v>
       </c>
-      <c r="Z16" s="121" t="n">
+      <c r="Z16" s="123" t="n">
         <f aca="false">Z15+Y16</f>
         <v>91832.8489996415</v>
       </c>
-      <c r="AA16" s="121" t="n">
+      <c r="AA16" s="123" t="n">
         <f aca="false">Z16-COMPARATIVO!J$34</f>
         <v>70599.8489996415</v>
       </c>
-      <c r="AB16" s="121" t="n">
+      <c r="AB16" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="AC16" s="121" t="n">
+      <c r="AC16" s="123" t="n">
         <f aca="false">AC15+AB16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="AD16" s="121" t="n">
+      <c r="AD16" s="123" t="n">
         <f aca="false">AC16-COMPARATIVO!K$34</f>
         <v>72939.4258967502</v>
       </c>
-      <c r="AE16" s="121" t="n">
+      <c r="AE16" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11261.2115235164</v>
       </c>
-      <c r="AF16" s="121" t="n">
+      <c r="AF16" s="123" t="n">
         <f aca="false">AF15+AE16</f>
         <v>92146.1090674342</v>
       </c>
-      <c r="AG16" s="121" t="n">
+      <c r="AG16" s="123" t="n">
         <f aca="false">AF16-COMPARATIVO!L$34</f>
         <v>73446.1090674342</v>
       </c>
-      <c r="AH16" s="121" t="n">
+      <c r="AH16" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="AI16" s="121" t="n">
+      <c r="AI16" s="123" t="n">
         <f aca="false">AI15+AH16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="AJ16" s="121" t="n">
+      <c r="AJ16" s="123" t="n">
         <f aca="false">AI16-COMPARATIVO!M$34</f>
         <v>62868.9458967502</v>
       </c>
-      <c r="AK16" s="121" t="n">
+      <c r="AK16" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C16/$C$6*(1+ENTRADAS!$C$27)^(11-1)</f>
         <v>11283.6147439198</v>
       </c>
-      <c r="AL16" s="121" t="n">
+      <c r="AL16" s="123" t="n">
         <f aca="false">AL15+AK16</f>
         <v>92329.4258967502</v>
       </c>
-      <c r="AM16" s="121" t="n">
+      <c r="AM16" s="123" t="n">
         <f aca="false">AL16-COMPARATIVO!N$34</f>
         <v>61068.9458967502</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="120" t="n">
+      <c r="B17" s="122" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(12-1)</f>
         <v>0.932566871869991</v>
       </c>
-      <c r="D17" s="121" t="n">
+      <c r="D17" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="E17" s="121" t="n">
+      <c r="E17" s="123" t="n">
         <f aca="false">E16+D17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="F17" s="121" t="n">
+      <c r="F17" s="123" t="n">
         <f aca="false">E17-COMPARATIVO!C$34</f>
         <v>74549.8630677524</v>
       </c>
-      <c r="G17" s="121" t="n">
+      <c r="G17" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="H17" s="121" t="n">
+      <c r="H17" s="123" t="n">
         <f aca="false">H16+G17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="I17" s="121" t="n">
+      <c r="I17" s="123" t="n">
         <f aca="false">H17-COMPARATIVO!D$34</f>
         <v>75470.6630677524</v>
       </c>
-      <c r="J17" s="121" t="n">
+      <c r="J17" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12003.4294271468</v>
       </c>
-      <c r="K17" s="121" t="n">
+      <c r="K17" s="123" t="n">
         <f aca="false">K16+J17</f>
         <v>104212.19050814</v>
       </c>
-      <c r="L17" s="121" t="n">
+      <c r="L17" s="123" t="n">
         <f aca="false">K17-COMPARATIVO!E$34</f>
         <v>85691.8505081396</v>
       </c>
-      <c r="M17" s="121" t="n">
+      <c r="M17" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12003.4294271468</v>
       </c>
-      <c r="N17" s="121" t="n">
+      <c r="N17" s="123" t="n">
         <f aca="false">N16+M17</f>
         <v>104212.19050814</v>
       </c>
-      <c r="O17" s="121" t="n">
+      <c r="O17" s="123" t="n">
         <f aca="false">N17-COMPARATIVO!F$34</f>
         <v>84691.8505081396</v>
       </c>
-      <c r="P17" s="121" t="n">
+      <c r="P17" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>10901.0922196123</v>
       </c>
-      <c r="Q17" s="121" t="n">
+      <c r="Q17" s="123" t="n">
         <f aca="false">Q16+P17</f>
         <v>94641.8443189086</v>
       </c>
-      <c r="R17" s="121" t="n">
+      <c r="R17" s="123" t="n">
         <f aca="false">Q17-COMPARATIVO!G$34</f>
         <v>73292.9343189086</v>
       </c>
-      <c r="S17" s="121" t="n">
+      <c r="S17" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>9423.03078828087</v>
       </c>
-      <c r="T17" s="121" t="n">
+      <c r="T17" s="123" t="n">
         <f aca="false">T16+S17</f>
         <v>81809.509993163</v>
       </c>
-      <c r="U17" s="121" t="n">
+      <c r="U17" s="123" t="n">
         <f aca="false">T17-COMPARATIVO!H$34</f>
         <v>66921.869993163</v>
       </c>
-      <c r="V17" s="121" t="n">
+      <c r="V17" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="W17" s="121" t="n">
+      <c r="W17" s="123" t="n">
         <f aca="false">W16+V17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="X17" s="121" t="n">
+      <c r="X17" s="123" t="n">
         <f aca="false">W17-COMPARATIVO!I$34</f>
         <v>76688.0830677524</v>
       </c>
-      <c r="Y17" s="121" t="n">
+      <c r="Y17" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>11954.4944443272</v>
       </c>
-      <c r="Z17" s="121" t="n">
+      <c r="Z17" s="123" t="n">
         <f aca="false">Z16+Y17</f>
         <v>103787.343443969</v>
       </c>
-      <c r="AA17" s="121" t="n">
+      <c r="AA17" s="123" t="n">
         <f aca="false">Z17-COMPARATIVO!J$34</f>
         <v>82554.3434439687</v>
       </c>
-      <c r="AB17" s="121" t="n">
+      <c r="AB17" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="AC17" s="121" t="n">
+      <c r="AC17" s="123" t="n">
         <f aca="false">AC16+AB17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="AD17" s="121" t="n">
+      <c r="AD17" s="123" t="n">
         <f aca="false">AC17-COMPARATIVO!K$34</f>
         <v>84958.5630677524</v>
       </c>
-      <c r="AE17" s="121" t="n">
+      <c r="AE17" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>11995.2735966768</v>
       </c>
-      <c r="AF17" s="121" t="n">
+      <c r="AF17" s="123" t="n">
         <f aca="false">AF16+AE17</f>
         <v>104141.382664111</v>
       </c>
-      <c r="AG17" s="121" t="n">
+      <c r="AG17" s="123" t="n">
         <f aca="false">AF17-COMPARATIVO!L$34</f>
         <v>85441.3826641111</v>
       </c>
-      <c r="AH17" s="121" t="n">
+      <c r="AH17" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="AI17" s="121" t="n">
+      <c r="AI17" s="123" t="n">
         <f aca="false">AI16+AH17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="AJ17" s="121" t="n">
+      <c r="AJ17" s="123" t="n">
         <f aca="false">AI17-COMPARATIVO!M$34</f>
         <v>74888.0830677524</v>
       </c>
-      <c r="AK17" s="121" t="n">
+      <c r="AK17" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C17/$C$6*(1+ENTRADAS!$C$27)^(12-1)</f>
         <v>12019.1371710022</v>
       </c>
-      <c r="AL17" s="121" t="n">
+      <c r="AL17" s="123" t="n">
         <f aca="false">AL16+AK17</f>
         <v>104348.563067752</v>
       </c>
-      <c r="AM17" s="121" t="n">
+      <c r="AM17" s="123" t="n">
         <f aca="false">AL17-COMPARATIVO!N$34</f>
         <v>73088.0830677524</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="120" t="n">
+      <c r="B18" s="122" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(13-1)</f>
         <v>0.928370320946576</v>
       </c>
-      <c r="D18" s="121" t="n">
+      <c r="D18" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="E18" s="121" t="n">
+      <c r="E18" s="123" t="n">
         <f aca="false">E17+D18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="F18" s="121" t="n">
+      <c r="F18" s="123" t="n">
         <f aca="false">E18-COMPARATIVO!C$34</f>
         <v>87352.4676952463</v>
       </c>
-      <c r="G18" s="121" t="n">
+      <c r="G18" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="H18" s="121" t="n">
+      <c r="H18" s="123" t="n">
         <f aca="false">H17+G18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="I18" s="121" t="n">
+      <c r="I18" s="123" t="n">
         <f aca="false">H18-COMPARATIVO!D$34</f>
         <v>88273.2676952463</v>
       </c>
-      <c r="J18" s="121" t="n">
+      <c r="J18" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12785.8729743553</v>
       </c>
-      <c r="K18" s="121" t="n">
+      <c r="K18" s="123" t="n">
         <f aca="false">K17+J18</f>
         <v>116998.063482495</v>
       </c>
-      <c r="L18" s="121" t="n">
+      <c r="L18" s="123" t="n">
         <f aca="false">K18-COMPARATIVO!E$34</f>
         <v>98477.7234824949</v>
       </c>
-      <c r="M18" s="121" t="n">
+      <c r="M18" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12785.8729743553</v>
       </c>
-      <c r="N18" s="121" t="n">
+      <c r="N18" s="123" t="n">
         <f aca="false">N17+M18</f>
         <v>116998.063482495</v>
       </c>
-      <c r="O18" s="121" t="n">
+      <c r="O18" s="123" t="n">
         <f aca="false">N18-COMPARATIVO!F$34</f>
         <v>97477.7234824949</v>
       </c>
-      <c r="P18" s="121" t="n">
+      <c r="P18" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>11611.6799159477</v>
       </c>
-      <c r="Q18" s="121" t="n">
+      <c r="Q18" s="123" t="n">
         <f aca="false">Q17+P18</f>
         <v>106253.524234856</v>
       </c>
-      <c r="R18" s="121" t="n">
+      <c r="R18" s="123" t="n">
         <f aca="false">Q18-COMPARATIVO!G$34</f>
         <v>84904.6142348563</v>
       </c>
-      <c r="S18" s="121" t="n">
+      <c r="S18" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>10037.271050215</v>
       </c>
-      <c r="T18" s="121" t="n">
+      <c r="T18" s="123" t="n">
         <f aca="false">T17+S18</f>
         <v>91846.781043378</v>
       </c>
-      <c r="U18" s="121" t="n">
+      <c r="U18" s="123" t="n">
         <f aca="false">T18-COMPARATIVO!H$34</f>
         <v>76959.141043378</v>
       </c>
-      <c r="V18" s="121" t="n">
+      <c r="V18" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="W18" s="121" t="n">
+      <c r="W18" s="123" t="n">
         <f aca="false">W17+V18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="X18" s="121" t="n">
+      <c r="X18" s="123" t="n">
         <f aca="false">W18-COMPARATIVO!I$34</f>
         <v>89490.6876952463</v>
       </c>
-      <c r="Y18" s="121" t="n">
+      <c r="Y18" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12733.7481646807</v>
       </c>
-      <c r="Z18" s="121" t="n">
+      <c r="Z18" s="123" t="n">
         <f aca="false">Z17+Y18</f>
         <v>116521.091608649</v>
       </c>
-      <c r="AA18" s="121" t="n">
+      <c r="AA18" s="123" t="n">
         <f aca="false">Z18-COMPARATIVO!J$34</f>
         <v>95288.0916086493</v>
       </c>
-      <c r="AB18" s="121" t="n">
+      <c r="AB18" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="AC18" s="121" t="n">
+      <c r="AC18" s="123" t="n">
         <f aca="false">AC17+AB18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="AD18" s="121" t="n">
+      <c r="AD18" s="123" t="n">
         <f aca="false">AC18-COMPARATIVO!K$34</f>
         <v>97761.1676952463</v>
       </c>
-      <c r="AE18" s="121" t="n">
+      <c r="AE18" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12777.1855060762</v>
       </c>
-      <c r="AF18" s="121" t="n">
+      <c r="AF18" s="123" t="n">
         <f aca="false">AF17+AE18</f>
         <v>116918.568170187</v>
       </c>
-      <c r="AG18" s="121" t="n">
+      <c r="AG18" s="123" t="n">
         <f aca="false">AF18-COMPARATIVO!L$34</f>
         <v>98218.5681701873</v>
       </c>
-      <c r="AH18" s="121" t="n">
+      <c r="AH18" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="AI18" s="121" t="n">
+      <c r="AI18" s="123" t="n">
         <f aca="false">AI17+AH18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="AJ18" s="121" t="n">
+      <c r="AJ18" s="123" t="n">
         <f aca="false">AI18-COMPARATIVO!M$34</f>
         <v>87690.6876952463</v>
       </c>
-      <c r="AK18" s="121" t="n">
+      <c r="AK18" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C18/$C$6*(1+ENTRADAS!$C$27)^(13-1)</f>
         <v>12802.6046274939</v>
       </c>
-      <c r="AL18" s="121" t="n">
+      <c r="AL18" s="123" t="n">
         <f aca="false">AL17+AK18</f>
         <v>117151.167695246</v>
       </c>
-      <c r="AM18" s="121" t="n">
+      <c r="AM18" s="123" t="n">
         <f aca="false">AL18-COMPARATIVO!N$34</f>
         <v>85890.6876952463</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="120" t="n">
+      <c r="B19" s="122" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(14-1)</f>
         <v>0.924192654502317</v>
       </c>
-      <c r="D19" s="121" t="n">
+      <c r="D19" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="E19" s="121" t="n">
+      <c r="E19" s="123" t="n">
         <f aca="false">E18+D19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="F19" s="121" t="n">
+      <c r="F19" s="123" t="n">
         <f aca="false">E19-COMPARATIVO!C$34</f>
         <v>100989.610105383</v>
       </c>
-      <c r="G19" s="121" t="n">
+      <c r="G19" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="H19" s="121" t="n">
+      <c r="H19" s="123" t="n">
         <f aca="false">H18+G19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="I19" s="121" t="n">
+      <c r="I19" s="123" t="n">
         <f aca="false">H19-COMPARATIVO!D$34</f>
         <v>101910.410105383</v>
       </c>
-      <c r="J19" s="121" t="n">
+      <c r="J19" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13619.3201041887</v>
       </c>
-      <c r="K19" s="121" t="n">
+      <c r="K19" s="123" t="n">
         <f aca="false">K18+J19</f>
         <v>130617.383586684</v>
       </c>
-      <c r="L19" s="121" t="n">
+      <c r="L19" s="123" t="n">
         <f aca="false">K19-COMPARATIVO!E$34</f>
         <v>112097.043586684</v>
       </c>
-      <c r="M19" s="121" t="n">
+      <c r="M19" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13619.3201041887</v>
       </c>
-      <c r="N19" s="121" t="n">
+      <c r="N19" s="123" t="n">
         <f aca="false">N18+M19</f>
         <v>130617.383586684</v>
       </c>
-      <c r="O19" s="121" t="n">
+      <c r="O19" s="123" t="n">
         <f aca="false">N19-COMPARATIVO!F$34</f>
         <v>111097.043586684</v>
       </c>
-      <c r="P19" s="121" t="n">
+      <c r="P19" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>12368.5872712687</v>
       </c>
-      <c r="Q19" s="121" t="n">
+      <c r="Q19" s="123" t="n">
         <f aca="false">Q18+P19</f>
         <v>118622.111506125</v>
       </c>
-      <c r="R19" s="121" t="n">
+      <c r="R19" s="123" t="n">
         <f aca="false">Q19-COMPARATIVO!G$34</f>
         <v>97273.2015061251</v>
       </c>
-      <c r="S19" s="121" t="n">
+      <c r="S19" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>10691.5505636232</v>
       </c>
-      <c r="T19" s="121" t="n">
+      <c r="T19" s="123" t="n">
         <f aca="false">T18+S19</f>
         <v>102538.331607001</v>
       </c>
-      <c r="U19" s="121" t="n">
+      <c r="U19" s="123" t="n">
         <f aca="false">T19-COMPARATIVO!H$34</f>
         <v>87650.6916070012</v>
       </c>
-      <c r="V19" s="121" t="n">
+      <c r="V19" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="W19" s="121" t="n">
+      <c r="W19" s="123" t="n">
         <f aca="false">W18+V19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="X19" s="121" t="n">
+      <c r="X19" s="123" t="n">
         <f aca="false">W19-COMPARATIVO!I$34</f>
         <v>103127.830105383</v>
       </c>
-      <c r="Y19" s="121" t="n">
+      <c r="Y19" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13563.7975387954</v>
       </c>
-      <c r="Z19" s="121" t="n">
+      <c r="Z19" s="123" t="n">
         <f aca="false">Z18+Y19</f>
         <v>130084.889147445</v>
       </c>
-      <c r="AA19" s="121" t="n">
+      <c r="AA19" s="123" t="n">
         <f aca="false">Z19-COMPARATIVO!J$34</f>
         <v>108851.889147445</v>
       </c>
-      <c r="AB19" s="121" t="n">
+      <c r="AB19" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="AC19" s="121" t="n">
+      <c r="AC19" s="123" t="n">
         <f aca="false">AC18+AB19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="AD19" s="121" t="n">
+      <c r="AD19" s="123" t="n">
         <f aca="false">AC19-COMPARATIVO!K$34</f>
         <v>111398.310105383</v>
       </c>
-      <c r="AE19" s="121" t="n">
+      <c r="AE19" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13610.0663432898</v>
       </c>
-      <c r="AF19" s="121" t="n">
+      <c r="AF19" s="123" t="n">
         <f aca="false">AF18+AE19</f>
         <v>130528.634513477</v>
       </c>
-      <c r="AG19" s="121" t="n">
+      <c r="AG19" s="123" t="n">
         <f aca="false">AF19-COMPARATIVO!L$34</f>
         <v>111828.634513477</v>
       </c>
-      <c r="AH19" s="121" t="n">
+      <c r="AH19" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="AI19" s="121" t="n">
+      <c r="AI19" s="123" t="n">
         <f aca="false">AI18+AH19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="AJ19" s="121" t="n">
+      <c r="AJ19" s="123" t="n">
         <f aca="false">AI19-COMPARATIVO!M$34</f>
         <v>101327.830105383</v>
       </c>
-      <c r="AK19" s="121" t="n">
+      <c r="AK19" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C19/$C$6*(1+ENTRADAS!$C$27)^(14-1)</f>
         <v>13637.1424101371</v>
       </c>
-      <c r="AL19" s="121" t="n">
+      <c r="AL19" s="123" t="n">
         <f aca="false">AL18+AK19</f>
         <v>130788.310105383</v>
       </c>
-      <c r="AM19" s="121" t="n">
+      <c r="AM19" s="123" t="n">
         <f aca="false">AL19-COMPARATIVO!N$34</f>
         <v>99527.8301053834</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="120" t="n">
+      <c r="B20" s="122" t="n">
         <v>15</v>
       </c>
       <c r="C20" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(15-1)</f>
         <v>0.920033787557056</v>
       </c>
-      <c r="D20" s="121" t="n">
+      <c r="D20" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="E20" s="121" t="n">
+      <c r="E20" s="123" t="n">
         <f aca="false">E19+D20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="F20" s="121" t="n">
+      <c r="F20" s="123" t="n">
         <f aca="false">E20-COMPARATIVO!C$34</f>
         <v>115515.689643525</v>
       </c>
-      <c r="G20" s="121" t="n">
+      <c r="G20" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="H20" s="121" t="n">
+      <c r="H20" s="123" t="n">
         <f aca="false">H19+G20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="I20" s="121" t="n">
+      <c r="I20" s="123" t="n">
         <f aca="false">H20-COMPARATIVO!D$34</f>
         <v>116436.489643525</v>
       </c>
-      <c r="J20" s="121" t="n">
+      <c r="J20" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14507.0954851802</v>
       </c>
-      <c r="K20" s="121" t="n">
+      <c r="K20" s="123" t="n">
         <f aca="false">K19+J20</f>
         <v>145124.479071864</v>
       </c>
-      <c r="L20" s="121" t="n">
+      <c r="L20" s="123" t="n">
         <f aca="false">K20-COMPARATIVO!E$34</f>
         <v>126604.139071864</v>
       </c>
-      <c r="M20" s="121" t="n">
+      <c r="M20" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14507.0954851802</v>
       </c>
-      <c r="N20" s="121" t="n">
+      <c r="N20" s="123" t="n">
         <f aca="false">N19+M20</f>
         <v>145124.479071864</v>
       </c>
-      <c r="O20" s="121" t="n">
+      <c r="O20" s="123" t="n">
         <f aca="false">N20-COMPARATIVO!F$34</f>
         <v>125604.139071864</v>
       </c>
-      <c r="P20" s="121" t="n">
+      <c r="P20" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>13174.8336325464</v>
       </c>
-      <c r="Q20" s="121" t="n">
+      <c r="Q20" s="123" t="n">
         <f aca="false">Q19+P20</f>
         <v>131796.945138671</v>
       </c>
-      <c r="R20" s="121" t="n">
+      <c r="R20" s="123" t="n">
         <f aca="false">Q20-COMPARATIVO!G$34</f>
         <v>110448.035138671</v>
       </c>
-      <c r="S20" s="121" t="n">
+      <c r="S20" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>11388.479287113</v>
       </c>
-      <c r="T20" s="121" t="n">
+      <c r="T20" s="123" t="n">
         <f aca="false">T19+S20</f>
         <v>113926.810894114</v>
       </c>
-      <c r="U20" s="121" t="n">
+      <c r="U20" s="123" t="n">
         <f aca="false">T20-COMPARATIVO!H$34</f>
         <v>99039.1708941142</v>
       </c>
-      <c r="V20" s="121" t="n">
+      <c r="V20" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="W20" s="121" t="n">
+      <c r="W20" s="123" t="n">
         <f aca="false">W19+V20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="X20" s="121" t="n">
+      <c r="X20" s="123" t="n">
         <f aca="false">W20-COMPARATIVO!I$34</f>
         <v>117653.909643525</v>
       </c>
-      <c r="Y20" s="121" t="n">
+      <c r="Y20" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14447.9536813618</v>
       </c>
-      <c r="Z20" s="121" t="n">
+      <c r="Z20" s="123" t="n">
         <f aca="false">Z19+Y20</f>
         <v>144532.842828806</v>
       </c>
-      <c r="AA20" s="121" t="n">
+      <c r="AA20" s="123" t="n">
         <f aca="false">Z20-COMPARATIVO!J$34</f>
         <v>123299.842828806</v>
       </c>
-      <c r="AB20" s="121" t="n">
+      <c r="AB20" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="AC20" s="121" t="n">
+      <c r="AC20" s="123" t="n">
         <f aca="false">AC19+AB20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="AD20" s="121" t="n">
+      <c r="AD20" s="123" t="n">
         <f aca="false">AC20-COMPARATIVO!K$34</f>
         <v>125924.389643525</v>
       </c>
-      <c r="AE20" s="121" t="n">
+      <c r="AE20" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14497.2385178771</v>
       </c>
-      <c r="AF20" s="121" t="n">
+      <c r="AF20" s="123" t="n">
         <f aca="false">AF19+AE20</f>
         <v>145025.873031354</v>
       </c>
-      <c r="AG20" s="121" t="n">
+      <c r="AG20" s="123" t="n">
         <f aca="false">AF20-COMPARATIVO!L$34</f>
         <v>126325.873031354</v>
       </c>
-      <c r="AH20" s="121" t="n">
+      <c r="AH20" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="AI20" s="121" t="n">
+      <c r="AI20" s="123" t="n">
         <f aca="false">AI19+AH20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="AJ20" s="121" t="n">
+      <c r="AJ20" s="123" t="n">
         <f aca="false">AI20-COMPARATIVO!M$34</f>
         <v>115853.909643525</v>
       </c>
-      <c r="AK20" s="121" t="n">
+      <c r="AK20" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C20/$C$6*(1+ENTRADAS!$C$27)^(15-1)</f>
         <v>14526.0795381419</v>
       </c>
-      <c r="AL20" s="121" t="n">
+      <c r="AL20" s="123" t="n">
         <f aca="false">AL19+AK20</f>
         <v>145314.389643525</v>
       </c>
-      <c r="AM20" s="121" t="n">
+      <c r="AM20" s="123" t="n">
         <f aca="false">AL20-COMPARATIVO!N$34</f>
         <v>114053.909643525</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="120" t="n">
+      <c r="B21" s="122" t="n">
         <v>16</v>
       </c>
       <c r="C21" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(16-1)</f>
         <v>0.91589363551305</v>
       </c>
-      <c r="D21" s="121" t="n">
+      <c r="D21" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="E21" s="121" t="n">
+      <c r="E21" s="123" t="n">
         <f aca="false">E20+D21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="F21" s="121" t="n">
+      <c r="F21" s="123" t="n">
         <f aca="false">E21-COMPARATIVO!C$34</f>
         <v>130988.651676361</v>
       </c>
-      <c r="G21" s="121" t="n">
+      <c r="G21" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="H21" s="121" t="n">
+      <c r="H21" s="123" t="n">
         <f aca="false">H20+G21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="I21" s="121" t="n">
+      <c r="I21" s="123" t="n">
         <f aca="false">H21-COMPARATIVO!D$34</f>
         <v>131909.451676361</v>
       </c>
-      <c r="J21" s="121" t="n">
+      <c r="J21" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15452.7405043817</v>
       </c>
-      <c r="K21" s="121" t="n">
+      <c r="K21" s="123" t="n">
         <f aca="false">K20+J21</f>
         <v>160577.219576246</v>
       </c>
-      <c r="L21" s="121" t="n">
+      <c r="L21" s="123" t="n">
         <f aca="false">K21-COMPARATIVO!E$34</f>
         <v>142056.879576246</v>
       </c>
-      <c r="M21" s="121" t="n">
+      <c r="M21" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15452.7405043817</v>
       </c>
-      <c r="N21" s="121" t="n">
+      <c r="N21" s="123" t="n">
         <f aca="false">N20+M21</f>
         <v>160577.219576246</v>
       </c>
-      <c r="O21" s="121" t="n">
+      <c r="O21" s="123" t="n">
         <f aca="false">N21-COMPARATIVO!F$34</f>
         <v>141056.879576246</v>
       </c>
-      <c r="P21" s="121" t="n">
+      <c r="P21" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>14033.6351628839</v>
       </c>
-      <c r="Q21" s="121" t="n">
+      <c r="Q21" s="123" t="n">
         <f aca="false">Q20+P21</f>
         <v>145830.580301555</v>
       </c>
-      <c r="R21" s="121" t="n">
+      <c r="R21" s="123" t="n">
         <f aca="false">Q21-COMPARATIVO!G$34</f>
         <v>124481.670301555</v>
       </c>
-      <c r="S21" s="121" t="n">
+      <c r="S21" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>12130.8373094435</v>
       </c>
-      <c r="T21" s="121" t="n">
+      <c r="T21" s="123" t="n">
         <f aca="false">T20+S21</f>
         <v>126057.648203558</v>
       </c>
-      <c r="U21" s="121" t="n">
+      <c r="U21" s="123" t="n">
         <f aca="false">T21-COMPARATIVO!H$34</f>
         <v>111170.008203558</v>
       </c>
-      <c r="V21" s="121" t="n">
+      <c r="V21" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="W21" s="121" t="n">
+      <c r="W21" s="123" t="n">
         <f aca="false">W20+V21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="X21" s="121" t="n">
+      <c r="X21" s="123" t="n">
         <f aca="false">W21-COMPARATIVO!I$34</f>
         <v>133126.871676361</v>
       </c>
-      <c r="Y21" s="121" t="n">
+      <c r="Y21" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15389.7435420813</v>
       </c>
-      <c r="Z21" s="121" t="n">
+      <c r="Z21" s="123" t="n">
         <f aca="false">Z20+Y21</f>
         <v>159922.586370888</v>
       </c>
-      <c r="AA21" s="121" t="n">
+      <c r="AA21" s="123" t="n">
         <f aca="false">Z21-COMPARATIVO!J$34</f>
         <v>138689.586370888</v>
       </c>
-      <c r="AB21" s="121" t="n">
+      <c r="AB21" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="AC21" s="121" t="n">
+      <c r="AC21" s="123" t="n">
         <f aca="false">AC20+AB21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="AD21" s="121" t="n">
+      <c r="AD21" s="123" t="n">
         <f aca="false">AC21-COMPARATIVO!K$34</f>
         <v>141397.351676361</v>
       </c>
-      <c r="AE21" s="121" t="n">
+      <c r="AE21" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15442.241010665</v>
       </c>
-      <c r="AF21" s="121" t="n">
+      <c r="AF21" s="123" t="n">
         <f aca="false">AF20+AE21</f>
         <v>160468.114042019</v>
       </c>
-      <c r="AG21" s="121" t="n">
+      <c r="AG21" s="123" t="n">
         <f aca="false">AF21-COMPARATIVO!L$34</f>
         <v>141768.114042019</v>
       </c>
-      <c r="AH21" s="121" t="n">
+      <c r="AH21" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="AI21" s="121" t="n">
+      <c r="AI21" s="123" t="n">
         <f aca="false">AI20+AH21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="AJ21" s="121" t="n">
+      <c r="AJ21" s="123" t="n">
         <f aca="false">AI21-COMPARATIVO!M$34</f>
         <v>131326.871676361</v>
       </c>
-      <c r="AK21" s="121" t="n">
+      <c r="AK21" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C21/$C$6*(1+ENTRADAS!$C$27)^(16-1)</f>
         <v>15472.9620328357</v>
       </c>
-      <c r="AL21" s="121" t="n">
+      <c r="AL21" s="123" t="n">
         <f aca="false">AL20+AK21</f>
         <v>160787.351676361</v>
       </c>
-      <c r="AM21" s="121" t="n">
+      <c r="AM21" s="123" t="n">
         <f aca="false">AL21-COMPARATIVO!N$34</f>
         <v>129526.871676361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="120" t="n">
+      <c r="B22" s="122" t="n">
         <v>17</v>
       </c>
       <c r="C22" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(17-1)</f>
         <v>0.911772114153241</v>
       </c>
-      <c r="D22" s="121" t="n">
+      <c r="D22" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="E22" s="121" t="n">
+      <c r="E22" s="123" t="n">
         <f aca="false">E21+D22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="F22" s="121" t="n">
+      <c r="F22" s="123" t="n">
         <f aca="false">E22-COMPARATIVO!C$34</f>
         <v>147470.218739307</v>
       </c>
-      <c r="G22" s="121" t="n">
+      <c r="G22" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="H22" s="121" t="n">
+      <c r="H22" s="123" t="n">
         <f aca="false">H21+G22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="I22" s="121" t="n">
+      <c r="I22" s="123" t="n">
         <f aca="false">H22-COMPARATIVO!D$34</f>
         <v>148391.018739307</v>
       </c>
-      <c r="J22" s="121" t="n">
+      <c r="J22" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16460.0273941598</v>
       </c>
-      <c r="K22" s="121" t="n">
+      <c r="K22" s="123" t="n">
         <f aca="false">K21+J22</f>
         <v>177037.246970405</v>
       </c>
-      <c r="L22" s="121" t="n">
+      <c r="L22" s="123" t="n">
         <f aca="false">K22-COMPARATIVO!E$34</f>
         <v>158516.906970405</v>
       </c>
-      <c r="M22" s="121" t="n">
+      <c r="M22" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16460.0273941598</v>
       </c>
-      <c r="N22" s="121" t="n">
+      <c r="N22" s="123" t="n">
         <f aca="false">N21+M22</f>
         <v>177037.246970405</v>
       </c>
-      <c r="O22" s="121" t="n">
+      <c r="O22" s="123" t="n">
         <f aca="false">N22-COMPARATIVO!F$34</f>
         <v>157516.906970405</v>
       </c>
-      <c r="P22" s="121" t="n">
+      <c r="P22" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>14948.4176709765</v>
       </c>
-      <c r="Q22" s="121" t="n">
+      <c r="Q22" s="123" t="n">
         <f aca="false">Q21+P22</f>
         <v>160778.997972532</v>
       </c>
-      <c r="R22" s="121" t="n">
+      <c r="R22" s="123" t="n">
         <f aca="false">Q22-COMPARATIVO!G$34</f>
         <v>139430.087972532</v>
       </c>
-      <c r="S22" s="121" t="n">
+      <c r="S22" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>12921.5859394595</v>
       </c>
-      <c r="T22" s="121" t="n">
+      <c r="T22" s="123" t="n">
         <f aca="false">T21+S22</f>
         <v>138979.234143017</v>
       </c>
-      <c r="U22" s="121" t="n">
+      <c r="U22" s="123" t="n">
         <f aca="false">T22-COMPARATIVO!H$34</f>
         <v>124091.594143017</v>
       </c>
-      <c r="V22" s="121" t="n">
+      <c r="V22" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="W22" s="121" t="n">
+      <c r="W22" s="123" t="n">
         <f aca="false">W21+V22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="X22" s="121" t="n">
+      <c r="X22" s="123" t="n">
         <f aca="false">W22-COMPARATIVO!I$34</f>
         <v>149608.438739307</v>
       </c>
-      <c r="Y22" s="121" t="n">
+      <c r="Y22" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16392.9239748719</v>
       </c>
-      <c r="Z22" s="121" t="n">
+      <c r="Z22" s="123" t="n">
         <f aca="false">Z21+Y22</f>
         <v>176315.51034576</v>
       </c>
-      <c r="AA22" s="121" t="n">
+      <c r="AA22" s="123" t="n">
         <f aca="false">Z22-COMPARATIVO!J$34</f>
         <v>155082.51034576</v>
       </c>
-      <c r="AB22" s="121" t="n">
+      <c r="AB22" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="AC22" s="121" t="n">
+      <c r="AC22" s="123" t="n">
         <f aca="false">AC21+AB22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="AD22" s="121" t="n">
+      <c r="AD22" s="123" t="n">
         <f aca="false">AC22-COMPARATIVO!K$34</f>
         <v>157878.918739307</v>
       </c>
-      <c r="AE22" s="121" t="n">
+      <c r="AE22" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16448.8434909452</v>
       </c>
-      <c r="AF22" s="121" t="n">
+      <c r="AF22" s="123" t="n">
         <f aca="false">AF21+AE22</f>
         <v>176916.957532964</v>
       </c>
-      <c r="AG22" s="121" t="n">
+      <c r="AG22" s="123" t="n">
         <f aca="false">AF22-COMPARATIVO!L$34</f>
         <v>158216.957532964</v>
       </c>
-      <c r="AH22" s="121" t="n">
+      <c r="AH22" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="AI22" s="121" t="n">
+      <c r="AI22" s="123" t="n">
         <f aca="false">AI21+AH22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="AJ22" s="121" t="n">
+      <c r="AJ22" s="123" t="n">
         <f aca="false">AI22-COMPARATIVO!M$34</f>
         <v>147808.438739307</v>
       </c>
-      <c r="AK22" s="121" t="n">
+      <c r="AK22" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C22/$C$6*(1+ENTRADAS!$C$27)^(17-1)</f>
         <v>16481.5670629461</v>
       </c>
-      <c r="AL22" s="121" t="n">
+      <c r="AL22" s="123" t="n">
         <f aca="false">AL21+AK22</f>
         <v>177268.918739307</v>
       </c>
-      <c r="AM22" s="121" t="n">
+      <c r="AM22" s="123" t="n">
         <f aca="false">AL22-COMPARATIVO!N$34</f>
         <v>146008.438739307</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="120" t="n">
+      <c r="B23" s="122" t="n">
         <v>18</v>
       </c>
       <c r="C23" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(18-1)</f>
         <v>0.907669139639551</v>
       </c>
-      <c r="D23" s="121" t="n">
+      <c r="D23" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="E23" s="121" t="n">
+      <c r="E23" s="123" t="n">
         <f aca="false">E22+D23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="F23" s="121" t="n">
+      <c r="F23" s="123" t="n">
         <f aca="false">E23-COMPARATIVO!C$34</f>
         <v>165026.136751251</v>
       </c>
-      <c r="G23" s="121" t="n">
+      <c r="G23" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="H23" s="121" t="n">
+      <c r="H23" s="123" t="n">
         <f aca="false">H22+G23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="I23" s="121" t="n">
+      <c r="I23" s="123" t="n">
         <f aca="false">H23-COMPARATIVO!D$34</f>
         <v>165946.936751251</v>
       </c>
-      <c r="J23" s="121" t="n">
+      <c r="J23" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17532.9742798481</v>
       </c>
-      <c r="K23" s="121" t="n">
+      <c r="K23" s="123" t="n">
         <f aca="false">K22+J23</f>
         <v>194570.221250253</v>
       </c>
-      <c r="L23" s="121" t="n">
+      <c r="L23" s="123" t="n">
         <f aca="false">K23-COMPARATIVO!E$34</f>
         <v>176049.881250253</v>
       </c>
-      <c r="M23" s="121" t="n">
+      <c r="M23" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17532.9742798481</v>
       </c>
-      <c r="N23" s="121" t="n">
+      <c r="N23" s="123" t="n">
         <f aca="false">N22+M23</f>
         <v>194570.221250253</v>
       </c>
-      <c r="O23" s="121" t="n">
+      <c r="O23" s="123" t="n">
         <f aca="false">N23-COMPARATIVO!F$34</f>
         <v>175049.881250253</v>
       </c>
-      <c r="P23" s="121" t="n">
+      <c r="P23" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>15922.8302768591</v>
       </c>
-      <c r="Q23" s="121" t="n">
+      <c r="Q23" s="123" t="n">
         <f aca="false">Q22+P23</f>
         <v>176701.828249391</v>
       </c>
-      <c r="R23" s="121" t="n">
+      <c r="R23" s="123" t="n">
         <f aca="false">Q23-COMPARATIVO!G$34</f>
         <v>155352.918249391</v>
       </c>
-      <c r="S23" s="121" t="n">
+      <c r="S23" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>13763.8795189232</v>
       </c>
-      <c r="T23" s="121" t="n">
+      <c r="T23" s="123" t="n">
         <f aca="false">T22+S23</f>
         <v>152743.11366194</v>
       </c>
-      <c r="U23" s="121" t="n">
+      <c r="U23" s="123" t="n">
         <f aca="false">T23-COMPARATIVO!H$34</f>
         <v>137855.47366194</v>
       </c>
-      <c r="V23" s="121" t="n">
+      <c r="V23" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="W23" s="121" t="n">
+      <c r="W23" s="123" t="n">
         <f aca="false">W22+V23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="X23" s="121" t="n">
+      <c r="X23" s="123" t="n">
         <f aca="false">W23-COMPARATIVO!I$34</f>
         <v>167164.356751251</v>
       </c>
-      <c r="Y23" s="121" t="n">
+      <c r="Y23" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17461.4967241739</v>
       </c>
-      <c r="Z23" s="121" t="n">
+      <c r="Z23" s="123" t="n">
         <f aca="false">Z22+Y23</f>
         <v>193777.007069934</v>
       </c>
-      <c r="AA23" s="121" t="n">
+      <c r="AA23" s="123" t="n">
         <f aca="false">Z23-COMPARATIVO!J$34</f>
         <v>172544.007069934</v>
       </c>
-      <c r="AB23" s="121" t="n">
+      <c r="AB23" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="AC23" s="121" t="n">
+      <c r="AC23" s="123" t="n">
         <f aca="false">AC22+AB23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="AD23" s="121" t="n">
+      <c r="AD23" s="123" t="n">
         <f aca="false">AC23-COMPARATIVO!K$34</f>
         <v>175434.836751251</v>
       </c>
-      <c r="AE23" s="121" t="n">
+      <c r="AE23" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17521.0613539024</v>
       </c>
-      <c r="AF23" s="121" t="n">
+      <c r="AF23" s="123" t="n">
         <f aca="false">AF22+AE23</f>
         <v>194438.018886867</v>
       </c>
-      <c r="AG23" s="121" t="n">
+      <c r="AG23" s="123" t="n">
         <f aca="false">AF23-COMPARATIVO!L$34</f>
         <v>175738.018886867</v>
       </c>
-      <c r="AH23" s="121" t="n">
+      <c r="AH23" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="AI23" s="121" t="n">
+      <c r="AI23" s="123" t="n">
         <f aca="false">AI22+AH23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="AJ23" s="121" t="n">
+      <c r="AJ23" s="123" t="n">
         <f aca="false">AI23-COMPARATIVO!M$34</f>
         <v>165364.356751251</v>
       </c>
-      <c r="AK23" s="121" t="n">
+      <c r="AK23" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C23/$C$6*(1+ENTRADAS!$C$27)^(18-1)</f>
         <v>17555.9180119442</v>
       </c>
-      <c r="AL23" s="121" t="n">
+      <c r="AL23" s="123" t="n">
         <f aca="false">AL22+AK23</f>
         <v>194824.836751251</v>
       </c>
-      <c r="AM23" s="121" t="n">
+      <c r="AM23" s="123" t="n">
         <f aca="false">AL23-COMPARATIVO!N$34</f>
         <v>163564.356751251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="120" t="n">
+      <c r="B24" s="122" t="n">
         <v>19</v>
       </c>
       <c r="C24" s="40" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(19-1)</f>
         <v>0.903584628511173</v>
       </c>
-      <c r="D24" s="121" t="n">
+      <c r="D24" s="123" t="n">
         <f aca="false">ECONOMIA!C$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="E24" s="121" t="n">
+      <c r="E24" s="123" t="n">
         <f aca="false">E23+D24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="F24" s="121" t="n">
+      <c r="F24" s="123" t="n">
         <f aca="false">E24-COMPARATIVO!C$34</f>
         <v>183726.437278804</v>
       </c>
-      <c r="G24" s="121" t="n">
+      <c r="G24" s="123" t="n">
         <f aca="false">ECONOMIA!D$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="H24" s="121" t="n">
+      <c r="H24" s="123" t="n">
         <f aca="false">H23+G24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="I24" s="121" t="n">
+      <c r="I24" s="123" t="n">
         <f aca="false">H24-COMPARATIVO!D$34</f>
         <v>184647.237278804</v>
       </c>
-      <c r="J24" s="121" t="n">
+      <c r="J24" s="123" t="n">
         <f aca="false">ECONOMIA!E$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18675.86120828</v>
       </c>
-      <c r="K24" s="121" t="n">
+      <c r="K24" s="123" t="n">
         <f aca="false">K23+J24</f>
         <v>213246.082458533</v>
       </c>
-      <c r="L24" s="121" t="n">
+      <c r="L24" s="123" t="n">
         <f aca="false">K24-COMPARATIVO!E$34</f>
         <v>194725.742458533</v>
       </c>
-      <c r="M24" s="121" t="n">
+      <c r="M24" s="123" t="n">
         <f aca="false">ECONOMIA!F$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18675.86120828</v>
       </c>
-      <c r="N24" s="121" t="n">
+      <c r="N24" s="123" t="n">
         <f aca="false">N23+M24</f>
         <v>213246.082458533</v>
       </c>
-      <c r="O24" s="121" t="n">
+      <c r="O24" s="123" t="n">
         <f aca="false">N24-COMPARATIVO!F$34</f>
         <v>193725.742458533</v>
       </c>
-      <c r="P24" s="121" t="n">
+      <c r="P24" s="123" t="n">
         <f aca="false">ECONOMIA!G$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>16960.7599684562</v>
       </c>
-      <c r="Q24" s="121" t="n">
+      <c r="Q24" s="123" t="n">
         <f aca="false">Q23+P24</f>
         <v>193662.588217847</v>
       </c>
-      <c r="R24" s="121" t="n">
+      <c r="R24" s="123" t="n">
         <f aca="false">Q24-COMPARATIVO!G$34</f>
         <v>172313.678217847</v>
       </c>
-      <c r="S24" s="121" t="n">
+      <c r="S24" s="123" t="n">
         <f aca="false">ECONOMIA!H$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>14661.0780053642</v>
       </c>
-      <c r="T24" s="121" t="n">
+      <c r="T24" s="123" t="n">
         <f aca="false">T23+S24</f>
         <v>167404.191667305</v>
       </c>
-      <c r="U24" s="121" t="n">
+      <c r="U24" s="123" t="n">
         <f aca="false">T24-COMPARATIVO!H$34</f>
         <v>152516.551667305</v>
       </c>
-      <c r="V24" s="121" t="n">
+      <c r="V24" s="123" t="n">
         <f aca="false">ECONOMIA!I$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="W24" s="121" t="n">
+      <c r="W24" s="123" t="n">
         <f aca="false">W23+V24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="X24" s="121" t="n">
+      <c r="X24" s="123" t="n">
         <f aca="false">W24-COMPARATIVO!I$34</f>
         <v>185864.657278804</v>
       </c>
-      <c r="Y24" s="121" t="n">
+      <c r="Y24" s="123" t="n">
         <f aca="false">ECONOMIA!J$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18599.7243881392</v>
       </c>
-      <c r="Z24" s="121" t="n">
+      <c r="Z24" s="123" t="n">
         <f aca="false">Z23+Y24</f>
         <v>212376.731458073</v>
       </c>
-      <c r="AA24" s="121" t="n">
+      <c r="AA24" s="123" t="n">
         <f aca="false">Z24-COMPARATIVO!J$34</f>
         <v>191143.731458073</v>
       </c>
-      <c r="AB24" s="121" t="n">
+      <c r="AB24" s="123" t="n">
         <f aca="false">ECONOMIA!K$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="AC24" s="121" t="n">
+      <c r="AC24" s="123" t="n">
         <f aca="false">AC23+AB24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="AD24" s="121" t="n">
+      <c r="AD24" s="123" t="n">
         <f aca="false">AC24-COMPARATIVO!K$34</f>
         <v>194135.137278804</v>
       </c>
-      <c r="AE24" s="121" t="n">
+      <c r="AE24" s="123" t="n">
         <f aca="false">ECONOMIA!L$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18663.1717382566</v>
       </c>
-      <c r="AF24" s="121" t="n">
+      <c r="AF24" s="123" t="n">
         <f aca="false">AF23+AE24</f>
         <v>213101.190625123</v>
       </c>
-      <c r="AG24" s="121" t="n">
+      <c r="AG24" s="123" t="n">
         <f aca="false">AF24-COMPARATIVO!L$34</f>
         <v>194401.190625123</v>
       </c>
-      <c r="AH24" s="121" t="n">
+      <c r="AH24" s="123" t="n">
         <f aca="false">ECONOMIA!M$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="AI24" s="121" t="n">
+      <c r="AI24" s="123" t="n">
         <f aca="false">AI23+AH24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="AJ24" s="121" t="n">
+      <c r="AJ24" s="123" t="n">
         <f aca="false">AI24-COMPARATIVO!M$34</f>
         <v>184064.657278804</v>
       </c>
-      <c r="AK24" s="121" t="n">
+      <c r="AK24" s="123" t="n">
         <f aca="false">ECONOMIA!N$26*C24/$C$6*(1+ENTRADAS!$C$27)^(19-1)</f>
         <v>18700.3005275528</v>
       </c>
-      <c r="AL24" s="121" t="n">
+      <c r="AL24" s="123" t="n">
         <f aca="false">AL23+AK24</f>
         <v>213525.137278804</v>
       </c>
-      <c r="AM24" s="121" t="n">
+      <c r="AM24" s="123" t="n">
         <f aca="false">AL24-COMPARATIVO!N$34</f>
         <v>182264.657278804</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="122" t="n">
+      <c r="B25" s="124" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="123" t="n">
+      <c r="C25" s="125" t="n">
         <f aca="false">(1-ENTRADAS!$C$33)*(1-ENTRADAS!$C$34)^(20-1)</f>
         <v>0.899518497682873</v>
       </c>
-      <c r="D25" s="124" t="n">
+      <c r="D25" s="126" t="n">
         <f aca="false">ECONOMIA!C$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="E25" s="124" t="n">
+      <c r="E25" s="126" t="n">
         <f aca="false">E24+D25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="F25" s="124" t="n">
+      <c r="F25" s="126" t="n">
         <f aca="false">E25-COMPARATIVO!C$34</f>
         <v>203645.716896246</v>
       </c>
-      <c r="G25" s="124" t="n">
+      <c r="G25" s="126" t="n">
         <f aca="false">ECONOMIA!D$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="H25" s="124" t="n">
+      <c r="H25" s="126" t="n">
         <f aca="false">H24+G25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="I25" s="124" t="n">
+      <c r="I25" s="126" t="n">
         <f aca="false">H25-COMPARATIVO!D$34</f>
         <v>204566.516896246</v>
       </c>
-      <c r="J25" s="124" t="n">
+      <c r="J25" s="126" t="n">
         <f aca="false">ECONOMIA!E$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19893.2472211418</v>
       </c>
-      <c r="K25" s="124" t="n">
+      <c r="K25" s="126" t="n">
         <f aca="false">K24+J25</f>
         <v>233139.329679675</v>
       </c>
-      <c r="L25" s="124" t="n">
+      <c r="L25" s="126" t="n">
         <f aca="false">K25-COMPARATIVO!E$34</f>
         <v>214618.989679675</v>
       </c>
-      <c r="M25" s="124" t="n">
+      <c r="M25" s="126" t="n">
         <f aca="false">ECONOMIA!F$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19893.2472211418</v>
       </c>
-      <c r="N25" s="124" t="n">
+      <c r="N25" s="126" t="n">
         <f aca="false">N24+M25</f>
         <v>233139.329679675</v>
       </c>
-      <c r="O25" s="124" t="n">
+      <c r="O25" s="126" t="n">
         <f aca="false">N25-COMPARATIVO!F$34</f>
         <v>213618.989679675</v>
       </c>
-      <c r="P25" s="124" t="n">
+      <c r="P25" s="126" t="n">
         <f aca="false">ECONOMIA!G$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>18066.347107</v>
       </c>
-      <c r="Q25" s="124" t="n">
+      <c r="Q25" s="126" t="n">
         <f aca="false">Q24+P25</f>
         <v>211728.935324847</v>
       </c>
-      <c r="R25" s="124" t="n">
+      <c r="R25" s="126" t="n">
         <f aca="false">Q25-COMPARATIVO!G$34</f>
         <v>190380.025324847</v>
       </c>
-      <c r="S25" s="124" t="n">
+      <c r="S25" s="126" t="n">
         <f aca="false">ECONOMIA!H$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>15616.7603751439</v>
       </c>
-      <c r="T25" s="124" t="n">
+      <c r="T25" s="126" t="n">
         <f aca="false">T24+S25</f>
         <v>183020.952042449</v>
       </c>
-      <c r="U25" s="124" t="n">
+      <c r="U25" s="126" t="n">
         <f aca="false">T25-COMPARATIVO!H$34</f>
         <v>168133.312042449</v>
       </c>
-      <c r="V25" s="124" t="n">
+      <c r="V25" s="126" t="n">
         <f aca="false">ECONOMIA!I$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="W25" s="124" t="n">
+      <c r="W25" s="126" t="n">
         <f aca="false">W24+V25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="X25" s="124" t="n">
+      <c r="X25" s="126" t="n">
         <f aca="false">W25-COMPARATIVO!I$34</f>
         <v>205783.936896246</v>
       </c>
-      <c r="Y25" s="124" t="n">
+      <c r="Y25" s="126" t="n">
         <f aca="false">ECONOMIA!J$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19812.1474223801</v>
       </c>
-      <c r="Z25" s="124" t="n">
+      <c r="Z25" s="126" t="n">
         <f aca="false">Z24+Y25</f>
         <v>232188.878880453</v>
       </c>
-      <c r="AA25" s="124" t="n">
+      <c r="AA25" s="126" t="n">
         <f aca="false">Z25-COMPARATIVO!J$34</f>
         <v>210955.878880453</v>
       </c>
-      <c r="AB25" s="124" t="n">
+      <c r="AB25" s="126" t="n">
         <f aca="false">ECONOMIA!K$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="AC25" s="124" t="n">
+      <c r="AC25" s="126" t="n">
         <f aca="false">AC24+AB25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="AD25" s="124" t="n">
+      <c r="AD25" s="126" t="n">
         <f aca="false">AC25-COMPARATIVO!K$34</f>
         <v>214054.416896246</v>
       </c>
-      <c r="AE25" s="124" t="n">
+      <c r="AE25" s="126" t="n">
         <f aca="false">ECONOMIA!L$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19879.7305880148</v>
       </c>
-      <c r="AF25" s="124" t="n">
+      <c r="AF25" s="126" t="n">
         <f aca="false">AF24+AE25</f>
         <v>232980.921213138</v>
       </c>
-      <c r="AG25" s="124" t="n">
+      <c r="AG25" s="126" t="n">
         <f aca="false">AF25-COMPARATIVO!L$34</f>
         <v>214280.921213138</v>
       </c>
-      <c r="AH25" s="124" t="n">
+      <c r="AH25" s="126" t="n">
         <f aca="false">ECONOMIA!M$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="AI25" s="124" t="n">
+      <c r="AI25" s="126" t="n">
         <f aca="false">AI24+AH25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="AJ25" s="124" t="n">
+      <c r="AJ25" s="126" t="n">
         <f aca="false">AI25-COMPARATIVO!M$34</f>
         <v>203983.936896246</v>
       </c>
-      <c r="AK25" s="124" t="n">
+      <c r="AK25" s="126" t="n">
         <f aca="false">ECONOMIA!N$26*C25/$C$6*(1+ENTRADAS!$C$27)^(20-1)</f>
         <v>19919.2796174414</v>
       </c>
-      <c r="AL25" s="124" t="n">
+      <c r="AL25" s="126" t="n">
         <f aca="false">AL24+AK25</f>
         <v>233444.416896246</v>
       </c>
-      <c r="AM25" s="124" t="n">
+      <c r="AM25" s="126" t="n">
         <f aca="false">AL25-COMPARATIVO!N$34</f>
         <v>202183.936896246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>1166</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>1167</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>1168</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>1169</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
@@ -8795,23 +8980,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1170</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1171</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="21" t="s">
-        <v>1172</v>
+        <v>1228</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1173</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8819,25 +9004,25 @@
         <v>292</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1174</v>
+        <v>1230</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1175</v>
+        <v>1231</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>1176</v>
+        <v>1232</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>1177</v>
+        <v>1233</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>1178</v>
+        <v>1234</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>1179</v>
+        <v>1235</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>1180</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9263,32 +9448,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>1181</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>1182</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>1183</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>1184</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>1185</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>1186</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9296,12 +9481,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>1187</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>1188</v>
+        <v>1244</v>
       </c>
     </row>
   </sheetData>
@@ -9320,7 +9505,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9332,32 +9517,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1189</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1190</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1191</v>
+        <v>1247</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1192</v>
+        <v>1248</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1193</v>
+        <v>1249</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1194</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>1195</v>
+        <v>1251</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -9366,54 +9551,54 @@
       <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="125" t="s">
-        <v>1196</v>
+      <c r="C6" s="127" t="s">
+        <v>1252</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E6" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="125" t="s">
-        <v>1198</v>
+      <c r="C7" s="127" t="s">
+        <v>1254</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E7" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E7" s="128"/>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="125" t="s">
-        <v>1199</v>
+      <c r="C8" s="127" t="s">
+        <v>1255</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E8" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E8" s="128"/>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="125" t="s">
-        <v>1200</v>
+      <c r="C9" s="127" t="s">
+        <v>1256</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E9" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E9" s="128"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
       <c r="C10" s="7" t="s">
-        <v>1201</v>
+        <v>1257</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -9422,1025 +9607,1061 @@
       <c r="B11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="127" t="s">
-        <v>1202</v>
+      <c r="C11" s="129" t="s">
+        <v>1258</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E11" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E11" s="128"/>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="125" t="s">
-        <v>1203</v>
+      <c r="C12" s="127" t="s">
+        <v>1259</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E12" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E12" s="128"/>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="125" t="s">
-        <v>1204</v>
+      <c r="C13" s="127" t="s">
+        <v>1260</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E13" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E13" s="128"/>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="127" t="s">
-        <v>1205</v>
+      <c r="C14" s="129" t="s">
+        <v>1261</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E14" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E14" s="128"/>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="125" t="s">
-        <v>1206</v>
+      <c r="C15" s="127" t="s">
+        <v>1262</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E15" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E15" s="128"/>
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="125" t="s">
-        <v>1207</v>
+      <c r="C16" s="127" t="s">
+        <v>1263</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E16" s="126"/>
-    </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E16" s="128"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="125" t="s">
-        <v>1208</v>
+      <c r="C17" s="129" t="s">
+        <v>1264</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E17" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E17" s="128"/>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="125" t="s">
-        <v>1209</v>
+      <c r="C18" s="127" t="s">
+        <v>1265</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E18" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E18" s="128"/>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="127" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E19" s="128"/>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="125" t="s">
-        <v>1210</v>
+        <v>14</v>
+      </c>
+      <c r="C20" s="127" t="s">
+        <v>1267</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E20" s="126"/>
-    </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E20" s="128"/>
+    </row>
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>1211</v>
+        <v>15</v>
+      </c>
+      <c r="C21" s="127" t="s">
+        <v>1268</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E21" s="126"/>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="125" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E22" s="126"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E21" s="128"/>
+    </row>
+    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="125" t="s">
-        <v>1213</v>
+      <c r="C23" s="127" t="s">
+        <v>1269</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E23" s="126"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E23" s="128"/>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="125" t="s">
-        <v>1214</v>
+      <c r="C24" s="127" t="s">
+        <v>1270</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E24" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E24" s="128"/>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="125" t="s">
-        <v>1215</v>
+      <c r="C25" s="127" t="s">
+        <v>1271</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E25" s="126"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E25" s="128"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="125" t="s">
-        <v>1216</v>
+      <c r="C26" s="127" t="s">
+        <v>1272</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E26" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E26" s="128"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8"/>
-      <c r="C27" s="7" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="127" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E27" s="128"/>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" s="127" t="s">
-        <v>1218</v>
+        <v>1274</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E28" s="126"/>
-    </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E28" s="128"/>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="127" t="s">
-        <v>1219</v>
+        <v>1275</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E29" s="126"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="127" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E30" s="126"/>
-    </row>
-    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E29" s="128"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="8"/>
+      <c r="C30" s="7" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C31" s="125" t="s">
-        <v>1221</v>
+      <c r="C31" s="129" t="s">
+        <v>1277</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E31" s="126"/>
-    </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E31" s="128"/>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="125" t="s">
-        <v>1222</v>
+      <c r="C32" s="129" t="s">
+        <v>1278</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E32" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E32" s="128"/>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C33" s="127" t="s">
-        <v>1223</v>
+      <c r="C33" s="129" t="s">
+        <v>1279</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E33" s="126"/>
-    </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E33" s="128"/>
+    </row>
+    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="n">
         <v>26</v>
       </c>
       <c r="C34" s="127" t="s">
-        <v>1224</v>
+        <v>1280</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E34" s="126"/>
-    </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E34" s="128"/>
+    </row>
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="n">
         <v>27</v>
       </c>
       <c r="C35" s="127" t="s">
-        <v>1225</v>
+        <v>1281</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E35" s="126"/>
-    </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E35" s="128"/>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C36" s="125" t="s">
-        <v>1226</v>
+      <c r="C36" s="129" t="s">
+        <v>1282</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E36" s="126"/>
-    </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E36" s="128"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C37" s="125" t="s">
-        <v>1227</v>
+      <c r="C37" s="129" t="s">
+        <v>1283</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E37" s="126"/>
-    </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E37" s="128"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C38" s="125" t="s">
-        <v>1228</v>
+      <c r="C38" s="129" t="s">
+        <v>1284</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E38" s="126"/>
-    </row>
-    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E38" s="128"/>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="C39" s="125" t="s">
-        <v>1229</v>
+      <c r="C39" s="127" t="s">
+        <v>1285</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E39" s="126"/>
-    </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E39" s="128"/>
+    </row>
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="C40" s="125" t="s">
-        <v>1230</v>
+      <c r="C40" s="127" t="s">
+        <v>1286</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E40" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E40" s="128"/>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="C41" s="125" t="s">
-        <v>1231</v>
+      <c r="C41" s="127" t="s">
+        <v>1287</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E41" s="126"/>
-    </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E41" s="128"/>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="n">
         <v>34</v>
       </c>
       <c r="C42" s="127" t="s">
-        <v>1232</v>
+        <v>1288</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E42" s="126"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8"/>
-      <c r="C44" s="7" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-    </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E42" s="128"/>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C43" s="127" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E43" s="128"/>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C44" s="127" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E44" s="128"/>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C45" s="125" t="s">
-        <v>1234</v>
+        <v>37</v>
+      </c>
+      <c r="C45" s="129" t="s">
+        <v>1291</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E45" s="126"/>
-    </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="C46" s="125" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E46" s="126"/>
-    </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="C47" s="125" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E47" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E45" s="128"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="8"/>
+      <c r="C47" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="C48" s="125" t="s">
-        <v>1237</v>
+      <c r="C48" s="127" t="s">
+        <v>1293</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E48" s="126"/>
-    </row>
-    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E48" s="128"/>
+    </row>
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="n">
         <v>39</v>
       </c>
       <c r="C49" s="127" t="s">
-        <v>1238</v>
+        <v>1294</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E49" s="126"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="8"/>
-      <c r="C51" s="7" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
+        <v>1253</v>
+      </c>
+      <c r="E49" s="128"/>
+    </row>
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C50" s="127" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E50" s="128"/>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C51" s="127" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E51" s="128"/>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C52" s="127" t="s">
-        <v>1240</v>
+        <v>42</v>
+      </c>
+      <c r="C52" s="129" t="s">
+        <v>1297</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E52" s="126"/>
-    </row>
-    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="C53" s="125" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E53" s="126"/>
-    </row>
-    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="C54" s="125" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E54" s="126"/>
-    </row>
-    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E52" s="128"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="8"/>
+      <c r="C54" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="C55" s="125" t="s">
-        <v>1243</v>
+      <c r="C55" s="129" t="s">
+        <v>1299</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E55" s="126"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="8"/>
-      <c r="C57" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-    </row>
-    <row r="58" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E55" s="128"/>
+    </row>
+    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C56" s="127" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E56" s="128"/>
+    </row>
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="C57" s="127" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E57" s="128"/>
+    </row>
+    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="C58" s="125" t="s">
-        <v>1245</v>
+        <v>46</v>
+      </c>
+      <c r="C58" s="127" t="s">
+        <v>1302</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E58" s="126"/>
-    </row>
-    <row r="59" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="C59" s="125" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E59" s="126"/>
-    </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="C60" s="127" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E60" s="126"/>
-    </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E58" s="128"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8"/>
+      <c r="C60" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="n">
         <v>47</v>
       </c>
       <c r="C61" s="127" t="s">
-        <v>1248</v>
+        <v>1304</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E61" s="126"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E61" s="128"/>
+    </row>
+    <row r="62" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="C62" s="125" t="s">
-        <v>1249</v>
+      <c r="C62" s="127" t="s">
+        <v>1305</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E62" s="126"/>
-    </row>
-    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E62" s="128"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="C63" s="125" t="s">
-        <v>1250</v>
+      <c r="C63" s="129" t="s">
+        <v>1306</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E63" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E63" s="128"/>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C64" s="127" t="s">
-        <v>1251</v>
+      <c r="C64" s="129" t="s">
+        <v>1307</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E64" s="126"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="8"/>
-      <c r="C66" s="7" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-    </row>
-    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E64" s="128"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C65" s="127" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E65" s="128"/>
+    </row>
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="C66" s="127" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E66" s="128"/>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="C67" s="125" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="129" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>1253</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E67" s="126"/>
-    </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="C68" s="125" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E68" s="126"/>
-    </row>
-    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="C69" s="125" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E69" s="126"/>
-    </row>
-    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="128"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="8"/>
+      <c r="C69" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="C70" s="125" t="s">
-        <v>1256</v>
+      <c r="C70" s="127" t="s">
+        <v>1312</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E70" s="126"/>
-    </row>
-    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E70" s="128"/>
+    </row>
+    <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="C71" s="125" t="s">
-        <v>1257</v>
+      <c r="C71" s="127" t="s">
+        <v>1313</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E71" s="126"/>
-    </row>
-    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E71" s="128"/>
+    </row>
+    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="C72" s="125" t="s">
-        <v>1258</v>
+      <c r="C72" s="127" t="s">
+        <v>1314</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E72" s="126"/>
-    </row>
-    <row r="73" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E72" s="128"/>
+    </row>
+    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="C73" s="125" t="s">
-        <v>1259</v>
+      <c r="C73" s="127" t="s">
+        <v>1315</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E73" s="126"/>
-    </row>
-    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E73" s="128"/>
+    </row>
+    <row r="74" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="C74" s="125" t="s">
-        <v>1260</v>
+      <c r="C74" s="127" t="s">
+        <v>1316</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E74" s="126"/>
-    </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E74" s="128"/>
+    </row>
+    <row r="75" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="C75" s="125" t="s">
-        <v>1261</v>
+      <c r="C75" s="127" t="s">
+        <v>1317</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E75" s="126"/>
-    </row>
-    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E75" s="128"/>
+    </row>
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C76" s="125" t="s">
-        <v>1262</v>
+      <c r="C76" s="127" t="s">
+        <v>1318</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E76" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E76" s="128"/>
     </row>
     <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="C77" s="125" t="s">
-        <v>1263</v>
+      <c r="C77" s="127" t="s">
+        <v>1319</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E77" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E77" s="128"/>
     </row>
     <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="C78" s="125" t="s">
-        <v>1264</v>
+      <c r="C78" s="127" t="s">
+        <v>1320</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E78" s="126"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E78" s="128"/>
+    </row>
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="C79" s="125" t="s">
-        <v>1265</v>
+      <c r="C79" s="127" t="s">
+        <v>1321</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E79" s="126"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="8"/>
-      <c r="C81" s="7" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+        <v>1253</v>
+      </c>
+      <c r="E79" s="128"/>
+    </row>
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C80" s="127" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E80" s="128"/>
+    </row>
+    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="C81" s="127" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E81" s="128"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C82" s="127" t="s">
-        <v>1267</v>
+        <v>1324</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E82" s="126"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="C83" s="127" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E83" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E82" s="128"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="C84" s="127" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E84" s="126"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="C85" s="127" t="s">
-        <v>1270</v>
+      <c r="C85" s="129" t="s">
+        <v>1326</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E85" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E85" s="128"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="C86" s="127" t="s">
-        <v>1271</v>
+      <c r="C86" s="129" t="s">
+        <v>1327</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E86" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E86" s="128"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="C87" s="127" t="s">
-        <v>1272</v>
+      <c r="C87" s="129" t="s">
+        <v>1328</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E87" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E87" s="128"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="C88" s="127" t="s">
-        <v>1273</v>
+      <c r="C88" s="129" t="s">
+        <v>1329</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E88" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E88" s="128"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="C89" s="127" t="s">
-        <v>1274</v>
+      <c r="C89" s="129" t="s">
+        <v>1330</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E89" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E89" s="128"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="C90" s="127" t="s">
-        <v>1275</v>
+      <c r="C90" s="129" t="s">
+        <v>1331</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E90" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E90" s="128"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="C91" s="129" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E91" s="128"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="8"/>
-      <c r="C92" s="7" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
+      <c r="B92" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="C92" s="129" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E92" s="128"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="C93" s="127" t="s">
-        <v>1277</v>
+        <v>75</v>
+      </c>
+      <c r="C93" s="129" t="s">
+        <v>1334</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E93" s="126"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="C94" s="127" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E94" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E93" s="128"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="C95" s="127" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E95" s="126"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="C96" s="127" t="s">
-        <v>1280</v>
+      <c r="C96" s="129" t="s">
+        <v>1336</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E96" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E96" s="128"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="C97" s="127" t="s">
-        <v>1281</v>
+      <c r="C97" s="129" t="s">
+        <v>1337</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E97" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E97" s="128"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="C98" s="127" t="s">
-        <v>1282</v>
+      <c r="C98" s="129" t="s">
+        <v>1338</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E98" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E98" s="128"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="C99" s="127" t="s">
-        <v>1283</v>
+      <c r="C99" s="129" t="s">
+        <v>1339</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E99" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E99" s="128"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C100" s="129" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E100" s="128"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="8"/>
-      <c r="C101" s="7" t="s">
-        <v>1284</v>
-      </c>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
+      <c r="B101" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C101" s="129" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E101" s="128"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C102" s="127" t="s">
-        <v>1285</v>
+        <v>82</v>
+      </c>
+      <c r="C102" s="129" t="s">
+        <v>1342</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E102" s="126"/>
-    </row>
-    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="C103" s="127" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E103" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E102" s="128"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="C104" s="127" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E104" s="126"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="C105" s="127" t="s">
-        <v>1288</v>
+      <c r="C105" s="129" t="s">
+        <v>1344</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E105" s="126"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1253</v>
+      </c>
+      <c r="E105" s="128"/>
+    </row>
+    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="C106" s="127" t="s">
-        <v>1289</v>
+      <c r="C106" s="129" t="s">
+        <v>1345</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E106" s="126"/>
+        <v>1253</v>
+      </c>
+      <c r="E106" s="128"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="C107" s="129" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E107" s="128"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="C108" s="129" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E108" s="128"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="C109" s="129" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E109" s="128"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10470,73 +10691,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1290</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1291</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1292</v>
+        <v>1351</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1293</v>
+        <v>1352</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1294</v>
+        <v>1353</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1295</v>
+        <v>1354</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1296</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>1297</v>
+        <v>1356</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="80" t="s">
-        <v>1298</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>1299</v>
+        <v>1358</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="80" t="s">
-        <v>1300</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>1301</v>
+        <v>1360</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="80" t="s">
-        <v>1302</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="51" t="s">
-        <v>1303</v>
+        <v>1362</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="80" t="s">
-        <v>1304</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10547,7 +10768,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="80" t="s">
-        <v>1305</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10558,40 +10779,40 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="80" t="s">
-        <v>1306</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>1307</v>
+        <v>1366</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="80" t="s">
-        <v>1308</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>1309</v>
+        <v>1368</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="80" t="s">
-        <v>1310</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>1311</v>
+        <v>1370</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="80" t="s">
-        <v>1312</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10602,29 +10823,29 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="80" t="s">
-        <v>1313</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>1314</v>
+        <v>1373</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="80" t="s">
-        <v>1315</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18" t="s">
-        <v>1316</v>
+        <v>1375</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="80" t="s">
-        <v>1317</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10635,194 +10856,194 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="80" t="s">
-        <v>1318</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>1319</v>
+        <v>1378</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="80" t="s">
-        <v>1320</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>1321</v>
+        <v>1380</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="80" t="s">
-        <v>1322</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>1323</v>
+        <v>1382</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="80" t="s">
-        <v>1324</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>1325</v>
+        <v>1384</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="80" t="s">
-        <v>1326</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>1327</v>
+        <v>1386</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="80" t="s">
-        <v>1328</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>1329</v>
+        <v>1388</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="80" t="s">
-        <v>1330</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18" t="s">
-        <v>1331</v>
+        <v>1390</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="80" t="s">
-        <v>1332</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>1333</v>
+        <v>1392</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="80" t="s">
-        <v>1334</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>1335</v>
+        <v>1394</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="80" t="s">
-        <v>1336</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>1337</v>
+        <v>1396</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="80" t="s">
-        <v>1338</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="51" t="s">
-        <v>1339</v>
+        <v>1398</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="80" t="s">
-        <v>1340</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>1341</v>
+        <v>1400</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="80" t="s">
-        <v>1342</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18" t="s">
-        <v>1343</v>
+        <v>1402</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="80" t="s">
-        <v>1344</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>1345</v>
+        <v>1404</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="80" t="s">
-        <v>1346</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="18" t="s">
-        <v>1347</v>
+        <v>1406</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="80" t="s">
-        <v>1348</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>1349</v>
+        <v>1408</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="80" t="s">
-        <v>1350</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="18" t="s">
-        <v>1351</v>
+        <v>1410</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="80" t="s">
-        <v>1352</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10833,7 +11054,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="80" t="s">
-        <v>1353</v>
+        <v>1412</v>
       </c>
     </row>
   </sheetData>
@@ -18707,7 +18928,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -19715,6 +19936,388 @@
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="4" t="s">
         <v>1048</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="E101" s="17" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="18" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C102" s="118" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D102" s="118" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E102" s="106" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="18" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C103" s="118" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D103" s="118" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E103" s="106" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="18" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C104" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D104" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E104" s="106" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="18" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C105" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D105" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E105" s="106" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C106" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D106" s="117" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E106" s="106" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="18" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C107" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D107" s="117" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E107" s="106"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="18" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C108" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D108" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E108" s="106"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="18" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C109" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D109" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E109" s="106"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="18" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C110" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D110" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E110" s="106" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="18" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C111" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D111" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E111" s="106"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C112" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D112" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E112" s="106"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="18" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C113" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D113" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E113" s="106"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="18" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C114" s="115" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D114" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E114" s="106" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="18" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C115" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D115" s="117" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E115" s="106"/>
+    </row>
+    <row r="116" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="18" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C116" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D116" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E116" s="106" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="3" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <f aca="false">C119*D119</f>
+        <v>8000</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="13" t="n">
+        <v>3851.19</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <f aca="false">C120*D120</f>
+        <v>3851.19</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>2650</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <f aca="false">C121*D121</f>
+        <v>2650</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <f aca="false">C122*D122</f>
+        <v>1200</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E123" s="35" t="n">
+        <f aca="false">SUM(E119:E122)</f>
+        <v>15701.19</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E125" s="119" t="n">
+        <f aca="false">E123*(1-D124)</f>
+        <v>12560.952</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E126" s="13" t="n">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <f aca="false">E126-E125</f>
+        <v>3639.048</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="3" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="4" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="4" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="4" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="4"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="4" t="s">
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -19744,64 +20347,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1049</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1050</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>1051</v>
+        <v>1107</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1052</v>
+        <v>1108</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1053</v>
+        <v>1109</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1054</v>
+        <v>1110</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>1055</v>
+        <v>1111</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>1056</v>
+        <v>1112</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>1057</v>
+        <v>1113</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>1058</v>
+        <v>1114</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>1059</v>
+        <v>1115</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>1060</v>
+        <v>1116</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>1061</v>
+        <v>1117</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>1062</v>
+        <v>1118</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>1063</v>
+        <v>1119</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>1064</v>
+        <v>1120</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>1065</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>1066</v>
+        <v>1122</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">BYD!$G$35</f>
@@ -19853,12 +20456,12 @@
       </c>
       <c r="O5" s="116"/>
       <c r="P5" s="80" t="s">
-        <v>1067</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>1068</v>
+        <v>1124</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">COMPARATIVO!C39</f>
@@ -19910,12 +20513,12 @@
       </c>
       <c r="O6" s="116"/>
       <c r="P6" s="80" t="s">
-        <v>1069</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>1070</v>
+        <v>1126</v>
       </c>
       <c r="C7" s="111" t="n">
         <f aca="false">ENTRADAS!$C$18</f>
@@ -19967,69 +20570,69 @@
       </c>
       <c r="O7" s="116"/>
       <c r="P7" s="80" t="s">
-        <v>1071</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C8" s="118" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C8" s="120" t="n">
         <f aca="false">C5*C7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="D8" s="118" t="n">
+      <c r="D8" s="120" t="n">
         <f aca="false">D5*D7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="E8" s="118" t="n">
+      <c r="E8" s="120" t="n">
         <f aca="false">E5*E7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="F8" s="118" t="n">
+      <c r="F8" s="120" t="n">
         <f aca="false">F5*F7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="G8" s="118" t="n">
+      <c r="G8" s="120" t="n">
         <f aca="false">G5*G7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="H8" s="118" t="n">
+      <c r="H8" s="120" t="n">
         <f aca="false">H5*H7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="I8" s="118" t="n">
+      <c r="I8" s="120" t="n">
         <f aca="false">I5*I7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="J8" s="118" t="n">
+      <c r="J8" s="120" t="n">
         <f aca="false">J5*J7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="K8" s="118" t="n">
+      <c r="K8" s="120" t="n">
         <f aca="false">K5*K7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="L8" s="118" t="n">
+      <c r="L8" s="120" t="n">
         <f aca="false">L5*L7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="M8" s="118" t="n">
+      <c r="M8" s="120" t="n">
         <f aca="false">M5*M7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
-      <c r="N8" s="118" t="n">
+      <c r="N8" s="120" t="n">
         <f aca="false">N5*N7+ENTRADAS!$C$26*12</f>
         <v>8384.43967641217</v>
       </c>
       <c r="O8" s="116"/>
       <c r="P8" s="80" t="s">
-        <v>1073</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>1074</v>
+        <v>1130</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">MIN(C5,C6)*ENTRADAS!$C$37</f>
@@ -20081,12 +20684,12 @@
       </c>
       <c r="O9" s="116"/>
       <c r="P9" s="80" t="s">
-        <v>1075</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>1076</v>
+        <v>1132</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">C6-C9</f>
@@ -20138,12 +20741,12 @@
       </c>
       <c r="O10" s="116"/>
       <c r="P10" s="80" t="s">
-        <v>1077</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>1078</v>
+        <v>1134</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">ENTRADAS!$C$17*12</f>
@@ -20195,12 +20798,12 @@
       </c>
       <c r="O11" s="116"/>
       <c r="P11" s="80" t="s">
-        <v>1079</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>1080</v>
+        <v>1136</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">MAX(0,MIN(C10,C5-C9-C11))</f>
@@ -20252,12 +20855,12 @@
       </c>
       <c r="O12" s="116"/>
       <c r="P12" s="80" t="s">
-        <v>1081</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>1082</v>
+        <v>1138</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">C10-C12</f>
@@ -20309,12 +20912,12 @@
       </c>
       <c r="O13" s="116"/>
       <c r="P13" s="80" t="s">
-        <v>1083</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>1084</v>
+        <v>1140</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">MAX(C11,C5-C9-C12)</f>
@@ -20366,12 +20969,12 @@
       </c>
       <c r="O14" s="116"/>
       <c r="P14" s="80" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>1086</v>
+        <v>1142</v>
       </c>
       <c r="C15" s="111" t="n">
         <f aca="false">C14*C7</f>
@@ -20426,7 +21029,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>1087</v>
+        <v>1143</v>
       </c>
       <c r="C16" s="111" t="n">
         <f aca="false">C12*ENTRADAS!$C$25</f>
@@ -20478,12 +21081,12 @@
       </c>
       <c r="O16" s="116"/>
       <c r="P16" s="80" t="s">
-        <v>1088</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>1089</v>
+        <v>1145</v>
       </c>
       <c r="C17" s="111" t="n">
         <f aca="false">ENTRADAS!$C$26*12</f>
@@ -20535,12 +21138,12 @@
       </c>
       <c r="O17" s="116"/>
       <c r="P17" s="80" t="s">
-        <v>1090</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>1091</v>
+        <v>1147</v>
       </c>
       <c r="C18" s="50" t="n">
         <f aca="false">C15+C16+C17</f>
@@ -20592,12 +21195,12 @@
       </c>
       <c r="O18" s="116"/>
       <c r="P18" s="80" t="s">
-        <v>1092</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>1093</v>
+        <v>1149</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">C18/12</f>
@@ -20649,12 +21252,12 @@
       </c>
       <c r="O19" s="116"/>
       <c r="P19" s="80" t="s">
-        <v>1094</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>1095</v>
+        <v>1151</v>
       </c>
       <c r="C20" s="40" t="n">
         <f aca="false">IFERROR(1-C18/C8,0)</f>
@@ -20709,7 +21312,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>1096</v>
+        <v>1152</v>
       </c>
       <c r="C21" s="111" t="n">
         <f aca="false">C8-C18</f>
@@ -20764,7 +21367,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>1097</v>
+        <v>1153</v>
       </c>
       <c r="C22" s="111" t="n">
         <f aca="false">ENTRADAS!$C$35</f>
@@ -20816,12 +21419,12 @@
       </c>
       <c r="O22" s="116"/>
       <c r="P22" s="80" t="s">
-        <v>1098</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>1099</v>
+        <v>1155</v>
       </c>
       <c r="C23" s="111" t="n">
         <f aca="false">ENTRADAS!$C$36</f>
@@ -20873,12 +21476,12 @@
       </c>
       <c r="O23" s="116"/>
       <c r="P23" s="80" t="s">
-        <v>1100</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>1101</v>
+        <v>1157</v>
       </c>
       <c r="C24" s="111" t="n">
         <f aca="false">0</f>
@@ -20930,12 +21533,12 @@
       </c>
       <c r="O24" s="116"/>
       <c r="P24" s="80" t="s">
-        <v>1102</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>1103</v>
+        <v>1159</v>
       </c>
       <c r="C25" s="111" t="n">
         <f aca="false">C22+C23</f>
@@ -20990,64 +21593,64 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C26" s="119" t="n">
+        <v>1160</v>
+      </c>
+      <c r="C26" s="121" t="n">
         <f aca="false">C21-C25</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="D26" s="119" t="n">
+      <c r="D26" s="121" t="n">
         <f aca="false">D21-D25</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="E26" s="119" t="n">
+      <c r="E26" s="121" t="n">
         <f aca="false">E21-E25</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="F26" s="119" t="n">
+      <c r="F26" s="121" t="n">
         <f aca="false">F21-F25</f>
         <v>5992.80133608224</v>
       </c>
-      <c r="G26" s="119" t="n">
+      <c r="G26" s="121" t="n">
         <f aca="false">G21-G25</f>
         <v>5442.45129401962</v>
       </c>
-      <c r="H26" s="119" t="n">
+      <c r="H26" s="121" t="n">
         <f aca="false">H21-H25</f>
         <v>4704.51814131062</v>
       </c>
-      <c r="I26" s="119" t="n">
+      <c r="I26" s="121" t="n">
         <f aca="false">I21-I25</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="J26" s="119" t="n">
+      <c r="J26" s="121" t="n">
         <f aca="false">J21-J25</f>
         <v>5968.37018228556</v>
       </c>
-      <c r="K26" s="119" t="n">
+      <c r="K26" s="121" t="n">
         <f aca="false">K21-K25</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="L26" s="119" t="n">
+      <c r="L26" s="121" t="n">
         <f aca="false">L21-L25</f>
         <v>5988.72947711613</v>
       </c>
-      <c r="M26" s="119" t="n">
+      <c r="M26" s="121" t="n">
         <f aca="false">M21-M25</f>
         <v>6000.64354392249</v>
       </c>
-      <c r="N26" s="119" t="n">
+      <c r="N26" s="121" t="n">
         <f aca="false">N21-N25</f>
         <v>6000.64354392249</v>
       </c>
       <c r="O26" s="116"/>
       <c r="P26" s="80" t="s">
-        <v>1105</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>1106</v>
+        <v>1162</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -21066,31 +21669,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>1107</v>
+        <v>1163</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">BYD!$F$33*12</f>
         <v>4221.92511679644</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1108</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>1109</v>
+        <v>1165</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">BYD!$F$34*12</f>
         <v>6921.92511679644</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1110</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>1111</v>
+        <v>1167</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C30-C29</f>
@@ -21102,86 +21705,86 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>1112</v>
+        <v>1168</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">IFERROR(C30/C29-1,0)</f>
         <v>0.639518685269514</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1113</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>1114</v>
+        <v>1170</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">C29*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>4565.88984905406</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1115</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>1116</v>
+        <v>1172</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">C30*ENTRADAS!C18+ENTRADAS!C26*12</f>
         <v>7323.85884905406</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1117</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>1118</v>
+        <v>1174</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C18</f>
         <v>2757.969</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1119</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>1120</v>
+        <v>1176</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">C31*ENTRADAS!C25</f>
         <v>579.72996</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1121</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>1122</v>
+        <v>1178</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C35-C36</f>
         <v>2178.23904</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1123</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>1124</v>
+        <v>1180</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IFERROR(ROUNDUP(C31/GERACAO!I17*1000/615,0),0)</f>
         <v>4</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1125</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>

--- a/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
+++ b/solar/Comparativo_Orcamentos_Solar_Henrique.xlsx
@@ -12599,7 +12599,7 @@
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="11" t="n">
         <v>540</v>
       </c>
       <c r="D18" s="11" t="n">
@@ -12611,10 +12611,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Linha 6 = Jul/25 (mes mais antigo). Linha 18 = Jul/26 (mes atual). Verde = menor consumo. Vermelho = maior consumo.</t>
-        </is>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Ago/26</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>705</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E19" s="19">
+        <f>IFERROR(C19/D19,0)</f>
+        <v/>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -12623,6 +12633,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Linha 6 = Jul/25 (mes mais antigo). Linha 19 = Ago/26 (mes atual). Verde = menor consumo. Vermelho = maior consumo.</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Distribuidora</t>
@@ -12661,7 +12676,7 @@
         </is>
       </c>
       <c r="C22" s="26">
-        <f>SUM(C7:C18)</f>
+        <f>SUM(C8:C19)</f>
         <v/>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -12713,7 +12728,7 @@
         </is>
       </c>
       <c r="C24" s="12">
-        <f>SUM(D7:D18)</f>
+        <f>SUM(D8:D19)</f>
         <v/>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -12761,11 +12776,11 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MAIOR CONSUMO (Jul/26)</t>
+          <t>MAIOR CONSUMO (Ago/26)</t>
         </is>
       </c>
       <c r="C26" s="12">
-        <f>MAX(C7:C18)</f>
+        <f>MAX(C8:C19)</f>
         <v/>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -12791,7 +12806,7 @@
         </is>
       </c>
       <c r="C27" s="12">
-        <f>MIN(C7:C18)</f>
+        <f>MIN(C8:C19)</f>
         <v/>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -12835,11 +12850,11 @@
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Consumo do mes atual (Jul/26)</t>
+          <t>Consumo do mes atual (Ago/26)</t>
         </is>
       </c>
       <c r="C29" s="12">
-        <f>C18</f>
+        <f>C19</f>
         <v/>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -12887,7 +12902,7 @@
         </is>
       </c>
       <c r="C31" s="29">
-        <f>AVERAGE(C7:C12)</f>
+        <f>AVERAGE(C8:C13)</f>
         <v/>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -12913,7 +12928,7 @@
         </is>
       </c>
       <c r="C32" s="29">
-        <f>AVERAGE(C13:C18)</f>
+        <f>AVERAGE(C14:C19)</f>
         <v/>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -12961,11 +12976,11 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>MESMO MES, ANO ANTERIOR: Jul/25 x Jul/26</t>
+          <t>MESMO MES, ANO ANTERIOR: Ago/25 x Ago/26</t>
         </is>
       </c>
       <c r="C34" s="31">
-        <f>IFERROR(C18/C6-1,0)</f>
+        <f>IFERROR(C19/C7-1,0)</f>
         <v/>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -13397,7 +13412,7 @@
         </is>
       </c>
       <c r="C78" s="29">
-        <f>AVERAGE(E16:E18)</f>
+        <f>AVERAGE(E16:E19)</f>
         <v/>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -13469,11 +13484,11 @@
     <row r="82">
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CONTROLE DE SAZONALIDADE - Jul/25</t>
+          <t>CONTROLE DE SAZONALIDADE - Ago/25</t>
         </is>
       </c>
       <c r="C82" s="29">
-        <f>E6</f>
+        <f>E7</f>
         <v/>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -13490,11 +13505,11 @@
     <row r="83">
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CONTROLE DE SAZONALIDADE - Jul/26</t>
+          <t>CONTROLE DE SAZONALIDADE - Ago/25 x Ago/26</t>
         </is>
       </c>
       <c r="C83" s="29">
-        <f>E18</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="D83" s="2" t="inlineStr">
